--- a/Security-data/data/output/ieee_sp_2025_us_institutions.xlsx
+++ b/Security-data/data/output/ieee_sp_2025_us_institutions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E369"/>
+  <dimension ref="A1:E374"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1757,7 +1757,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Munshi Rejwan Ala Muid</t>
+          <t>Sourav Das 0001</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-AccuRevoke: Enhancing Certificate Revocation with Distributed Cryptographic Accumulators.</t>
+          <t>IEEE_S&amp;P-Verifiable Secret Sharing Simplified.</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -1773,14 +1773,14 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Virginia Tech</t>
+          <t>University of Illinois Urbana-Champaign</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Taejoong Chung</t>
+          <t>Ling Ren 0001</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -1788,22 +1788,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-AccuRevoke: Enhancing Certificate Revocation with Distributed Cryptographic Accumulators.</t>
+          <t>IEEE_S&amp;P-Verifiable Secret Sharing Simplified.</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Virginia Tech</t>
+          <t>University of Illinois Urbana-Champaign</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Thang Hoang</t>
+          <t>Munshi Rejwan Ala Muid</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -1815,7 +1815,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Doowon Kim</t>
+          <t>Taejoong Chung</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -1834,22 +1834,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Open Sesame! On the Security and Memorability of Verbal Passwords.</t>
+          <t>IEEE_S&amp;P-AccuRevoke: Enhancing Certificate Revocation with Distributed Cryptographic Accumulators.</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>University of Tennessee at Knoxville</t>
+          <t>Virginia Tech</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Lei Yu</t>
+          <t>Thang Hoang</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -1857,22 +1857,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-CMASan: Custom Memory Allocator-aware Address Sanitizer.</t>
+          <t>IEEE_S&amp;P-AccuRevoke: Enhancing Certificate Revocation with Distributed Cryptographic Accumulators.</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Rensselaer Polytechnic Institute</t>
+          <t>Virginia Tech</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Yonghwi Kwon 0001</t>
+          <t>Doowon Kim</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -1880,22 +1880,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-CMASan: Custom Memory Allocator-aware Address Sanitizer.</t>
+          <t>IEEE_S&amp;P-Open Sesame! On the Security and Memorability of Verbal Passwords.</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>University of Maryland, College Park</t>
+          <t>University of Tennessee at Knoxville</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Md Sakib Anwar</t>
+          <t>Lei Yu</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -1903,22 +1903,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-GoSonar: Detecting Logical Vulnerabilities in Memory Safe Language Using Inductive Constraint Reasoning.</t>
+          <t>IEEE_S&amp;P-CMASan: Custom Memory Allocator-aware Address Sanitizer.</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>The Ohio State University</t>
+          <t>Rensselaer Polytechnic Institute</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Carter Yagemann</t>
+          <t>Yonghwi Kwon 0001</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -1926,22 +1926,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-GoSonar: Detecting Logical Vulnerabilities in Memory Safe Language Using Inductive Constraint Reasoning.</t>
+          <t>IEEE_S&amp;P-CMASan: Custom Memory Allocator-aware Address Sanitizer.</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>The Ohio State University</t>
+          <t>University of Maryland, College Park</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Zhiqiang Lin 0001</t>
+          <t>Md Sakib Anwar</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -1953,7 +1953,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Zhiyun Qian</t>
+          <t>Carter Yagemann</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -1972,22 +1972,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-SoK: Challenges and Paths Toward Memory Safety for eBPF.</t>
+          <t>IEEE_S&amp;P-GoSonar: Detecting Logical Vulnerabilities in Memory Safe Language Using Inductive Constraint Reasoning.</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>University of California, Riverside</t>
+          <t>The Ohio State University</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Trent Jaeger</t>
+          <t>Zhiqiang Lin 0001</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -1995,22 +1995,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-SoK: Challenges and Paths Toward Memory Safety for eBPF.</t>
+          <t>IEEE_S&amp;P-GoSonar: Detecting Logical Vulnerabilities in Memory Safe Language Using Inductive Constraint Reasoning.</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>University of California, Riverside</t>
+          <t>The Ohio State University</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Alexander J. Gaidis</t>
+          <t>Zhiyun Qian</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -2018,22 +2018,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-IUBIK: Isolating User Bytes in Commodity Operating System Kernels via Memory Tagging Extensions.</t>
+          <t>IEEE_S&amp;P-SoK: Challenges and Paths Toward Memory Safety for eBPF.</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>John Brown University</t>
+          <t>University of California, Riverside</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Vasileios P. Kemerlis</t>
+          <t>Trent Jaeger</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -2041,22 +2041,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-IUBIK: Isolating User Bytes in Commodity Operating System Kernels via Memory Tagging Extensions.</t>
+          <t>IEEE_S&amp;P-SoK: Challenges and Paths Toward Memory Safety for eBPF.</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>John Brown University</t>
+          <t>University of California, Riverside</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Penghui Li 0001</t>
+          <t>Alexander J. Gaidis</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -2064,22 +2064,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Predator: Directed Web Application Fuzzing for Efficient Vulnerability Validation.</t>
+          <t>IEEE_S&amp;P-IUBIK: Isolating User Bytes in Commodity Operating System Kernels via Memory Tagging Extensions.</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Columbia University</t>
+          <t>John Brown University</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Zifeng Kang</t>
+          <t>Vasileios P. Kemerlis</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -2087,22 +2087,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Follow My Flow: Unveiling Client-Side Prototype Pollution Gadgets from One Million Real-World Websites.</t>
+          <t>IEEE_S&amp;P-IUBIK: Isolating User Bytes in Commodity Operating System Kernels via Memory Tagging Extensions.</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Johns Hopkins University</t>
+          <t>John Brown University</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Muxi Lyu</t>
+          <t>Penghui Li 0001</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -2110,22 +2110,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Follow My Flow: Unveiling Client-Side Prototype Pollution Gadgets from One Million Real-World Websites.</t>
+          <t>IEEE_S&amp;P-Predator: Directed Web Application Fuzzing for Efficient Vulnerability Validation.</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Johns Hopkins University</t>
+          <t>Columbia University</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Zhengyu Liu</t>
+          <t>Yonghwi Kwon 0001</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -2133,22 +2133,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Follow My Flow: Unveiling Client-Side Prototype Pollution Gadgets from One Million Real-World Websites.</t>
+          <t>IEEE_S&amp;P-Racedb: Detecting Request Race Vulnerabilities in Database-Backed Web Applications.</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Johns Hopkins University</t>
+          <t>University of Maryland, College Park</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Jianjia Yu</t>
+          <t>Zifeng Kang</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -2160,7 +2160,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Yinzhi Cao</t>
+          <t>Muxi Lyu</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -2183,7 +2183,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Tommaso Innocenti</t>
+          <t>Zhengyu Liu</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -2202,22 +2202,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-"Only as Strong as the Weakest Link": On the Security of Brokered Single Sign-On on the Web.</t>
+          <t>IEEE_S&amp;P-Follow My Flow: Unveiling Client-Side Prototype Pollution Gadgets from One Million Real-World Websites.</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Northeastern University</t>
+          <t>Johns Hopkins University</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Engin Kirda</t>
+          <t>Jianjia Yu</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -2225,22 +2225,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-"Only as Strong as the Weakest Link": On the Security of Brokered Single Sign-On on the Web.</t>
+          <t>IEEE_S&amp;P-Follow My Flow: Unveiling Client-Side Prototype Pollution Gadgets from One Million Real-World Websites.</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Northeastern University</t>
+          <t>Johns Hopkins University</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Jose Luis Castanon Remy</t>
+          <t>Yinzhi Cao</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -2248,22 +2248,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-SoK: Space Infrastructures Vulnerabilities, Attacks and Defenses.</t>
+          <t>IEEE_S&amp;P-Follow My Flow: Unveiling Client-Side Prototype Pollution Gadgets from One Million Real-World Websites.</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>University of Colorado Colorado Springs</t>
+          <t>Johns Hopkins University</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Ekzhin Ear</t>
+          <t>Tommaso Innocenti</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -2271,22 +2271,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-SoK: Space Infrastructures Vulnerabilities, Attacks and Defenses.</t>
+          <t>IEEE_S&amp;P-"Only as Strong as the Weakest Link": On the Security of Brokered Single Sign-On on the Web.</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>University of Colorado Colorado Springs</t>
+          <t>Northeastern University</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Caleb Chang</t>
+          <t>Engin Kirda</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -2294,22 +2294,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-SoK: Space Infrastructures Vulnerabilities, Attacks and Defenses.</t>
+          <t>IEEE_S&amp;P-"Only as Strong as the Weakest Link": On the Security of Brokered Single Sign-On on the Web.</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>University of Colorado Colorado Springs</t>
+          <t>Northeastern University</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Antonia Feffer</t>
+          <t>Jose Luis Castanon Remy</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -2321,7 +2321,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Shouhuai Xu</t>
+          <t>Ekzhin Ear</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Tao Wan 0004</t>
+          <t>Caleb Chang</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -2363,22 +2363,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Invade the Walled Garden: Evaluating GTP Security in Cellular Networks.</t>
+          <t>IEEE_S&amp;P-SoK: Space Infrastructures Vulnerabilities, Attacks and Defenses.</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Cablevision (United States)</t>
+          <t>University of Colorado Colorado Springs</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Jinhe Wen</t>
+          <t>Antonia Feffer</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -2386,22 +2386,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Teaching Data Science Students to Sketch Privacy Designs Through Heuristics.</t>
+          <t>IEEE_S&amp;P-SoK: Space Infrastructures Vulnerabilities, Attacks and Defenses.</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>University of California, San Diego</t>
+          <t>University of Colorado Colorado Springs</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Yingxi Zhao</t>
+          <t>Shouhuai Xu</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -2409,22 +2409,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Teaching Data Science Students to Sketch Privacy Designs Through Heuristics.</t>
+          <t>IEEE_S&amp;P-SoK: Space Infrastructures Vulnerabilities, Attacks and Defenses.</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>University of California, San Diego</t>
+          <t>University of Colorado Colorado Springs</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Yaxing Yao</t>
+          <t>Tao Wan 0004</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Teaching Data Science Students to Sketch Privacy Designs Through Heuristics.</t>
+          <t>IEEE_S&amp;P-Invade the Walled Garden: Evaluating GTP Security in Cellular Networks.</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Virginia Tech</t>
+          <t>Cablevision (United States)</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Haojian Jin</t>
+          <t>Jinhe Wen</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -2459,7 +2459,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Phoebe Moh</t>
+          <t>Yingxi Zhao</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -2478,22 +2478,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Characterizing the Usability and Usefulness of U.S. Ad Transparency Systems.</t>
+          <t>IEEE_S&amp;P-Teaching Data Science Students to Sketch Privacy Designs Through Heuristics.</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>University of Maryland, College Park</t>
+          <t>University of California, San Diego</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Tobias Lauinger</t>
+          <t>Yaxing Yao</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -2501,22 +2501,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Characterizing the Usability and Usefulness of U.S. Ad Transparency Systems.</t>
+          <t>IEEE_S&amp;P-Teaching Data Science Students to Sketch Privacy Designs Through Heuristics.</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>New York University</t>
+          <t>Virginia Tech</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Michelle L. Mazurek</t>
+          <t>Haojian Jin</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -2524,22 +2524,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Characterizing the Usability and Usefulness of U.S. Ad Transparency Systems.</t>
+          <t>IEEE_S&amp;P-Teaching Data Science Students to Sketch Privacy Designs Through Heuristics.</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>University of Maryland, College Park</t>
+          <t>University of California, San Diego</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Damon McCoy</t>
+          <t>Phoebe Moh</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -2551,18 +2551,18 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>New York University</t>
+          <t>University of Maryland, College Park</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Lanjing Liu</t>
+          <t>Tobias Lauinger</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -2570,22 +2570,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Supporting Family Discussions About Digital Privacy Through Perspective-Taking: An Empirical Investigation.</t>
+          <t>IEEE_S&amp;P-Characterizing the Usability and Usefulness of U.S. Ad Transparency Systems.</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Virginia Tech</t>
+          <t>New York University</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Yaxing Yao</t>
+          <t>Michelle L. Mazurek</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -2593,22 +2593,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Supporting Family Discussions About Digital Privacy Through Perspective-Taking: An Empirical Investigation.</t>
+          <t>IEEE_S&amp;P-Characterizing the Usability and Usefulness of U.S. Ad Transparency Systems.</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Virginia Tech</t>
+          <t>University of Maryland, College Park</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Elham Pourabbas Vafa</t>
+          <t>Damon McCoy</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -2616,22 +2616,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Learning from Censored Experiences: Social Media Discussions around Censorship Circumvention Technologies.</t>
+          <t>IEEE_S&amp;P-Characterizing the Usability and Usefulness of U.S. Ad Transparency Systems.</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>The University of Texas at Arlington</t>
+          <t>New York University</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Mohit Singhal</t>
+          <t>Lanjing Liu</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Learning from Censored Experiences: Social Media Discussions around Censorship Circumvention Technologies.</t>
+          <t>IEEE_S&amp;P-Supporting Family Discussions About Digital Privacy Through Perspective-Taking: An Empirical Investigation.</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -2647,14 +2647,14 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>The University of Texas at Arlington</t>
+          <t>Virginia Tech</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Poojitha Thota</t>
+          <t>Yaxing Yao</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -2662,7 +2662,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Learning from Censored Experiences: Social Media Discussions around Censorship Circumvention Technologies.</t>
+          <t>IEEE_S&amp;P-Supporting Family Discussions About Digital Privacy Through Perspective-Taking: An Empirical Investigation.</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -2670,14 +2670,14 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>The University of Texas at Arlington</t>
+          <t>Virginia Tech</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Sayak Saha Roy</t>
+          <t>Elham Pourabbas Vafa</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -2689,7 +2689,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Zakir Durumeric</t>
+          <t>Mohit Singhal</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -2708,22 +2708,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-A Wall Behind A Wall: Emerging Regional Censorship in China.</t>
+          <t>IEEE_S&amp;P-Learning from Censored Experiences: Social Media Discussions around Censorship Circumvention Technologies.</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Stanford University</t>
+          <t>The University of Texas at Arlington</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Amir Houmansadr</t>
+          <t>Poojitha Thota</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -2731,22 +2731,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-A Wall Behind A Wall: Emerging Regional Censorship in China.</t>
+          <t>IEEE_S&amp;P-Learning from Censored Experiences: Social Media Discussions around Censorship Circumvention Technologies.</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>University of Massachusetts Amherst</t>
+          <t>The University of Texas at Arlington</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Eric Wustrow</t>
+          <t>Sayak Saha Roy</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -2754,22 +2754,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-A Wall Behind A Wall: Emerging Regional Censorship in China.</t>
+          <t>IEEE_S&amp;P-Learning from Censored Experiences: Social Media Discussions around Censorship Circumvention Technologies.</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>University of Colorado System; University of Colorado Boulder</t>
+          <t>The University of Texas at Arlington</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Sadia Nourin</t>
+          <t>Zakir Durumeric</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -2777,22 +2777,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Is Nobody There? Good! Globally Measuring Connection Tampering Without Responsive Endhosts.</t>
+          <t>IEEE_S&amp;P-A Wall Behind A Wall: Emerging Regional Censorship in China.</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>University of Maryland, College Park</t>
+          <t>Stanford University</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Erik C. Rye</t>
+          <t>Amir Houmansadr</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -2800,22 +2800,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Is Nobody There? Good! Globally Measuring Connection Tampering Without Responsive Endhosts.</t>
+          <t>IEEE_S&amp;P-A Wall Behind A Wall: Emerging Regional Censorship in China.</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>University of Maryland, College Park</t>
+          <t>University of Massachusetts Amherst</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Dave Levin</t>
+          <t>Eric Wustrow</t>
         </is>
       </c>
       <c r="B105" t="n">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Is Nobody There? Good! Globally Measuring Connection Tampering Without Responsive Endhosts.</t>
+          <t>IEEE_S&amp;P-A Wall Behind A Wall: Emerging Regional Censorship in China.</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -2831,14 +2831,14 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>University of Maryland, College Park</t>
+          <t>University of Colorado System; University of Colorado Boulder</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Kyle Fredrickson</t>
+          <t>Sadia Nourin</t>
         </is>
       </c>
       <c r="B106" t="n">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Sparta: Practical Anonymity with Long-Term Resistance to Traffic Analysis.</t>
+          <t>IEEE_S&amp;P-Is Nobody There? Good! Globally Measuring Connection Tampering Without Responsive Endhosts.</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -2854,14 +2854,14 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>University of California, Santa Cruz</t>
+          <t>University of Maryland, College Park</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Ioannis Demertzis</t>
+          <t>Erik C. Rye</t>
         </is>
       </c>
       <c r="B107" t="n">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Sparta: Practical Anonymity with Long-Term Resistance to Traffic Analysis.</t>
+          <t>IEEE_S&amp;P-Is Nobody There? Good! Globally Measuring Connection Tampering Without Responsive Endhosts.</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -2877,14 +2877,14 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>University of California, Santa Cruz</t>
+          <t>University of Maryland, College Park</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>James P. Hughes 0001</t>
+          <t>Dave Levin</t>
         </is>
       </c>
       <c r="B108" t="n">
@@ -2892,22 +2892,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Sparta: Practical Anonymity with Long-Term Resistance to Traffic Analysis.</t>
+          <t>IEEE_S&amp;P-Is Nobody There? Good! Globally Measuring Connection Tampering Without Responsive Endhosts.</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>University of California, Santa Cruz</t>
+          <t>University of Maryland, College Park</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Darrell D. E. Long</t>
+          <t>Kyle Fredrickson</t>
         </is>
       </c>
       <c r="B109" t="n">
@@ -2919,7 +2919,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>James Austgen</t>
+          <t>Ioannis Demertzis</t>
         </is>
       </c>
       <c r="B110" t="n">
@@ -2938,22 +2938,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Liquefaction: Privately Liquefying Blockchain Assets.</t>
+          <t>IEEE_S&amp;P-Sparta: Practical Anonymity with Long-Term Resistance to Traffic Analysis.</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Cornell University</t>
+          <t>University of California, Santa Cruz</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Andrés Fábrega</t>
+          <t>James P. Hughes 0001</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -2961,22 +2961,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Liquefaction: Privately Liquefying Blockchain Assets.</t>
+          <t>IEEE_S&amp;P-Sparta: Practical Anonymity with Long-Term Resistance to Traffic Analysis.</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Cornell University</t>
+          <t>University of California, Santa Cruz</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Mahimna Kelkar</t>
+          <t>Darrell D. E. Long</t>
         </is>
       </c>
       <c r="B112" t="n">
@@ -2984,22 +2984,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Liquefaction: Privately Liquefying Blockchain Assets.</t>
+          <t>IEEE_S&amp;P-Sparta: Practical Anonymity with Long-Term Resistance to Traffic Analysis.</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Cornell University</t>
+          <t>University of California, Santa Cruz</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Dani Vilardell</t>
+          <t>James Austgen</t>
         </is>
       </c>
       <c r="B113" t="n">
@@ -3011,7 +3011,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -3022,7 +3022,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Kushal Babel</t>
+          <t>Andrés Fábrega</t>
         </is>
       </c>
       <c r="B114" t="n">
@@ -3034,7 +3034,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Ari Juels</t>
+          <t>Mahimna Kelkar</t>
         </is>
       </c>
       <c r="B115" t="n">
@@ -3057,7 +3057,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -3068,7 +3068,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Sen Yang</t>
+          <t>Dani Vilardell</t>
         </is>
       </c>
       <c r="B116" t="n">
@@ -3076,22 +3076,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Decentralization of Ethereum's Builder Market.</t>
+          <t>IEEE_S&amp;P-Liquefaction: Privately Liquefying Blockchain Assets.</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Yale University</t>
+          <t>Cornell University</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Kartik Nayak</t>
+          <t>Kushal Babel</t>
         </is>
       </c>
       <c r="B117" t="n">
@@ -3099,22 +3099,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Decentralization of Ethereum's Builder Market.</t>
+          <t>IEEE_S&amp;P-Liquefaction: Privately Liquefying Blockchain Assets.</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Duke University</t>
+          <t>Cornell University</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Fan Zhang 0022</t>
+          <t>Ari Juels</t>
         </is>
       </c>
       <c r="B118" t="n">
@@ -3122,22 +3122,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Decentralization of Ethereum's Builder Market.</t>
+          <t>IEEE_S&amp;P-Liquefaction: Privately Liquefying Blockchain Assets.</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Yale University</t>
+          <t>Cornell University</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Darya Kaviani</t>
+          <t>Sen Yang</t>
         </is>
       </c>
       <c r="B119" t="n">
@@ -3145,22 +3145,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Papercraft: Lattice-Based Verifiable Delay Function Implemented.</t>
+          <t>IEEE_S&amp;P-Decentralization of Ethereum's Builder Market.</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Berkeley College; University of California, Berkeley</t>
+          <t>Yale University</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Jiongxiao Wang</t>
+          <t>Kartik Nayak</t>
         </is>
       </c>
       <c r="B120" t="n">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Preference Poisoning Attacks on Reward Model Learning.</t>
+          <t>IEEE_S&amp;P-Decentralization of Ethereum's Builder Market.</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -3176,14 +3176,14 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>University of Wisconsin–Madison</t>
+          <t>Duke University</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Chaowei Xiao</t>
+          <t>Fan Zhang 0022</t>
         </is>
       </c>
       <c r="B121" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Preference Poisoning Attacks on Reward Model Learning.</t>
+          <t>IEEE_S&amp;P-Decentralization of Ethereum's Builder Market.</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -3199,14 +3199,14 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>University of Wisconsin–Madison</t>
+          <t>Yale University</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Ziqi Zhang</t>
+          <t>Darya Kaviani</t>
         </is>
       </c>
       <c r="B122" t="n">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Query Provenance Analysis: Efficient and Robust Defense Against Query-Based Black-Box Attacks.</t>
+          <t>IEEE_S&amp;P-Papercraft: Lattice-Based Verifiable Delay Function Implemented.</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -3222,14 +3222,14 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>University of Illinois Urbana-Champaign</t>
+          <t>Berkeley College; University of California, Berkeley</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Guangyu Shen</t>
+          <t>Jiongxiao Wang</t>
         </is>
       </c>
       <c r="B123" t="n">
@@ -3237,22 +3237,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-BAIT: Large Language Model Backdoor Scanning by Inverting Attack Target.</t>
+          <t>IEEE_S&amp;P-Preference Poisoning Attacks on Reward Model Learning.</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Purdue University West Lafayette</t>
+          <t>University of Wisconsin–Madison</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Siyuan Cheng 0005</t>
+          <t>Chaowei Xiao</t>
         </is>
       </c>
       <c r="B124" t="n">
@@ -3260,22 +3260,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-BAIT: Large Language Model Backdoor Scanning by Inverting Attack Target.</t>
+          <t>IEEE_S&amp;P-Preference Poisoning Attacks on Reward Model Learning.</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Purdue University West Lafayette</t>
+          <t>University of Wisconsin–Madison</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Zhuo Zhang 0002</t>
+          <t>Ziqi Zhang</t>
         </is>
       </c>
       <c r="B125" t="n">
@@ -3283,22 +3283,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-BAIT: Large Language Model Backdoor Scanning by Inverting Attack Target.</t>
+          <t>IEEE_S&amp;P-Query Provenance Analysis: Efficient and Robust Defense Against Query-Based Black-Box Attacks.</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Purdue University West Lafayette</t>
+          <t>University of Illinois Urbana-Champaign</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Guanhong Tao 0001</t>
+          <t>Guangyu Shen</t>
         </is>
       </c>
       <c r="B126" t="n">
@@ -3310,18 +3310,18 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>University of Utah</t>
+          <t>Purdue University West Lafayette</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Kaiyuan Zhang 0002</t>
+          <t>Siyuan Cheng 0005</t>
         </is>
       </c>
       <c r="B127" t="n">
@@ -3333,7 +3333,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Hanxi Guo</t>
+          <t>Zhuo Zhang 0002</t>
         </is>
       </c>
       <c r="B128" t="n">
@@ -3356,7 +3356,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -3367,7 +3367,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Xiaolong Jin 0002</t>
+          <t>Guanhong Tao 0001</t>
         </is>
       </c>
       <c r="B129" t="n">
@@ -3379,18 +3379,18 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Purdue University West Lafayette</t>
+          <t>University of Utah</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Shengwei An</t>
+          <t>Kaiyuan Zhang 0002</t>
         </is>
       </c>
       <c r="B130" t="n">
@@ -3402,7 +3402,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Shiqing Ma</t>
+          <t>Hanxi Guo</t>
         </is>
       </c>
       <c r="B131" t="n">
@@ -3425,18 +3425,18 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>University of Massachusetts Amherst</t>
+          <t>Purdue University West Lafayette</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Xiangyu Zhang 0001</t>
+          <t>Xiaolong Jin 0002</t>
         </is>
       </c>
       <c r="B132" t="n">
@@ -3448,7 +3448,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Yongji Wu</t>
+          <t>Shengwei An</t>
         </is>
       </c>
       <c r="B133" t="n">
@@ -3467,22 +3467,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Prompt Inversion Attack Against Collaborative Inference of Large Language Models.</t>
+          <t>IEEE_S&amp;P-BAIT: Large Language Model Backdoor Scanning by Inverting Attack Target.</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Berkeley College; University of California, Berkeley</t>
+          <t>Purdue University West Lafayette</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Tingsong Xiao</t>
+          <t>Shiqing Ma</t>
         </is>
       </c>
       <c r="B134" t="n">
@@ -3490,22 +3490,22 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Prompt Inversion Attack Against Collaborative Inference of Large Language Models.</t>
+          <t>IEEE_S&amp;P-BAIT: Large Language Model Backdoor Scanning by Inverting Attack Target.</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>University of Florida</t>
+          <t>University of Massachusetts Amherst</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Qing Deng</t>
+          <t>Xiangyu Zhang 0001</t>
         </is>
       </c>
       <c r="B135" t="n">
@@ -3513,22 +3513,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Beyond the Horizon: Uncovering Hosts and Services Behind Misconfigured Firewalls.</t>
+          <t>IEEE_S&amp;P-BAIT: Large Language Model Backdoor Scanning by Inverting Attack Target.</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>University of California, Riverside</t>
+          <t>Purdue University West Lafayette</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Juefei Pu</t>
+          <t>Yongji Wu</t>
         </is>
       </c>
       <c r="B136" t="n">
@@ -3536,22 +3536,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Beyond the Horizon: Uncovering Hosts and Services Behind Misconfigured Firewalls.</t>
+          <t>IEEE_S&amp;P-Prompt Inversion Attack Against Collaborative Inference of Large Language Models.</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>University of California, Riverside</t>
+          <t>Berkeley College; University of California, Berkeley</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Zhaowei Tan</t>
+          <t>Tingsong Xiao</t>
         </is>
       </c>
       <c r="B137" t="n">
@@ -3559,22 +3559,22 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Beyond the Horizon: Uncovering Hosts and Services Behind Misconfigured Firewalls.</t>
+          <t>IEEE_S&amp;P-Prompt Inversion Attack Against Collaborative Inference of Large Language Models.</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>University of California, Riverside</t>
+          <t>University of Florida</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Zhiyun Qian</t>
+          <t>Qing Deng</t>
         </is>
       </c>
       <c r="B138" t="n">
@@ -3586,7 +3586,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Srikanth V. Krishnamurthy</t>
+          <t>Juefei Pu</t>
         </is>
       </c>
       <c r="B139" t="n">
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Mohamed Nabeel</t>
+          <t>Zhaowei Tan</t>
         </is>
       </c>
       <c r="B140" t="n">
@@ -3628,22 +3628,22 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-MANTIS: Detection of Zero-Day Malicious Domains Leveraging Low Reputed Hosting Infrastructure.</t>
+          <t>IEEE_S&amp;P-Beyond the Horizon: Uncovering Hosts and Services Behind Misconfigured Firewalls.</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Palo Alto Networks (United States)</t>
+          <t>University of California, Riverside</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Daiping Liu</t>
+          <t>Zhiyun Qian</t>
         </is>
       </c>
       <c r="B141" t="n">
@@ -3651,22 +3651,22 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Resolution Without Dissent: In-Path Per-Query Sanitization to Defeat Surreptitious Communication Over DNS.</t>
+          <t>IEEE_S&amp;P-Beyond the Horizon: Uncovering Hosts and Services Behind Misconfigured Firewalls.</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Palo Alto Networks (United States)</t>
+          <t>University of California, Riverside</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Ruian Duan</t>
+          <t>Srikanth V. Krishnamurthy</t>
         </is>
       </c>
       <c r="B142" t="n">
@@ -3674,22 +3674,22 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Resolution Without Dissent: In-Path Per-Query Sanitization to Defeat Surreptitious Communication Over DNS.</t>
+          <t>IEEE_S&amp;P-Beyond the Horizon: Uncovering Hosts and Services Behind Misconfigured Firewalls.</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Palo Alto Networks (United States)</t>
+          <t>University of California, Riverside</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Jun Wang</t>
+          <t>Mohamed Nabeel</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -3697,11 +3697,11 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Resolution Without Dissent: In-Path Per-Query Sanitization to Defeat Surreptitious Communication Over DNS.</t>
+          <t>IEEE_S&amp;P-MANTIS: Detection of Zero-Day Malicious Domains Leveraging Low Reputed Hosting Infrastructure.</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Gene Tsudik</t>
+          <t>Daiping Liu</t>
         </is>
       </c>
       <c r="B144" t="n">
@@ -3720,22 +3720,22 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-SoK: Decoding the Enigma of Encrypted Network Traffic Classifiers.</t>
+          <t>IEEE_S&amp;P-Resolution Without Dissent: In-Path Per-Query Sanitization to Defeat Surreptitious Communication Over DNS.</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>University of California, Irvine</t>
+          <t>Palo Alto Networks (United States)</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Keyu Man</t>
+          <t>Ruian Duan</t>
         </is>
       </c>
       <c r="B145" t="n">
@@ -3743,22 +3743,22 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-SCAD: Towards a Universal and Automated Network Side-Channel Vulnerability Detection.</t>
+          <t>IEEE_S&amp;P-Resolution Without Dissent: In-Path Per-Query Sanitization to Defeat Surreptitious Communication Over DNS.</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>University of California, Riverside</t>
+          <t>Palo Alto Networks (United States)</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Zhongjie Wang 0002</t>
+          <t>Jun Wang</t>
         </is>
       </c>
       <c r="B146" t="n">
@@ -3766,22 +3766,22 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-SCAD: Towards a Universal and Automated Network Side-Channel Vulnerability Detection.</t>
+          <t>IEEE_S&amp;P-Resolution Without Dissent: In-Path Per-Query Sanitization to Defeat Surreptitious Communication Over DNS.</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>University of California, Riverside</t>
+          <t>Palo Alto Networks (United States)</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Shenghan Zheng</t>
+          <t>Gene Tsudik</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -3789,22 +3789,22 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-SCAD: Towards a Universal and Automated Network Side-Channel Vulnerability Detection.</t>
+          <t>IEEE_S&amp;P-SoK: Decoding the Enigma of Encrypted Network Traffic Classifiers.</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>University of California, Riverside</t>
+          <t>University of California, Irvine</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Xin'an Zhou</t>
+          <t>Keyu Man</t>
         </is>
       </c>
       <c r="B148" t="n">
@@ -3816,7 +3816,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Yue Cao 0003</t>
+          <t>Zhongjie Wang 0002</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -3839,7 +3839,7 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
@@ -3850,7 +3850,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Zhiyun Qian</t>
+          <t>Shenghan Zheng</t>
         </is>
       </c>
       <c r="B150" t="n">
@@ -3862,7 +3862,7 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Aniket Kate</t>
+          <t>Xin'an Zhou</t>
         </is>
       </c>
       <c r="B151" t="n">
@@ -3881,22 +3881,22 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Sailfish: Towards Improving the Latency of DAG-Based BFT.</t>
+          <t>IEEE_S&amp;P-SCAD: Towards a Universal and Automated Network Side-Channel Vulnerability Detection.</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Purdue University West Lafayette</t>
+          <t>University of California, Riverside</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Kartik Nayak</t>
+          <t>Yue Cao 0003</t>
         </is>
       </c>
       <c r="B152" t="n">
@@ -3904,22 +3904,22 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Sailfish: Towards Improving the Latency of DAG-Based BFT.</t>
+          <t>IEEE_S&amp;P-SCAD: Towards a Universal and Automated Network Side-Channel Vulnerability Detection.</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Duke University</t>
+          <t>University of California, Riverside</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Zhongtang Luo</t>
+          <t>Zhiyun Qian</t>
         </is>
       </c>
       <c r="B153" t="n">
@@ -3927,22 +3927,22 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Cauchyproofs: Batch-Updatable Vector Commitment with Easy Aggregation and Application to Stateless Blockchains.</t>
+          <t>IEEE_S&amp;P-SCAD: Towards a Universal and Automated Network Side-Channel Vulnerability Detection.</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Purdue University West Lafayette</t>
+          <t>University of California, Riverside</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Yanxue Jia</t>
+          <t>Aniket Kate</t>
         </is>
       </c>
       <c r="B154" t="n">
@@ -3950,11 +3950,11 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Cauchyproofs: Batch-Updatable Vector Commitment with Easy Aggregation and Application to Stateless Blockchains.</t>
+          <t>IEEE_S&amp;P-Sailfish: Towards Improving the Latency of DAG-Based BFT.</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Weidong Cui</t>
+          <t>Kartik Nayak</t>
         </is>
       </c>
       <c r="B155" t="n">
@@ -3973,22 +3973,22 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-MicroNova: Folding-Based Arguments with Efficient (On-Chain) Verification.</t>
+          <t>IEEE_S&amp;P-Sailfish: Towards Improving the Latency of DAG-Based BFT.</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Microsoft Research (United Kingdom)</t>
+          <t>Duke University</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Greg Zaverucha</t>
+          <t>Zhongtang Luo</t>
         </is>
       </c>
       <c r="B156" t="n">
@@ -3996,22 +3996,22 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-MicroNova: Folding-Based Arguments with Efficient (On-Chain) Verification.</t>
+          <t>IEEE_S&amp;P-Cauchyproofs: Batch-Updatable Vector Commitment with Easy Aggregation and Application to Stateless Blockchains.</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Microsoft Research (United Kingdom)</t>
+          <t>Purdue University West Lafayette</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Ben Fisch</t>
+          <t>Yanxue Jia</t>
         </is>
       </c>
       <c r="B157" t="n">
@@ -4019,22 +4019,22 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Permissionless Verifiable Information Dispersal (Data Availability for Bitcoin Rollups).</t>
+          <t>IEEE_S&amp;P-Cauchyproofs: Batch-Updatable Vector Commitment with Easy Aggregation and Application to Stateless Blockchains.</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Yale University</t>
+          <t>Purdue University West Lafayette</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Arthur Lazzaretti</t>
+          <t>Weidong Cui</t>
         </is>
       </c>
       <c r="B158" t="n">
@@ -4042,22 +4042,22 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Permissionless Verifiable Information Dispersal (Data Availability for Bitcoin Rollups).</t>
+          <t>IEEE_S&amp;P-MicroNova: Folding-Based Arguments with Efficient (On-Chain) Verification.</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Yale University</t>
+          <t>Microsoft Research (United Kingdom)</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Zeyu Liu 0004</t>
+          <t>Greg Zaverucha</t>
         </is>
       </c>
       <c r="B159" t="n">
@@ -4065,22 +4065,22 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Permissionless Verifiable Information Dispersal (Data Availability for Bitcoin Rollups).</t>
+          <t>IEEE_S&amp;P-MicroNova: Folding-Based Arguments with Efficient (On-Chain) Verification.</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Yale University</t>
+          <t>Microsoft Research (United Kingdom)</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Jiadong Lou</t>
+          <t>Ben Fisch</t>
         </is>
       </c>
       <c r="B160" t="n">
@@ -4088,7 +4088,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-GRID: Protecting Training Graph from Link Stealing Attacks on GNN Models.</t>
+          <t>IEEE_S&amp;P-Permissionless Verifiable Information Dispersal (Data Availability for Bitcoin Rollups).</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -4096,14 +4096,14 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>University of Delaware</t>
+          <t>Yale University</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Rui Zhang</t>
+          <t>Arthur Lazzaretti</t>
         </is>
       </c>
       <c r="B161" t="n">
@@ -4111,22 +4111,22 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-GRID: Protecting Training Graph from Link Stealing Attacks on GNN Models.</t>
+          <t>IEEE_S&amp;P-Permissionless Verifiable Information Dispersal (Data Availability for Bitcoin Rollups).</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>University of Delaware</t>
+          <t>Yale University</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Neil Zhenqiang Gong</t>
+          <t>Zeyu Liu 0004</t>
         </is>
       </c>
       <c r="B162" t="n">
@@ -4134,22 +4134,22 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-GRID: Protecting Training Graph from Link Stealing Attacks on GNN Models.</t>
+          <t>IEEE_S&amp;P-Permissionless Verifiable Information Dispersal (Data Availability for Bitcoin Rollups).</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Duke University</t>
+          <t>Yale University</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Kang Yang</t>
+          <t>Jiadong Lou</t>
         </is>
       </c>
       <c r="B163" t="n">
@@ -4157,7 +4157,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Alleviating the Fear of Losing Alignment in LLM Fine-tuning.</t>
+          <t>IEEE_S&amp;P-GRID: Protecting Training Graph from Link Stealing Attacks on GNN Models.</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -4165,14 +4165,14 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>University of Utah</t>
+          <t>University of Delaware</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Guanhong Tao 0001</t>
+          <t>Rui Zhang</t>
         </is>
       </c>
       <c r="B164" t="n">
@@ -4180,22 +4180,22 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Alleviating the Fear of Losing Alignment in LLM Fine-tuning.</t>
+          <t>IEEE_S&amp;P-GRID: Protecting Training Graph from Link Stealing Attacks on GNN Models.</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>University of Utah</t>
+          <t>University of Delaware</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Jun Xu 0024</t>
+          <t>Neil Zhenqiang Gong</t>
         </is>
       </c>
       <c r="B165" t="n">
@@ -4203,22 +4203,22 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Alleviating the Fear of Losing Alignment in LLM Fine-tuning.</t>
+          <t>IEEE_S&amp;P-GRID: Protecting Training Graph from Link Stealing Attacks on GNN Models.</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>University of Utah</t>
+          <t>Duke University</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Yuqi Jia</t>
+          <t>Kang Yang</t>
         </is>
       </c>
       <c r="B166" t="n">
@@ -4226,22 +4226,22 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-DataSentinel: A Game-Theoretic Detection of Prompt Injection Attacks.</t>
+          <t>IEEE_S&amp;P-Alleviating the Fear of Losing Alignment in LLM Fine-tuning.</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Duke University</t>
+          <t>University of Utah</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Dawn Song</t>
+          <t>Guanhong Tao 0001</t>
         </is>
       </c>
       <c r="B167" t="n">
@@ -4249,22 +4249,22 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-DataSentinel: A Game-Theoretic Detection of Prompt Injection Attacks.</t>
+          <t>IEEE_S&amp;P-Alleviating the Fear of Losing Alignment in LLM Fine-tuning.</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>University of California, Berkeley; Berkeley College</t>
+          <t>University of Utah</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Neil Zhenqiang Gong</t>
+          <t>Jun Xu 0024</t>
         </is>
       </c>
       <c r="B168" t="n">
@@ -4272,22 +4272,22 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-DataSentinel: A Game-Theoretic Detection of Prompt Injection Attacks.</t>
+          <t>IEEE_S&amp;P-Alleviating the Fear of Losing Alignment in LLM Fine-tuning.</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Duke University</t>
+          <t>University of Utah</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Yasemin Acar</t>
+          <t>Yuqi Jia</t>
         </is>
       </c>
       <c r="B169" t="n">
@@ -4295,22 +4295,22 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-"It's Time. Time for Digital Security.": An End User Study on Actionable Security and Privacy Advice.</t>
+          <t>IEEE_S&amp;P-DataSentinel: A Game-Theoretic Detection of Prompt Injection Attacks.</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>George Washington University</t>
+          <t>Duke University</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>John Sadik</t>
+          <t>Dawn Song</t>
         </is>
       </c>
       <c r="B170" t="n">
@@ -4318,22 +4318,22 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Security and Privacy Experiences of First- and Second-Generation Pakistani Immigrants to the US: Perceptions, Practices, Challenges, and Parent-Child Dynamics.</t>
+          <t>IEEE_S&amp;P-DataSentinel: A Game-Theoretic Detection of Prompt Injection Attacks.</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>University of Tennessee at Knoxville</t>
+          <t>University of California, Berkeley; Berkeley College</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Taha</t>
+          <t>Neil Zhenqiang Gong</t>
         </is>
       </c>
       <c r="B171" t="n">
@@ -4341,22 +4341,22 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Security and Privacy Experiences of First- and Second-Generation Pakistani Immigrants to the US: Perceptions, Practices, Challenges, and Parent-Child Dynamics.</t>
+          <t>IEEE_S&amp;P-DataSentinel: A Game-Theoretic Detection of Prompt Injection Attacks.</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Purdue University West Lafayette</t>
+          <t>Duke University</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Ran Elgedawy</t>
+          <t>Yasemin Acar</t>
         </is>
       </c>
       <c r="B172" t="n">
@@ -4364,22 +4364,22 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Security and Privacy Experiences of First- and Second-Generation Pakistani Immigrants to the US: Perceptions, Practices, Challenges, and Parent-Child Dynamics.</t>
+          <t>IEEE_S&amp;P-"It's Time. Time for Digital Security.": An End User Study on Actionable Security and Privacy Advice.</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>University of Tennessee at Knoxville</t>
+          <t>George Washington University</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Scott Ruoti</t>
+          <t>John Sadik</t>
         </is>
       </c>
       <c r="B173" t="n">
@@ -4391,7 +4391,7 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
@@ -4402,7 +4402,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Yaxin Tu</t>
+          <t>Taha</t>
         </is>
       </c>
       <c r="B174" t="n">
@@ -4410,22 +4410,22 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Improved Constructions for Distributed Multi-Point Functions.</t>
+          <t>IEEE_S&amp;P-Security and Privacy Experiences of First- and Second-Generation Pakistani Immigrants to the US: Perceptions, Practices, Challenges, and Parent-Child Dynamics.</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Princeton University</t>
+          <t>Purdue University West Lafayette</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Kanav Gupta</t>
+          <t>Ran Elgedawy</t>
         </is>
       </c>
       <c r="B175" t="n">
@@ -4433,22 +4433,22 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-SHARK: Actively Secure Inference Using Function Secret Sharing.</t>
+          <t>IEEE_S&amp;P-Security and Privacy Experiences of First- and Second-Generation Pakistani Immigrants to the US: Perceptions, Practices, Challenges, and Parent-Child Dynamics.</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>University of Maryland, College Park</t>
+          <t>University of Tennessee at Knoxville</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Nishanth Chandran</t>
+          <t>Scott Ruoti</t>
         </is>
       </c>
       <c r="B176" t="n">
@@ -4456,22 +4456,22 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-SHARK: Actively Secure Inference Using Function Secret Sharing.</t>
+          <t>IEEE_S&amp;P-Security and Privacy Experiences of First- and Second-Generation Pakistani Immigrants to the US: Perceptions, Practices, Challenges, and Parent-Child Dynamics.</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Microsoft Research (United Kingdom)</t>
+          <t>University of Tennessee at Knoxville</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Divya Gupta 0001</t>
+          <t>Yaxin Tu</t>
         </is>
       </c>
       <c r="B177" t="n">
@@ -4479,22 +4479,22 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-SHARK: Actively Secure Inference Using Function Secret Sharing.</t>
+          <t>IEEE_S&amp;P-Improved Constructions for Distributed Multi-Point Functions.</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Microsoft Research (United Kingdom)</t>
+          <t>Princeton University</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Jonathan Katz</t>
+          <t>Kanav Gupta</t>
         </is>
       </c>
       <c r="B178" t="n">
@@ -4506,18 +4506,18 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Google (United States)</t>
+          <t>University of Maryland, College Park</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Rahul Sharma 0001</t>
+          <t>Nishanth Chandran</t>
         </is>
       </c>
       <c r="B179" t="n">
@@ -4529,18 +4529,18 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>University of Maryland, College Park</t>
+          <t>Microsoft Research (United Kingdom)</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Zhenting Wang</t>
+          <t>Divya Gupta 0001</t>
         </is>
       </c>
       <c r="B180" t="n">
@@ -4548,22 +4548,22 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Towards Reliable Verification of Unauthorized Data Usage in Personalized Text-to-Image Diffusion Models.</t>
+          <t>IEEE_S&amp;P-SHARK: Actively Secure Inference Using Function Secret Sharing.</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Rutgers, The State University of New Jersey</t>
+          <t>Microsoft Research (United Kingdom)</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Xuandong Zhao</t>
+          <t>Jonathan Katz</t>
         </is>
       </c>
       <c r="B181" t="n">
@@ -4571,22 +4571,22 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-SoK: Watermarking for AI-Generated Content.</t>
+          <t>IEEE_S&amp;P-SHARK: Actively Secure Inference Using Function Secret Sharing.</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Berkeley College; University of California, Berkeley</t>
+          <t>Google (United States)</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Sam Gunn</t>
+          <t>Rahul Sharma 0001</t>
         </is>
       </c>
       <c r="B182" t="n">
@@ -4594,22 +4594,22 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-SoK: Watermarking for AI-Generated Content.</t>
+          <t>IEEE_S&amp;P-SHARK: Actively Secure Inference Using Function Secret Sharing.</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Berkeley College; University of California, Berkeley</t>
+          <t>University of Maryland, College Park</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Miranda Christ</t>
+          <t>Zhenting Wang</t>
         </is>
       </c>
       <c r="B183" t="n">
@@ -4617,22 +4617,22 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-SoK: Watermarking for AI-Generated Content.</t>
+          <t>IEEE_S&amp;P-Towards Reliable Verification of Unauthorized Data Usage in Personalized Text-to-Image Diffusion Models.</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Columbia University</t>
+          <t>Rutgers, The State University of New Jersey</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Jaiden Fairoze</t>
+          <t>Xuandong Zhao</t>
         </is>
       </c>
       <c r="B184" t="n">
@@ -4644,7 +4644,7 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Andrés Fábrega</t>
+          <t>Sam Gunn</t>
         </is>
       </c>
       <c r="B185" t="n">
@@ -4667,18 +4667,18 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Cornell University</t>
+          <t>Berkeley College; University of California, Berkeley</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Sanjam Garg</t>
+          <t>Miranda Christ</t>
         </is>
       </c>
       <c r="B186" t="n">
@@ -4690,18 +4690,18 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Berkeley College; University of California, Berkeley</t>
+          <t>Columbia University</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Sanghyun Hong 0001</t>
+          <t>Jaiden Fairoze</t>
         </is>
       </c>
       <c r="B187" t="n">
@@ -4713,18 +4713,18 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Oregon State University</t>
+          <t>Berkeley College; University of California, Berkeley</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Milad Nasr</t>
+          <t>Andrés Fábrega</t>
         </is>
       </c>
       <c r="B188" t="n">
@@ -4736,18 +4736,18 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Google (United States); Google DeepMind (United Kingdom)</t>
+          <t>Cornell University</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Somesh Jha</t>
+          <t>Sanjam Garg</t>
         </is>
       </c>
       <c r="B189" t="n">
@@ -4759,18 +4759,18 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>University of Wisconsin–Madison</t>
+          <t>Berkeley College; University of California, Berkeley</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Lei Li 0005</t>
+          <t>Sanghyun Hong 0001</t>
         </is>
       </c>
       <c r="B190" t="n">
@@ -4782,18 +4782,18 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>Oregon State University</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Dawn Song</t>
+          <t>Milad Nasr</t>
         </is>
       </c>
       <c r="B191" t="n">
@@ -4805,18 +4805,18 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Berkeley College; University of California, Berkeley</t>
+          <t>Google (United States); Google DeepMind (United Kingdom)</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Florian Schaub</t>
+          <t>Somesh Jha</t>
         </is>
       </c>
       <c r="B192" t="n">
@@ -4824,22 +4824,22 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Transparency in Usable Privacy and Security Research: Scholars' Perspectives, Practices, and Recommendations.</t>
+          <t>IEEE_S&amp;P-SoK: Watermarking for AI-Generated Content.</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>University of Michigan–Ann Arbor</t>
+          <t>University of Wisconsin–Madison</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Anna Crowder</t>
+          <t>Lei Li 0005</t>
         </is>
       </c>
       <c r="B193" t="n">
@@ -4847,22 +4847,22 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Data to Infinity and Beyond: Examining Data Sharing and Reuse Practices in the Computer Security Community.</t>
+          <t>IEEE_S&amp;P-SoK: Watermarking for AI-Generated Content.</t>
         </is>
       </c>
       <c r="D193" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>University of Florida</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Kevin Childs</t>
+          <t>Dawn Song</t>
         </is>
       </c>
       <c r="B194" t="n">
@@ -4870,22 +4870,22 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Data to Infinity and Beyond: Examining Data Sharing and Reuse Practices in the Computer Security Community.</t>
+          <t>IEEE_S&amp;P-SoK: Watermarking for AI-Generated Content.</t>
         </is>
       </c>
       <c r="D194" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>University of Florida</t>
+          <t>Berkeley College; University of California, Berkeley</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Carson Stillman</t>
+          <t>G. Edward Suh</t>
         </is>
       </c>
       <c r="B195" t="n">
@@ -4893,22 +4893,22 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Data to Infinity and Beyond: Examining Data Sharing and Reuse Practices in the Computer Security Community.</t>
+          <t>IEEE_S&amp;P-Machine Learning with Privacy for Protected Attributes.</t>
         </is>
       </c>
       <c r="D195" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>University of Florida</t>
+          <t>Cornell University; Nvidia (United Kingdom)</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Patrick Traynor</t>
+          <t>Florian Schaub</t>
         </is>
       </c>
       <c r="B196" t="n">
@@ -4916,22 +4916,22 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Data to Infinity and Beyond: Examining Data Sharing and Reuse Practices in the Computer Security Community.</t>
+          <t>IEEE_S&amp;P-Transparency in Usable Privacy and Security Research: Scholars' Perspectives, Practices, and Recommendations.</t>
         </is>
       </c>
       <c r="D196" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>University of Florida</t>
+          <t>University of Michigan–Ann Arbor</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Yaman Yu</t>
+          <t>Anna Crowder</t>
         </is>
       </c>
       <c r="B197" t="n">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Exploring Parent-Child Perceptions on Safety in Generative AI: Concerns, Mitigation Strategies, and Design Implications.</t>
+          <t>IEEE_S&amp;P-Data to Infinity and Beyond: Examining Data Sharing and Reuse Practices in the Computer Security Community.</t>
         </is>
       </c>
       <c r="D197" t="n">
@@ -4947,14 +4947,14 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>University of Illinois Urbana-Champaign</t>
+          <t>University of Florida</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Yang Wang 0005</t>
+          <t>Kevin Childs</t>
         </is>
       </c>
       <c r="B198" t="n">
@@ -4962,22 +4962,22 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Exploring Parent-Child Perceptions on Safety in Generative AI: Concerns, Mitigation Strategies, and Design Implications.</t>
+          <t>IEEE_S&amp;P-Data to Infinity and Beyond: Examining Data Sharing and Reuse Practices in the Computer Security Community.</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>University of Illinois Urbana-Champaign</t>
+          <t>University of Florida</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Yaman Yu</t>
+          <t>Carson Stillman</t>
         </is>
       </c>
       <c r="B199" t="n">
@@ -4985,22 +4985,22 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Security Perceptions of Users in Stablecoins: Advantages and Risks within the Cryptocurrency Ecosystem.</t>
+          <t>IEEE_S&amp;P-Data to Infinity and Beyond: Examining Data Sharing and Reuse Practices in the Computer Security Community.</t>
         </is>
       </c>
       <c r="D199" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>University of Illinois Urbana-Champaign</t>
+          <t>University of Florida</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Kaihua Qin</t>
+          <t>Patrick Traynor</t>
         </is>
       </c>
       <c r="B200" t="n">
@@ -5008,7 +5008,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Security Perceptions of Users in Stablecoins: Advantages and Risks within the Cryptocurrency Ecosystem.</t>
+          <t>IEEE_S&amp;P-Data to Infinity and Beyond: Examining Data Sharing and Reuse Practices in the Computer Security Community.</t>
         </is>
       </c>
       <c r="D200" t="n">
@@ -5016,14 +5016,14 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Yale University</t>
+          <t>University of Florida</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Yang Wang 0005</t>
+          <t>Yaman Yu</t>
         </is>
       </c>
       <c r="B201" t="n">
@@ -5031,11 +5031,11 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Security Perceptions of Users in Stablecoins: Advantages and Risks within the Cryptocurrency Ecosystem.</t>
+          <t>IEEE_S&amp;P-Exploring Parent-Child Perceptions on Safety in Generative AI: Concerns, Mitigation Strategies, and Design Implications.</t>
         </is>
       </c>
       <c r="D201" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Kurt Thomas</t>
+          <t>Yang Wang 0005</t>
         </is>
       </c>
       <c r="B202" t="n">
@@ -5054,22 +5054,22 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Supporting Human Raters with the Detection of Harmful Content Using Large Language Models.</t>
+          <t>IEEE_S&amp;P-Exploring Parent-Child Perceptions on Safety in Generative AI: Concerns, Mitigation Strategies, and Design Implications.</t>
         </is>
       </c>
       <c r="D202" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Google (United States)</t>
+          <t>University of Illinois Urbana-Champaign</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Patrick Gage Kelley</t>
+          <t>Yaman Yu</t>
         </is>
       </c>
       <c r="B203" t="n">
@@ -5077,7 +5077,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Supporting Human Raters with the Detection of Harmful Content Using Large Language Models.</t>
+          <t>IEEE_S&amp;P-Security Perceptions of Users in Stablecoins: Advantages and Risks within the Cryptocurrency Ecosystem.</t>
         </is>
       </c>
       <c r="D203" t="n">
@@ -5085,14 +5085,14 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Google (United States)</t>
+          <t>University of Illinois Urbana-Champaign</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>David Tao</t>
+          <t>Kaihua Qin</t>
         </is>
       </c>
       <c r="B204" t="n">
@@ -5100,22 +5100,22 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Supporting Human Raters with the Detection of Harmful Content Using Large Language Models.</t>
+          <t>IEEE_S&amp;P-Security Perceptions of Users in Stablecoins: Advantages and Risks within the Cryptocurrency Ecosystem.</t>
         </is>
       </c>
       <c r="D204" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Google (United States)</t>
+          <t>Yale University</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Sarah Meiklejohn</t>
+          <t>Yang Wang 0005</t>
         </is>
       </c>
       <c r="B205" t="n">
@@ -5123,22 +5123,22 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Supporting Human Raters with the Detection of Harmful Content Using Large Language Models.</t>
+          <t>IEEE_S&amp;P-Security Perceptions of Users in Stablecoins: Advantages and Risks within the Cryptocurrency Ecosystem.</t>
         </is>
       </c>
       <c r="D205" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Google (United States)</t>
+          <t>University of Illinois Urbana-Champaign</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Owen Vallis</t>
+          <t>Kurt Thomas</t>
         </is>
       </c>
       <c r="B206" t="n">
@@ -5150,7 +5150,7 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
@@ -5161,7 +5161,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Shunwen Tan</t>
+          <t>Patrick Gage Kelley</t>
         </is>
       </c>
       <c r="B207" t="n">
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
@@ -5184,7 +5184,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Felipe Tiengo Ferreira</t>
+          <t>David Tao</t>
         </is>
       </c>
       <c r="B208" t="n">
@@ -5196,18 +5196,18 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Google (United States); DeepMind (United Kingdom)</t>
+          <t>Google (United States)</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Elie Bursztein</t>
+          <t>Sarah Meiklejohn</t>
         </is>
       </c>
       <c r="B209" t="n">
@@ -5219,7 +5219,7 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E209" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Lucy Simko</t>
+          <t>Owen Vallis</t>
         </is>
       </c>
       <c r="B210" t="n">
@@ -5238,22 +5238,22 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-"It's been Lovely Watching you": Institutional Decision-Making on Online Proctoring Software.</t>
+          <t>IEEE_S&amp;P-Supporting Human Raters with the Detection of Harmful Content Using Large Language Models.</t>
         </is>
       </c>
       <c r="D210" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>George Washington University</t>
+          <t>Google (United States)</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Ryan Watkins</t>
+          <t>Shunwen Tan</t>
         </is>
       </c>
       <c r="B211" t="n">
@@ -5261,22 +5261,22 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-"It's been Lovely Watching you": Institutional Decision-Making on Online Proctoring Software.</t>
+          <t>IEEE_S&amp;P-Supporting Human Raters with the Detection of Harmful Content Using Large Language Models.</t>
         </is>
       </c>
       <c r="D211" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>George Washington University</t>
+          <t>Google (United States)</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Adam J. Aviv</t>
+          <t>Felipe Tiengo Ferreira</t>
         </is>
       </c>
       <c r="B212" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-"It's been Lovely Watching you": Institutional Decision-Making on Online Proctoring Software.</t>
+          <t>IEEE_S&amp;P-Supporting Human Raters with the Detection of Harmful Content Using Large Language Models.</t>
         </is>
       </c>
       <c r="D212" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>George Washington University</t>
+          <t>Google (United States); DeepMind (United Kingdom)</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Tung Le 0005</t>
+          <t>Elie Bursztein</t>
         </is>
       </c>
       <c r="B213" t="n">
@@ -5307,22 +5307,22 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Hermes: Efficient and Secure Multi-Writer Encrypted Database.</t>
+          <t>IEEE_S&amp;P-Supporting Human Raters with the Detection of Harmful Content Using Large Language Models.</t>
         </is>
       </c>
       <c r="D213" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Virginia Tech</t>
+          <t>Google (United States)</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Borja Balle</t>
+          <t>Lucy Simko</t>
         </is>
       </c>
       <c r="B214" t="n">
@@ -5330,22 +5330,22 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Hash-Prune-Invert: Improved Differentially Private Heavy-Hitter Detection in the Two-Server Model.</t>
+          <t>IEEE_S&amp;P-"It's been Lovely Watching you": Institutional Decision-Making on Online Proctoring Software.</t>
         </is>
       </c>
       <c r="D214" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Google (United States); DeepMind (United Kingdom)</t>
+          <t>George Washington University</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>James Bell-Clark</t>
+          <t>Ryan Watkins</t>
         </is>
       </c>
       <c r="B215" t="n">
@@ -5353,22 +5353,22 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Hash-Prune-Invert: Improved Differentially Private Heavy-Hitter Detection in the Two-Server Model.</t>
+          <t>IEEE_S&amp;P-"It's been Lovely Watching you": Institutional Decision-Making on Online Proctoring Software.</t>
         </is>
       </c>
       <c r="D215" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Google (United States)</t>
+          <t>George Washington University</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Albert Cheu</t>
+          <t>Adam J. Aviv</t>
         </is>
       </c>
       <c r="B216" t="n">
@@ -5376,22 +5376,22 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Hash-Prune-Invert: Improved Differentially Private Heavy-Hitter Detection in the Two-Server Model.</t>
+          <t>IEEE_S&amp;P-"It's been Lovely Watching you": Institutional Decision-Making on Online Proctoring Software.</t>
         </is>
       </c>
       <c r="D216" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Google (United States)</t>
+          <t>George Washington University</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Adrià Gascón</t>
+          <t>Tung Le 0005</t>
         </is>
       </c>
       <c r="B217" t="n">
@@ -5399,22 +5399,22 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Hash-Prune-Invert: Improved Differentially Private Heavy-Hitter Detection in the Two-Server Model.</t>
+          <t>IEEE_S&amp;P-Hermes: Efficient and Secure Multi-Writer Encrypted Database.</t>
         </is>
       </c>
       <c r="D217" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Google (United States)</t>
+          <t>Virginia Tech</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Jonathan Katz</t>
+          <t>Borja Balle</t>
         </is>
       </c>
       <c r="B218" t="n">
@@ -5426,18 +5426,18 @@
         </is>
       </c>
       <c r="D218" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Google (United States)</t>
+          <t>Google (United States); DeepMind (United Kingdom)</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Mariana Raykova 0001</t>
+          <t>James Bell-Clark</t>
         </is>
       </c>
       <c r="B219" t="n">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="D219" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E219" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Phillipp Schoppmann</t>
+          <t>Albert Cheu</t>
         </is>
       </c>
       <c r="B220" t="n">
@@ -5472,7 +5472,7 @@
         </is>
       </c>
       <c r="D220" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E220" t="inlineStr">
         <is>
@@ -5483,7 +5483,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Thomas Steinke 0002</t>
+          <t>Adrià Gascón</t>
         </is>
       </c>
       <c r="B221" t="n">
@@ -5495,18 +5495,18 @@
         </is>
       </c>
       <c r="D221" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>DeepMind (United Kingdom); Google (United States)</t>
+          <t>Google (United States)</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Guoren Li</t>
+          <t>Jonathan Katz</t>
         </is>
       </c>
       <c r="B222" t="n">
@@ -5514,22 +5514,22 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Redefining Indirect Call Analysis with KallGraph.</t>
+          <t>IEEE_S&amp;P-Hash-Prune-Invert: Improved Differentially Private Heavy-Hitter Detection in the Two-Server Model.</t>
         </is>
       </c>
       <c r="D222" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>University of California, Riverside</t>
+          <t>Google (United States)</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Manu Sridharan</t>
+          <t>Mariana Raykova 0001</t>
         </is>
       </c>
       <c r="B223" t="n">
@@ -5537,22 +5537,22 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Redefining Indirect Call Analysis with KallGraph.</t>
+          <t>IEEE_S&amp;P-Hash-Prune-Invert: Improved Differentially Private Heavy-Hitter Detection in the Two-Server Model.</t>
         </is>
       </c>
       <c r="D223" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>University of California, Riverside</t>
+          <t>Google (United States)</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Zhiyun Qian</t>
+          <t>Phillipp Schoppmann</t>
         </is>
       </c>
       <c r="B224" t="n">
@@ -5560,22 +5560,22 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Redefining Indirect Call Analysis with KallGraph.</t>
+          <t>IEEE_S&amp;P-Hash-Prune-Invert: Improved Differentially Private Heavy-Hitter Detection in the Two-Server Model.</t>
         </is>
       </c>
       <c r="D224" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>University of California, Riverside</t>
+          <t>Google (United States)</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Elliot Tarbet</t>
+          <t>Thomas Steinke 0002</t>
         </is>
       </c>
       <c r="B225" t="n">
@@ -5583,22 +5583,22 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-PyLingual: Toward Perfect Decompilation of Evolving High-Level Languages.</t>
+          <t>IEEE_S&amp;P-Hash-Prune-Invert: Improved Differentially Private Heavy-Hitter Detection in the Two-Server Model.</t>
         </is>
       </c>
       <c r="D225" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>The University of Texas at Dallas</t>
+          <t>DeepMind (United Kingdom); Google (United States)</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Max Zheng</t>
+          <t>Danfeng Zhang</t>
         </is>
       </c>
       <c r="B226" t="n">
@@ -5606,22 +5606,22 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-PyLingual: Toward Perfect Decompilation of Evolving High-Level Languages.</t>
+          <t>IEEE_S&amp;P-Click Without Compromise: Online Advertising Measurement via Per User Differential Privacy.</t>
         </is>
       </c>
       <c r="D226" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>The University of Texas at Dallas</t>
+          <t>Duke University</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Sangsoo Ko</t>
+          <t>Guoren Li</t>
         </is>
       </c>
       <c r="B227" t="n">
@@ -5629,22 +5629,22 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-PyLingual: Toward Perfect Decompilation of Evolving High-Level Languages.</t>
+          <t>IEEE_S&amp;P-Redefining Indirect Call Analysis with KallGraph.</t>
         </is>
       </c>
       <c r="D227" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>The University of Texas at Dallas</t>
+          <t>University of California, Riverside</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Jessica Ouyang 0001</t>
+          <t>Manu Sridharan</t>
         </is>
       </c>
       <c r="B228" t="n">
@@ -5652,22 +5652,22 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-PyLingual: Toward Perfect Decompilation of Evolving High-Level Languages.</t>
+          <t>IEEE_S&amp;P-Redefining Indirect Call Analysis with KallGraph.</t>
         </is>
       </c>
       <c r="D228" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>The University of Texas at Dallas</t>
+          <t>University of California, Riverside</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Kangkook Jee</t>
+          <t>Zhiyun Qian</t>
         </is>
       </c>
       <c r="B229" t="n">
@@ -5675,22 +5675,22 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-PyLingual: Toward Perfect Decompilation of Evolving High-Level Languages.</t>
+          <t>IEEE_S&amp;P-Redefining Indirect Call Analysis with KallGraph.</t>
         </is>
       </c>
       <c r="D229" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>The University of Texas at Dallas</t>
+          <t>University of California, Riverside</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Antonio Flores-Montoya</t>
+          <t>Elliot Tarbet</t>
         </is>
       </c>
       <c r="B230" t="n">
@@ -5698,22 +5698,22 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Disassembly as Weighted Interval Scheduling with Learned Weights.</t>
+          <t>IEEE_S&amp;P-PyLingual: Toward Perfect Decompilation of Evolving High-Level Languages.</t>
         </is>
       </c>
       <c r="D230" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>GrammaTech (United States)</t>
+          <t>The University of Texas at Dallas</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Junghee Lim</t>
+          <t>Max Zheng</t>
         </is>
       </c>
       <c r="B231" t="n">
@@ -5721,22 +5721,22 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Disassembly as Weighted Interval Scheduling with Learned Weights.</t>
+          <t>IEEE_S&amp;P-PyLingual: Toward Perfect Decompilation of Evolving High-Level Languages.</t>
         </is>
       </c>
       <c r="D231" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>GrammaTech (United States)</t>
+          <t>The University of Texas at Dallas</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Adam Seitz</t>
+          <t>Sangsoo Ko</t>
         </is>
       </c>
       <c r="B232" t="n">
@@ -5744,22 +5744,22 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Disassembly as Weighted Interval Scheduling with Learned Weights.</t>
+          <t>IEEE_S&amp;P-PyLingual: Toward Perfect Decompilation of Evolving High-Level Languages.</t>
         </is>
       </c>
       <c r="D232" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>GrammaTech (United States)</t>
+          <t>The University of Texas at Dallas</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Akshay Sood</t>
+          <t>Jessica Ouyang 0001</t>
         </is>
       </c>
       <c r="B233" t="n">
@@ -5767,22 +5767,22 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Disassembly as Weighted Interval Scheduling with Learned Weights.</t>
+          <t>IEEE_S&amp;P-PyLingual: Toward Perfect Decompilation of Evolving High-Level Languages.</t>
         </is>
       </c>
       <c r="D233" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>GrammaTech (United States)</t>
+          <t>The University of Texas at Dallas</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Edward Raff</t>
+          <t>Kangkook Jee</t>
         </is>
       </c>
       <c r="B234" t="n">
@@ -5790,22 +5790,22 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Disassembly as Weighted Interval Scheduling with Learned Weights.</t>
+          <t>IEEE_S&amp;P-PyLingual: Toward Perfect Decompilation of Evolving High-Level Languages.</t>
         </is>
       </c>
       <c r="D234" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton (United States)</t>
+          <t>The University of Texas at Dallas</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Jun Xu 0024</t>
+          <t>Antonio Flores-Montoya</t>
         </is>
       </c>
       <c r="B235" t="n">
@@ -5813,22 +5813,22 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Inspecting Virtual Machine Diversification Inside Virtualization Obfuscation.</t>
+          <t>IEEE_S&amp;P-Disassembly as Weighted Interval Scheduling with Learned Weights.</t>
         </is>
       </c>
       <c r="D235" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>University of Utah</t>
+          <t>GrammaTech (United States)</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Jiwon Kim 0001</t>
+          <t>Junghee Lim</t>
         </is>
       </c>
       <c r="B236" t="n">
@@ -5836,22 +5836,22 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Chimera: Fuzzing P4 Network Infrastructure for Multi-Plane Bug Detection and Vulnerability Discovery.</t>
+          <t>IEEE_S&amp;P-Disassembly as Weighted Interval Scheduling with Learned Weights.</t>
         </is>
       </c>
       <c r="D236" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Purdue University West Lafayette</t>
+          <t>GrammaTech (United States)</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>David Chisnall</t>
+          <t>Adam Seitz</t>
         </is>
       </c>
       <c r="B237" t="n">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-SoK: Software Compartmentalization.</t>
+          <t>IEEE_S&amp;P-Disassembly as Weighted Interval Scheduling with Learned Weights.</t>
         </is>
       </c>
       <c r="D237" t="n">
@@ -5867,14 +5867,14 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>ON Semiconductor (United States)</t>
+          <t>GrammaTech (United States)</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Zheng Yang</t>
+          <t>Akshay Sood</t>
         </is>
       </c>
       <c r="B238" t="n">
@@ -5882,22 +5882,22 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-CoinDef: A Comprehensive Code Injection Defense for the Electron Framework.</t>
+          <t>IEEE_S&amp;P-Disassembly as Weighted Interval Scheduling with Learned Weights.</t>
         </is>
       </c>
       <c r="D238" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>GrammaTech (United States)</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Simon P. Chung</t>
+          <t>Edward Raff</t>
         </is>
       </c>
       <c r="B239" t="n">
@@ -5905,22 +5905,22 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-CoinDef: A Comprehensive Code Injection Defense for the Electron Framework.</t>
+          <t>IEEE_S&amp;P-Disassembly as Weighted Interval Scheduling with Learned Weights.</t>
         </is>
       </c>
       <c r="D239" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>Booz Allen Hamilton (United States)</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Jizhou Chen</t>
+          <t>Jun Xu 0024</t>
         </is>
       </c>
       <c r="B240" t="n">
@@ -5928,22 +5928,22 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-CoinDef: A Comprehensive Code Injection Defense for the Electron Framework.</t>
+          <t>IEEE_S&amp;P-Inspecting Virtual Machine Diversification Inside Virtualization Obfuscation.</t>
         </is>
       </c>
       <c r="D240" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>University of Utah</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Runze Zhang</t>
+          <t>Jiwon Kim 0001</t>
         </is>
       </c>
       <c r="B241" t="n">
@@ -5951,22 +5951,22 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-CoinDef: A Comprehensive Code Injection Defense for the Electron Framework.</t>
+          <t>IEEE_S&amp;P-Chimera: Fuzzing P4 Network Infrastructure for Multi-Plane Bug Detection and Vulnerability Discovery.</t>
         </is>
       </c>
       <c r="D241" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>Purdue University West Lafayette</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Brendan Saltaformaggio</t>
+          <t>David Chisnall</t>
         </is>
       </c>
       <c r="B242" t="n">
@@ -5974,22 +5974,22 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-CoinDef: A Comprehensive Code Injection Defense for the Electron Framework.</t>
+          <t>IEEE_S&amp;P-SoK: Software Compartmentalization.</t>
         </is>
       </c>
       <c r="D242" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>ON Semiconductor (United States)</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Wenke Lee</t>
+          <t>Zheng Yang</t>
         </is>
       </c>
       <c r="B243" t="n">
@@ -6001,7 +6001,7 @@
         </is>
       </c>
       <c r="D243" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E243" t="inlineStr">
         <is>
@@ -6012,7 +6012,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Quinn Burke 0002</t>
+          <t>Simon P. Chung</t>
         </is>
       </c>
       <c r="B244" t="n">
@@ -6020,22 +6020,22 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Efficient Storage Integrity in Adversarial Settings.</t>
+          <t>IEEE_S&amp;P-CoinDef: A Comprehensive Code Injection Defense for the Electron Framework.</t>
         </is>
       </c>
       <c r="D244" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>University of Wisconsin–Madison</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Ryan Sheatsley</t>
+          <t>Jizhou Chen</t>
         </is>
       </c>
       <c r="B245" t="n">
@@ -6043,22 +6043,22 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Efficient Storage Integrity in Adversarial Settings.</t>
+          <t>IEEE_S&amp;P-CoinDef: A Comprehensive Code Injection Defense for the Electron Framework.</t>
         </is>
       </c>
       <c r="D245" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>University of Wisconsin–Madison</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Yohan Beugin</t>
+          <t>Runze Zhang</t>
         </is>
       </c>
       <c r="B246" t="n">
@@ -6066,22 +6066,22 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Efficient Storage Integrity in Adversarial Settings.</t>
+          <t>IEEE_S&amp;P-CoinDef: A Comprehensive Code Injection Defense for the Electron Framework.</t>
         </is>
       </c>
       <c r="D246" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>University of Wisconsin–Madison</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Eric Pauley</t>
+          <t>Brendan Saltaformaggio</t>
         </is>
       </c>
       <c r="B247" t="n">
@@ -6089,22 +6089,22 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Efficient Storage Integrity in Adversarial Settings.</t>
+          <t>IEEE_S&amp;P-CoinDef: A Comprehensive Code Injection Defense for the Electron Framework.</t>
         </is>
       </c>
       <c r="D247" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>University of Wisconsin–Madison</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Owen Hines</t>
+          <t>Wenke Lee</t>
         </is>
       </c>
       <c r="B248" t="n">
@@ -6112,22 +6112,22 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Efficient Storage Integrity in Adversarial Settings.</t>
+          <t>IEEE_S&amp;P-CoinDef: A Comprehensive Code Injection Defense for the Electron Framework.</t>
         </is>
       </c>
       <c r="D248" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>University of Wisconsin–Madison</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Ananta Soneji</t>
+          <t>Quinn Burke 0002</t>
         </is>
       </c>
       <c r="B249" t="n">
@@ -6135,22 +6135,22 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-"It's almost like Frankenstein": Investigating the Complexities of Scientific Collaboration and Privilege Management within Research Computing Infrastructures.</t>
+          <t>IEEE_S&amp;P-Efficient Storage Integrity in Adversarial Settings.</t>
         </is>
       </c>
       <c r="D249" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Arizona State University</t>
+          <t>University of Wisconsin–Madison</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Jaejong Baek</t>
+          <t>Ryan Sheatsley</t>
         </is>
       </c>
       <c r="B250" t="n">
@@ -6158,22 +6158,22 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-"It's almost like Frankenstein": Investigating the Complexities of Scientific Collaboration and Privilege Management within Research Computing Infrastructures.</t>
+          <t>IEEE_S&amp;P-Efficient Storage Integrity in Adversarial Settings.</t>
         </is>
       </c>
       <c r="D250" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Arizona State University</t>
+          <t>University of Wisconsin–Madison</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Tiffany Bao</t>
+          <t>Yohan Beugin</t>
         </is>
       </c>
       <c r="B251" t="n">
@@ -6181,22 +6181,22 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-"It's almost like Frankenstein": Investigating the Complexities of Scientific Collaboration and Privilege Management within Research Computing Infrastructures.</t>
+          <t>IEEE_S&amp;P-Efficient Storage Integrity in Adversarial Settings.</t>
         </is>
       </c>
       <c r="D251" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Arizona State University</t>
+          <t>University of Wisconsin–Madison</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Adam Doupé</t>
+          <t>Eric Pauley</t>
         </is>
       </c>
       <c r="B252" t="n">
@@ -6204,22 +6204,22 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-"It's almost like Frankenstein": Investigating the Complexities of Scientific Collaboration and Privilege Management within Research Computing Infrastructures.</t>
+          <t>IEEE_S&amp;P-Efficient Storage Integrity in Adversarial Settings.</t>
         </is>
       </c>
       <c r="D252" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Arizona State University</t>
+          <t>University of Wisconsin–Madison</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Anna P. Y. Woo</t>
+          <t>Owen Hines</t>
         </is>
       </c>
       <c r="B253" t="n">
@@ -6227,22 +6227,22 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Efficient Proofs of Possession for Legacy Signatures.</t>
+          <t>IEEE_S&amp;P-Efficient Storage Integrity in Adversarial Settings.</t>
         </is>
       </c>
       <c r="D253" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>University of Michigan–Ann Arbor</t>
+          <t>University of Wisconsin–Madison</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Alex Ozdemir</t>
+          <t>Ananta Soneji</t>
         </is>
       </c>
       <c r="B254" t="n">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Efficient Proofs of Possession for Legacy Signatures.</t>
+          <t>IEEE_S&amp;P-"It's almost like Frankenstein": Investigating the Complexities of Scientific Collaboration and Privilege Management within Research Computing Infrastructures.</t>
         </is>
       </c>
       <c r="D254" t="n">
@@ -6258,14 +6258,14 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Stanford University</t>
+          <t>Arizona State University</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Chad Sharp</t>
+          <t>Jaejong Baek</t>
         </is>
       </c>
       <c r="B255" t="n">
@@ -6273,7 +6273,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Efficient Proofs of Possession for Legacy Signatures.</t>
+          <t>IEEE_S&amp;P-"It's almost like Frankenstein": Investigating the Complexities of Scientific Collaboration and Privilege Management within Research Computing Infrastructures.</t>
         </is>
       </c>
       <c r="D255" t="n">
@@ -6281,14 +6281,14 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>University of Michigan–Ann Arbor</t>
+          <t>Arizona State University</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Paul Grubbs</t>
+          <t>Tiffany Bao</t>
         </is>
       </c>
       <c r="B256" t="n">
@@ -6296,22 +6296,22 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Efficient Proofs of Possession for Legacy Signatures.</t>
+          <t>IEEE_S&amp;P-"It's almost like Frankenstein": Investigating the Complexities of Scientific Collaboration and Privilege Management within Research Computing Infrastructures.</t>
         </is>
       </c>
       <c r="D256" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>University of Michigan–Ann Arbor</t>
+          <t>Arizona State University</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Kunming Jiang</t>
+          <t>Adam Doupé</t>
         </is>
       </c>
       <c r="B257" t="n">
@@ -6319,22 +6319,22 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-CoBBL: Dynamic Constraint Generation for SNARKs.</t>
+          <t>IEEE_S&amp;P-"It's almost like Frankenstein": Investigating the Complexities of Scientific Collaboration and Privilege Management within Research Computing Infrastructures.</t>
         </is>
       </c>
       <c r="D257" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>Arizona State University</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Fraser Brown</t>
+          <t>Anna P. Y. Woo</t>
         </is>
       </c>
       <c r="B258" t="n">
@@ -6342,22 +6342,22 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-CoBBL: Dynamic Constraint Generation for SNARKs.</t>
+          <t>IEEE_S&amp;P-Efficient Proofs of Possession for Legacy Signatures.</t>
         </is>
       </c>
       <c r="D258" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>University of Michigan–Ann Arbor</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Riad S. Wahby</t>
+          <t>Alex Ozdemir</t>
         </is>
       </c>
       <c r="B259" t="n">
@@ -6365,22 +6365,22 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-CoBBL: Dynamic Constraint Generation for SNARKs.</t>
+          <t>IEEE_S&amp;P-Efficient Proofs of Possession for Legacy Signatures.</t>
         </is>
       </c>
       <c r="D259" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>Stanford University</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Jiwon Kim</t>
+          <t>Chad Sharp</t>
         </is>
       </c>
       <c r="B260" t="n">
@@ -6388,22 +6388,22 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-ALPACA: Anonymous Blocklisting with Constant-Sized Updatable Proofs.</t>
+          <t>IEEE_S&amp;P-Efficient Proofs of Possession for Legacy Signatures.</t>
         </is>
       </c>
       <c r="D260" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>University of Michigan</t>
+          <t>University of Michigan–Ann Arbor</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Abhiram Kothapalli</t>
+          <t>Paul Grubbs</t>
         </is>
       </c>
       <c r="B261" t="n">
@@ -6411,22 +6411,22 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-ALPACA: Anonymous Blocklisting with Constant-Sized Updatable Proofs.</t>
+          <t>IEEE_S&amp;P-Efficient Proofs of Possession for Legacy Signatures.</t>
         </is>
       </c>
       <c r="D261" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>University of California, Berkeley</t>
+          <t>University of Michigan–Ann Arbor</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Orestis Chardouvelis</t>
+          <t>Kunming Jiang</t>
         </is>
       </c>
       <c r="B262" t="n">
@@ -6434,11 +6434,11 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-ALPACA: Anonymous Blocklisting with Constant-Sized Updatable Proofs.</t>
+          <t>IEEE_S&amp;P-CoBBL: Dynamic Constraint Generation for SNARKs.</t>
         </is>
       </c>
       <c r="D262" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E262" t="inlineStr">
         <is>
@@ -6449,7 +6449,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Riad S. Wahby</t>
+          <t>Fraser Brown</t>
         </is>
       </c>
       <c r="B263" t="n">
@@ -6457,11 +6457,11 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-ALPACA: Anonymous Blocklisting with Constant-Sized Updatable Proofs.</t>
+          <t>IEEE_S&amp;P-CoBBL: Dynamic Constraint Generation for SNARKs.</t>
         </is>
       </c>
       <c r="D263" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E263" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Paul Grubbs</t>
+          <t>Riad S. Wahby</t>
         </is>
       </c>
       <c r="B264" t="n">
@@ -6480,22 +6480,22 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-ALPACA: Anonymous Blocklisting with Constant-Sized Updatable Proofs.</t>
+          <t>IEEE_S&amp;P-CoBBL: Dynamic Constraint Generation for SNARKs.</t>
         </is>
       </c>
       <c r="D264" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>University of Michigan</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Charalampos Papamanthou</t>
+          <t>Jiwon Kim</t>
         </is>
       </c>
       <c r="B265" t="n">
@@ -6503,22 +6503,22 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-HydraProofs: Optimally Computing All Proofs in a Vector Commitment (With Applications to Efficient zkSNARKs Over Data from Multiple Users).</t>
+          <t>IEEE_S&amp;P-ALPACA: Anonymous Blocklisting with Constant-Sized Updatable Proofs.</t>
         </is>
       </c>
       <c r="D265" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Yale University</t>
+          <t>University of Michigan</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Tianyu Zhang</t>
+          <t>Abhiram Kothapalli</t>
         </is>
       </c>
       <c r="B266" t="n">
@@ -6526,22 +6526,22 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-FairZK: A Scalable System to Prove Machine Learning Fairness in Zero-Knowledge.</t>
+          <t>IEEE_S&amp;P-ALPACA: Anonymous Blocklisting with Constant-Sized Updatable Proofs.</t>
         </is>
       </c>
       <c r="D266" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>University of Illinois Urbana-Champaign</t>
+          <t>University of California, Berkeley</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Shen Dong</t>
+          <t>Orestis Chardouvelis</t>
         </is>
       </c>
       <c r="B267" t="n">
@@ -6549,22 +6549,22 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-FairZK: A Scalable System to Prove Machine Learning Fairness in Zero-Knowledge.</t>
+          <t>IEEE_S&amp;P-ALPACA: Anonymous Blocklisting with Constant-Sized Updatable Proofs.</t>
         </is>
       </c>
       <c r="D267" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>University of Illinois Urbana-Champaign</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Yupeng Zhang</t>
+          <t>Riad S. Wahby</t>
         </is>
       </c>
       <c r="B268" t="n">
@@ -6572,22 +6572,22 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-FairZK: A Scalable System to Prove Machine Learning Fairness in Zero-Knowledge.</t>
+          <t>IEEE_S&amp;P-ALPACA: Anonymous Blocklisting with Constant-Sized Updatable Proofs.</t>
         </is>
       </c>
       <c r="D268" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>University of Illinois Urbana-Champaign</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Stephan van Schaik</t>
+          <t>Paul Grubbs</t>
         </is>
       </c>
       <c r="B269" t="n">
@@ -6595,22 +6595,22 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Slice+Slice Baby: Generating Last-Level Cache Eviction Sets in the Blink of an Eye.</t>
+          <t>IEEE_S&amp;P-ALPACA: Anonymous Blocklisting with Constant-Sized Updatable Proofs.</t>
         </is>
       </c>
       <c r="D269" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>University of Michigan–Ann Arbor</t>
+          <t>University of Michigan</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Daniel Genkin</t>
+          <t>Charalampos Papamanthou</t>
         </is>
       </c>
       <c r="B270" t="n">
@@ -6618,22 +6618,22 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Slice+Slice Baby: Generating Last-Level Cache Eviction Sets in the Blink of an Eye.</t>
+          <t>IEEE_S&amp;P-HydraProofs: Optimally Computing All Proofs in a Vector Commitment (With Applications to Efficient zkSNARKs Over Data from Multiple Users).</t>
         </is>
       </c>
       <c r="D270" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>Yale University</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Boru Chen</t>
+          <t>Tianyu Zhang</t>
         </is>
       </c>
       <c r="B271" t="n">
@@ -6641,22 +6641,22 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Peek-a-Walk: Leaking Secrets via Page Walk Side Channels.</t>
+          <t>IEEE_S&amp;P-FairZK: A Scalable System to Prove Machine Learning Fairness in Zero-Knowledge.</t>
         </is>
       </c>
       <c r="D271" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Berkeley College; University of California, Berkeley</t>
+          <t>University of Illinois Urbana-Champaign</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Yingchen Wang</t>
+          <t>Shen Dong</t>
         </is>
       </c>
       <c r="B272" t="n">
@@ -6664,22 +6664,22 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Peek-a-Walk: Leaking Secrets via Page Walk Side Channels.</t>
+          <t>IEEE_S&amp;P-FairZK: A Scalable System to Prove Machine Learning Fairness in Zero-Knowledge.</t>
         </is>
       </c>
       <c r="D272" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Berkeley College; University of California, Berkeley</t>
+          <t>University of Illinois Urbana-Champaign</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Christopher W. Fletcher</t>
+          <t>Yupeng Zhang</t>
         </is>
       </c>
       <c r="B273" t="n">
@@ -6687,22 +6687,22 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Peek-a-Walk: Leaking Secrets via Page Walk Side Channels.</t>
+          <t>IEEE_S&amp;P-FairZK: A Scalable System to Prove Machine Learning Fairness in Zero-Knowledge.</t>
         </is>
       </c>
       <c r="D273" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Berkeley College; University of California, Berkeley</t>
+          <t>University of Illinois Urbana-Champaign</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Daniel Genkin</t>
+          <t>Stephan van Schaik</t>
         </is>
       </c>
       <c r="B274" t="n">
@@ -6710,22 +6710,22 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Peek-a-Walk: Leaking Secrets via Page Walk Side Channels.</t>
+          <t>IEEE_S&amp;P-Slice+Slice Baby: Generating Last-Level Cache Eviction Sets in the Blink of an Eye.</t>
         </is>
       </c>
       <c r="D274" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>University of Michigan–Ann Arbor</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>David Kohlbrenner</t>
+          <t>Daniel Genkin</t>
         </is>
       </c>
       <c r="B275" t="n">
@@ -6733,7 +6733,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Peek-a-Walk: Leaking Secrets via Page Walk Side Channels.</t>
+          <t>IEEE_S&amp;P-Slice+Slice Baby: Generating Last-Level Cache Eviction Sets in the Blink of an Eye.</t>
         </is>
       </c>
       <c r="D275" t="n">
@@ -6741,14 +6741,14 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>University of Washington</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Riccardo Paccagnella</t>
+          <t>Boru Chen</t>
         </is>
       </c>
       <c r="B276" t="n">
@@ -6760,18 +6760,18 @@
         </is>
       </c>
       <c r="D276" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>Berkeley College; University of California, Berkeley</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Daniel Genkin</t>
+          <t>Yingchen Wang</t>
         </is>
       </c>
       <c r="B277" t="n">
@@ -6779,22 +6779,22 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-SLAP: Data Speculation Attacks via Load Address Prediction on Apple Silicon.</t>
+          <t>IEEE_S&amp;P-Peek-a-Walk: Leaking Secrets via Page Walk Side Channels.</t>
         </is>
       </c>
       <c r="D277" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>Berkeley College; University of California, Berkeley</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Samy Amer</t>
+          <t>Christopher W. Fletcher</t>
         </is>
       </c>
       <c r="B278" t="n">
@@ -6802,22 +6802,22 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-PQ-Hammer: End-to-End Key Recovery Attacks on Post-Quantum Cryptography Using Rowhammer.</t>
+          <t>IEEE_S&amp;P-Peek-a-Walk: Leaking Secrets via Page Walk Side Channels.</t>
         </is>
       </c>
       <c r="D278" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>Berkeley College; University of California, Berkeley</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Yingchen Wang</t>
+          <t>Daniel Genkin</t>
         </is>
       </c>
       <c r="B279" t="n">
@@ -6825,22 +6825,22 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-PQ-Hammer: End-to-End Key Recovery Attacks on Post-Quantum Cryptography Using Rowhammer.</t>
+          <t>IEEE_S&amp;P-Peek-a-Walk: Leaking Secrets via Page Walk Side Channels.</t>
         </is>
       </c>
       <c r="D279" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Berkeley College; University of California, Berkeley</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Daniel Genkin</t>
+          <t>David Kohlbrenner</t>
         </is>
       </c>
       <c r="B280" t="n">
@@ -6848,22 +6848,22 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-PQ-Hammer: End-to-End Key Recovery Attacks on Post-Quantum Cryptography Using Rowhammer.</t>
+          <t>IEEE_S&amp;P-Peek-a-Walk: Leaking Secrets via Page Walk Side Channels.</t>
         </is>
       </c>
       <c r="D280" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>University of Washington</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Andrew Kwong</t>
+          <t>Riccardo Paccagnella</t>
         </is>
       </c>
       <c r="B281" t="n">
@@ -6871,22 +6871,22 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-PQ-Hammer: End-to-End Key Recovery Attacks on Post-Quantum Cryptography Using Rowhammer.</t>
+          <t>IEEE_S&amp;P-Peek-a-Walk: Leaking Secrets via Page Walk Side Channels.</t>
         </is>
       </c>
       <c r="D281" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>University of North Carolina Health Care; University of North Carolina at Chapel Hill</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Arkady Yerukhimovich</t>
+          <t>Daniel Genkin</t>
         </is>
       </c>
       <c r="B282" t="n">
@@ -6894,22 +6894,22 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-PQ-Hammer: End-to-End Key Recovery Attacks on Post-Quantum Cryptography Using Rowhammer.</t>
+          <t>IEEE_S&amp;P-SLAP: Data Speculation Attacks via Load Address Prediction on Apple Silicon.</t>
         </is>
       </c>
       <c r="D282" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>George Washington University</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Inwhan Chun</t>
+          <t>Samy Amer</t>
         </is>
       </c>
       <c r="B283" t="n">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Scheduled Disclosure: Turning Power into Timing Without Frequency Scaling.</t>
+          <t>IEEE_S&amp;P-PQ-Hammer: End-to-End Key Recovery Attacks on Post-Quantum Cryptography Using Rowhammer.</t>
         </is>
       </c>
       <c r="D283" t="n">
@@ -6925,14 +6925,14 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Isabella Siu</t>
+          <t>Yingchen Wang</t>
         </is>
       </c>
       <c r="B284" t="n">
@@ -6940,7 +6940,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Scheduled Disclosure: Turning Power into Timing Without Frequency Scaling.</t>
+          <t>IEEE_S&amp;P-PQ-Hammer: End-to-End Key Recovery Attacks on Post-Quantum Cryptography Using Rowhammer.</t>
         </is>
       </c>
       <c r="D284" t="n">
@@ -6948,14 +6948,14 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>Berkeley College; University of California, Berkeley</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Riccardo Paccagnella</t>
+          <t>Daniel Genkin</t>
         </is>
       </c>
       <c r="B285" t="n">
@@ -6963,22 +6963,22 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Scheduled Disclosure: Turning Power into Timing Without Frequency Scaling.</t>
+          <t>IEEE_S&amp;P-PQ-Hammer: End-to-End Key Recovery Attacks on Post-Quantum Cryptography Using Rowhammer.</t>
         </is>
       </c>
       <c r="D285" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Cheng Gu</t>
+          <t>Andrew Kwong</t>
         </is>
       </c>
       <c r="B286" t="n">
@@ -6986,22 +6986,22 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-I know What You Sync: Covert and Side Channel Attacks on File Systems via syncfs.</t>
+          <t>IEEE_S&amp;P-PQ-Hammer: End-to-End Key Recovery Attacks on Post-Quantum Cryptography Using Rowhammer.</t>
         </is>
       </c>
       <c r="D286" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>University of California, Riverside</t>
+          <t>University of North Carolina Health Care; University of North Carolina at Chapel Hill</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Yicheng Zhang 0004</t>
+          <t>Arkady Yerukhimovich</t>
         </is>
       </c>
       <c r="B287" t="n">
@@ -7009,22 +7009,22 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-I know What You Sync: Covert and Side Channel Attacks on File Systems via syncfs.</t>
+          <t>IEEE_S&amp;P-PQ-Hammer: End-to-End Key Recovery Attacks on Post-Quantum Cryptography Using Rowhammer.</t>
         </is>
       </c>
       <c r="D287" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>University of California, Riverside</t>
+          <t>George Washington University</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Muhammad Daniyal Pirwani Dar</t>
+          <t>Inwhan Chun</t>
         </is>
       </c>
       <c r="B288" t="n">
@@ -7032,7 +7032,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Saecred: A State-Aware, Over-the-Air Protocol Testing Approach for Discovering Parsing Bugs in SAE Handshake Implementations of COTS Wi-Fi Access Points.</t>
+          <t>IEEE_S&amp;P-Scheduled Disclosure: Turning Power into Timing Without Frequency Scaling.</t>
         </is>
       </c>
       <c r="D288" t="n">
@@ -7040,14 +7040,14 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Stony Brook University</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Aliakbar Sadeghi</t>
+          <t>Isabella Siu</t>
         </is>
       </c>
       <c r="B289" t="n">
@@ -7055,22 +7055,22 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Saecred: A State-Aware, Over-the-Air Protocol Testing Approach for Discovering Parsing Bugs in SAE Handshake Implementations of COTS Wi-Fi Access Points.</t>
+          <t>IEEE_S&amp;P-Scheduled Disclosure: Turning Power into Timing Without Frequency Scaling.</t>
         </is>
       </c>
       <c r="D289" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Stony Brook University</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Vincenzo Sorcigli</t>
+          <t>Riccardo Paccagnella</t>
         </is>
       </c>
       <c r="B290" t="n">
@@ -7078,22 +7078,22 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Saecred: A State-Aware, Over-the-Air Protocol Testing Approach for Discovering Parsing Bugs in SAE Handshake Implementations of COTS Wi-Fi Access Points.</t>
+          <t>IEEE_S&amp;P-Scheduled Disclosure: Turning Power into Timing Without Frequency Scaling.</t>
         </is>
       </c>
       <c r="D290" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Stony Brook University</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Cesare Tinelli</t>
+          <t>Cheng Gu</t>
         </is>
       </c>
       <c r="B291" t="n">
@@ -7101,22 +7101,22 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Saecred: A State-Aware, Over-the-Air Protocol Testing Approach for Discovering Parsing Bugs in SAE Handshake Implementations of COTS Wi-Fi Access Points.</t>
+          <t>IEEE_S&amp;P-I know What You Sync: Covert and Side Channel Attacks on File Systems via syncfs.</t>
         </is>
       </c>
       <c r="D291" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>University of Iowa</t>
+          <t>University of California, Riverside</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Omar Chowdhury</t>
+          <t>Yicheng Zhang 0004</t>
         </is>
       </c>
       <c r="B292" t="n">
@@ -7124,22 +7124,22 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Saecred: A State-Aware, Over-the-Air Protocol Testing Approach for Discovering Parsing Bugs in SAE Handshake Implementations of COTS Wi-Fi Access Points.</t>
+          <t>IEEE_S&amp;P-I know What You Sync: Covert and Side Channel Attacks on File Systems via syncfs.</t>
         </is>
       </c>
       <c r="D292" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Stony Brook University</t>
+          <t>University of California, Riverside</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Lina Pu</t>
+          <t>Muhammad Daniyal Pirwani Dar</t>
         </is>
       </c>
       <c r="B293" t="n">
@@ -7147,7 +7147,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Your Cable, My Antenna: Eavesdropping Serial Communication via Backscatter Signals.</t>
+          <t>IEEE_S&amp;P-Saecred: A State-Aware, Over-the-Air Protocol Testing Approach for Discovering Parsing Bugs in SAE Handshake Implementations of COTS Wi-Fi Access Points.</t>
         </is>
       </c>
       <c r="D293" t="n">
@@ -7155,14 +7155,14 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>University of Alabama</t>
+          <t>Stony Brook University</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Song Han 0002</t>
+          <t>Aliakbar Sadeghi</t>
         </is>
       </c>
       <c r="B294" t="n">
@@ -7170,7 +7170,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Your Cable, My Antenna: Eavesdropping Serial Communication via Backscatter Signals.</t>
+          <t>IEEE_S&amp;P-Saecred: A State-Aware, Over-the-Air Protocol Testing Approach for Discovering Parsing Bugs in SAE Handshake Implementations of COTS Wi-Fi Access Points.</t>
         </is>
       </c>
       <c r="D294" t="n">
@@ -7178,14 +7178,14 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>University of Connecticut</t>
+          <t>Stony Brook University</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Hadjer Benkraouda</t>
+          <t>Vincenzo Sorcigli</t>
         </is>
       </c>
       <c r="B295" t="n">
@@ -7193,22 +7193,22 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-You Can't Judge a Binary by Its Header: Data-Code Separation for Non-Standard ARM Binaries Using Pseudo Labels.</t>
+          <t>IEEE_S&amp;P-Saecred: A State-Aware, Over-the-Air Protocol Testing Approach for Discovering Parsing Bugs in SAE Handshake Implementations of COTS Wi-Fi Access Points.</t>
         </is>
       </c>
       <c r="D295" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>University of Illinois Urbana-Champaign</t>
+          <t>Stony Brook University</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Nirav Diwan</t>
+          <t>Cesare Tinelli</t>
         </is>
       </c>
       <c r="B296" t="n">
@@ -7216,22 +7216,22 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-You Can't Judge a Binary by Its Header: Data-Code Separation for Non-Standard ARM Binaries Using Pseudo Labels.</t>
+          <t>IEEE_S&amp;P-Saecred: A State-Aware, Over-the-Air Protocol Testing Approach for Discovering Parsing Bugs in SAE Handshake Implementations of COTS Wi-Fi Access Points.</t>
         </is>
       </c>
       <c r="D296" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>University of Illinois Urbana-Champaign</t>
+          <t>University of Iowa</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Gang Wang 0011</t>
+          <t>Omar Chowdhury</t>
         </is>
       </c>
       <c r="B297" t="n">
@@ -7239,22 +7239,22 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-You Can't Judge a Binary by Its Header: Data-Code Separation for Non-Standard ARM Binaries Using Pseudo Labels.</t>
+          <t>IEEE_S&amp;P-Saecred: A State-Aware, Over-the-Air Protocol Testing Approach for Discovering Parsing Bugs in SAE Handshake Implementations of COTS Wi-Fi Access Points.</t>
         </is>
       </c>
       <c r="D297" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>University of Illinois Urbana-Champaign</t>
+          <t>Stony Brook University</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Iria Giuffrida</t>
+          <t>Lina Pu</t>
         </is>
       </c>
       <c r="B298" t="n">
@@ -7262,22 +7262,22 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-"We can't Allow IoT Vendors to Pass off all Such Liability to the Consumer": Investigating the U.S. Legal Perspectives on Liability for IoT Product Security.</t>
+          <t>IEEE_S&amp;P-Your Cable, My Antenna: Eavesdropping Serial Communication via Backscatter Signals.</t>
         </is>
       </c>
       <c r="D298" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>William &amp; Mary; Williams (United States)</t>
+          <t>University of Alabama</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Daniel Shin</t>
+          <t>Song Han 0002</t>
         </is>
       </c>
       <c r="B299" t="n">
@@ -7285,22 +7285,22 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-"We can't Allow IoT Vendors to Pass off all Such Liability to the Consumer": Investigating the U.S. Legal Perspectives on Liability for IoT Product Security.</t>
+          <t>IEEE_S&amp;P-Your Cable, My Antenna: Eavesdropping Serial Communication via Backscatter Signals.</t>
         </is>
       </c>
       <c r="D299" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>William &amp; Mary; Williams (United States)</t>
+          <t>University of Connecticut</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Ella Sullivan</t>
+          <t>Hadjer Benkraouda</t>
         </is>
       </c>
       <c r="B300" t="n">
@@ -7308,22 +7308,22 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-"We can't Allow IoT Vendors to Pass off all Such Liability to the Consumer": Investigating the U.S. Legal Perspectives on Liability for IoT Product Security.</t>
+          <t>IEEE_S&amp;P-You Can't Judge a Binary by Its Header: Data-Code Separation for Non-Standard ARM Binaries Using Pseudo Labels.</t>
         </is>
       </c>
       <c r="D300" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>William &amp; Mary; Williams (United States)</t>
+          <t>University of Illinois Urbana-Champaign</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Raheem Beyah</t>
+          <t>Nirav Diwan</t>
         </is>
       </c>
       <c r="B301" t="n">
@@ -7331,22 +7331,22 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Firmrca: Towards Post-Fuzzing Analysis on ARM Embedded Firmware with Efficient Event-Based Fault Localization.</t>
+          <t>IEEE_S&amp;P-You Can't Judge a Binary by Its Header: Data-Code Separation for Non-Standard ARM Binaries Using Pseudo Labels.</t>
         </is>
       </c>
       <c r="D301" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>University of Illinois Urbana-Champaign</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Mayuri Sridhar</t>
+          <t>Gang Wang 0011</t>
         </is>
       </c>
       <c r="B302" t="n">
@@ -7354,22 +7354,22 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-PAC-Private Algorithms.</t>
+          <t>IEEE_S&amp;P-You Can't Judge a Binary by Its Header: Data-Code Separation for Non-Standard ARM Binaries Using Pseudo Labels.</t>
         </is>
       </c>
       <c r="D302" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>IIT@MIT</t>
+          <t>University of Illinois Urbana-Champaign</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Srinivas Devadas</t>
+          <t>Iria Giuffrida</t>
         </is>
       </c>
       <c r="B303" t="n">
@@ -7377,7 +7377,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-PAC-Private Algorithms.</t>
+          <t>IEEE_S&amp;P-"We can't Allow IoT Vendors to Pass off all Such Liability to the Consumer": Investigating the U.S. Legal Perspectives on Liability for IoT Product Security.</t>
         </is>
       </c>
       <c r="D303" t="n">
@@ -7385,14 +7385,14 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>IIT@MIT</t>
+          <t>William &amp; Mary; Williams (United States)</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Shlomi Hod</t>
+          <t>Daniel Shin</t>
         </is>
       </c>
       <c r="B304" t="n">
@@ -7400,22 +7400,22 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Differentially Private Release of Israel's National Registry of Live Births.</t>
+          <t>IEEE_S&amp;P-"We can't Allow IoT Vendors to Pass off all Such Liability to the Consumer": Investigating the U.S. Legal Perspectives on Liability for IoT Product Security.</t>
         </is>
       </c>
       <c r="D304" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Boston University</t>
+          <t>William &amp; Mary; Williams (United States)</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Ran Canetti</t>
+          <t>Ella Sullivan</t>
         </is>
       </c>
       <c r="B305" t="n">
@@ -7423,22 +7423,22 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Differentially Private Release of Israel's National Registry of Live Births.</t>
+          <t>IEEE_S&amp;P-"We can't Allow IoT Vendors to Pass off all Such Liability to the Consumer": Investigating the U.S. Legal Perspectives on Liability for IoT Product Security.</t>
         </is>
       </c>
       <c r="D305" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Boston University</t>
+          <t>William &amp; Mary; Williams (United States)</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Alexander Viand</t>
+          <t>Raheem Beyah</t>
         </is>
       </c>
       <c r="B306" t="n">
@@ -7446,22 +7446,22 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-DPolicy: Managing Privacy Risks Across Multiple Releases with Differential Privacy.</t>
+          <t>IEEE_S&amp;P-Firmrca: Towards Post-Fuzzing Analysis on ARM Embedded Firmware with Efficient Event-Based Fault Localization.</t>
         </is>
       </c>
       <c r="D306" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Intel (United States)</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Chen Gong 0005</t>
+          <t>Mayuri Sridhar</t>
         </is>
       </c>
       <c r="B307" t="n">
@@ -7469,22 +7469,22 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-From Easy to Hard: Building a Shortcut for Differentially Private Image Synthesis.</t>
+          <t>IEEE_S&amp;P-PAC-Private Algorithms.</t>
         </is>
       </c>
       <c r="D307" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>University of Virginia</t>
+          <t>IIT@MIT</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Xiaochen Li</t>
+          <t>Srinivas Devadas</t>
         </is>
       </c>
       <c r="B308" t="n">
@@ -7492,7 +7492,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-From Easy to Hard: Building a Shortcut for Differentially Private Image Synthesis.</t>
+          <t>IEEE_S&amp;P-PAC-Private Algorithms.</t>
         </is>
       </c>
       <c r="D308" t="n">
@@ -7500,14 +7500,14 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>University of Virginia</t>
+          <t>IIT@MIT</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Tianhao Wang 0001</t>
+          <t>Shlomi Hod</t>
         </is>
       </c>
       <c r="B309" t="n">
@@ -7515,22 +7515,22 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-From Easy to Hard: Building a Shortcut for Differentially Private Image Synthesis.</t>
+          <t>IEEE_S&amp;P-Differentially Private Release of Israel's National Registry of Live Births.</t>
         </is>
       </c>
       <c r="D309" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>University of Virginia</t>
+          <t>Boston University</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Emiliano De Cristofaro</t>
+          <t>Ran Canetti</t>
         </is>
       </c>
       <c r="B310" t="n">
@@ -7538,7 +7538,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-The Inadequacy of Similarity-Based Privacy Metrics: Privacy Attacks Against "Truly Anonymous" Synthetic Datasets.</t>
+          <t>IEEE_S&amp;P-Differentially Private Release of Israel's National Registry of Live Births.</t>
         </is>
       </c>
       <c r="D310" t="n">
@@ -7546,14 +7546,14 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>University of California, Riverside</t>
+          <t>Boston University</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Arnabjyoti Kalita</t>
+          <t>Alexander Viand</t>
         </is>
       </c>
       <c r="B311" t="n">
@@ -7561,22 +7561,22 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Ceviche: Capability-Enhanced Secure Virtualization of Caches.</t>
+          <t>IEEE_S&amp;P-DPolicy: Managing Privacy Risks Across Multiple Releases with Differential Privacy.</t>
         </is>
       </c>
       <c r="D311" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>University of Virginia</t>
+          <t>Intel (United States)</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Yilong Yang</t>
+          <t>Chen Gong 0005</t>
         </is>
       </c>
       <c r="B312" t="n">
@@ -7584,7 +7584,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Ceviche: Capability-Enhanced Secure Virtualization of Caches.</t>
+          <t>IEEE_S&amp;P-From Easy to Hard: Building a Shortcut for Differentially Private Image Synthesis.</t>
         </is>
       </c>
       <c r="D312" t="n">
@@ -7599,7 +7599,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Ashish Venkat</t>
+          <t>Xiaochen Li</t>
         </is>
       </c>
       <c r="B313" t="n">
@@ -7607,11 +7607,11 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Ceviche: Capability-Enhanced Secure Virtualization of Caches.</t>
+          <t>IEEE_S&amp;P-From Easy to Hard: Building a Shortcut for Differentially Private Image Synthesis.</t>
         </is>
       </c>
       <c r="D313" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E313" t="inlineStr">
         <is>
@@ -7622,7 +7622,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Fan Sang</t>
+          <t>Tianhao Wang 0001</t>
         </is>
       </c>
       <c r="B314" t="n">
@@ -7630,22 +7630,22 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Portal: Fast and Secure Device Access with Arm CCA for Modern Arm Mobile System-on-Chips (SoCs).</t>
+          <t>IEEE_S&amp;P-From Easy to Hard: Building a Shortcut for Differentially Private Image Synthesis.</t>
         </is>
       </c>
       <c r="D314" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>University of Virginia</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Jaehyuk Lee</t>
+          <t>Emiliano De Cristofaro</t>
         </is>
       </c>
       <c r="B315" t="n">
@@ -7653,7 +7653,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Portal: Fast and Secure Device Access with Arm CCA for Modern Arm Mobile System-on-Chips (SoCs).</t>
+          <t>IEEE_S&amp;P-The Inadequacy of Similarity-Based Privacy Metrics: Privacy Attacks Against "Truly Anonymous" Synthetic Datasets.</t>
         </is>
       </c>
       <c r="D315" t="n">
@@ -7661,14 +7661,14 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>University of California, Riverside</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Xiaokuan Zhang</t>
+          <t>Arnabjyoti Kalita</t>
         </is>
       </c>
       <c r="B316" t="n">
@@ -7676,22 +7676,22 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Portal: Fast and Secure Device Access with Arm CCA for Modern Arm Mobile System-on-Chips (SoCs).</t>
+          <t>IEEE_S&amp;P-Ceviche: Capability-Enhanced Secure Virtualization of Caches.</t>
         </is>
       </c>
       <c r="D316" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>George Mason University</t>
+          <t>University of Virginia</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Taesoo Kim</t>
+          <t>Yilong Yang</t>
         </is>
       </c>
       <c r="B317" t="n">
@@ -7699,22 +7699,22 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Portal: Fast and Secure Device Access with Arm CCA for Modern Arm Mobile System-on-Chips (SoCs).</t>
+          <t>IEEE_S&amp;P-Ceviche: Capability-Enhanced Secure Virtualization of Caches.</t>
         </is>
       </c>
       <c r="D317" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>University of Virginia</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Shidong Pan</t>
+          <t>Ashish Venkat</t>
         </is>
       </c>
       <c r="B318" t="n">
@@ -7722,22 +7722,22 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-A Big Step Forward? A User-Centric Examination of iOS App Privacy Report and Enhancements.</t>
+          <t>IEEE_S&amp;P-Ceviche: Capability-Enhanced Secure Virtualization of Caches.</t>
         </is>
       </c>
       <c r="D318" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>Columbia University</t>
+          <t>University of Virginia</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Mona Wang</t>
+          <t>Fan Sang</t>
         </is>
       </c>
       <c r="B319" t="n">
@@ -7745,7 +7745,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-WireWatch: Measuring the Security of Proprietary Network Encryption in the Global Android Ecosystem.</t>
+          <t>IEEE_S&amp;P-Portal: Fast and Secure Device Access with Arm CCA for Modern Arm Mobile System-on-Chips (SoCs).</t>
         </is>
       </c>
       <c r="D319" t="n">
@@ -7753,14 +7753,14 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>Princeton University</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Prateek Mittal</t>
+          <t>Jaehyuk Lee</t>
         </is>
       </c>
       <c r="B320" t="n">
@@ -7768,22 +7768,22 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-WireWatch: Measuring the Security of Proprietary Network Encryption in the Global Android Ecosystem.</t>
+          <t>IEEE_S&amp;P-Portal: Fast and Secure Device Access with Arm CCA for Modern Arm Mobile System-on-Chips (SoCs).</t>
         </is>
       </c>
       <c r="D320" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>Princeton University</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Zhiqiang Lin 0001</t>
+          <t>Xiaokuan Zhang</t>
         </is>
       </c>
       <c r="B321" t="n">
@@ -7791,7 +7791,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Code Speaks Louder: Exploring Security and Privacy Relevant Regional Variations in Mobile Applications.</t>
+          <t>IEEE_S&amp;P-Portal: Fast and Secure Device Access with Arm CCA for Modern Arm Mobile System-on-Chips (SoCs).</t>
         </is>
       </c>
       <c r="D321" t="n">
@@ -7799,14 +7799,14 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>The Ohio State University</t>
+          <t>George Mason University</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Aafaq Sabir</t>
+          <t>Taesoo Kim</t>
         </is>
       </c>
       <c r="B322" t="n">
@@ -7814,22 +7814,22 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Analyzing Ad Prevalence, Characteristics, and Compliance in Alexa Skills.</t>
+          <t>IEEE_S&amp;P-Portal: Fast and Secure Device Access with Arm CCA for Modern Arm Mobile System-on-Chips (SoCs).</t>
         </is>
       </c>
       <c r="D322" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>North Carolina State University</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Dilawer Ahmed</t>
+          <t>Shidong Pan</t>
         </is>
       </c>
       <c r="B323" t="n">
@@ -7837,7 +7837,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Analyzing Ad Prevalence, Characteristics, and Compliance in Alexa Skills.</t>
+          <t>IEEE_S&amp;P-A Big Step Forward? A User-Centric Examination of iOS App Privacy Report and Enhancements.</t>
         </is>
       </c>
       <c r="D323" t="n">
@@ -7845,14 +7845,14 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>North Carolina State University</t>
+          <t>Columbia University</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Anupam Das 0001</t>
+          <t>Mona Wang</t>
         </is>
       </c>
       <c r="B324" t="n">
@@ -7860,22 +7860,22 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Analyzing Ad Prevalence, Characteristics, and Compliance in Alexa Skills.</t>
+          <t>IEEE_S&amp;P-WireWatch: Measuring the Security of Proprietary Network Encryption in the Global Android Ecosystem.</t>
         </is>
       </c>
       <c r="D324" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>North Carolina State University</t>
+          <t>Princeton University</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Ahmed Tanvir Mahdad</t>
+          <t>Prateek Mittal</t>
         </is>
       </c>
       <c r="B325" t="n">
@@ -7883,22 +7883,22 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-BPSniff: Continuously Surveilling Private Blood Pressure Information in the Metaverse via Unrestricted Inbuilt Motion Sensors.</t>
+          <t>IEEE_S&amp;P-WireWatch: Measuring the Security of Proprietary Network Encryption in the Global Android Ecosystem.</t>
         </is>
       </c>
       <c r="D325" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Texas A&amp;M University</t>
+          <t>Princeton University</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Yingying Chen 0001</t>
+          <t>Zhiqiang Lin 0001</t>
         </is>
       </c>
       <c r="B326" t="n">
@@ -7906,22 +7906,22 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-BPSniff: Continuously Surveilling Private Blood Pressure Information in the Metaverse via Unrestricted Inbuilt Motion Sensors.</t>
+          <t>IEEE_S&amp;P-Code Speaks Louder: Exploring Security and Privacy Relevant Regional Variations in Mobile Applications.</t>
         </is>
       </c>
       <c r="D326" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>Rutgers, The State University of New Jersey</t>
+          <t>The Ohio State University</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Nitesh Saxena</t>
+          <t>Aafaq Sabir</t>
         </is>
       </c>
       <c r="B327" t="n">
@@ -7929,22 +7929,22 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-BPSniff: Continuously Surveilling Private Blood Pressure Information in the Metaverse via Unrestricted Inbuilt Motion Sensors.</t>
+          <t>IEEE_S&amp;P-Analyzing Ad Prevalence, Characteristics, and Compliance in Alexa Skills.</t>
         </is>
       </c>
       <c r="D327" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Texas A&amp;M University</t>
+          <t>North Carolina State University</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Jonathan Protzenko</t>
+          <t>Dilawer Ahmed</t>
         </is>
       </c>
       <c r="B328" t="n">
@@ -7952,22 +7952,22 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-TreeKEM: A Modular Machine-Checked Symbolic Security Analysis of Group Key Agreement in Messaging Layer Security.</t>
+          <t>IEEE_S&amp;P-Analyzing Ad Prevalence, Characteristics, and Compliance in Alexa Skills.</t>
         </is>
       </c>
       <c r="D328" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Microsoft (Germany)</t>
+          <t>North Carolina State University</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Liron David</t>
+          <t>Anupam Das 0001</t>
         </is>
       </c>
       <c r="B329" t="n">
@@ -7975,22 +7975,22 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Extended Diffie-Hellman Encryption for Secure and Efficient Real-Time Beacon Notifications.</t>
+          <t>IEEE_S&amp;P-Analyzing Ad Prevalence, Characteristics, and Compliance in Alexa Skills.</t>
         </is>
       </c>
       <c r="D329" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>Google (United States)</t>
+          <t>North Carolina State University</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Avinatan Hassidim</t>
+          <t>Ahmed Tanvir Mahdad</t>
         </is>
       </c>
       <c r="B330" t="n">
@@ -7998,22 +7998,22 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Extended Diffie-Hellman Encryption for Secure and Efficient Real-Time Beacon Notifications.</t>
+          <t>IEEE_S&amp;P-BPSniff: Continuously Surveilling Private Blood Pressure Information in the Metaverse via Unrestricted Inbuilt Motion Sensors.</t>
         </is>
       </c>
       <c r="D330" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>Google (United States); Bar-Ilan University</t>
+          <t>Texas A&amp;M University</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>David Lazarov</t>
+          <t>Yingying Chen 0001</t>
         </is>
       </c>
       <c r="B331" t="n">
@@ -8021,22 +8021,22 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Extended Diffie-Hellman Encryption for Secure and Efficient Real-Time Beacon Notifications.</t>
+          <t>IEEE_S&amp;P-BPSniff: Continuously Surveilling Private Blood Pressure Information in the Metaverse via Unrestricted Inbuilt Motion Sensors.</t>
         </is>
       </c>
       <c r="D331" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>Google (United States)</t>
+          <t>Rutgers, The State University of New Jersey</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Moti Yung</t>
+          <t>Nitesh Saxena</t>
         </is>
       </c>
       <c r="B332" t="n">
@@ -8044,7 +8044,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Extended Diffie-Hellman Encryption for Secure and Efficient Real-Time Beacon Notifications.</t>
+          <t>IEEE_S&amp;P-BPSniff: Continuously Surveilling Private Blood Pressure Information in the Metaverse via Unrestricted Inbuilt Motion Sensors.</t>
         </is>
       </c>
       <c r="D332" t="n">
@@ -8052,14 +8052,14 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>Google (United States)</t>
+          <t>Texas A&amp;M University</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Darya Kaviani</t>
+          <t>Jonathan Protzenko</t>
         </is>
       </c>
       <c r="B333" t="n">
@@ -8067,22 +8067,22 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Myco: Unlocking Polylogarithmic Accesses in Metadata-Private Messaging.</t>
+          <t>IEEE_S&amp;P-TreeKEM: A Modular Machine-Checked Symbolic Security Analysis of Group Key Agreement in Messaging Layer Security.</t>
         </is>
       </c>
       <c r="D333" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>Berkeley College; University of California, Berkeley</t>
+          <t>Microsoft (Germany)</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Deevashwer Rathee</t>
+          <t>Liron David</t>
         </is>
       </c>
       <c r="B334" t="n">
@@ -8090,22 +8090,22 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Myco: Unlocking Polylogarithmic Accesses in Metadata-Private Messaging.</t>
+          <t>IEEE_S&amp;P-Extended Diffie-Hellman Encryption for Secure and Efficient Real-Time Beacon Notifications.</t>
         </is>
       </c>
       <c r="D334" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>Berkeley College; University of California, Berkeley</t>
+          <t>Google (United States)</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Raluca Ada Popa</t>
+          <t>Avinatan Hassidim</t>
         </is>
       </c>
       <c r="B335" t="n">
@@ -8113,22 +8113,22 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Myco: Unlocking Polylogarithmic Accesses in Metadata-Private Messaging.</t>
+          <t>IEEE_S&amp;P-Extended Diffie-Hellman Encryption for Secure and Efficient Real-Time Beacon Notifications.</t>
         </is>
       </c>
       <c r="D335" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>University of California, Berkeley; Berkeley College</t>
+          <t>Google (United States); Bar-Ilan University</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Quang Cao</t>
+          <t>David Lazarov</t>
         </is>
       </c>
       <c r="B336" t="n">
@@ -8136,22 +8136,22 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-TreePIR: Efficient Private Retrieval of Merkle Proofs via Tree Colorings with Fast Indexing and Zero Storage Overhead.</t>
+          <t>IEEE_S&amp;P-Extended Diffie-Hellman Encryption for Secure and Efficient Real-Time Beacon Notifications.</t>
         </is>
       </c>
       <c r="D336" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>MIT University; RMIT University</t>
+          <t>Google (United States)</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Son Hoang Dau</t>
+          <t>Moti Yung</t>
         </is>
       </c>
       <c r="B337" t="n">
@@ -8159,22 +8159,22 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-TreePIR: Efficient Private Retrieval of Merkle Proofs via Tree Colorings with Fast Indexing and Zero Storage Overhead.</t>
+          <t>IEEE_S&amp;P-Extended Diffie-Hellman Encryption for Secure and Efficient Real-Time Beacon Notifications.</t>
         </is>
       </c>
       <c r="D337" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>RMIT University; MIT University</t>
+          <t>Google (United States)</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Rinaldo Gagiano</t>
+          <t>Darya Kaviani</t>
         </is>
       </c>
       <c r="B338" t="n">
@@ -8182,22 +8182,22 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-TreePIR: Efficient Private Retrieval of Merkle Proofs via Tree Colorings with Fast Indexing and Zero Storage Overhead.</t>
+          <t>IEEE_S&amp;P-Myco: Unlocking Polylogarithmic Accesses in Metadata-Private Messaging.</t>
         </is>
       </c>
       <c r="D338" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>RMIT University; MIT University</t>
+          <t>Berkeley College; University of California, Berkeley</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Xun Yi</t>
+          <t>Deevashwer Rathee</t>
         </is>
       </c>
       <c r="B339" t="n">
@@ -8205,22 +8205,22 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-TreePIR: Efficient Private Retrieval of Merkle Proofs via Tree Colorings with Fast Indexing and Zero Storage Overhead.</t>
+          <t>IEEE_S&amp;P-Myco: Unlocking Polylogarithmic Accesses in Metadata-Private Messaging.</t>
         </is>
       </c>
       <c r="D339" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>RMIT University; MIT University</t>
+          <t>Berkeley College; University of California, Berkeley</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Quang-Hung Luu</t>
+          <t>Raluca Ada Popa</t>
         </is>
       </c>
       <c r="B340" t="n">
@@ -8228,22 +8228,22 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-TreePIR: Efficient Private Retrieval of Merkle Proofs via Tree Colorings with Fast Indexing and Zero Storage Overhead.</t>
+          <t>IEEE_S&amp;P-Myco: Unlocking Polylogarithmic Accesses in Metadata-Private Messaging.</t>
         </is>
       </c>
       <c r="D340" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>MIT University; RMIT University</t>
+          <t>University of California, Berkeley; Berkeley College</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Collins W. Munyendo</t>
+          <t>Quang Cao</t>
         </is>
       </c>
       <c r="B341" t="n">
@@ -8251,7 +8251,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-"You Have to Ignore the Dangers": User Perceptions of the Security and Privacy Benefits of WhatsApp Mods.</t>
+          <t>IEEE_S&amp;P-TreePIR: Efficient Private Retrieval of Merkle Proofs via Tree Colorings with Fast Indexing and Zero Storage Overhead.</t>
         </is>
       </c>
       <c r="D341" t="n">
@@ -8259,14 +8259,14 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>George Washington University</t>
+          <t>MIT University; RMIT University</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Kentrell Owens</t>
+          <t>Son Hoang Dau</t>
         </is>
       </c>
       <c r="B342" t="n">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-"You Have to Ignore the Dangers": User Perceptions of the Security and Privacy Benefits of WhatsApp Mods.</t>
+          <t>IEEE_S&amp;P-TreePIR: Efficient Private Retrieval of Merkle Proofs via Tree Colorings with Fast Indexing and Zero Storage Overhead.</t>
         </is>
       </c>
       <c r="D342" t="n">
@@ -8282,14 +8282,14 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>University of Washington</t>
+          <t>RMIT University; MIT University</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Adam J. Aviv</t>
+          <t>Rinaldo Gagiano</t>
         </is>
       </c>
       <c r="B343" t="n">
@@ -8297,22 +8297,22 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-"You Have to Ignore the Dangers": User Perceptions of the Security and Privacy Benefits of WhatsApp Mods.</t>
+          <t>IEEE_S&amp;P-TreePIR: Efficient Private Retrieval of Merkle Proofs via Tree Colorings with Fast Indexing and Zero Storage Overhead.</t>
         </is>
       </c>
       <c r="D343" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>George Washington University</t>
+          <t>RMIT University; MIT University</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>Tadayoshi Kohno</t>
+          <t>Xun Yi</t>
         </is>
       </c>
       <c r="B344" t="n">
@@ -8320,22 +8320,22 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-"You Have to Ignore the Dangers": User Perceptions of the Security and Privacy Benefits of WhatsApp Mods.</t>
+          <t>IEEE_S&amp;P-TreePIR: Efficient Private Retrieval of Merkle Proofs via Tree Colorings with Fast Indexing and Zero Storage Overhead.</t>
         </is>
       </c>
       <c r="D344" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>University of Washington</t>
+          <t>RMIT University; MIT University</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Franziska Roesner</t>
+          <t>Quang-Hung Luu</t>
         </is>
       </c>
       <c r="B345" t="n">
@@ -8343,7 +8343,7 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-"You Have to Ignore the Dangers": User Perceptions of the Security and Privacy Benefits of WhatsApp Mods.</t>
+          <t>IEEE_S&amp;P-TreePIR: Efficient Private Retrieval of Merkle Proofs via Tree Colorings with Fast Indexing and Zero Storage Overhead.</t>
         </is>
       </c>
       <c r="D345" t="n">
@@ -8351,14 +8351,14 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>University of Washington</t>
+          <t>MIT University; RMIT University</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Jung-Woo Chang</t>
+          <t>Collins W. Munyendo</t>
         </is>
       </c>
       <c r="B346" t="n">
@@ -8366,7 +8366,7 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-EveGuard: Defeating Vibration-based Side-Channel Eavesdropping with Audio Adversarial Perturbations.</t>
+          <t>IEEE_S&amp;P-"You Have to Ignore the Dangers": User Perceptions of the Security and Privacy Benefits of WhatsApp Mods.</t>
         </is>
       </c>
       <c r="D346" t="n">
@@ -8374,14 +8374,14 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>University of California, San Diego</t>
+          <t>George Washington University</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Ke Sun 0012</t>
+          <t>Kentrell Owens</t>
         </is>
       </c>
       <c r="B347" t="n">
@@ -8389,7 +8389,7 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-EveGuard: Defeating Vibration-based Side-Channel Eavesdropping with Audio Adversarial Perturbations.</t>
+          <t>IEEE_S&amp;P-"You Have to Ignore the Dangers": User Perceptions of the Security and Privacy Benefits of WhatsApp Mods.</t>
         </is>
       </c>
       <c r="D347" t="n">
@@ -8397,14 +8397,14 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>University of California, San Diego</t>
+          <t>University of Washington</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>David Xia</t>
+          <t>Adam J. Aviv</t>
         </is>
       </c>
       <c r="B348" t="n">
@@ -8412,22 +8412,22 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-EveGuard: Defeating Vibration-based Side-Channel Eavesdropping with Audio Adversarial Perturbations.</t>
+          <t>IEEE_S&amp;P-"You Have to Ignore the Dangers": User Perceptions of the Security and Privacy Benefits of WhatsApp Mods.</t>
         </is>
       </c>
       <c r="D348" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>University of Illinois Urbana-Champaign</t>
+          <t>George Washington University</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Xinyu Zhang 0003</t>
+          <t>Tadayoshi Kohno</t>
         </is>
       </c>
       <c r="B349" t="n">
@@ -8435,22 +8435,22 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-EveGuard: Defeating Vibration-based Side-Channel Eavesdropping with Audio Adversarial Perturbations.</t>
+          <t>IEEE_S&amp;P-"You Have to Ignore the Dangers": User Perceptions of the Security and Privacy Benefits of WhatsApp Mods.</t>
         </is>
       </c>
       <c r="D349" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>University of California, San Diego</t>
+          <t>University of Washington</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Farinaz Koushanfar</t>
+          <t>Franziska Roesner</t>
         </is>
       </c>
       <c r="B350" t="n">
@@ -8458,22 +8458,22 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-EveGuard: Defeating Vibration-based Side-Channel Eavesdropping with Audio Adversarial Perturbations.</t>
+          <t>IEEE_S&amp;P-"You Have to Ignore the Dangers": User Perceptions of the Security and Privacy Benefits of WhatsApp Mods.</t>
         </is>
       </c>
       <c r="D350" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>University of California, San Diego</t>
+          <t>University of Washington</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Zhambyl Shaikhanov</t>
+          <t>Jung-Woo Chang</t>
         </is>
       </c>
       <c r="B351" t="n">
@@ -8481,7 +8481,7 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Spoofing Eavesdroppers with Audio Misinformation.</t>
+          <t>IEEE_S&amp;P-EveGuard: Defeating Vibration-based Side-Channel Eavesdropping with Audio Adversarial Perturbations.</t>
         </is>
       </c>
       <c r="D351" t="n">
@@ -8489,14 +8489,14 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>University of Maryland, College Park</t>
+          <t>University of California, San Diego</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Mahmoud Al-Madi</t>
+          <t>Ke Sun 0012</t>
         </is>
       </c>
       <c r="B352" t="n">
@@ -8504,7 +8504,7 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Spoofing Eavesdroppers with Audio Misinformation.</t>
+          <t>IEEE_S&amp;P-EveGuard: Defeating Vibration-based Side-Channel Eavesdropping with Audio Adversarial Perturbations.</t>
         </is>
       </c>
       <c r="D352" t="n">
@@ -8512,14 +8512,14 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>Rice University</t>
+          <t>University of California, San Diego</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Chun-Chieh Chang</t>
+          <t>David Xia</t>
         </is>
       </c>
       <c r="B353" t="n">
@@ -8527,22 +8527,22 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Spoofing Eavesdroppers with Audio Misinformation.</t>
+          <t>IEEE_S&amp;P-EveGuard: Defeating Vibration-based Side-Channel Eavesdropping with Audio Adversarial Perturbations.</t>
         </is>
       </c>
       <c r="D353" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>Los Alamos National Laboratory</t>
+          <t>University of Illinois Urbana-Champaign</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>Sadhvikas Addamane</t>
+          <t>Xinyu Zhang 0003</t>
         </is>
       </c>
       <c r="B354" t="n">
@@ -8550,22 +8550,22 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Spoofing Eavesdroppers with Audio Misinformation.</t>
+          <t>IEEE_S&amp;P-EveGuard: Defeating Vibration-based Side-Channel Eavesdropping with Audio Adversarial Perturbations.</t>
         </is>
       </c>
       <c r="D354" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>Sandia National Laboratories</t>
+          <t>University of California, San Diego</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Daniel M. Mittleman</t>
+          <t>Farinaz Koushanfar</t>
         </is>
       </c>
       <c r="B355" t="n">
@@ -8573,22 +8573,22 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Spoofing Eavesdroppers with Audio Misinformation.</t>
+          <t>IEEE_S&amp;P-EveGuard: Defeating Vibration-based Side-Channel Eavesdropping with Audio Adversarial Perturbations.</t>
         </is>
       </c>
       <c r="D355" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>John Brown University</t>
+          <t>University of California, San Diego</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Edward W. Knightly</t>
+          <t>Zhambyl Shaikhanov</t>
         </is>
       </c>
       <c r="B356" t="n">
@@ -8600,18 +8600,18 @@
         </is>
       </c>
       <c r="D356" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>Rice University</t>
+          <t>University of Maryland, College Park</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Shengzhi Zhang</t>
+          <t>Mahmoud Al-Madi</t>
         </is>
       </c>
       <c r="B357" t="n">
@@ -8619,22 +8619,22 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-EvilHarmony: Stealthy Adversarial Attacks Against Black-Box Speech Recognition Systems.</t>
+          <t>IEEE_S&amp;P-Spoofing Eavesdroppers with Audio Misinformation.</t>
         </is>
       </c>
       <c r="D357" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>Boston University; Metropolitan College of New York</t>
+          <t>Rice University</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>Dun Liu</t>
+          <t>Chun-Chieh Chang</t>
         </is>
       </c>
       <c r="B358" t="n">
@@ -8642,22 +8642,22 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-EvilHarmony: Stealthy Adversarial Attacks Against Black-Box Speech Recognition Systems.</t>
+          <t>IEEE_S&amp;P-Spoofing Eavesdroppers with Audio Misinformation.</t>
         </is>
       </c>
       <c r="D358" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>Boston University; Metropolitan College of New York</t>
+          <t>Los Alamos National Laboratory</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>Ruoyu Song 0001</t>
+          <t>Sadhvikas Addamane</t>
         </is>
       </c>
       <c r="B359" t="n">
@@ -8665,22 +8665,22 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Investigating Physical Latency Attacks Against Camera-Based Perception.</t>
+          <t>IEEE_S&amp;P-Spoofing Eavesdroppers with Audio Misinformation.</t>
         </is>
       </c>
       <c r="D359" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>Purdue University West Lafayette</t>
+          <t>Sandia National Laboratories</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Chenyi Wang 0005</t>
+          <t>Daniel M. Mittleman</t>
         </is>
       </c>
       <c r="B360" t="n">
@@ -8688,22 +8688,22 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Investigating Physical Latency Attacks Against Camera-Based Perception.</t>
+          <t>IEEE_S&amp;P-Spoofing Eavesdroppers with Audio Misinformation.</t>
         </is>
       </c>
       <c r="D360" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>University of Arizona</t>
+          <t>John Brown University</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Yuxia Zhan</t>
+          <t>Edward W. Knightly</t>
         </is>
       </c>
       <c r="B361" t="n">
@@ -8711,22 +8711,22 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Investigating Physical Latency Attacks Against Camera-Based Perception.</t>
+          <t>IEEE_S&amp;P-Spoofing Eavesdroppers with Audio Misinformation.</t>
         </is>
       </c>
       <c r="D361" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>New York University</t>
+          <t>Rice University</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Ming Li 0003</t>
+          <t>Shengzhi Zhang</t>
         </is>
       </c>
       <c r="B362" t="n">
@@ -8734,22 +8734,22 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Investigating Physical Latency Attacks Against Camera-Based Perception.</t>
+          <t>IEEE_S&amp;P-EvilHarmony: Stealthy Adversarial Attacks Against Black-Box Speech Recognition Systems.</t>
         </is>
       </c>
       <c r="D362" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>University of Arizona</t>
+          <t>Boston University; Metropolitan College of New York</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Jonathan Petit</t>
+          <t>Dun Liu</t>
         </is>
       </c>
       <c r="B363" t="n">
@@ -8757,22 +8757,22 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Investigating Physical Latency Attacks Against Camera-Based Perception.</t>
+          <t>IEEE_S&amp;P-EvilHarmony: Stealthy Adversarial Attacks Against Black-Box Speech Recognition Systems.</t>
         </is>
       </c>
       <c r="D363" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>Qualcomm (United Kingdom)</t>
+          <t>Boston University; Metropolitan College of New York</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Z. Berkay Celik</t>
+          <t>Ruoyu Song 0001</t>
         </is>
       </c>
       <c r="B364" t="n">
@@ -8784,7 +8784,7 @@
         </is>
       </c>
       <c r="D364" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E364" t="inlineStr">
         <is>
@@ -8795,7 +8795,7 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>Trisha Datta</t>
+          <t>Chenyi Wang 0005</t>
         </is>
       </c>
       <c r="B365" t="n">
@@ -8803,22 +8803,22 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-VerITAS: Verifying Image Transformations at Scale.</t>
+          <t>IEEE_S&amp;P-Investigating Physical Latency Attacks Against Camera-Based Perception.</t>
         </is>
       </c>
       <c r="D365" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>Stanford University</t>
+          <t>University of Arizona</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Binyi Chen</t>
+          <t>Yuxia Zhan</t>
         </is>
       </c>
       <c r="B366" t="n">
@@ -8826,22 +8826,22 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-VerITAS: Verifying Image Transformations at Scale.</t>
+          <t>IEEE_S&amp;P-Investigating Physical Latency Attacks Against Camera-Based Perception.</t>
         </is>
       </c>
       <c r="D366" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>Stanford University</t>
+          <t>New York University</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>Dan Boneh</t>
+          <t>Ming Li 0003</t>
         </is>
       </c>
       <c r="B367" t="n">
@@ -8849,22 +8849,22 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-VerITAS: Verifying Image Transformations at Scale.</t>
+          <t>IEEE_S&amp;P-Investigating Physical Latency Attacks Against Camera-Based Perception.</t>
         </is>
       </c>
       <c r="D367" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>Stanford University</t>
+          <t>University of Arizona</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>Long Huang</t>
+          <t>Jonathan Petit</t>
         </is>
       </c>
       <c r="B368" t="n">
@@ -8872,36 +8872,151 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Sniffing Location Privacy of Video Conference Users Using Free Audio Channels.</t>
+          <t>IEEE_S&amp;P-Investigating Physical Latency Attacks Against Camera-Based Perception.</t>
         </is>
       </c>
       <c r="D368" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>Southern Methodist University</t>
+          <t>Qualcomm (United Kingdom)</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
+          <t>Z. Berkay Celik</t>
+        </is>
+      </c>
+      <c r="B369" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>IEEE_S&amp;P-Investigating Physical Latency Attacks Against Camera-Based Perception.</t>
+        </is>
+      </c>
+      <c r="D369" t="n">
+        <v>9</v>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>Purdue University West Lafayette</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>Trisha Datta</t>
+        </is>
+      </c>
+      <c r="B370" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>IEEE_S&amp;P-VerITAS: Verifying Image Transformations at Scale.</t>
+        </is>
+      </c>
+      <c r="D370" t="n">
+        <v>0</v>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>Stanford University</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>Binyi Chen</t>
+        </is>
+      </c>
+      <c r="B371" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>IEEE_S&amp;P-VerITAS: Verifying Image Transformations at Scale.</t>
+        </is>
+      </c>
+      <c r="D371" t="n">
+        <v>1</v>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>Stanford University</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>Dan Boneh</t>
+        </is>
+      </c>
+      <c r="B372" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>IEEE_S&amp;P-VerITAS: Verifying Image Transformations at Scale.</t>
+        </is>
+      </c>
+      <c r="D372" t="n">
+        <v>2</v>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>Stanford University</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>Long Huang</t>
+        </is>
+      </c>
+      <c r="B373" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>IEEE_S&amp;P-Sniffing Location Privacy of Video Conference Users Using Free Audio Channels.</t>
+        </is>
+      </c>
+      <c r="D373" t="n">
+        <v>0</v>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>Southern Methodist University</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
           <t>Chen Wang 0009</t>
         </is>
       </c>
-      <c r="B369" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C369" t="inlineStr">
+      <c r="B374" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C374" t="inlineStr">
         <is>
           <t>IEEE_S&amp;P-Sniffing Location Privacy of Video Conference Users Using Free Audio Channels.</t>
         </is>
       </c>
-      <c r="D369" t="n">
+      <c r="D374" t="n">
         <v>1</v>
       </c>
-      <c r="E369" t="inlineStr">
+      <c r="E374" t="inlineStr">
         <is>
           <t>Southern Methodist University</t>
         </is>

--- a/Security-data/data/output/ieee_sp_2025_us_institutions.xlsx
+++ b/Security-data/data/output/ieee_sp_2025_us_institutions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E374"/>
+  <dimension ref="A1:E402"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1481,7 +1481,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Mutahar Ali</t>
+          <t>Kristin E. Lauter</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -1489,22 +1489,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Understanding Users' Security and Privacy Concerns and Attitudes Towards Conversational AI Platforms.</t>
+          <t>IEEE_S&amp;P-Benchmarking Attacks on Learning with Errors.</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>University of California, Irvine</t>
+          <t>Meta AI, USA</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Arjun Arunasalam</t>
+          <t>Mutahar Ali</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -1516,18 +1516,18 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Purdue University</t>
+          <t>University of California, Irvine</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Habiba Farrukh</t>
+          <t>Arjun Arunasalam</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -1539,18 +1539,18 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>University of California, Irvine</t>
+          <t>Purdue University</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Ning Yu 0006</t>
+          <t>Habiba Farrukh</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Fuzz-Testing Meets LLM-Based Agents: An Automated and Efficient Framework for Jailbreaking Text-to-Image Generation Models.</t>
+          <t>IEEE_S&amp;P-Understanding Users' Security and Privacy Concerns and Attitudes Towards Conversational AI Platforms.</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -1566,14 +1566,14 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Netflix (United States)</t>
+          <t>University of California, Irvine</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Ashish Hooda</t>
+          <t>Ning Yu 0006</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Fun-tuning: Characterizing the Vulnerability of Proprietary LLMs to Optimization-Based Prompt Injection Attacks via the Fine-Tuning Interface.</t>
+          <t>IEEE_S&amp;P-Fuzz-Testing Meets LLM-Based Agents: An Automated and Efficient Framework for Jailbreaking Text-to-Image Generation Models.</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -1589,14 +1589,14 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>University of Wisconsin–Madison</t>
+          <t>Netflix (United States)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Syed Irfan Ali Meerza</t>
+          <t>Ashish Hooda</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -1604,22 +1604,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Harmonycloak: Making Music Unlearnable for Generative AI.</t>
+          <t>IEEE_S&amp;P-Fun-tuning: Characterizing the Vulnerability of Proprietary LLMs to Optimization-Based Prompt Injection Attacks via the Fine-Tuning Interface.</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>University of Tennessee at Knoxville</t>
+          <t>University of Wisconsin–Madison</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Jian Liu 0001</t>
+          <t>Syed Irfan Ali Meerza</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Jessy Ayala</t>
+          <t>Jian Liu 0001</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -1650,22 +1650,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-A Deep Dive into How Open-Source Project Maintainers Review and Resolve Bug Bounty Reports.</t>
+          <t>IEEE_S&amp;P-Harmonycloak: Making Music Unlearnable for Generative AI.</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>University of California, Irvine</t>
+          <t>University of Tennessee at Knoxville</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Steven Ngo</t>
+          <t>Jessy Ayala</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -1677,7 +1677,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Joshua Garcia</t>
+          <t>Steven Ngo</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -1700,7 +1700,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Yue Zhang 0025</t>
+          <t>Joshua Garcia</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -1719,22 +1719,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Make a Feint to the East While Attacking in the West: Blinding LLM-Based Code Auditors with Flashboom Attacks.</t>
+          <t>IEEE_S&amp;P-A Deep Dive into How Open-Source Project Maintainers Review and Resolve Bug Bounty Reports.</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Drexel University</t>
+          <t>University of California, Irvine</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Kaidi Xu</t>
+          <t>Yue Zhang 0025</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -1746,7 +1746,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sourav Das 0001</t>
+          <t>Kaidi Xu</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -1765,22 +1765,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Verifiable Secret Sharing Simplified.</t>
+          <t>IEEE_S&amp;P-Make a Feint to the East While Attacking in the West: Blinding LLM-Based Code Auditors with Flashboom Attacks.</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>University of Illinois Urbana-Champaign</t>
+          <t>Drexel University</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Ling Ren 0001</t>
+          <t>Sourav Das 0001</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -1792,7 +1792,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Munshi Rejwan Ala Muid</t>
+          <t>Ling Ren 0001</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -1811,22 +1811,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-AccuRevoke: Enhancing Certificate Revocation with Distributed Cryptographic Accumulators.</t>
+          <t>IEEE_S&amp;P-Verifiable Secret Sharing Simplified.</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Virginia Tech</t>
+          <t>University of Illinois Urbana-Champaign</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Taejoong Chung</t>
+          <t>Munshi Rejwan Ala Muid</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -1838,7 +1838,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Thang Hoang</t>
+          <t>Taejoong Chung</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Doowon Kim</t>
+          <t>Thang Hoang</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Open Sesame! On the Security and Memorability of Verbal Passwords.</t>
+          <t>IEEE_S&amp;P-AccuRevoke: Enhancing Certificate Revocation with Distributed Cryptographic Accumulators.</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -1888,14 +1888,14 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>University of Tennessee at Knoxville</t>
+          <t>Virginia Tech</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Lei Yu</t>
+          <t>Doowon Kim</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -1903,22 +1903,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-CMASan: Custom Memory Allocator-aware Address Sanitizer.</t>
+          <t>IEEE_S&amp;P-Open Sesame! On the Security and Memorability of Verbal Passwords.</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Rensselaer Polytechnic Institute</t>
+          <t>University of Tennessee at Knoxville</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Yonghwi Kwon 0001</t>
+          <t>Lei Yu</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -1930,18 +1930,18 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>University of Maryland, College Park</t>
+          <t>Rensselaer Polytechnic Institute</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Md Sakib Anwar</t>
+          <t>Yonghwi Kwon 0001</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -1949,22 +1949,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-GoSonar: Detecting Logical Vulnerabilities in Memory Safe Language Using Inductive Constraint Reasoning.</t>
+          <t>IEEE_S&amp;P-CMASan: Custom Memory Allocator-aware Address Sanitizer.</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>The Ohio State University</t>
+          <t>University of Maryland, College Park</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Carter Yagemann</t>
+          <t>Md Sakib Anwar</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -1976,7 +1976,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Zhiqiang Lin 0001</t>
+          <t>Carter Yagemann</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -1999,7 +1999,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Zhiyun Qian</t>
+          <t>Zhiqiang Lin 0001</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-SoK: Challenges and Paths Toward Memory Safety for eBPF.</t>
+          <t>IEEE_S&amp;P-GoSonar: Detecting Logical Vulnerabilities in Memory Safe Language Using Inductive Constraint Reasoning.</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2026,14 +2026,14 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>University of California, Riverside</t>
+          <t>The Ohio State University</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Trent Jaeger</t>
+          <t>Zhiyun Qian</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -2045,7 +2045,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Alexander J. Gaidis</t>
+          <t>Trent Jaeger</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -2064,22 +2064,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-IUBIK: Isolating User Bytes in Commodity Operating System Kernels via Memory Tagging Extensions.</t>
+          <t>IEEE_S&amp;P-SoK: Challenges and Paths Toward Memory Safety for eBPF.</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>John Brown University</t>
+          <t>University of California, Riverside</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Vasileios P. Kemerlis</t>
+          <t>Alexander J. Gaidis</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -2091,7 +2091,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Penghui Li 0001</t>
+          <t>Vasileios P. Kemerlis</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Predator: Directed Web Application Fuzzing for Efficient Vulnerability Validation.</t>
+          <t>IEEE_S&amp;P-IUBIK: Isolating User Bytes in Commodity Operating System Kernels via Memory Tagging Extensions.</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -2118,14 +2118,14 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Columbia University</t>
+          <t>John Brown University</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Yonghwi Kwon 0001</t>
+          <t>Penghui Li 0001</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -2133,22 +2133,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Racedb: Detecting Request Race Vulnerabilities in Database-Backed Web Applications.</t>
+          <t>IEEE_S&amp;P-Predator: Directed Web Application Fuzzing for Efficient Vulnerability Validation.</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>University of Maryland, College Park</t>
+          <t>Columbia University</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Zifeng Kang</t>
+          <t>Yonghwi Kwon 0001</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -2156,22 +2156,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Follow My Flow: Unveiling Client-Side Prototype Pollution Gadgets from One Million Real-World Websites.</t>
+          <t>IEEE_S&amp;P-Racedb: Detecting Request Race Vulnerabilities in Database-Backed Web Applications.</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Johns Hopkins University</t>
+          <t>University of Maryland, College Park</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Muxi Lyu</t>
+          <t>Zifeng Kang</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -2183,7 +2183,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Zhengyu Liu</t>
+          <t>Muxi Lyu</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -2206,7 +2206,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Jianjia Yu</t>
+          <t>Zhengyu Liu</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -2229,7 +2229,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Yinzhi Cao</t>
+          <t>Jianjia Yu</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Tommaso Innocenti</t>
+          <t>Yinzhi Cao</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -2271,22 +2271,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-"Only as Strong as the Weakest Link": On the Security of Brokered Single Sign-On on the Web.</t>
+          <t>IEEE_S&amp;P-Follow My Flow: Unveiling Client-Side Prototype Pollution Gadgets from One Million Real-World Websites.</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Northeastern University</t>
+          <t>Johns Hopkins University</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Engin Kirda</t>
+          <t>Tommaso Innocenti</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -2298,7 +2298,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Jose Luis Castanon Remy</t>
+          <t>Engin Kirda</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -2317,22 +2317,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-SoK: Space Infrastructures Vulnerabilities, Attacks and Defenses.</t>
+          <t>IEEE_S&amp;P-"Only as Strong as the Weakest Link": On the Security of Brokered Single Sign-On on the Web.</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>University of Colorado Colorado Springs</t>
+          <t>Northeastern University</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Ekzhin Ear</t>
+          <t>Jose Luis Castanon Remy</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Caleb Chang</t>
+          <t>Ekzhin Ear</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -2367,7 +2367,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Antonia Feffer</t>
+          <t>Caleb Chang</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -2390,7 +2390,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Shouhuai Xu</t>
+          <t>Antonia Feffer</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -2413,7 +2413,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Tao Wan 0004</t>
+          <t>Shouhuai Xu</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Invade the Walled Garden: Evaluating GTP Security in Cellular Networks.</t>
+          <t>IEEE_S&amp;P-SoK: Space Infrastructures Vulnerabilities, Attacks and Defenses.</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Cablevision (United States)</t>
+          <t>University of Colorado Colorado Springs</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Jinhe Wen</t>
+          <t>Tao Wan 0004</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -2455,22 +2455,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Teaching Data Science Students to Sketch Privacy Designs Through Heuristics.</t>
+          <t>IEEE_S&amp;P-Invade the Walled Garden: Evaluating GTP Security in Cellular Networks.</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>University of California, San Diego</t>
+          <t>Cablevision (United States)</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Yingxi Zhao</t>
+          <t>Jinhe Wen</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -2482,7 +2482,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Yaxing Yao</t>
+          <t>Yingxi Zhao</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -2505,18 +2505,18 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Virginia Tech</t>
+          <t>University of California, San Diego</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Haojian Jin</t>
+          <t>Wenqian Xu</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -2528,7 +2528,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Phoebe Moh</t>
+          <t>Yaxing Yao</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -2547,22 +2547,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Characterizing the Usability and Usefulness of U.S. Ad Transparency Systems.</t>
+          <t>IEEE_S&amp;P-Teaching Data Science Students to Sketch Privacy Designs Through Heuristics.</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>University of Maryland, College Park</t>
+          <t>Virginia Tech</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Tobias Lauinger</t>
+          <t>Haojian Jin</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -2570,22 +2570,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Characterizing the Usability and Usefulness of U.S. Ad Transparency Systems.</t>
+          <t>IEEE_S&amp;P-Teaching Data Science Students to Sketch Privacy Designs Through Heuristics.</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>New York University</t>
+          <t>University of California, San Diego</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Michelle L. Mazurek</t>
+          <t>Phoebe Moh</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -2597,7 +2597,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Damon McCoy</t>
+          <t>Tobias Lauinger</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -2620,7 +2620,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Lanjing Liu</t>
+          <t>Michelle L. Mazurek</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -2639,22 +2639,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Supporting Family Discussions About Digital Privacy Through Perspective-Taking: An Empirical Investigation.</t>
+          <t>IEEE_S&amp;P-Characterizing the Usability and Usefulness of U.S. Ad Transparency Systems.</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Virginia Tech</t>
+          <t>University of Maryland, College Park</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Yaxing Yao</t>
+          <t>Damon McCoy</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -2662,22 +2662,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Supporting Family Discussions About Digital Privacy Through Perspective-Taking: An Empirical Investigation.</t>
+          <t>IEEE_S&amp;P-Characterizing the Usability and Usefulness of U.S. Ad Transparency Systems.</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Virginia Tech</t>
+          <t>New York University</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Elham Pourabbas Vafa</t>
+          <t>Zikai Wen</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Learning from Censored Experiences: Social Media Discussions around Censorship Circumvention Technologies.</t>
+          <t>IEEE_S&amp;P-Supporting Family Discussions About Digital Privacy Through Perspective-Taking: An Empirical Investigation.</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -2693,14 +2693,14 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>The University of Texas at Arlington</t>
+          <t>Virginia Tech</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Mohit Singhal</t>
+          <t>Lanjing Liu</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -2708,7 +2708,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Learning from Censored Experiences: Social Media Discussions around Censorship Circumvention Technologies.</t>
+          <t>IEEE_S&amp;P-Supporting Family Discussions About Digital Privacy Through Perspective-Taking: An Empirical Investigation.</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -2716,14 +2716,14 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>The University of Texas at Arlington</t>
+          <t>Virginia Tech</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Poojitha Thota</t>
+          <t>Yaxing Yao</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Learning from Censored Experiences: Social Media Discussions around Censorship Circumvention Technologies.</t>
+          <t>IEEE_S&amp;P-Supporting Family Discussions About Digital Privacy Through Perspective-Taking: An Empirical Investigation.</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -2739,14 +2739,14 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>The University of Texas at Arlington</t>
+          <t>Virginia Tech</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Sayak Saha Roy</t>
+          <t>Elham Pourabbas Vafa</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -2758,7 +2758,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Zakir Durumeric</t>
+          <t>Mohit Singhal</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -2777,22 +2777,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-A Wall Behind A Wall: Emerging Regional Censorship in China.</t>
+          <t>IEEE_S&amp;P-Learning from Censored Experiences: Social Media Discussions around Censorship Circumvention Technologies.</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Stanford University</t>
+          <t>The University of Texas at Arlington</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Amir Houmansadr</t>
+          <t>Poojitha Thota</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -2800,22 +2800,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-A Wall Behind A Wall: Emerging Regional Censorship in China.</t>
+          <t>IEEE_S&amp;P-Learning from Censored Experiences: Social Media Discussions around Censorship Circumvention Technologies.</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>University of Massachusetts Amherst</t>
+          <t>The University of Texas at Arlington</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Eric Wustrow</t>
+          <t>Sayak Saha Roy</t>
         </is>
       </c>
       <c r="B105" t="n">
@@ -2823,22 +2823,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-A Wall Behind A Wall: Emerging Regional Censorship in China.</t>
+          <t>IEEE_S&amp;P-Learning from Censored Experiences: Social Media Discussions around Censorship Circumvention Technologies.</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>University of Colorado System; University of Colorado Boulder</t>
+          <t>The University of Texas at Arlington</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Sadia Nourin</t>
+          <t>Zakir Durumeric</t>
         </is>
       </c>
       <c r="B106" t="n">
@@ -2846,22 +2846,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Is Nobody There? Good! Globally Measuring Connection Tampering Without Responsive Endhosts.</t>
+          <t>IEEE_S&amp;P-A Wall Behind A Wall: Emerging Regional Censorship in China.</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>University of Maryland, College Park</t>
+          <t>Stanford University</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Erik C. Rye</t>
+          <t>Amir Houmansadr</t>
         </is>
       </c>
       <c r="B107" t="n">
@@ -2869,22 +2869,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Is Nobody There? Good! Globally Measuring Connection Tampering Without Responsive Endhosts.</t>
+          <t>IEEE_S&amp;P-A Wall Behind A Wall: Emerging Regional Censorship in China.</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>University of Maryland, College Park</t>
+          <t>University of Massachusetts Amherst</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Dave Levin</t>
+          <t>Eric Wustrow</t>
         </is>
       </c>
       <c r="B108" t="n">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Is Nobody There? Good! Globally Measuring Connection Tampering Without Responsive Endhosts.</t>
+          <t>IEEE_S&amp;P-A Wall Behind A Wall: Emerging Regional Censorship in China.</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -2900,14 +2900,14 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>University of Maryland, College Park</t>
+          <t>University of Colorado System; University of Colorado Boulder</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Kyle Fredrickson</t>
+          <t>Sadia Nourin</t>
         </is>
       </c>
       <c r="B109" t="n">
@@ -2915,7 +2915,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Sparta: Practical Anonymity with Long-Term Resistance to Traffic Analysis.</t>
+          <t>IEEE_S&amp;P-Is Nobody There? Good! Globally Measuring Connection Tampering Without Responsive Endhosts.</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -2923,14 +2923,14 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>University of California, Santa Cruz</t>
+          <t>University of Maryland, College Park</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Ioannis Demertzis</t>
+          <t>Erik C. Rye</t>
         </is>
       </c>
       <c r="B110" t="n">
@@ -2938,7 +2938,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Sparta: Practical Anonymity with Long-Term Resistance to Traffic Analysis.</t>
+          <t>IEEE_S&amp;P-Is Nobody There? Good! Globally Measuring Connection Tampering Without Responsive Endhosts.</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -2946,14 +2946,14 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>University of California, Santa Cruz</t>
+          <t>University of Maryland, College Park</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>James P. Hughes 0001</t>
+          <t>Dave Levin</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -2961,22 +2961,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Sparta: Practical Anonymity with Long-Term Resistance to Traffic Analysis.</t>
+          <t>IEEE_S&amp;P-Is Nobody There? Good! Globally Measuring Connection Tampering Without Responsive Endhosts.</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>University of California, Santa Cruz</t>
+          <t>University of Maryland, College Park</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Darrell D. E. Long</t>
+          <t>Kyle Fredrickson</t>
         </is>
       </c>
       <c r="B112" t="n">
@@ -2988,7 +2988,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>James Austgen</t>
+          <t>Ioannis Demertzis</t>
         </is>
       </c>
       <c r="B113" t="n">
@@ -3007,22 +3007,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Liquefaction: Privately Liquefying Blockchain Assets.</t>
+          <t>IEEE_S&amp;P-Sparta: Practical Anonymity with Long-Term Resistance to Traffic Analysis.</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Cornell University</t>
+          <t>University of California, Santa Cruz</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Andrés Fábrega</t>
+          <t>James P. Hughes 0001</t>
         </is>
       </c>
       <c r="B114" t="n">
@@ -3030,22 +3030,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Liquefaction: Privately Liquefying Blockchain Assets.</t>
+          <t>IEEE_S&amp;P-Sparta: Practical Anonymity with Long-Term Resistance to Traffic Analysis.</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Cornell University</t>
+          <t>University of California, Santa Cruz</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Mahimna Kelkar</t>
+          <t>Darrell D. E. Long</t>
         </is>
       </c>
       <c r="B115" t="n">
@@ -3053,22 +3053,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Liquefaction: Privately Liquefying Blockchain Assets.</t>
+          <t>IEEE_S&amp;P-Sparta: Practical Anonymity with Long-Term Resistance to Traffic Analysis.</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Cornell University</t>
+          <t>University of California, Santa Cruz</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Dani Vilardell</t>
+          <t>James Austgen</t>
         </is>
       </c>
       <c r="B116" t="n">
@@ -3080,7 +3080,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Kushal Babel</t>
+          <t>Andrés Fábrega</t>
         </is>
       </c>
       <c r="B117" t="n">
@@ -3103,7 +3103,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Ari Juels</t>
+          <t>Mahimna Kelkar</t>
         </is>
       </c>
       <c r="B118" t="n">
@@ -3126,7 +3126,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -3137,7 +3137,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Sen Yang</t>
+          <t>Dani Vilardell</t>
         </is>
       </c>
       <c r="B119" t="n">
@@ -3145,22 +3145,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Decentralization of Ethereum's Builder Market.</t>
+          <t>IEEE_S&amp;P-Liquefaction: Privately Liquefying Blockchain Assets.</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Yale University</t>
+          <t>Cornell University</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Kartik Nayak</t>
+          <t>Kushal Babel</t>
         </is>
       </c>
       <c r="B120" t="n">
@@ -3168,22 +3168,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Decentralization of Ethereum's Builder Market.</t>
+          <t>IEEE_S&amp;P-Liquefaction: Privately Liquefying Blockchain Assets.</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Duke University</t>
+          <t>Cornell University</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Fan Zhang 0022</t>
+          <t>Jay Yu</t>
         </is>
       </c>
       <c r="B121" t="n">
@@ -3191,22 +3191,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Decentralization of Ethereum's Builder Market.</t>
+          <t>IEEE_S&amp;P-Liquefaction: Privately Liquefying Blockchain Assets.</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Yale University</t>
+          <t>Stanford University</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Darya Kaviani</t>
+          <t>Ari Juels</t>
         </is>
       </c>
       <c r="B122" t="n">
@@ -3214,22 +3214,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Papercraft: Lattice-Based Verifiable Delay Function Implemented.</t>
+          <t>IEEE_S&amp;P-Liquefaction: Privately Liquefying Blockchain Assets.</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Berkeley College; University of California, Berkeley</t>
+          <t>Cornell University</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Jiongxiao Wang</t>
+          <t>Sen Yang</t>
         </is>
       </c>
       <c r="B123" t="n">
@@ -3237,22 +3237,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Preference Poisoning Attacks on Reward Model Learning.</t>
+          <t>IEEE_S&amp;P-Decentralization of Ethereum's Builder Market.</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>University of Wisconsin–Madison</t>
+          <t>Yale University</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Chaowei Xiao</t>
+          <t>Kartik Nayak</t>
         </is>
       </c>
       <c r="B124" t="n">
@@ -3260,22 +3260,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Preference Poisoning Attacks on Reward Model Learning.</t>
+          <t>IEEE_S&amp;P-Decentralization of Ethereum's Builder Market.</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>University of Wisconsin–Madison</t>
+          <t>Duke University</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Ziqi Zhang</t>
+          <t>Fan Zhang 0022</t>
         </is>
       </c>
       <c r="B125" t="n">
@@ -3283,22 +3283,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Query Provenance Analysis: Efficient and Robust Defense Against Query-Based Black-Box Attacks.</t>
+          <t>IEEE_S&amp;P-Decentralization of Ethereum's Builder Market.</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>University of Illinois Urbana-Champaign</t>
+          <t>Yale University</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Guangyu Shen</t>
+          <t>Darya Kaviani</t>
         </is>
       </c>
       <c r="B126" t="n">
@@ -3306,22 +3306,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-BAIT: Large Language Model Backdoor Scanning by Inverting Attack Target.</t>
+          <t>IEEE_S&amp;P-Papercraft: Lattice-Based Verifiable Delay Function Implemented.</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Purdue University West Lafayette</t>
+          <t>Berkeley College; University of California, Berkeley</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Siyuan Cheng 0005</t>
+          <t>Jiongxiao Wang</t>
         </is>
       </c>
       <c r="B127" t="n">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-BAIT: Large Language Model Backdoor Scanning by Inverting Attack Target.</t>
+          <t>IEEE_S&amp;P-Preference Poisoning Attacks on Reward Model Learning.</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -3337,14 +3337,14 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Purdue University West Lafayette</t>
+          <t>University of Wisconsin–Madison</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Zhuo Zhang 0002</t>
+          <t>Chaowei Xiao</t>
         </is>
       </c>
       <c r="B128" t="n">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-BAIT: Large Language Model Backdoor Scanning by Inverting Attack Target.</t>
+          <t>IEEE_S&amp;P-Preference Poisoning Attacks on Reward Model Learning.</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -3360,14 +3360,14 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Purdue University West Lafayette</t>
+          <t>University of Wisconsin–Madison</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Guanhong Tao 0001</t>
+          <t>Ziqi Zhang</t>
         </is>
       </c>
       <c r="B129" t="n">
@@ -3375,22 +3375,22 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-BAIT: Large Language Model Backdoor Scanning by Inverting Attack Target.</t>
+          <t>IEEE_S&amp;P-Query Provenance Analysis: Efficient and Robust Defense Against Query-Based Black-Box Attacks.</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>University of Utah</t>
+          <t>University of Illinois Urbana-Champaign</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Kaiyuan Zhang 0002</t>
+          <t>Guangyu Shen</t>
         </is>
       </c>
       <c r="B130" t="n">
@@ -3402,7 +3402,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Hanxi Guo</t>
+          <t>Siyuan Cheng 0005</t>
         </is>
       </c>
       <c r="B131" t="n">
@@ -3425,7 +3425,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Xiaolong Jin 0002</t>
+          <t>Zhuo Zhang 0002</t>
         </is>
       </c>
       <c r="B132" t="n">
@@ -3448,7 +3448,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Shengwei An</t>
+          <t>Guanhong Tao 0001</t>
         </is>
       </c>
       <c r="B133" t="n">
@@ -3471,18 +3471,18 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Purdue University West Lafayette</t>
+          <t>University of Utah</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Shiqing Ma</t>
+          <t>Kaiyuan Zhang 0002</t>
         </is>
       </c>
       <c r="B134" t="n">
@@ -3494,18 +3494,18 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>University of Massachusetts Amherst</t>
+          <t>Purdue University West Lafayette</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Xiangyu Zhang 0001</t>
+          <t>Hanxi Guo</t>
         </is>
       </c>
       <c r="B135" t="n">
@@ -3517,7 +3517,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Yongji Wu</t>
+          <t>Xiaolong Jin 0002</t>
         </is>
       </c>
       <c r="B136" t="n">
@@ -3536,22 +3536,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Prompt Inversion Attack Against Collaborative Inference of Large Language Models.</t>
+          <t>IEEE_S&amp;P-BAIT: Large Language Model Backdoor Scanning by Inverting Attack Target.</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Berkeley College; University of California, Berkeley</t>
+          <t>Purdue University West Lafayette</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Tingsong Xiao</t>
+          <t>Shengwei An</t>
         </is>
       </c>
       <c r="B137" t="n">
@@ -3559,22 +3559,22 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Prompt Inversion Attack Against Collaborative Inference of Large Language Models.</t>
+          <t>IEEE_S&amp;P-BAIT: Large Language Model Backdoor Scanning by Inverting Attack Target.</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>University of Florida</t>
+          <t>Purdue University West Lafayette</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Qing Deng</t>
+          <t>Shiqing Ma</t>
         </is>
       </c>
       <c r="B138" t="n">
@@ -3582,22 +3582,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Beyond the Horizon: Uncovering Hosts and Services Behind Misconfigured Firewalls.</t>
+          <t>IEEE_S&amp;P-BAIT: Large Language Model Backdoor Scanning by Inverting Attack Target.</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>University of California, Riverside</t>
+          <t>University of Massachusetts Amherst</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Juefei Pu</t>
+          <t>Xiangyu Zhang 0001</t>
         </is>
       </c>
       <c r="B139" t="n">
@@ -3605,22 +3605,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Beyond the Horizon: Uncovering Hosts and Services Behind Misconfigured Firewalls.</t>
+          <t>IEEE_S&amp;P-BAIT: Large Language Model Backdoor Scanning by Inverting Attack Target.</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>University of California, Riverside</t>
+          <t>Purdue University West Lafayette</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Zhaowei Tan</t>
+          <t>Yongji Wu</t>
         </is>
       </c>
       <c r="B140" t="n">
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Beyond the Horizon: Uncovering Hosts and Services Behind Misconfigured Firewalls.</t>
+          <t>IEEE_S&amp;P-Prompt Inversion Attack Against Collaborative Inference of Large Language Models.</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -3636,14 +3636,14 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>University of California, Riverside</t>
+          <t>Berkeley College; University of California, Berkeley</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Zhiyun Qian</t>
+          <t>Tingsong Xiao</t>
         </is>
       </c>
       <c r="B141" t="n">
@@ -3651,7 +3651,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Beyond the Horizon: Uncovering Hosts and Services Behind Misconfigured Firewalls.</t>
+          <t>IEEE_S&amp;P-Prompt Inversion Attack Against Collaborative Inference of Large Language Models.</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -3659,14 +3659,14 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>University of California, Riverside</t>
+          <t>University of Florida</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Srikanth V. Krishnamurthy</t>
+          <t>Qing Deng</t>
         </is>
       </c>
       <c r="B142" t="n">
@@ -3678,7 +3678,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Mohamed Nabeel</t>
+          <t>Juefei Pu</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -3697,7 +3697,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-MANTIS: Detection of Zero-Day Malicious Domains Leveraging Low Reputed Hosting Infrastructure.</t>
+          <t>IEEE_S&amp;P-Beyond the Horizon: Uncovering Hosts and Services Behind Misconfigured Firewalls.</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -3705,14 +3705,14 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Palo Alto Networks (United States)</t>
+          <t>University of California, Riverside</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Daiping Liu</t>
+          <t>Zhaowei Tan</t>
         </is>
       </c>
       <c r="B144" t="n">
@@ -3720,22 +3720,22 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Resolution Without Dissent: In-Path Per-Query Sanitization to Defeat Surreptitious Communication Over DNS.</t>
+          <t>IEEE_S&amp;P-Beyond the Horizon: Uncovering Hosts and Services Behind Misconfigured Firewalls.</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Palo Alto Networks (United States)</t>
+          <t>University of California, Riverside</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Ruian Duan</t>
+          <t>Zhiyun Qian</t>
         </is>
       </c>
       <c r="B145" t="n">
@@ -3743,22 +3743,22 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Resolution Without Dissent: In-Path Per-Query Sanitization to Defeat Surreptitious Communication Over DNS.</t>
+          <t>IEEE_S&amp;P-Beyond the Horizon: Uncovering Hosts and Services Behind Misconfigured Firewalls.</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Palo Alto Networks (United States)</t>
+          <t>University of California, Riverside</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Jun Wang</t>
+          <t>Srikanth V. Krishnamurthy</t>
         </is>
       </c>
       <c r="B146" t="n">
@@ -3766,22 +3766,22 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Resolution Without Dissent: In-Path Per-Query Sanitization to Defeat Surreptitious Communication Over DNS.</t>
+          <t>IEEE_S&amp;P-Beyond the Horizon: Uncovering Hosts and Services Behind Misconfigured Firewalls.</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Palo Alto Networks (United States)</t>
+          <t>University of California, Riverside</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Gene Tsudik</t>
+          <t>Mohamed Nabeel</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -3789,22 +3789,22 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-SoK: Decoding the Enigma of Encrypted Network Traffic Classifiers.</t>
+          <t>IEEE_S&amp;P-MANTIS: Detection of Zero-Day Malicious Domains Leveraging Low Reputed Hosting Infrastructure.</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>University of California, Irvine</t>
+          <t>Palo Alto Networks (United States)</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Keyu Man</t>
+          <t>Daiping Liu</t>
         </is>
       </c>
       <c r="B148" t="n">
@@ -3812,7 +3812,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-SCAD: Towards a Universal and Automated Network Side-Channel Vulnerability Detection.</t>
+          <t>IEEE_S&amp;P-Resolution Without Dissent: In-Path Per-Query Sanitization to Defeat Surreptitious Communication Over DNS.</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -3820,14 +3820,14 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>University of California, Riverside</t>
+          <t>Palo Alto Networks (United States)</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Zhongjie Wang 0002</t>
+          <t>Ruian Duan</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -3835,7 +3835,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-SCAD: Towards a Universal and Automated Network Side-Channel Vulnerability Detection.</t>
+          <t>IEEE_S&amp;P-Resolution Without Dissent: In-Path Per-Query Sanitization to Defeat Surreptitious Communication Over DNS.</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -3843,14 +3843,14 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>University of California, Riverside</t>
+          <t>Palo Alto Networks (United States)</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Shenghan Zheng</t>
+          <t>Jun Wang</t>
         </is>
       </c>
       <c r="B150" t="n">
@@ -3858,22 +3858,22 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-SCAD: Towards a Universal and Automated Network Side-Channel Vulnerability Detection.</t>
+          <t>IEEE_S&amp;P-Resolution Without Dissent: In-Path Per-Query Sanitization to Defeat Surreptitious Communication Over DNS.</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>University of California, Riverside</t>
+          <t>Palo Alto Networks (United States)</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Xin'an Zhou</t>
+          <t>Gene Tsudik</t>
         </is>
       </c>
       <c r="B151" t="n">
@@ -3881,22 +3881,22 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-SCAD: Towards a Universal and Automated Network Side-Channel Vulnerability Detection.</t>
+          <t>IEEE_S&amp;P-SoK: Decoding the Enigma of Encrypted Network Traffic Classifiers.</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>University of California, Riverside</t>
+          <t>University of California, Irvine</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Yue Cao 0003</t>
+          <t>Keyu Man</t>
         </is>
       </c>
       <c r="B152" t="n">
@@ -3908,7 +3908,7 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
@@ -3919,7 +3919,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Zhiyun Qian</t>
+          <t>Zhongjie Wang 0002</t>
         </is>
       </c>
       <c r="B153" t="n">
@@ -3931,7 +3931,7 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
@@ -3942,7 +3942,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Aniket Kate</t>
+          <t>Shenghan Zheng</t>
         </is>
       </c>
       <c r="B154" t="n">
@@ -3950,22 +3950,22 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Sailfish: Towards Improving the Latency of DAG-Based BFT.</t>
+          <t>IEEE_S&amp;P-SCAD: Towards a Universal and Automated Network Side-Channel Vulnerability Detection.</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Purdue University West Lafayette</t>
+          <t>University of California, Riverside</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Kartik Nayak</t>
+          <t>Xin'an Zhou</t>
         </is>
       </c>
       <c r="B155" t="n">
@@ -3973,22 +3973,22 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Sailfish: Towards Improving the Latency of DAG-Based BFT.</t>
+          <t>IEEE_S&amp;P-SCAD: Towards a Universal and Automated Network Side-Channel Vulnerability Detection.</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Duke University</t>
+          <t>University of California, Riverside</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Zhongtang Luo</t>
+          <t>Yue Cao 0003</t>
         </is>
       </c>
       <c r="B156" t="n">
@@ -3996,22 +3996,22 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Cauchyproofs: Batch-Updatable Vector Commitment with Easy Aggregation and Application to Stateless Blockchains.</t>
+          <t>IEEE_S&amp;P-SCAD: Towards a Universal and Automated Network Side-Channel Vulnerability Detection.</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Purdue University West Lafayette</t>
+          <t>University of California, Riverside</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Yanxue Jia</t>
+          <t>Zhiyun Qian</t>
         </is>
       </c>
       <c r="B157" t="n">
@@ -4019,22 +4019,22 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Cauchyproofs: Batch-Updatable Vector Commitment with Easy Aggregation and Application to Stateless Blockchains.</t>
+          <t>IEEE_S&amp;P-SCAD: Towards a Universal and Automated Network Side-Channel Vulnerability Detection.</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Purdue University West Lafayette</t>
+          <t>University of California, Riverside</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Weidong Cui</t>
+          <t>Aniket Kate</t>
         </is>
       </c>
       <c r="B158" t="n">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-MicroNova: Folding-Based Arguments with Efficient (On-Chain) Verification.</t>
+          <t>IEEE_S&amp;P-Sailfish: Towards Improving the Latency of DAG-Based BFT.</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -4050,14 +4050,14 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Microsoft Research (United Kingdom)</t>
+          <t>Purdue University West Lafayette</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Greg Zaverucha</t>
+          <t>Kartik Nayak</t>
         </is>
       </c>
       <c r="B159" t="n">
@@ -4065,7 +4065,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-MicroNova: Folding-Based Arguments with Efficient (On-Chain) Verification.</t>
+          <t>IEEE_S&amp;P-Sailfish: Towards Improving the Latency of DAG-Based BFT.</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -4073,14 +4073,14 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Microsoft Research (United Kingdom)</t>
+          <t>Duke University</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Ben Fisch</t>
+          <t>Zhongtang Luo</t>
         </is>
       </c>
       <c r="B160" t="n">
@@ -4088,7 +4088,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Permissionless Verifiable Information Dispersal (Data Availability for Bitcoin Rollups).</t>
+          <t>IEEE_S&amp;P-Cauchyproofs: Batch-Updatable Vector Commitment with Easy Aggregation and Application to Stateless Blockchains.</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -4096,14 +4096,14 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Yale University</t>
+          <t>Purdue University West Lafayette</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Arthur Lazzaretti</t>
+          <t>Yanxue Jia</t>
         </is>
       </c>
       <c r="B161" t="n">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Permissionless Verifiable Information Dispersal (Data Availability for Bitcoin Rollups).</t>
+          <t>IEEE_S&amp;P-Cauchyproofs: Batch-Updatable Vector Commitment with Easy Aggregation and Application to Stateless Blockchains.</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -4119,14 +4119,14 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Yale University</t>
+          <t>Purdue University West Lafayette</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Zeyu Liu 0004</t>
+          <t>Srinath T. V. Setty</t>
         </is>
       </c>
       <c r="B162" t="n">
@@ -4134,22 +4134,22 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Permissionless Verifiable Information Dispersal (Data Availability for Bitcoin Rollups).</t>
+          <t>IEEE_S&amp;P-MicroNova: Folding-Based Arguments with Efficient (On-Chain) Verification.</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Yale University</t>
+          <t>Microsoft Research (United Kingdom)</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Jiadong Lou</t>
+          <t>Weidong Cui</t>
         </is>
       </c>
       <c r="B163" t="n">
@@ -4157,22 +4157,22 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-GRID: Protecting Training Graph from Link Stealing Attacks on GNN Models.</t>
+          <t>IEEE_S&amp;P-MicroNova: Folding-Based Arguments with Efficient (On-Chain) Verification.</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>University of Delaware</t>
+          <t>Microsoft Research (United Kingdom)</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Rui Zhang</t>
+          <t>Greg Zaverucha</t>
         </is>
       </c>
       <c r="B164" t="n">
@@ -4180,22 +4180,22 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-GRID: Protecting Training Graph from Link Stealing Attacks on GNN Models.</t>
+          <t>IEEE_S&amp;P-MicroNova: Folding-Based Arguments with Efficient (On-Chain) Verification.</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>University of Delaware</t>
+          <t>Microsoft Research (United Kingdom)</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Neil Zhenqiang Gong</t>
+          <t>Ben Fisch</t>
         </is>
       </c>
       <c r="B165" t="n">
@@ -4203,22 +4203,22 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-GRID: Protecting Training Graph from Link Stealing Attacks on GNN Models.</t>
+          <t>IEEE_S&amp;P-Permissionless Verifiable Information Dispersal (Data Availability for Bitcoin Rollups).</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Duke University</t>
+          <t>Yale University</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Kang Yang</t>
+          <t>Arthur Lazzaretti</t>
         </is>
       </c>
       <c r="B166" t="n">
@@ -4226,22 +4226,22 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Alleviating the Fear of Losing Alignment in LLM Fine-tuning.</t>
+          <t>IEEE_S&amp;P-Permissionless Verifiable Information Dispersal (Data Availability for Bitcoin Rollups).</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>University of Utah</t>
+          <t>Yale University</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Guanhong Tao 0001</t>
+          <t>Zeyu Liu 0004</t>
         </is>
       </c>
       <c r="B167" t="n">
@@ -4249,22 +4249,22 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Alleviating the Fear of Losing Alignment in LLM Fine-tuning.</t>
+          <t>IEEE_S&amp;P-Permissionless Verifiable Information Dispersal (Data Availability for Bitcoin Rollups).</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>University of Utah</t>
+          <t>Yale University</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Jun Xu 0024</t>
+          <t>Jiadong Lou</t>
         </is>
       </c>
       <c r="B168" t="n">
@@ -4272,22 +4272,22 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Alleviating the Fear of Losing Alignment in LLM Fine-tuning.</t>
+          <t>IEEE_S&amp;P-GRID: Protecting Training Graph from Link Stealing Attacks on GNN Models.</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>University of Utah</t>
+          <t>University of Delaware</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Yuqi Jia</t>
+          <t>Rui Zhang</t>
         </is>
       </c>
       <c r="B169" t="n">
@@ -4295,22 +4295,22 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-DataSentinel: A Game-Theoretic Detection of Prompt Injection Attacks.</t>
+          <t>IEEE_S&amp;P-GRID: Protecting Training Graph from Link Stealing Attacks on GNN Models.</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Duke University</t>
+          <t>University of Delaware</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Dawn Song</t>
+          <t>Neil Zhenqiang Gong</t>
         </is>
       </c>
       <c r="B170" t="n">
@@ -4318,22 +4318,22 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-DataSentinel: A Game-Theoretic Detection of Prompt Injection Attacks.</t>
+          <t>IEEE_S&amp;P-GRID: Protecting Training Graph from Link Stealing Attacks on GNN Models.</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>University of California, Berkeley; Berkeley College</t>
+          <t>Duke University</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Neil Zhenqiang Gong</t>
+          <t>Kang Yang</t>
         </is>
       </c>
       <c r="B171" t="n">
@@ -4341,22 +4341,22 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-DataSentinel: A Game-Theoretic Detection of Prompt Injection Attacks.</t>
+          <t>IEEE_S&amp;P-Alleviating the Fear of Losing Alignment in LLM Fine-tuning.</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Duke University</t>
+          <t>University of Utah</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Yasemin Acar</t>
+          <t>Guanhong Tao 0001</t>
         </is>
       </c>
       <c r="B172" t="n">
@@ -4364,22 +4364,22 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-"It's Time. Time for Digital Security.": An End User Study on Actionable Security and Privacy Advice.</t>
+          <t>IEEE_S&amp;P-Alleviating the Fear of Losing Alignment in LLM Fine-tuning.</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>George Washington University</t>
+          <t>University of Utah</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>John Sadik</t>
+          <t>Jun Xu 0024</t>
         </is>
       </c>
       <c r="B173" t="n">
@@ -4387,22 +4387,22 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Security and Privacy Experiences of First- and Second-Generation Pakistani Immigrants to the US: Perceptions, Practices, Challenges, and Parent-Child Dynamics.</t>
+          <t>IEEE_S&amp;P-Alleviating the Fear of Losing Alignment in LLM Fine-tuning.</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>University of Tennessee at Knoxville</t>
+          <t>University of Utah</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Taha</t>
+          <t>Yuqi Jia</t>
         </is>
       </c>
       <c r="B174" t="n">
@@ -4410,22 +4410,22 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Security and Privacy Experiences of First- and Second-Generation Pakistani Immigrants to the US: Perceptions, Practices, Challenges, and Parent-Child Dynamics.</t>
+          <t>IEEE_S&amp;P-DataSentinel: A Game-Theoretic Detection of Prompt Injection Attacks.</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Purdue University West Lafayette</t>
+          <t>Duke University</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Ran Elgedawy</t>
+          <t>Dawn Song</t>
         </is>
       </c>
       <c r="B175" t="n">
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Security and Privacy Experiences of First- and Second-Generation Pakistani Immigrants to the US: Perceptions, Practices, Challenges, and Parent-Child Dynamics.</t>
+          <t>IEEE_S&amp;P-DataSentinel: A Game-Theoretic Detection of Prompt Injection Attacks.</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -4441,14 +4441,14 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>University of Tennessee at Knoxville</t>
+          <t>University of California, Berkeley; Berkeley College</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Scott Ruoti</t>
+          <t>Neil Zhenqiang Gong</t>
         </is>
       </c>
       <c r="B176" t="n">
@@ -4456,7 +4456,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Security and Privacy Experiences of First- and Second-Generation Pakistani Immigrants to the US: Perceptions, Practices, Challenges, and Parent-Child Dynamics.</t>
+          <t>IEEE_S&amp;P-DataSentinel: A Game-Theoretic Detection of Prompt Injection Attacks.</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -4464,14 +4464,14 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>University of Tennessee at Knoxville</t>
+          <t>Duke University</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Yaxin Tu</t>
+          <t>Yasemin Acar</t>
         </is>
       </c>
       <c r="B177" t="n">
@@ -4479,7 +4479,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Improved Constructions for Distributed Multi-Point Functions.</t>
+          <t>IEEE_S&amp;P-"It's Time. Time for Digital Security.": An End User Study on Actionable Security and Privacy Advice.</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -4487,14 +4487,14 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Princeton University</t>
+          <t>George Washington University</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Kanav Gupta</t>
+          <t>John Sadik</t>
         </is>
       </c>
       <c r="B178" t="n">
@@ -4502,22 +4502,22 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-SHARK: Actively Secure Inference Using Function Secret Sharing.</t>
+          <t>IEEE_S&amp;P-Security and Privacy Experiences of First- and Second-Generation Pakistani Immigrants to the US: Perceptions, Practices, Challenges, and Parent-Child Dynamics.</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>University of Maryland, College Park</t>
+          <t>University of Tennessee at Knoxville</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Nishanth Chandran</t>
+          <t>Taha</t>
         </is>
       </c>
       <c r="B179" t="n">
@@ -4525,22 +4525,22 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-SHARK: Actively Secure Inference Using Function Secret Sharing.</t>
+          <t>IEEE_S&amp;P-Security and Privacy Experiences of First- and Second-Generation Pakistani Immigrants to the US: Perceptions, Practices, Challenges, and Parent-Child Dynamics.</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Microsoft Research (United Kingdom)</t>
+          <t>Purdue University West Lafayette</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Divya Gupta 0001</t>
+          <t>Ran Elgedawy</t>
         </is>
       </c>
       <c r="B180" t="n">
@@ -4548,22 +4548,22 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-SHARK: Actively Secure Inference Using Function Secret Sharing.</t>
+          <t>IEEE_S&amp;P-Security and Privacy Experiences of First- and Second-Generation Pakistani Immigrants to the US: Perceptions, Practices, Challenges, and Parent-Child Dynamics.</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Microsoft Research (United Kingdom)</t>
+          <t>University of Tennessee at Knoxville</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Jonathan Katz</t>
+          <t>Scott Ruoti</t>
         </is>
       </c>
       <c r="B181" t="n">
@@ -4571,22 +4571,22 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-SHARK: Actively Secure Inference Using Function Secret Sharing.</t>
+          <t>IEEE_S&amp;P-Security and Privacy Experiences of First- and Second-Generation Pakistani Immigrants to the US: Perceptions, Practices, Challenges, and Parent-Child Dynamics.</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Google (United States)</t>
+          <t>University of Tennessee at Knoxville</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Rahul Sharma 0001</t>
+          <t>Yaxin Tu</t>
         </is>
       </c>
       <c r="B182" t="n">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-SHARK: Actively Secure Inference Using Function Secret Sharing.</t>
+          <t>IEEE_S&amp;P-Improved Constructions for Distributed Multi-Point Functions.</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -4602,14 +4602,14 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>University of Maryland, College Park</t>
+          <t>Princeton University</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Zhenting Wang</t>
+          <t>Kanav Gupta</t>
         </is>
       </c>
       <c r="B183" t="n">
@@ -4617,22 +4617,22 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Towards Reliable Verification of Unauthorized Data Usage in Personalized Text-to-Image Diffusion Models.</t>
+          <t>IEEE_S&amp;P-SHARK: Actively Secure Inference Using Function Secret Sharing.</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Rutgers, The State University of New Jersey</t>
+          <t>University of Maryland, College Park</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Xuandong Zhao</t>
+          <t>Nishanth Chandran</t>
         </is>
       </c>
       <c r="B184" t="n">
@@ -4640,22 +4640,22 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-SoK: Watermarking for AI-Generated Content.</t>
+          <t>IEEE_S&amp;P-SHARK: Actively Secure Inference Using Function Secret Sharing.</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Berkeley College; University of California, Berkeley</t>
+          <t>Microsoft Research (United Kingdom)</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Sam Gunn</t>
+          <t>Divya Gupta 0001</t>
         </is>
       </c>
       <c r="B185" t="n">
@@ -4663,22 +4663,22 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-SoK: Watermarking for AI-Generated Content.</t>
+          <t>IEEE_S&amp;P-SHARK: Actively Secure Inference Using Function Secret Sharing.</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Berkeley College; University of California, Berkeley</t>
+          <t>Microsoft Research (United Kingdom)</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Miranda Christ</t>
+          <t>Jonathan Katz</t>
         </is>
       </c>
       <c r="B186" t="n">
@@ -4686,22 +4686,22 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-SoK: Watermarking for AI-Generated Content.</t>
+          <t>IEEE_S&amp;P-SHARK: Actively Secure Inference Using Function Secret Sharing.</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Columbia University</t>
+          <t>Google (United States)</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Jaiden Fairoze</t>
+          <t>Rahul Sharma 0001</t>
         </is>
       </c>
       <c r="B187" t="n">
@@ -4709,22 +4709,22 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-SoK: Watermarking for AI-Generated Content.</t>
+          <t>IEEE_S&amp;P-SHARK: Actively Secure Inference Using Function Secret Sharing.</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Berkeley College; University of California, Berkeley</t>
+          <t>University of Maryland, College Park</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Andrés Fábrega</t>
+          <t>Zhenting Wang</t>
         </is>
       </c>
       <c r="B188" t="n">
@@ -4732,22 +4732,22 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-SoK: Watermarking for AI-Generated Content.</t>
+          <t>IEEE_S&amp;P-Towards Reliable Verification of Unauthorized Data Usage in Personalized Text-to-Image Diffusion Models.</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Cornell University</t>
+          <t>Rutgers, The State University of New Jersey</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Sanjam Garg</t>
+          <t>Xuandong Zhao</t>
         </is>
       </c>
       <c r="B189" t="n">
@@ -4759,7 +4759,7 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
@@ -4770,7 +4770,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Sanghyun Hong 0001</t>
+          <t>Sam Gunn</t>
         </is>
       </c>
       <c r="B190" t="n">
@@ -4782,18 +4782,18 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Oregon State University</t>
+          <t>Berkeley College; University of California, Berkeley</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Milad Nasr</t>
+          <t>Miranda Christ</t>
         </is>
       </c>
       <c r="B191" t="n">
@@ -4805,18 +4805,18 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Google (United States); Google DeepMind (United Kingdom)</t>
+          <t>Columbia University</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Somesh Jha</t>
+          <t>Jaiden Fairoze</t>
         </is>
       </c>
       <c r="B192" t="n">
@@ -4828,18 +4828,18 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>University of Wisconsin–Madison</t>
+          <t>Berkeley College; University of California, Berkeley</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Lei Li 0005</t>
+          <t>Andrés Fábrega</t>
         </is>
       </c>
       <c r="B193" t="n">
@@ -4851,18 +4851,18 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>Cornell University</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Dawn Song</t>
+          <t>Sanjam Garg</t>
         </is>
       </c>
       <c r="B194" t="n">
@@ -4874,7 +4874,7 @@
         </is>
       </c>
       <c r="D194" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>G. Edward Suh</t>
+          <t>Sanghyun Hong 0001</t>
         </is>
       </c>
       <c r="B195" t="n">
@@ -4893,22 +4893,22 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Machine Learning with Privacy for Protected Attributes.</t>
+          <t>IEEE_S&amp;P-SoK: Watermarking for AI-Generated Content.</t>
         </is>
       </c>
       <c r="D195" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Cornell University; Nvidia (United Kingdom)</t>
+          <t>Oregon State University</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Florian Schaub</t>
+          <t>Milad Nasr</t>
         </is>
       </c>
       <c r="B196" t="n">
@@ -4916,22 +4916,22 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Transparency in Usable Privacy and Security Research: Scholars' Perspectives, Practices, and Recommendations.</t>
+          <t>IEEE_S&amp;P-SoK: Watermarking for AI-Generated Content.</t>
         </is>
       </c>
       <c r="D196" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>University of Michigan–Ann Arbor</t>
+          <t>Google (United States); Google DeepMind (United Kingdom)</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Anna Crowder</t>
+          <t>Somesh Jha</t>
         </is>
       </c>
       <c r="B197" t="n">
@@ -4939,22 +4939,22 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Data to Infinity and Beyond: Examining Data Sharing and Reuse Practices in the Computer Security Community.</t>
+          <t>IEEE_S&amp;P-SoK: Watermarking for AI-Generated Content.</t>
         </is>
       </c>
       <c r="D197" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>University of Florida</t>
+          <t>University of Wisconsin–Madison</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Kevin Childs</t>
+          <t>Lei Li 0005</t>
         </is>
       </c>
       <c r="B198" t="n">
@@ -4962,22 +4962,22 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Data to Infinity and Beyond: Examining Data Sharing and Reuse Practices in the Computer Security Community.</t>
+          <t>IEEE_S&amp;P-SoK: Watermarking for AI-Generated Content.</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>University of Florida</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Carson Stillman</t>
+          <t>Dawn Song</t>
         </is>
       </c>
       <c r="B199" t="n">
@@ -4985,22 +4985,22 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Data to Infinity and Beyond: Examining Data Sharing and Reuse Practices in the Computer Security Community.</t>
+          <t>IEEE_S&amp;P-SoK: Watermarking for AI-Generated Content.</t>
         </is>
       </c>
       <c r="D199" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>University of Florida</t>
+          <t>Berkeley College; University of California, Berkeley</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Patrick Traynor</t>
+          <t>G. Edward Suh</t>
         </is>
       </c>
       <c r="B200" t="n">
@@ -5008,22 +5008,22 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Data to Infinity and Beyond: Examining Data Sharing and Reuse Practices in the Computer Security Community.</t>
+          <t>IEEE_S&amp;P-Machine Learning with Privacy for Protected Attributes.</t>
         </is>
       </c>
       <c r="D200" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>University of Florida</t>
+          <t>Cornell University; Nvidia (United Kingdom)</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Yaman Yu</t>
+          <t>Byron M. Lowens</t>
         </is>
       </c>
       <c r="B201" t="n">
@@ -5031,22 +5031,22 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Exploring Parent-Child Perceptions on Safety in Generative AI: Concerns, Mitigation Strategies, and Design Implications.</t>
+          <t>IEEE_S&amp;P-Transparency in Usable Privacy and Security Research: Scholars' Perspectives, Practices, and Recommendations.</t>
         </is>
       </c>
       <c r="D201" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>University of Illinois Urbana-Champaign</t>
+          <t>University of Michigan–Ann Arbor</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Yang Wang 0005</t>
+          <t>Florian Schaub</t>
         </is>
       </c>
       <c r="B202" t="n">
@@ -5054,22 +5054,22 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Exploring Parent-Child Perceptions on Safety in Generative AI: Concerns, Mitigation Strategies, and Design Implications.</t>
+          <t>IEEE_S&amp;P-Transparency in Usable Privacy and Security Research: Scholars' Perspectives, Practices, and Recommendations.</t>
         </is>
       </c>
       <c r="D202" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>University of Illinois Urbana-Champaign</t>
+          <t>University of Michigan–Ann Arbor</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Yaman Yu</t>
+          <t>Anna Crowder</t>
         </is>
       </c>
       <c r="B203" t="n">
@@ -5077,22 +5077,22 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Security Perceptions of Users in Stablecoins: Advantages and Risks within the Cryptocurrency Ecosystem.</t>
+          <t>IEEE_S&amp;P-Data to Infinity and Beyond: Examining Data Sharing and Reuse Practices in the Computer Security Community.</t>
         </is>
       </c>
       <c r="D203" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>University of Illinois Urbana-Champaign</t>
+          <t>University of Florida</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Kaihua Qin</t>
+          <t>Allison Lu</t>
         </is>
       </c>
       <c r="B204" t="n">
@@ -5100,22 +5100,22 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Security Perceptions of Users in Stablecoins: Advantages and Risks within the Cryptocurrency Ecosystem.</t>
+          <t>IEEE_S&amp;P-Data to Infinity and Beyond: Examining Data Sharing and Reuse Practices in the Computer Security Community.</t>
         </is>
       </c>
       <c r="D204" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Yale University</t>
+          <t>University of Florida</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Yang Wang 0005</t>
+          <t>Kevin Childs</t>
         </is>
       </c>
       <c r="B205" t="n">
@@ -5123,22 +5123,22 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Security Perceptions of Users in Stablecoins: Advantages and Risks within the Cryptocurrency Ecosystem.</t>
+          <t>IEEE_S&amp;P-Data to Infinity and Beyond: Examining Data Sharing and Reuse Practices in the Computer Security Community.</t>
         </is>
       </c>
       <c r="D205" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>University of Illinois Urbana-Champaign</t>
+          <t>University of Florida</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Kurt Thomas</t>
+          <t>Carson Stillman</t>
         </is>
       </c>
       <c r="B206" t="n">
@@ -5146,22 +5146,22 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Supporting Human Raters with the Detection of Harmful Content Using Large Language Models.</t>
+          <t>IEEE_S&amp;P-Data to Infinity and Beyond: Examining Data Sharing and Reuse Practices in the Computer Security Community.</t>
         </is>
       </c>
       <c r="D206" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Google (United States)</t>
+          <t>University of Florida</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Patrick Gage Kelley</t>
+          <t>Patrick Traynor</t>
         </is>
       </c>
       <c r="B207" t="n">
@@ -5169,22 +5169,22 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Supporting Human Raters with the Detection of Harmful Content Using Large Language Models.</t>
+          <t>IEEE_S&amp;P-Data to Infinity and Beyond: Examining Data Sharing and Reuse Practices in the Computer Security Community.</t>
         </is>
       </c>
       <c r="D207" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Google (United States)</t>
+          <t>University of Florida</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>David Tao</t>
+          <t>Kevin R. B. Butler</t>
         </is>
       </c>
       <c r="B208" t="n">
@@ -5192,22 +5192,22 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Supporting Human Raters with the Detection of Harmful Content Using Large Language Models.</t>
+          <t>IEEE_S&amp;P-Data to Infinity and Beyond: Examining Data Sharing and Reuse Practices in the Computer Security Community.</t>
         </is>
       </c>
       <c r="D208" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Google (United States)</t>
+          <t>University of Florida</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Sarah Meiklejohn</t>
+          <t>Yaman Yu</t>
         </is>
       </c>
       <c r="B209" t="n">
@@ -5215,22 +5215,22 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Supporting Human Raters with the Detection of Harmful Content Using Large Language Models.</t>
+          <t>IEEE_S&amp;P-Exploring Parent-Child Perceptions on Safety in Generative AI: Concerns, Mitigation Strategies, and Design Implications.</t>
         </is>
       </c>
       <c r="D209" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Google (United States)</t>
+          <t>University of Illinois Urbana-Champaign</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Owen Vallis</t>
+          <t>Yang Wang 0005</t>
         </is>
       </c>
       <c r="B210" t="n">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Supporting Human Raters with the Detection of Harmful Content Using Large Language Models.</t>
+          <t>IEEE_S&amp;P-Exploring Parent-Child Perceptions on Safety in Generative AI: Concerns, Mitigation Strategies, and Design Implications.</t>
         </is>
       </c>
       <c r="D210" t="n">
@@ -5246,14 +5246,14 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Google (United States)</t>
+          <t>University of Illinois Urbana-Champaign</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Shunwen Tan</t>
+          <t>Yaman Yu</t>
         </is>
       </c>
       <c r="B211" t="n">
@@ -5261,22 +5261,22 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Supporting Human Raters with the Detection of Harmful Content Using Large Language Models.</t>
+          <t>IEEE_S&amp;P-Security Perceptions of Users in Stablecoins: Advantages and Risks within the Cryptocurrency Ecosystem.</t>
         </is>
       </c>
       <c r="D211" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Google (United States)</t>
+          <t>University of Illinois Urbana-Champaign</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Felipe Tiengo Ferreira</t>
+          <t>Kaihua Qin</t>
         </is>
       </c>
       <c r="B212" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Supporting Human Raters with the Detection of Harmful Content Using Large Language Models.</t>
+          <t>IEEE_S&amp;P-Security Perceptions of Users in Stablecoins: Advantages and Risks within the Cryptocurrency Ecosystem.</t>
         </is>
       </c>
       <c r="D212" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Google (United States); DeepMind (United Kingdom)</t>
+          <t>Yale University</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Elie Bursztein</t>
+          <t>Yang Wang 0005</t>
         </is>
       </c>
       <c r="B213" t="n">
@@ -5307,22 +5307,22 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Supporting Human Raters with the Detection of Harmful Content Using Large Language Models.</t>
+          <t>IEEE_S&amp;P-Security Perceptions of Users in Stablecoins: Advantages and Risks within the Cryptocurrency Ecosystem.</t>
         </is>
       </c>
       <c r="D213" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Google (United States)</t>
+          <t>University of Illinois Urbana-Champaign</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Lucy Simko</t>
+          <t>Kurt Thomas</t>
         </is>
       </c>
       <c r="B214" t="n">
@@ -5330,22 +5330,22 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-"It's been Lovely Watching you": Institutional Decision-Making on Online Proctoring Software.</t>
+          <t>IEEE_S&amp;P-Supporting Human Raters with the Detection of Harmful Content Using Large Language Models.</t>
         </is>
       </c>
       <c r="D214" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>George Washington University</t>
+          <t>Google (United States)</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Ryan Watkins</t>
+          <t>Patrick Gage Kelley</t>
         </is>
       </c>
       <c r="B215" t="n">
@@ -5353,22 +5353,22 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-"It's been Lovely Watching you": Institutional Decision-Making on Online Proctoring Software.</t>
+          <t>IEEE_S&amp;P-Supporting Human Raters with the Detection of Harmful Content Using Large Language Models.</t>
         </is>
       </c>
       <c r="D215" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>George Washington University</t>
+          <t>Google (United States)</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Adam J. Aviv</t>
+          <t>David Tao</t>
         </is>
       </c>
       <c r="B216" t="n">
@@ -5376,22 +5376,22 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-"It's been Lovely Watching you": Institutional Decision-Making on Online Proctoring Software.</t>
+          <t>IEEE_S&amp;P-Supporting Human Raters with the Detection of Harmful Content Using Large Language Models.</t>
         </is>
       </c>
       <c r="D216" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>George Washington University</t>
+          <t>Google (United States)</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Tung Le 0005</t>
+          <t>Sarah Meiklejohn</t>
         </is>
       </c>
       <c r="B217" t="n">
@@ -5399,22 +5399,22 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Hermes: Efficient and Secure Multi-Writer Encrypted Database.</t>
+          <t>IEEE_S&amp;P-Supporting Human Raters with the Detection of Harmful Content Using Large Language Models.</t>
         </is>
       </c>
       <c r="D217" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Virginia Tech</t>
+          <t>Google (United States)</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Borja Balle</t>
+          <t>Owen Vallis</t>
         </is>
       </c>
       <c r="B218" t="n">
@@ -5422,22 +5422,22 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Hash-Prune-Invert: Improved Differentially Private Heavy-Hitter Detection in the Two-Server Model.</t>
+          <t>IEEE_S&amp;P-Supporting Human Raters with the Detection of Harmful Content Using Large Language Models.</t>
         </is>
       </c>
       <c r="D218" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Google (United States); DeepMind (United Kingdom)</t>
+          <t>Google (United States)</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>James Bell-Clark</t>
+          <t>Shunwen Tan</t>
         </is>
       </c>
       <c r="B219" t="n">
@@ -5445,11 +5445,11 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Hash-Prune-Invert: Improved Differentially Private Heavy-Hitter Detection in the Two-Server Model.</t>
+          <t>IEEE_S&amp;P-Supporting Human Raters with the Detection of Harmful Content Using Large Language Models.</t>
         </is>
       </c>
       <c r="D219" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E219" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Albert Cheu</t>
+          <t>Felipe Tiengo Ferreira</t>
         </is>
       </c>
       <c r="B220" t="n">
@@ -5468,22 +5468,22 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Hash-Prune-Invert: Improved Differentially Private Heavy-Hitter Detection in the Two-Server Model.</t>
+          <t>IEEE_S&amp;P-Supporting Human Raters with the Detection of Harmful Content Using Large Language Models.</t>
         </is>
       </c>
       <c r="D220" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Google (United States)</t>
+          <t>Google (United States); DeepMind (United Kingdom)</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Adrià Gascón</t>
+          <t>Vijay Kumar Eranti</t>
         </is>
       </c>
       <c r="B221" t="n">
@@ -5491,11 +5491,11 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Hash-Prune-Invert: Improved Differentially Private Heavy-Hitter Detection in the Two-Server Model.</t>
+          <t>IEEE_S&amp;P-Supporting Human Raters with the Detection of Harmful Content Using Large Language Models.</t>
         </is>
       </c>
       <c r="D221" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E221" t="inlineStr">
         <is>
@@ -5506,7 +5506,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Jonathan Katz</t>
+          <t>Elie Bursztein</t>
         </is>
       </c>
       <c r="B222" t="n">
@@ -5514,11 +5514,11 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Hash-Prune-Invert: Improved Differentially Private Heavy-Hitter Detection in the Two-Server Model.</t>
+          <t>IEEE_S&amp;P-Supporting Human Raters with the Detection of Harmful Content Using Large Language Models.</t>
         </is>
       </c>
       <c r="D222" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E222" t="inlineStr">
         <is>
@@ -5529,7 +5529,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Mariana Raykova 0001</t>
+          <t>Ani Meliksetyan</t>
         </is>
       </c>
       <c r="B223" t="n">
@@ -5537,22 +5537,22 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Hash-Prune-Invert: Improved Differentially Private Heavy-Hitter Detection in the Two-Server Model.</t>
+          <t>IEEE_S&amp;P-"It's been Lovely Watching you": Institutional Decision-Making on Online Proctoring Software.</t>
         </is>
       </c>
       <c r="D223" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Google (United States)</t>
+          <t>George Washington University</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Phillipp Schoppmann</t>
+          <t>Lucy Simko</t>
         </is>
       </c>
       <c r="B224" t="n">
@@ -5560,22 +5560,22 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Hash-Prune-Invert: Improved Differentially Private Heavy-Hitter Detection in the Two-Server Model.</t>
+          <t>IEEE_S&amp;P-"It's been Lovely Watching you": Institutional Decision-Making on Online Proctoring Software.</t>
         </is>
       </c>
       <c r="D224" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Google (United States)</t>
+          <t>George Washington University</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Thomas Steinke 0002</t>
+          <t>Ryan Watkins</t>
         </is>
       </c>
       <c r="B225" t="n">
@@ -5583,22 +5583,22 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Hash-Prune-Invert: Improved Differentially Private Heavy-Hitter Detection in the Two-Server Model.</t>
+          <t>IEEE_S&amp;P-"It's been Lovely Watching you": Institutional Decision-Making on Online Proctoring Software.</t>
         </is>
       </c>
       <c r="D225" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>DeepMind (United Kingdom); Google (United States)</t>
+          <t>George Washington University</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Danfeng Zhang</t>
+          <t>Adam J. Aviv</t>
         </is>
       </c>
       <c r="B226" t="n">
@@ -5606,22 +5606,22 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Click Without Compromise: Online Advertising Measurement via Per User Differential Privacy.</t>
+          <t>IEEE_S&amp;P-"It's been Lovely Watching you": Institutional Decision-Making on Online Proctoring Software.</t>
         </is>
       </c>
       <c r="D226" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Duke University</t>
+          <t>George Washington University</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Guoren Li</t>
+          <t>Tung Le 0005</t>
         </is>
       </c>
       <c r="B227" t="n">
@@ -5629,7 +5629,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Redefining Indirect Call Analysis with KallGraph.</t>
+          <t>IEEE_S&amp;P-Hermes: Efficient and Secure Multi-Writer Encrypted Database.</t>
         </is>
       </c>
       <c r="D227" t="n">
@@ -5637,14 +5637,14 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>University of California, Riverside</t>
+          <t>Virginia Tech</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Manu Sridharan</t>
+          <t>Thang Hoang</t>
         </is>
       </c>
       <c r="B228" t="n">
@@ -5652,7 +5652,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Redefining Indirect Call Analysis with KallGraph.</t>
+          <t>IEEE_S&amp;P-Hermes: Efficient and Secure Multi-Writer Encrypted Database.</t>
         </is>
       </c>
       <c r="D228" t="n">
@@ -5660,14 +5660,14 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>University of California, Riverside</t>
+          <t>Virginia Tech</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Zhiyun Qian</t>
+          <t>Borja Balle</t>
         </is>
       </c>
       <c r="B229" t="n">
@@ -5675,22 +5675,22 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Redefining Indirect Call Analysis with KallGraph.</t>
+          <t>IEEE_S&amp;P-Hash-Prune-Invert: Improved Differentially Private Heavy-Hitter Detection in the Two-Server Model.</t>
         </is>
       </c>
       <c r="D229" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>University of California, Riverside</t>
+          <t>Google (United States); DeepMind (United Kingdom)</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Elliot Tarbet</t>
+          <t>James Bell-Clark</t>
         </is>
       </c>
       <c r="B230" t="n">
@@ -5698,7 +5698,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-PyLingual: Toward Perfect Decompilation of Evolving High-Level Languages.</t>
+          <t>IEEE_S&amp;P-Hash-Prune-Invert: Improved Differentially Private Heavy-Hitter Detection in the Two-Server Model.</t>
         </is>
       </c>
       <c r="D230" t="n">
@@ -5706,14 +5706,14 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>The University of Texas at Dallas</t>
+          <t>Google (United States)</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Max Zheng</t>
+          <t>Albert Cheu</t>
         </is>
       </c>
       <c r="B231" t="n">
@@ -5721,7 +5721,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-PyLingual: Toward Perfect Decompilation of Evolving High-Level Languages.</t>
+          <t>IEEE_S&amp;P-Hash-Prune-Invert: Improved Differentially Private Heavy-Hitter Detection in the Two-Server Model.</t>
         </is>
       </c>
       <c r="D231" t="n">
@@ -5729,14 +5729,14 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>The University of Texas at Dallas</t>
+          <t>Google (United States)</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Sangsoo Ko</t>
+          <t>Adrià Gascón</t>
         </is>
       </c>
       <c r="B232" t="n">
@@ -5744,7 +5744,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-PyLingual: Toward Perfect Decompilation of Evolving High-Level Languages.</t>
+          <t>IEEE_S&amp;P-Hash-Prune-Invert: Improved Differentially Private Heavy-Hitter Detection in the Two-Server Model.</t>
         </is>
       </c>
       <c r="D232" t="n">
@@ -5752,14 +5752,14 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>The University of Texas at Dallas</t>
+          <t>Google (United States)</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Jessica Ouyang 0001</t>
+          <t>Jonathan Katz</t>
         </is>
       </c>
       <c r="B233" t="n">
@@ -5767,7 +5767,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-PyLingual: Toward Perfect Decompilation of Evolving High-Level Languages.</t>
+          <t>IEEE_S&amp;P-Hash-Prune-Invert: Improved Differentially Private Heavy-Hitter Detection in the Two-Server Model.</t>
         </is>
       </c>
       <c r="D233" t="n">
@@ -5775,14 +5775,14 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>The University of Texas at Dallas</t>
+          <t>Google (United States)</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Kangkook Jee</t>
+          <t>Mariana Raykova 0001</t>
         </is>
       </c>
       <c r="B234" t="n">
@@ -5790,22 +5790,22 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-PyLingual: Toward Perfect Decompilation of Evolving High-Level Languages.</t>
+          <t>IEEE_S&amp;P-Hash-Prune-Invert: Improved Differentially Private Heavy-Hitter Detection in the Two-Server Model.</t>
         </is>
       </c>
       <c r="D234" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>The University of Texas at Dallas</t>
+          <t>Google (United States)</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Antonio Flores-Montoya</t>
+          <t>Phillipp Schoppmann</t>
         </is>
       </c>
       <c r="B235" t="n">
@@ -5813,22 +5813,22 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Disassembly as Weighted Interval Scheduling with Learned Weights.</t>
+          <t>IEEE_S&amp;P-Hash-Prune-Invert: Improved Differentially Private Heavy-Hitter Detection in the Two-Server Model.</t>
         </is>
       </c>
       <c r="D235" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>GrammaTech (United States)</t>
+          <t>Google (United States)</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Junghee Lim</t>
+          <t>Thomas Steinke 0002</t>
         </is>
       </c>
       <c r="B236" t="n">
@@ -5836,22 +5836,22 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Disassembly as Weighted Interval Scheduling with Learned Weights.</t>
+          <t>IEEE_S&amp;P-Hash-Prune-Invert: Improved Differentially Private Heavy-Hitter Detection in the Two-Server Model.</t>
         </is>
       </c>
       <c r="D236" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>GrammaTech (United States)</t>
+          <t>DeepMind (United Kingdom); Google (United States)</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Adam Seitz</t>
+          <t>Danfeng Zhang</t>
         </is>
       </c>
       <c r="B237" t="n">
@@ -5859,22 +5859,22 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Disassembly as Weighted Interval Scheduling with Learned Weights.</t>
+          <t>IEEE_S&amp;P-Click Without Compromise: Online Advertising Measurement via Per User Differential Privacy.</t>
         </is>
       </c>
       <c r="D237" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>GrammaTech (United States)</t>
+          <t>Duke University</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Akshay Sood</t>
+          <t>Guoren Li</t>
         </is>
       </c>
       <c r="B238" t="n">
@@ -5882,22 +5882,22 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Disassembly as Weighted Interval Scheduling with Learned Weights.</t>
+          <t>IEEE_S&amp;P-Redefining Indirect Call Analysis with KallGraph.</t>
         </is>
       </c>
       <c r="D238" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>GrammaTech (United States)</t>
+          <t>University of California, Riverside</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Edward Raff</t>
+          <t>Manu Sridharan</t>
         </is>
       </c>
       <c r="B239" t="n">
@@ -5905,22 +5905,22 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Disassembly as Weighted Interval Scheduling with Learned Weights.</t>
+          <t>IEEE_S&amp;P-Redefining Indirect Call Analysis with KallGraph.</t>
         </is>
       </c>
       <c r="D239" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton (United States)</t>
+          <t>University of California, Riverside</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Jun Xu 0024</t>
+          <t>Zhiyun Qian</t>
         </is>
       </c>
       <c r="B240" t="n">
@@ -5928,22 +5928,22 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Inspecting Virtual Machine Diversification Inside Virtualization Obfuscation.</t>
+          <t>IEEE_S&amp;P-Redefining Indirect Call Analysis with KallGraph.</t>
         </is>
       </c>
       <c r="D240" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>University of Utah</t>
+          <t>University of California, Riverside</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Jiwon Kim 0001</t>
+          <t>Joshua Wiedemeier</t>
         </is>
       </c>
       <c r="B241" t="n">
@@ -5951,7 +5951,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Chimera: Fuzzing P4 Network Infrastructure for Multi-Plane Bug Detection and Vulnerability Discovery.</t>
+          <t>IEEE_S&amp;P-PyLingual: Toward Perfect Decompilation of Evolving High-Level Languages.</t>
         </is>
       </c>
       <c r="D241" t="n">
@@ -5959,14 +5959,14 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Purdue University West Lafayette</t>
+          <t>The University of Texas at Dallas</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>David Chisnall</t>
+          <t>Elliot Tarbet</t>
         </is>
       </c>
       <c r="B242" t="n">
@@ -5974,22 +5974,22 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-SoK: Software Compartmentalization.</t>
+          <t>IEEE_S&amp;P-PyLingual: Toward Perfect Decompilation of Evolving High-Level Languages.</t>
         </is>
       </c>
       <c r="D242" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>ON Semiconductor (United States)</t>
+          <t>The University of Texas at Dallas</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Zheng Yang</t>
+          <t>Max Zheng</t>
         </is>
       </c>
       <c r="B243" t="n">
@@ -5997,22 +5997,22 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-CoinDef: A Comprehensive Code Injection Defense for the Electron Framework.</t>
+          <t>IEEE_S&amp;P-PyLingual: Toward Perfect Decompilation of Evolving High-Level Languages.</t>
         </is>
       </c>
       <c r="D243" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>The University of Texas at Dallas</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Simon P. Chung</t>
+          <t>Sangsoo Ko</t>
         </is>
       </c>
       <c r="B244" t="n">
@@ -6020,22 +6020,22 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-CoinDef: A Comprehensive Code Injection Defense for the Electron Framework.</t>
+          <t>IEEE_S&amp;P-PyLingual: Toward Perfect Decompilation of Evolving High-Level Languages.</t>
         </is>
       </c>
       <c r="D244" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>The University of Texas at Dallas</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Jizhou Chen</t>
+          <t>Jessica Ouyang 0001</t>
         </is>
       </c>
       <c r="B245" t="n">
@@ -6043,22 +6043,22 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-CoinDef: A Comprehensive Code Injection Defense for the Electron Framework.</t>
+          <t>IEEE_S&amp;P-PyLingual: Toward Perfect Decompilation of Evolving High-Level Languages.</t>
         </is>
       </c>
       <c r="D245" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>The University of Texas at Dallas</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Runze Zhang</t>
+          <t>Kangkook Jee</t>
         </is>
       </c>
       <c r="B246" t="n">
@@ -6066,22 +6066,22 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-CoinDef: A Comprehensive Code Injection Defense for the Electron Framework.</t>
+          <t>IEEE_S&amp;P-PyLingual: Toward Perfect Decompilation of Evolving High-Level Languages.</t>
         </is>
       </c>
       <c r="D246" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>The University of Texas at Dallas</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Brendan Saltaformaggio</t>
+          <t>Antonio Flores-Montoya</t>
         </is>
       </c>
       <c r="B247" t="n">
@@ -6089,22 +6089,22 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-CoinDef: A Comprehensive Code Injection Defense for the Electron Framework.</t>
+          <t>IEEE_S&amp;P-Disassembly as Weighted Interval Scheduling with Learned Weights.</t>
         </is>
       </c>
       <c r="D247" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>GrammaTech (United States)</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Wenke Lee</t>
+          <t>Junghee Lim</t>
         </is>
       </c>
       <c r="B248" t="n">
@@ -6112,22 +6112,22 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-CoinDef: A Comprehensive Code Injection Defense for the Electron Framework.</t>
+          <t>IEEE_S&amp;P-Disassembly as Weighted Interval Scheduling with Learned Weights.</t>
         </is>
       </c>
       <c r="D248" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>GrammaTech (United States)</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Quinn Burke 0002</t>
+          <t>Adam Seitz</t>
         </is>
       </c>
       <c r="B249" t="n">
@@ -6135,22 +6135,22 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Efficient Storage Integrity in Adversarial Settings.</t>
+          <t>IEEE_S&amp;P-Disassembly as Weighted Interval Scheduling with Learned Weights.</t>
         </is>
       </c>
       <c r="D249" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>University of Wisconsin–Madison</t>
+          <t>GrammaTech (United States)</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Ryan Sheatsley</t>
+          <t>Akshay Sood</t>
         </is>
       </c>
       <c r="B250" t="n">
@@ -6158,22 +6158,22 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Efficient Storage Integrity in Adversarial Settings.</t>
+          <t>IEEE_S&amp;P-Disassembly as Weighted Interval Scheduling with Learned Weights.</t>
         </is>
       </c>
       <c r="D250" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>University of Wisconsin–Madison</t>
+          <t>GrammaTech (United States)</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Yohan Beugin</t>
+          <t>Edward Raff</t>
         </is>
       </c>
       <c r="B251" t="n">
@@ -6181,22 +6181,22 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Efficient Storage Integrity in Adversarial Settings.</t>
+          <t>IEEE_S&amp;P-Disassembly as Weighted Interval Scheduling with Learned Weights.</t>
         </is>
       </c>
       <c r="D251" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>University of Wisconsin–Madison</t>
+          <t>Booz Allen Hamilton (United States)</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Eric Pauley</t>
+          <t>Jun Xu 0024</t>
         </is>
       </c>
       <c r="B252" t="n">
@@ -6204,7 +6204,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Efficient Storage Integrity in Adversarial Settings.</t>
+          <t>IEEE_S&amp;P-Inspecting Virtual Machine Diversification Inside Virtualization Obfuscation.</t>
         </is>
       </c>
       <c r="D252" t="n">
@@ -6212,14 +6212,14 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>University of Wisconsin–Madison</t>
+          <t>University of Utah</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Owen Hines</t>
+          <t>Jiwon Kim 0001</t>
         </is>
       </c>
       <c r="B253" t="n">
@@ -6227,22 +6227,22 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Efficient Storage Integrity in Adversarial Settings.</t>
+          <t>IEEE_S&amp;P-Chimera: Fuzzing P4 Network Infrastructure for Multi-Plane Bug Detection and Vulnerability Discovery.</t>
         </is>
       </c>
       <c r="D253" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>University of Wisconsin–Madison</t>
+          <t>Purdue University West Lafayette</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Ananta Soneji</t>
+          <t>Dave Jing Tian</t>
         </is>
       </c>
       <c r="B254" t="n">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-"It's almost like Frankenstein": Investigating the Complexities of Scientific Collaboration and Privilege Management within Research Computing Infrastructures.</t>
+          <t>IEEE_S&amp;P-Chimera: Fuzzing P4 Network Infrastructure for Multi-Plane Bug Detection and Vulnerability Discovery.</t>
         </is>
       </c>
       <c r="D254" t="n">
@@ -6258,14 +6258,14 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Arizona State University</t>
+          <t>Purdue University West Lafayette</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Jaejong Baek</t>
+          <t>David Chisnall</t>
         </is>
       </c>
       <c r="B255" t="n">
@@ -6273,7 +6273,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-"It's almost like Frankenstein": Investigating the Complexities of Scientific Collaboration and Privilege Management within Research Computing Infrastructures.</t>
+          <t>IEEE_S&amp;P-SoK: Software Compartmentalization.</t>
         </is>
       </c>
       <c r="D255" t="n">
@@ -6281,14 +6281,14 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Arizona State University</t>
+          <t>ON Semiconductor (United States)</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Tiffany Bao</t>
+          <t>Zheng Yang</t>
         </is>
       </c>
       <c r="B256" t="n">
@@ -6296,22 +6296,22 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-"It's almost like Frankenstein": Investigating the Complexities of Scientific Collaboration and Privilege Management within Research Computing Infrastructures.</t>
+          <t>IEEE_S&amp;P-CoinDef: A Comprehensive Code Injection Defense for the Electron Framework.</t>
         </is>
       </c>
       <c r="D256" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Arizona State University</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Adam Doupé</t>
+          <t>Simon P. Chung</t>
         </is>
       </c>
       <c r="B257" t="n">
@@ -6319,22 +6319,22 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-"It's almost like Frankenstein": Investigating the Complexities of Scientific Collaboration and Privilege Management within Research Computing Infrastructures.</t>
+          <t>IEEE_S&amp;P-CoinDef: A Comprehensive Code Injection Defense for the Electron Framework.</t>
         </is>
       </c>
       <c r="D257" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Arizona State University</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Anna P. Y. Woo</t>
+          <t>Jizhou Chen</t>
         </is>
       </c>
       <c r="B258" t="n">
@@ -6342,22 +6342,22 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Efficient Proofs of Possession for Legacy Signatures.</t>
+          <t>IEEE_S&amp;P-CoinDef: A Comprehensive Code Injection Defense for the Electron Framework.</t>
         </is>
       </c>
       <c r="D258" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>University of Michigan–Ann Arbor</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Alex Ozdemir</t>
+          <t>Runze Zhang</t>
         </is>
       </c>
       <c r="B259" t="n">
@@ -6365,22 +6365,22 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Efficient Proofs of Possession for Legacy Signatures.</t>
+          <t>IEEE_S&amp;P-CoinDef: A Comprehensive Code Injection Defense for the Electron Framework.</t>
         </is>
       </c>
       <c r="D259" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Stanford University</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Chad Sharp</t>
+          <t>Brendan Saltaformaggio</t>
         </is>
       </c>
       <c r="B260" t="n">
@@ -6388,22 +6388,22 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Efficient Proofs of Possession for Legacy Signatures.</t>
+          <t>IEEE_S&amp;P-CoinDef: A Comprehensive Code Injection Defense for the Electron Framework.</t>
         </is>
       </c>
       <c r="D260" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>University of Michigan–Ann Arbor</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Paul Grubbs</t>
+          <t>Wenke Lee</t>
         </is>
       </c>
       <c r="B261" t="n">
@@ -6411,22 +6411,22 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Efficient Proofs of Possession for Legacy Signatures.</t>
+          <t>IEEE_S&amp;P-CoinDef: A Comprehensive Code Injection Defense for the Electron Framework.</t>
         </is>
       </c>
       <c r="D261" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>University of Michigan–Ann Arbor</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Kunming Jiang</t>
+          <t>Quinn Burke 0002</t>
         </is>
       </c>
       <c r="B262" t="n">
@@ -6434,7 +6434,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-CoBBL: Dynamic Constraint Generation for SNARKs.</t>
+          <t>IEEE_S&amp;P-Efficient Storage Integrity in Adversarial Settings.</t>
         </is>
       </c>
       <c r="D262" t="n">
@@ -6442,14 +6442,14 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>University of Wisconsin–Madison</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Fraser Brown</t>
+          <t>Ryan Sheatsley</t>
         </is>
       </c>
       <c r="B263" t="n">
@@ -6457,7 +6457,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-CoBBL: Dynamic Constraint Generation for SNARKs.</t>
+          <t>IEEE_S&amp;P-Efficient Storage Integrity in Adversarial Settings.</t>
         </is>
       </c>
       <c r="D263" t="n">
@@ -6465,14 +6465,14 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>University of Wisconsin–Madison</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Riad S. Wahby</t>
+          <t>Yohan Beugin</t>
         </is>
       </c>
       <c r="B264" t="n">
@@ -6480,7 +6480,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-CoBBL: Dynamic Constraint Generation for SNARKs.</t>
+          <t>IEEE_S&amp;P-Efficient Storage Integrity in Adversarial Settings.</t>
         </is>
       </c>
       <c r="D264" t="n">
@@ -6488,14 +6488,14 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>University of Wisconsin–Madison</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Jiwon Kim</t>
+          <t>Eric Pauley</t>
         </is>
       </c>
       <c r="B265" t="n">
@@ -6503,22 +6503,22 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-ALPACA: Anonymous Blocklisting with Constant-Sized Updatable Proofs.</t>
+          <t>IEEE_S&amp;P-Efficient Storage Integrity in Adversarial Settings.</t>
         </is>
       </c>
       <c r="D265" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>University of Michigan</t>
+          <t>University of Wisconsin–Madison</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Abhiram Kothapalli</t>
+          <t>Owen Hines</t>
         </is>
       </c>
       <c r="B266" t="n">
@@ -6526,22 +6526,22 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-ALPACA: Anonymous Blocklisting with Constant-Sized Updatable Proofs.</t>
+          <t>IEEE_S&amp;P-Efficient Storage Integrity in Adversarial Settings.</t>
         </is>
       </c>
       <c r="D266" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>University of California, Berkeley</t>
+          <t>University of Wisconsin–Madison</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Orestis Chardouvelis</t>
+          <t>Michael Swift</t>
         </is>
       </c>
       <c r="B267" t="n">
@@ -6549,22 +6549,22 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-ALPACA: Anonymous Blocklisting with Constant-Sized Updatable Proofs.</t>
+          <t>IEEE_S&amp;P-Efficient Storage Integrity in Adversarial Settings.</t>
         </is>
       </c>
       <c r="D267" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>University of Wisconsin–Madison</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Riad S. Wahby</t>
+          <t>Patrick D. McDaniel</t>
         </is>
       </c>
       <c r="B268" t="n">
@@ -6572,22 +6572,22 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-ALPACA: Anonymous Blocklisting with Constant-Sized Updatable Proofs.</t>
+          <t>IEEE_S&amp;P-Efficient Storage Integrity in Adversarial Settings.</t>
         </is>
       </c>
       <c r="D268" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>University of Wisconsin–Madison</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Paul Grubbs</t>
+          <t>Souradip Nath</t>
         </is>
       </c>
       <c r="B269" t="n">
@@ -6595,22 +6595,22 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-ALPACA: Anonymous Blocklisting with Constant-Sized Updatable Proofs.</t>
+          <t>IEEE_S&amp;P-"It's almost like Frankenstein": Investigating the Complexities of Scientific Collaboration and Privilege Management within Research Computing Infrastructures.</t>
         </is>
       </c>
       <c r="D269" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>University of Michigan</t>
+          <t>Arizona State University</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Charalampos Papamanthou</t>
+          <t>Ananta Soneji</t>
         </is>
       </c>
       <c r="B270" t="n">
@@ -6618,22 +6618,22 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-HydraProofs: Optimally Computing All Proofs in a Vector Commitment (With Applications to Efficient zkSNARKs Over Data from Multiple Users).</t>
+          <t>IEEE_S&amp;P-"It's almost like Frankenstein": Investigating the Complexities of Scientific Collaboration and Privilege Management within Research Computing Infrastructures.</t>
         </is>
       </c>
       <c r="D270" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Yale University</t>
+          <t>Arizona State University</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Tianyu Zhang</t>
+          <t>Jaejong Baek</t>
         </is>
       </c>
       <c r="B271" t="n">
@@ -6641,22 +6641,22 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-FairZK: A Scalable System to Prove Machine Learning Fairness in Zero-Knowledge.</t>
+          <t>IEEE_S&amp;P-"It's almost like Frankenstein": Investigating the Complexities of Scientific Collaboration and Privilege Management within Research Computing Infrastructures.</t>
         </is>
       </c>
       <c r="D271" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>University of Illinois Urbana-Champaign</t>
+          <t>Arizona State University</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Shen Dong</t>
+          <t>Tiffany Bao</t>
         </is>
       </c>
       <c r="B272" t="n">
@@ -6664,22 +6664,22 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-FairZK: A Scalable System to Prove Machine Learning Fairness in Zero-Knowledge.</t>
+          <t>IEEE_S&amp;P-"It's almost like Frankenstein": Investigating the Complexities of Scientific Collaboration and Privilege Management within Research Computing Infrastructures.</t>
         </is>
       </c>
       <c r="D272" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>University of Illinois Urbana-Champaign</t>
+          <t>Arizona State University</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Yupeng Zhang</t>
+          <t>Adam Doupé</t>
         </is>
       </c>
       <c r="B273" t="n">
@@ -6687,7 +6687,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-FairZK: A Scalable System to Prove Machine Learning Fairness in Zero-Knowledge.</t>
+          <t>IEEE_S&amp;P-"It's almost like Frankenstein": Investigating the Complexities of Scientific Collaboration and Privilege Management within Research Computing Infrastructures.</t>
         </is>
       </c>
       <c r="D273" t="n">
@@ -6695,14 +6695,14 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>University of Illinois Urbana-Champaign</t>
+          <t>Arizona State University</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Stephan van Schaik</t>
+          <t>Carlos E. Rubio-Medrano</t>
         </is>
       </c>
       <c r="B274" t="n">
@@ -6710,22 +6710,22 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Slice+Slice Baby: Generating Last-Level Cache Eviction Sets in the Blink of an Eye.</t>
+          <t>IEEE_S&amp;P-"It's almost like Frankenstein": Investigating the Complexities of Scientific Collaboration and Privilege Management within Research Computing Infrastructures.</t>
         </is>
       </c>
       <c r="D274" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>University of Michigan–Ann Arbor</t>
+          <t>Texas A&amp;M University – Corpus Christi</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Daniel Genkin</t>
+          <t>Gail-Joon Ahn</t>
         </is>
       </c>
       <c r="B275" t="n">
@@ -6733,22 +6733,22 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Slice+Slice Baby: Generating Last-Level Cache Eviction Sets in the Blink of an Eye.</t>
+          <t>IEEE_S&amp;P-"It's almost like Frankenstein": Investigating the Complexities of Scientific Collaboration and Privilege Management within Research Computing Infrastructures.</t>
         </is>
       </c>
       <c r="D275" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>Arizona State University</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Boru Chen</t>
+          <t>Anna P. Y. Woo</t>
         </is>
       </c>
       <c r="B276" t="n">
@@ -6756,22 +6756,22 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Peek-a-Walk: Leaking Secrets via Page Walk Side Channels.</t>
+          <t>IEEE_S&amp;P-Efficient Proofs of Possession for Legacy Signatures.</t>
         </is>
       </c>
       <c r="D276" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Berkeley College; University of California, Berkeley</t>
+          <t>University of Michigan–Ann Arbor</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Yingchen Wang</t>
+          <t>Alex Ozdemir</t>
         </is>
       </c>
       <c r="B277" t="n">
@@ -6779,22 +6779,22 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Peek-a-Walk: Leaking Secrets via Page Walk Side Channels.</t>
+          <t>IEEE_S&amp;P-Efficient Proofs of Possession for Legacy Signatures.</t>
         </is>
       </c>
       <c r="D277" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Berkeley College; University of California, Berkeley</t>
+          <t>Stanford University</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Christopher W. Fletcher</t>
+          <t>Chad Sharp</t>
         </is>
       </c>
       <c r="B278" t="n">
@@ -6802,22 +6802,22 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Peek-a-Walk: Leaking Secrets via Page Walk Side Channels.</t>
+          <t>IEEE_S&amp;P-Efficient Proofs of Possession for Legacy Signatures.</t>
         </is>
       </c>
       <c r="D278" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Berkeley College; University of California, Berkeley</t>
+          <t>University of Michigan–Ann Arbor</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Daniel Genkin</t>
+          <t>Paul Grubbs</t>
         </is>
       </c>
       <c r="B279" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Peek-a-Walk: Leaking Secrets via Page Walk Side Channels.</t>
+          <t>IEEE_S&amp;P-Efficient Proofs of Possession for Legacy Signatures.</t>
         </is>
       </c>
       <c r="D279" t="n">
@@ -6833,14 +6833,14 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>University of Michigan–Ann Arbor</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>David Kohlbrenner</t>
+          <t>Kunming Jiang</t>
         </is>
       </c>
       <c r="B280" t="n">
@@ -6848,22 +6848,22 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Peek-a-Walk: Leaking Secrets via Page Walk Side Channels.</t>
+          <t>IEEE_S&amp;P-CoBBL: Dynamic Constraint Generation for SNARKs.</t>
         </is>
       </c>
       <c r="D280" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>University of Washington</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Riccardo Paccagnella</t>
+          <t>Fraser Brown</t>
         </is>
       </c>
       <c r="B281" t="n">
@@ -6871,11 +6871,11 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Peek-a-Walk: Leaking Secrets via Page Walk Side Channels.</t>
+          <t>IEEE_S&amp;P-CoBBL: Dynamic Constraint Generation for SNARKs.</t>
         </is>
       </c>
       <c r="D281" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E281" t="inlineStr">
         <is>
@@ -6886,7 +6886,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Daniel Genkin</t>
+          <t>Riad S. Wahby</t>
         </is>
       </c>
       <c r="B282" t="n">
@@ -6894,22 +6894,22 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-SLAP: Data Speculation Attacks via Load Address Prediction on Apple Silicon.</t>
+          <t>IEEE_S&amp;P-CoBBL: Dynamic Constraint Generation for SNARKs.</t>
         </is>
       </c>
       <c r="D282" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Samy Amer</t>
+          <t>Jiwon Kim</t>
         </is>
       </c>
       <c r="B283" t="n">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-PQ-Hammer: End-to-End Key Recovery Attacks on Post-Quantum Cryptography Using Rowhammer.</t>
+          <t>IEEE_S&amp;P-ALPACA: Anonymous Blocklisting with Constant-Sized Updatable Proofs.</t>
         </is>
       </c>
       <c r="D283" t="n">
@@ -6925,14 +6925,14 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>University of Michigan</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Yingchen Wang</t>
+          <t>Abhiram Kothapalli</t>
         </is>
       </c>
       <c r="B284" t="n">
@@ -6940,7 +6940,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-PQ-Hammer: End-to-End Key Recovery Attacks on Post-Quantum Cryptography Using Rowhammer.</t>
+          <t>IEEE_S&amp;P-ALPACA: Anonymous Blocklisting with Constant-Sized Updatable Proofs.</t>
         </is>
       </c>
       <c r="D284" t="n">
@@ -6948,14 +6948,14 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Berkeley College; University of California, Berkeley</t>
+          <t>University of California, Berkeley</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Daniel Genkin</t>
+          <t>Orestis Chardouvelis</t>
         </is>
       </c>
       <c r="B285" t="n">
@@ -6963,22 +6963,22 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-PQ-Hammer: End-to-End Key Recovery Attacks on Post-Quantum Cryptography Using Rowhammer.</t>
+          <t>IEEE_S&amp;P-ALPACA: Anonymous Blocklisting with Constant-Sized Updatable Proofs.</t>
         </is>
       </c>
       <c r="D285" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Andrew Kwong</t>
+          <t>Riad S. Wahby</t>
         </is>
       </c>
       <c r="B286" t="n">
@@ -6986,22 +6986,22 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-PQ-Hammer: End-to-End Key Recovery Attacks on Post-Quantum Cryptography Using Rowhammer.</t>
+          <t>IEEE_S&amp;P-ALPACA: Anonymous Blocklisting with Constant-Sized Updatable Proofs.</t>
         </is>
       </c>
       <c r="D286" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>University of North Carolina Health Care; University of North Carolina at Chapel Hill</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Arkady Yerukhimovich</t>
+          <t>Paul Grubbs</t>
         </is>
       </c>
       <c r="B287" t="n">
@@ -7009,22 +7009,22 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-PQ-Hammer: End-to-End Key Recovery Attacks on Post-Quantum Cryptography Using Rowhammer.</t>
+          <t>IEEE_S&amp;P-ALPACA: Anonymous Blocklisting with Constant-Sized Updatable Proofs.</t>
         </is>
       </c>
       <c r="D287" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>George Washington University</t>
+          <t>University of Michigan</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Inwhan Chun</t>
+          <t>Charalampos Papamanthou</t>
         </is>
       </c>
       <c r="B288" t="n">
@@ -7032,22 +7032,22 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Scheduled Disclosure: Turning Power into Timing Without Frequency Scaling.</t>
+          <t>IEEE_S&amp;P-HydraProofs: Optimally Computing All Proofs in a Vector Commitment (With Applications to Efficient zkSNARKs Over Data from Multiple Users).</t>
         </is>
       </c>
       <c r="D288" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>Yale University</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Isabella Siu</t>
+          <t>Tianyu Zhang</t>
         </is>
       </c>
       <c r="B289" t="n">
@@ -7055,22 +7055,22 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Scheduled Disclosure: Turning Power into Timing Without Frequency Scaling.</t>
+          <t>IEEE_S&amp;P-FairZK: A Scalable System to Prove Machine Learning Fairness in Zero-Knowledge.</t>
         </is>
       </c>
       <c r="D289" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>University of Illinois Urbana-Champaign</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Riccardo Paccagnella</t>
+          <t>Shen Dong</t>
         </is>
       </c>
       <c r="B290" t="n">
@@ -7078,22 +7078,22 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Scheduled Disclosure: Turning Power into Timing Without Frequency Scaling.</t>
+          <t>IEEE_S&amp;P-FairZK: A Scalable System to Prove Machine Learning Fairness in Zero-Knowledge.</t>
         </is>
       </c>
       <c r="D290" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>University of Illinois Urbana-Champaign</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Cheng Gu</t>
+          <t>Oyku Deniz Kose</t>
         </is>
       </c>
       <c r="B291" t="n">
@@ -7101,22 +7101,22 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-I know What You Sync: Covert and Side Channel Attacks on File Systems via syncfs.</t>
+          <t>IEEE_S&amp;P-FairZK: A Scalable System to Prove Machine Learning Fairness in Zero-Knowledge.</t>
         </is>
       </c>
       <c r="D291" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>University of California, Riverside</t>
+          <t>University of California, Irvine</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Yicheng Zhang 0004</t>
+          <t>Yupeng Zhang</t>
         </is>
       </c>
       <c r="B292" t="n">
@@ -7124,22 +7124,22 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-I know What You Sync: Covert and Side Channel Attacks on File Systems via syncfs.</t>
+          <t>IEEE_S&amp;P-FairZK: A Scalable System to Prove Machine Learning Fairness in Zero-Knowledge.</t>
         </is>
       </c>
       <c r="D292" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>University of California, Riverside</t>
+          <t>University of Illinois Urbana-Champaign</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Muhammad Daniyal Pirwani Dar</t>
+          <t>Stephan van Schaik</t>
         </is>
       </c>
       <c r="B293" t="n">
@@ -7147,22 +7147,22 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Saecred: A State-Aware, Over-the-Air Protocol Testing Approach for Discovering Parsing Bugs in SAE Handshake Implementations of COTS Wi-Fi Access Points.</t>
+          <t>IEEE_S&amp;P-Slice+Slice Baby: Generating Last-Level Cache Eviction Sets in the Blink of an Eye.</t>
         </is>
       </c>
       <c r="D293" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Stony Brook University</t>
+          <t>University of Michigan–Ann Arbor</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Aliakbar Sadeghi</t>
+          <t>Daniel Genkin</t>
         </is>
       </c>
       <c r="B294" t="n">
@@ -7170,22 +7170,22 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Saecred: A State-Aware, Over-the-Air Protocol Testing Approach for Discovering Parsing Bugs in SAE Handshake Implementations of COTS Wi-Fi Access Points.</t>
+          <t>IEEE_S&amp;P-Slice+Slice Baby: Generating Last-Level Cache Eviction Sets in the Blink of an Eye.</t>
         </is>
       </c>
       <c r="D294" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Stony Brook University</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Vincenzo Sorcigli</t>
+          <t>Boru Chen</t>
         </is>
       </c>
       <c r="B295" t="n">
@@ -7193,22 +7193,22 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Saecred: A State-Aware, Over-the-Air Protocol Testing Approach for Discovering Parsing Bugs in SAE Handshake Implementations of COTS Wi-Fi Access Points.</t>
+          <t>IEEE_S&amp;P-Peek-a-Walk: Leaking Secrets via Page Walk Side Channels.</t>
         </is>
       </c>
       <c r="D295" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Stony Brook University</t>
+          <t>Berkeley College; University of California, Berkeley</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Cesare Tinelli</t>
+          <t>Yingchen Wang</t>
         </is>
       </c>
       <c r="B296" t="n">
@@ -7216,22 +7216,22 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Saecred: A State-Aware, Over-the-Air Protocol Testing Approach for Discovering Parsing Bugs in SAE Handshake Implementations of COTS Wi-Fi Access Points.</t>
+          <t>IEEE_S&amp;P-Peek-a-Walk: Leaking Secrets via Page Walk Side Channels.</t>
         </is>
       </c>
       <c r="D296" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>University of Iowa</t>
+          <t>Berkeley College; University of California, Berkeley</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Omar Chowdhury</t>
+          <t>Christopher W. Fletcher</t>
         </is>
       </c>
       <c r="B297" t="n">
@@ -7239,22 +7239,22 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Saecred: A State-Aware, Over-the-Air Protocol Testing Approach for Discovering Parsing Bugs in SAE Handshake Implementations of COTS Wi-Fi Access Points.</t>
+          <t>IEEE_S&amp;P-Peek-a-Walk: Leaking Secrets via Page Walk Side Channels.</t>
         </is>
       </c>
       <c r="D297" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Stony Brook University</t>
+          <t>Berkeley College; University of California, Berkeley</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Lina Pu</t>
+          <t>Daniel Genkin</t>
         </is>
       </c>
       <c r="B298" t="n">
@@ -7262,22 +7262,22 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Your Cable, My Antenna: Eavesdropping Serial Communication via Backscatter Signals.</t>
+          <t>IEEE_S&amp;P-Peek-a-Walk: Leaking Secrets via Page Walk Side Channels.</t>
         </is>
       </c>
       <c r="D298" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>University of Alabama</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Song Han 0002</t>
+          <t>David Kohlbrenner</t>
         </is>
       </c>
       <c r="B299" t="n">
@@ -7285,22 +7285,22 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Your Cable, My Antenna: Eavesdropping Serial Communication via Backscatter Signals.</t>
+          <t>IEEE_S&amp;P-Peek-a-Walk: Leaking Secrets via Page Walk Side Channels.</t>
         </is>
       </c>
       <c r="D299" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>University of Connecticut</t>
+          <t>University of Washington</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Hadjer Benkraouda</t>
+          <t>Riccardo Paccagnella</t>
         </is>
       </c>
       <c r="B300" t="n">
@@ -7308,22 +7308,22 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-You Can't Judge a Binary by Its Header: Data-Code Separation for Non-Standard ARM Binaries Using Pseudo Labels.</t>
+          <t>IEEE_S&amp;P-Peek-a-Walk: Leaking Secrets via Page Walk Side Channels.</t>
         </is>
       </c>
       <c r="D300" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>University of Illinois Urbana-Champaign</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Nirav Diwan</t>
+          <t>Daniel Genkin</t>
         </is>
       </c>
       <c r="B301" t="n">
@@ -7331,7 +7331,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-You Can't Judge a Binary by Its Header: Data-Code Separation for Non-Standard ARM Binaries Using Pseudo Labels.</t>
+          <t>IEEE_S&amp;P-SLAP: Data Speculation Attacks via Load Address Prediction on Apple Silicon.</t>
         </is>
       </c>
       <c r="D301" t="n">
@@ -7339,14 +7339,14 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>University of Illinois Urbana-Champaign</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Gang Wang 0011</t>
+          <t>Samy Amer</t>
         </is>
       </c>
       <c r="B302" t="n">
@@ -7354,22 +7354,22 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-You Can't Judge a Binary by Its Header: Data-Code Separation for Non-Standard ARM Binaries Using Pseudo Labels.</t>
+          <t>IEEE_S&amp;P-PQ-Hammer: End-to-End Key Recovery Attacks on Post-Quantum Cryptography Using Rowhammer.</t>
         </is>
       </c>
       <c r="D302" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>University of Illinois Urbana-Champaign</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Iria Giuffrida</t>
+          <t>Yingchen Wang</t>
         </is>
       </c>
       <c r="B303" t="n">
@@ -7377,22 +7377,22 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-"We can't Allow IoT Vendors to Pass off all Such Liability to the Consumer": Investigating the U.S. Legal Perspectives on Liability for IoT Product Security.</t>
+          <t>IEEE_S&amp;P-PQ-Hammer: End-to-End Key Recovery Attacks on Post-Quantum Cryptography Using Rowhammer.</t>
         </is>
       </c>
       <c r="D303" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>William &amp; Mary; Williams (United States)</t>
+          <t>Berkeley College; University of California, Berkeley</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Daniel Shin</t>
+          <t>Daniel Genkin</t>
         </is>
       </c>
       <c r="B304" t="n">
@@ -7400,22 +7400,22 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-"We can't Allow IoT Vendors to Pass off all Such Liability to the Consumer": Investigating the U.S. Legal Perspectives on Liability for IoT Product Security.</t>
+          <t>IEEE_S&amp;P-PQ-Hammer: End-to-End Key Recovery Attacks on Post-Quantum Cryptography Using Rowhammer.</t>
         </is>
       </c>
       <c r="D304" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>William &amp; Mary; Williams (United States)</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Ella Sullivan</t>
+          <t>Andrew Kwong</t>
         </is>
       </c>
       <c r="B305" t="n">
@@ -7423,22 +7423,22 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-"We can't Allow IoT Vendors to Pass off all Such Liability to the Consumer": Investigating the U.S. Legal Perspectives on Liability for IoT Product Security.</t>
+          <t>IEEE_S&amp;P-PQ-Hammer: End-to-End Key Recovery Attacks on Post-Quantum Cryptography Using Rowhammer.</t>
         </is>
       </c>
       <c r="D305" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>William &amp; Mary; Williams (United States)</t>
+          <t>University of North Carolina Health Care; University of North Carolina at Chapel Hill</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Raheem Beyah</t>
+          <t>Arkady Yerukhimovich</t>
         </is>
       </c>
       <c r="B306" t="n">
@@ -7446,22 +7446,22 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Firmrca: Towards Post-Fuzzing Analysis on ARM Embedded Firmware with Efficient Event-Based Fault Localization.</t>
+          <t>IEEE_S&amp;P-PQ-Hammer: End-to-End Key Recovery Attacks on Post-Quantum Cryptography Using Rowhammer.</t>
         </is>
       </c>
       <c r="D306" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>George Washington University</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Mayuri Sridhar</t>
+          <t>Inwhan Chun</t>
         </is>
       </c>
       <c r="B307" t="n">
@@ -7469,7 +7469,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-PAC-Private Algorithms.</t>
+          <t>IEEE_S&amp;P-Scheduled Disclosure: Turning Power into Timing Without Frequency Scaling.</t>
         </is>
       </c>
       <c r="D307" t="n">
@@ -7477,14 +7477,14 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>IIT@MIT</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Srinivas Devadas</t>
+          <t>Isabella Siu</t>
         </is>
       </c>
       <c r="B308" t="n">
@@ -7492,22 +7492,22 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-PAC-Private Algorithms.</t>
+          <t>IEEE_S&amp;P-Scheduled Disclosure: Turning Power into Timing Without Frequency Scaling.</t>
         </is>
       </c>
       <c r="D308" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>IIT@MIT</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Shlomi Hod</t>
+          <t>Riccardo Paccagnella</t>
         </is>
       </c>
       <c r="B309" t="n">
@@ -7515,22 +7515,22 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Differentially Private Release of Israel's National Registry of Live Births.</t>
+          <t>IEEE_S&amp;P-Scheduled Disclosure: Turning Power into Timing Without Frequency Scaling.</t>
         </is>
       </c>
       <c r="D309" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Boston University</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Ran Canetti</t>
+          <t>Cheng Gu</t>
         </is>
       </c>
       <c r="B310" t="n">
@@ -7538,22 +7538,22 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Differentially Private Release of Israel's National Registry of Live Births.</t>
+          <t>IEEE_S&amp;P-I know What You Sync: Covert and Side Channel Attacks on File Systems via syncfs.</t>
         </is>
       </c>
       <c r="D310" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Boston University</t>
+          <t>University of California, Riverside</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Alexander Viand</t>
+          <t>Yicheng Zhang 0004</t>
         </is>
       </c>
       <c r="B311" t="n">
@@ -7561,7 +7561,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-DPolicy: Managing Privacy Risks Across Multiple Releases with Differential Privacy.</t>
+          <t>IEEE_S&amp;P-I know What You Sync: Covert and Side Channel Attacks on File Systems via syncfs.</t>
         </is>
       </c>
       <c r="D311" t="n">
@@ -7569,14 +7569,14 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Intel (United States)</t>
+          <t>University of California, Riverside</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Chen Gong 0005</t>
+          <t>Muhammad Daniyal Pirwani Dar</t>
         </is>
       </c>
       <c r="B312" t="n">
@@ -7584,22 +7584,22 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-From Easy to Hard: Building a Shortcut for Differentially Private Image Synthesis.</t>
+          <t>IEEE_S&amp;P-Saecred: A State-Aware, Over-the-Air Protocol Testing Approach for Discovering Parsing Bugs in SAE Handshake Implementations of COTS Wi-Fi Access Points.</t>
         </is>
       </c>
       <c r="D312" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>University of Virginia</t>
+          <t>Stony Brook University</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Xiaochen Li</t>
+          <t>Robert Lorch</t>
         </is>
       </c>
       <c r="B313" t="n">
@@ -7607,22 +7607,22 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-From Easy to Hard: Building a Shortcut for Differentially Private Image Synthesis.</t>
+          <t>IEEE_S&amp;P-Saecred: A State-Aware, Over-the-Air Protocol Testing Approach for Discovering Parsing Bugs in SAE Handshake Implementations of COTS Wi-Fi Access Points.</t>
         </is>
       </c>
       <c r="D313" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>University of Virginia</t>
+          <t>University of Iowa</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Tianhao Wang 0001</t>
+          <t>Aliakbar Sadeghi</t>
         </is>
       </c>
       <c r="B314" t="n">
@@ -7630,22 +7630,22 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-From Easy to Hard: Building a Shortcut for Differentially Private Image Synthesis.</t>
+          <t>IEEE_S&amp;P-Saecred: A State-Aware, Over-the-Air Protocol Testing Approach for Discovering Parsing Bugs in SAE Handshake Implementations of COTS Wi-Fi Access Points.</t>
         </is>
       </c>
       <c r="D314" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>University of Virginia</t>
+          <t>Stony Brook University</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Emiliano De Cristofaro</t>
+          <t>Vincenzo Sorcigli</t>
         </is>
       </c>
       <c r="B315" t="n">
@@ -7653,22 +7653,22 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-The Inadequacy of Similarity-Based Privacy Metrics: Privacy Attacks Against "Truly Anonymous" Synthetic Datasets.</t>
+          <t>IEEE_S&amp;P-Saecred: A State-Aware, Over-the-Air Protocol Testing Approach for Discovering Parsing Bugs in SAE Handshake Implementations of COTS Wi-Fi Access Points.</t>
         </is>
       </c>
       <c r="D315" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>University of California, Riverside</t>
+          <t>Stony Brook University</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Arnabjyoti Kalita</t>
+          <t>Cesare Tinelli</t>
         </is>
       </c>
       <c r="B316" t="n">
@@ -7676,22 +7676,22 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Ceviche: Capability-Enhanced Secure Virtualization of Caches.</t>
+          <t>IEEE_S&amp;P-Saecred: A State-Aware, Over-the-Air Protocol Testing Approach for Discovering Parsing Bugs in SAE Handshake Implementations of COTS Wi-Fi Access Points.</t>
         </is>
       </c>
       <c r="D316" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>University of Virginia</t>
+          <t>University of Iowa</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Yilong Yang</t>
+          <t>Omar Chowdhury</t>
         </is>
       </c>
       <c r="B317" t="n">
@@ -7699,22 +7699,22 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Ceviche: Capability-Enhanced Secure Virtualization of Caches.</t>
+          <t>IEEE_S&amp;P-Saecred: A State-Aware, Over-the-Air Protocol Testing Approach for Discovering Parsing Bugs in SAE Handshake Implementations of COTS Wi-Fi Access Points.</t>
         </is>
       </c>
       <c r="D317" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>University of Virginia</t>
+          <t>Stony Brook University</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Ashish Venkat</t>
+          <t>Lina Pu</t>
         </is>
       </c>
       <c r="B318" t="n">
@@ -7722,22 +7722,22 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Ceviche: Capability-Enhanced Secure Virtualization of Caches.</t>
+          <t>IEEE_S&amp;P-Your Cable, My Antenna: Eavesdropping Serial Communication via Backscatter Signals.</t>
         </is>
       </c>
       <c r="D318" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>University of Virginia</t>
+          <t>University of Alabama</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Fan Sang</t>
+          <t>Song Han 0002</t>
         </is>
       </c>
       <c r="B319" t="n">
@@ -7745,22 +7745,22 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Portal: Fast and Secure Device Access with Arm CCA for Modern Arm Mobile System-on-Chips (SoCs).</t>
+          <t>IEEE_S&amp;P-Your Cable, My Antenna: Eavesdropping Serial Communication via Backscatter Signals.</t>
         </is>
       </c>
       <c r="D319" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>University of Connecticut</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Jaehyuk Lee</t>
+          <t>Hadjer Benkraouda</t>
         </is>
       </c>
       <c r="B320" t="n">
@@ -7768,22 +7768,22 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Portal: Fast and Secure Device Access with Arm CCA for Modern Arm Mobile System-on-Chips (SoCs).</t>
+          <t>IEEE_S&amp;P-You Can't Judge a Binary by Its Header: Data-Code Separation for Non-Standard ARM Binaries Using Pseudo Labels.</t>
         </is>
       </c>
       <c r="D320" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>University of Illinois Urbana-Champaign</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Xiaokuan Zhang</t>
+          <t>Nirav Diwan</t>
         </is>
       </c>
       <c r="B321" t="n">
@@ -7791,22 +7791,22 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Portal: Fast and Secure Device Access with Arm CCA for Modern Arm Mobile System-on-Chips (SoCs).</t>
+          <t>IEEE_S&amp;P-You Can't Judge a Binary by Its Header: Data-Code Separation for Non-Standard ARM Binaries Using Pseudo Labels.</t>
         </is>
       </c>
       <c r="D321" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>George Mason University</t>
+          <t>University of Illinois Urbana-Champaign</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Taesoo Kim</t>
+          <t>Gang Wang 0011</t>
         </is>
       </c>
       <c r="B322" t="n">
@@ -7814,22 +7814,22 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Portal: Fast and Secure Device Access with Arm CCA for Modern Arm Mobile System-on-Chips (SoCs).</t>
+          <t>IEEE_S&amp;P-You Can't Judge a Binary by Its Header: Data-Code Separation for Non-Standard ARM Binaries Using Pseudo Labels.</t>
         </is>
       </c>
       <c r="D322" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>University of Illinois Urbana-Champaign</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Shidong Pan</t>
+          <t>Iria Giuffrida</t>
         </is>
       </c>
       <c r="B323" t="n">
@@ -7837,7 +7837,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-A Big Step Forward? A User-Centric Examination of iOS App Privacy Report and Enhancements.</t>
+          <t>IEEE_S&amp;P-"We can't Allow IoT Vendors to Pass off all Such Liability to the Consumer": Investigating the U.S. Legal Perspectives on Liability for IoT Product Security.</t>
         </is>
       </c>
       <c r="D323" t="n">
@@ -7845,14 +7845,14 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Columbia University</t>
+          <t>William &amp; Mary; Williams (United States)</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Mona Wang</t>
+          <t>Daniel Shin</t>
         </is>
       </c>
       <c r="B324" t="n">
@@ -7860,22 +7860,22 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-WireWatch: Measuring the Security of Proprietary Network Encryption in the Global Android Ecosystem.</t>
+          <t>IEEE_S&amp;P-"We can't Allow IoT Vendors to Pass off all Such Liability to the Consumer": Investigating the U.S. Legal Perspectives on Liability for IoT Product Security.</t>
         </is>
       </c>
       <c r="D324" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>Princeton University</t>
+          <t>William &amp; Mary; Williams (United States)</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Prateek Mittal</t>
+          <t>Ella Sullivan</t>
         </is>
       </c>
       <c r="B325" t="n">
@@ -7883,22 +7883,22 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-WireWatch: Measuring the Security of Proprietary Network Encryption in the Global Android Ecosystem.</t>
+          <t>IEEE_S&amp;P-"We can't Allow IoT Vendors to Pass off all Such Liability to the Consumer": Investigating the U.S. Legal Perspectives on Liability for IoT Product Security.</t>
         </is>
       </c>
       <c r="D325" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Princeton University</t>
+          <t>William &amp; Mary; Williams (United States)</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Zhiqiang Lin 0001</t>
+          <t>Raheem Beyah</t>
         </is>
       </c>
       <c r="B326" t="n">
@@ -7906,22 +7906,22 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Code Speaks Louder: Exploring Security and Privacy Relevant Regional Variations in Mobile Applications.</t>
+          <t>IEEE_S&amp;P-Firmrca: Towards Post-Fuzzing Analysis on ARM Embedded Firmware with Efficient Event-Based Fault Localization.</t>
         </is>
       </c>
       <c r="D326" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>The Ohio State University</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Aafaq Sabir</t>
+          <t>Mayuri Sridhar</t>
         </is>
       </c>
       <c r="B327" t="n">
@@ -7929,7 +7929,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Analyzing Ad Prevalence, Characteristics, and Compliance in Alexa Skills.</t>
+          <t>IEEE_S&amp;P-PAC-Private Algorithms.</t>
         </is>
       </c>
       <c r="D327" t="n">
@@ -7937,14 +7937,14 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>North Carolina State University</t>
+          <t>IIT@MIT</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Dilawer Ahmed</t>
+          <t>Srinivas Devadas</t>
         </is>
       </c>
       <c r="B328" t="n">
@@ -7952,7 +7952,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Analyzing Ad Prevalence, Characteristics, and Compliance in Alexa Skills.</t>
+          <t>IEEE_S&amp;P-PAC-Private Algorithms.</t>
         </is>
       </c>
       <c r="D328" t="n">
@@ -7960,14 +7960,14 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>North Carolina State University</t>
+          <t>IIT@MIT</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Anupam Das 0001</t>
+          <t>Shlomi Hod</t>
         </is>
       </c>
       <c r="B329" t="n">
@@ -7975,22 +7975,22 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Analyzing Ad Prevalence, Characteristics, and Compliance in Alexa Skills.</t>
+          <t>IEEE_S&amp;P-Differentially Private Release of Israel's National Registry of Live Births.</t>
         </is>
       </c>
       <c r="D329" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>North Carolina State University</t>
+          <t>Boston University</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Ahmed Tanvir Mahdad</t>
+          <t>Ran Canetti</t>
         </is>
       </c>
       <c r="B330" t="n">
@@ -7998,7 +7998,7 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-BPSniff: Continuously Surveilling Private Blood Pressure Information in the Metaverse via Unrestricted Inbuilt Motion Sensors.</t>
+          <t>IEEE_S&amp;P-Differentially Private Release of Israel's National Registry of Live Births.</t>
         </is>
       </c>
       <c r="D330" t="n">
@@ -8006,14 +8006,14 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>Texas A&amp;M University</t>
+          <t>Boston University</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Yingying Chen 0001</t>
+          <t>Alexander Viand</t>
         </is>
       </c>
       <c r="B331" t="n">
@@ -8021,22 +8021,22 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-BPSniff: Continuously Surveilling Private Blood Pressure Information in the Metaverse via Unrestricted Inbuilt Motion Sensors.</t>
+          <t>IEEE_S&amp;P-DPolicy: Managing Privacy Risks Across Multiple Releases with Differential Privacy.</t>
         </is>
       </c>
       <c r="D331" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>Rutgers, The State University of New Jersey</t>
+          <t>Intel (United States)</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Nitesh Saxena</t>
+          <t>Chen Gong 0005</t>
         </is>
       </c>
       <c r="B332" t="n">
@@ -8044,22 +8044,22 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-BPSniff: Continuously Surveilling Private Blood Pressure Information in the Metaverse via Unrestricted Inbuilt Motion Sensors.</t>
+          <t>IEEE_S&amp;P-From Easy to Hard: Building a Shortcut for Differentially Private Image Synthesis.</t>
         </is>
       </c>
       <c r="D332" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>Texas A&amp;M University</t>
+          <t>University of Virginia</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Jonathan Protzenko</t>
+          <t>Xiaochen Li</t>
         </is>
       </c>
       <c r="B333" t="n">
@@ -8067,22 +8067,22 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-TreeKEM: A Modular Machine-Checked Symbolic Security Analysis of Group Key Agreement in Messaging Layer Security.</t>
+          <t>IEEE_S&amp;P-From Easy to Hard: Building a Shortcut for Differentially Private Image Synthesis.</t>
         </is>
       </c>
       <c r="D333" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>Microsoft (Germany)</t>
+          <t>University of Virginia</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Liron David</t>
+          <t>Tianhao Wang 0001</t>
         </is>
       </c>
       <c r="B334" t="n">
@@ -8090,22 +8090,22 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Extended Diffie-Hellman Encryption for Secure and Efficient Real-Time Beacon Notifications.</t>
+          <t>IEEE_S&amp;P-From Easy to Hard: Building a Shortcut for Differentially Private Image Synthesis.</t>
         </is>
       </c>
       <c r="D334" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>Google (United States)</t>
+          <t>University of Virginia</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Avinatan Hassidim</t>
+          <t>Emiliano De Cristofaro</t>
         </is>
       </c>
       <c r="B335" t="n">
@@ -8113,22 +8113,22 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Extended Diffie-Hellman Encryption for Secure and Efficient Real-Time Beacon Notifications.</t>
+          <t>IEEE_S&amp;P-The Inadequacy of Similarity-Based Privacy Metrics: Privacy Attacks Against "Truly Anonymous" Synthetic Datasets.</t>
         </is>
       </c>
       <c r="D335" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>Google (United States); Bar-Ilan University</t>
+          <t>University of California, Riverside</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>David Lazarov</t>
+          <t>Arnabjyoti Kalita</t>
         </is>
       </c>
       <c r="B336" t="n">
@@ -8136,22 +8136,22 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Extended Diffie-Hellman Encryption for Secure and Efficient Real-Time Beacon Notifications.</t>
+          <t>IEEE_S&amp;P-Ceviche: Capability-Enhanced Secure Virtualization of Caches.</t>
         </is>
       </c>
       <c r="D336" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>Google (United States)</t>
+          <t>University of Virginia</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Moti Yung</t>
+          <t>Yilong Yang</t>
         </is>
       </c>
       <c r="B337" t="n">
@@ -8159,22 +8159,22 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Extended Diffie-Hellman Encryption for Secure and Efficient Real-Time Beacon Notifications.</t>
+          <t>IEEE_S&amp;P-Ceviche: Capability-Enhanced Secure Virtualization of Caches.</t>
         </is>
       </c>
       <c r="D337" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>Google (United States)</t>
+          <t>University of Virginia</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Darya Kaviani</t>
+          <t>Alenkruth Krishnan Murali</t>
         </is>
       </c>
       <c r="B338" t="n">
@@ -8182,22 +8182,22 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Myco: Unlocking Polylogarithmic Accesses in Metadata-Private Messaging.</t>
+          <t>IEEE_S&amp;P-Ceviche: Capability-Enhanced Secure Virtualization of Caches.</t>
         </is>
       </c>
       <c r="D338" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>Berkeley College; University of California, Berkeley</t>
+          <t>University of Virginia</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Deevashwer Rathee</t>
+          <t>Ashish Venkat</t>
         </is>
       </c>
       <c r="B339" t="n">
@@ -8205,22 +8205,22 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Myco: Unlocking Polylogarithmic Accesses in Metadata-Private Messaging.</t>
+          <t>IEEE_S&amp;P-Ceviche: Capability-Enhanced Secure Virtualization of Caches.</t>
         </is>
       </c>
       <c r="D339" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>Berkeley College; University of California, Berkeley</t>
+          <t>University of Virginia</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Raluca Ada Popa</t>
+          <t>Fan Sang</t>
         </is>
       </c>
       <c r="B340" t="n">
@@ -8228,22 +8228,22 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Myco: Unlocking Polylogarithmic Accesses in Metadata-Private Messaging.</t>
+          <t>IEEE_S&amp;P-Portal: Fast and Secure Device Access with Arm CCA for Modern Arm Mobile System-on-Chips (SoCs).</t>
         </is>
       </c>
       <c r="D340" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>University of California, Berkeley; Berkeley College</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Quang Cao</t>
+          <t>Jaehyuk Lee</t>
         </is>
       </c>
       <c r="B341" t="n">
@@ -8251,22 +8251,22 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-TreePIR: Efficient Private Retrieval of Merkle Proofs via Tree Colorings with Fast Indexing and Zero Storage Overhead.</t>
+          <t>IEEE_S&amp;P-Portal: Fast and Secure Device Access with Arm CCA for Modern Arm Mobile System-on-Chips (SoCs).</t>
         </is>
       </c>
       <c r="D341" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>MIT University; RMIT University</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Son Hoang Dau</t>
+          <t>Xiaokuan Zhang</t>
         </is>
       </c>
       <c r="B342" t="n">
@@ -8274,22 +8274,22 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-TreePIR: Efficient Private Retrieval of Merkle Proofs via Tree Colorings with Fast Indexing and Zero Storage Overhead.</t>
+          <t>IEEE_S&amp;P-Portal: Fast and Secure Device Access with Arm CCA for Modern Arm Mobile System-on-Chips (SoCs).</t>
         </is>
       </c>
       <c r="D342" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>RMIT University; MIT University</t>
+          <t>George Mason University</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Rinaldo Gagiano</t>
+          <t>Taesoo Kim</t>
         </is>
       </c>
       <c r="B343" t="n">
@@ -8297,22 +8297,22 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-TreePIR: Efficient Private Retrieval of Merkle Proofs via Tree Colorings with Fast Indexing and Zero Storage Overhead.</t>
+          <t>IEEE_S&amp;P-Portal: Fast and Secure Device Access with Arm CCA for Modern Arm Mobile System-on-Chips (SoCs).</t>
         </is>
       </c>
       <c r="D343" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>RMIT University; MIT University</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>Xun Yi</t>
+          <t>Shidong Pan</t>
         </is>
       </c>
       <c r="B344" t="n">
@@ -8320,22 +8320,22 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-TreePIR: Efficient Private Retrieval of Merkle Proofs via Tree Colorings with Fast Indexing and Zero Storage Overhead.</t>
+          <t>IEEE_S&amp;P-A Big Step Forward? A User-Centric Examination of iOS App Privacy Report and Enhancements.</t>
         </is>
       </c>
       <c r="D344" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>RMIT University; MIT University</t>
+          <t>Columbia University</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Quang-Hung Luu</t>
+          <t>Mona Wang</t>
         </is>
       </c>
       <c r="B345" t="n">
@@ -8343,22 +8343,22 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-TreePIR: Efficient Private Retrieval of Merkle Proofs via Tree Colorings with Fast Indexing and Zero Storage Overhead.</t>
+          <t>IEEE_S&amp;P-WireWatch: Measuring the Security of Proprietary Network Encryption in the Global Android Ecosystem.</t>
         </is>
       </c>
       <c r="D345" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>MIT University; RMIT University</t>
+          <t>Princeton University</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Collins W. Munyendo</t>
+          <t>Prateek Mittal</t>
         </is>
       </c>
       <c r="B346" t="n">
@@ -8366,22 +8366,22 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-"You Have to Ignore the Dangers": User Perceptions of the Security and Privacy Benefits of WhatsApp Mods.</t>
+          <t>IEEE_S&amp;P-WireWatch: Measuring the Security of Proprietary Network Encryption in the Global Android Ecosystem.</t>
         </is>
       </c>
       <c r="D346" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>George Washington University</t>
+          <t>Princeton University</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Kentrell Owens</t>
+          <t>Jonathan R. Mayer</t>
         </is>
       </c>
       <c r="B347" t="n">
@@ -8389,22 +8389,22 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-"You Have to Ignore the Dangers": User Perceptions of the Security and Privacy Benefits of WhatsApp Mods.</t>
+          <t>IEEE_S&amp;P-WireWatch: Measuring the Security of Proprietary Network Encryption in the Global Android Ecosystem.</t>
         </is>
       </c>
       <c r="D347" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>University of Washington</t>
+          <t>Princeton University</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Adam J. Aviv</t>
+          <t>Zhiqiang Lin 0001</t>
         </is>
       </c>
       <c r="B348" t="n">
@@ -8412,22 +8412,22 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-"You Have to Ignore the Dangers": User Perceptions of the Security and Privacy Benefits of WhatsApp Mods.</t>
+          <t>IEEE_S&amp;P-Code Speaks Louder: Exploring Security and Privacy Relevant Regional Variations in Mobile Applications.</t>
         </is>
       </c>
       <c r="D348" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>George Washington University</t>
+          <t>The Ohio State University</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Tadayoshi Kohno</t>
+          <t>Aafaq Sabir</t>
         </is>
       </c>
       <c r="B349" t="n">
@@ -8435,22 +8435,22 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-"You Have to Ignore the Dangers": User Perceptions of the Security and Privacy Benefits of WhatsApp Mods.</t>
+          <t>IEEE_S&amp;P-Analyzing Ad Prevalence, Characteristics, and Compliance in Alexa Skills.</t>
         </is>
       </c>
       <c r="D349" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>University of Washington</t>
+          <t>North Carolina State University</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Franziska Roesner</t>
+          <t>Dilawer Ahmed</t>
         </is>
       </c>
       <c r="B350" t="n">
@@ -8458,22 +8458,22 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-"You Have to Ignore the Dangers": User Perceptions of the Security and Privacy Benefits of WhatsApp Mods.</t>
+          <t>IEEE_S&amp;P-Analyzing Ad Prevalence, Characteristics, and Compliance in Alexa Skills.</t>
         </is>
       </c>
       <c r="D350" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>University of Washington</t>
+          <t>North Carolina State University</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Jung-Woo Chang</t>
+          <t>Anupam Das 0001</t>
         </is>
       </c>
       <c r="B351" t="n">
@@ -8481,22 +8481,22 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-EveGuard: Defeating Vibration-based Side-Channel Eavesdropping with Audio Adversarial Perturbations.</t>
+          <t>IEEE_S&amp;P-Analyzing Ad Prevalence, Characteristics, and Compliance in Alexa Skills.</t>
         </is>
       </c>
       <c r="D351" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>University of California, San Diego</t>
+          <t>North Carolina State University</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Ke Sun 0012</t>
+          <t>Ahmed Tanvir Mahdad</t>
         </is>
       </c>
       <c r="B352" t="n">
@@ -8504,7 +8504,7 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-EveGuard: Defeating Vibration-based Side-Channel Eavesdropping with Audio Adversarial Perturbations.</t>
+          <t>IEEE_S&amp;P-BPSniff: Continuously Surveilling Private Blood Pressure Information in the Metaverse via Unrestricted Inbuilt Motion Sensors.</t>
         </is>
       </c>
       <c r="D352" t="n">
@@ -8512,14 +8512,14 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>University of California, San Diego</t>
+          <t>Texas A&amp;M University</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>David Xia</t>
+          <t>Yingying Chen 0001</t>
         </is>
       </c>
       <c r="B353" t="n">
@@ -8527,22 +8527,22 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-EveGuard: Defeating Vibration-based Side-Channel Eavesdropping with Audio Adversarial Perturbations.</t>
+          <t>IEEE_S&amp;P-BPSniff: Continuously Surveilling Private Blood Pressure Information in the Metaverse via Unrestricted Inbuilt Motion Sensors.</t>
         </is>
       </c>
       <c r="D353" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>University of Illinois Urbana-Champaign</t>
+          <t>Rutgers, The State University of New Jersey</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>Xinyu Zhang 0003</t>
+          <t>Nitesh Saxena</t>
         </is>
       </c>
       <c r="B354" t="n">
@@ -8550,22 +8550,22 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-EveGuard: Defeating Vibration-based Side-Channel Eavesdropping with Audio Adversarial Perturbations.</t>
+          <t>IEEE_S&amp;P-BPSniff: Continuously Surveilling Private Blood Pressure Information in the Metaverse via Unrestricted Inbuilt Motion Sensors.</t>
         </is>
       </c>
       <c r="D354" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>University of California, San Diego</t>
+          <t>Texas A&amp;M University</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Farinaz Koushanfar</t>
+          <t>Jonathan Protzenko</t>
         </is>
       </c>
       <c r="B355" t="n">
@@ -8573,22 +8573,22 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-EveGuard: Defeating Vibration-based Side-Channel Eavesdropping with Audio Adversarial Perturbations.</t>
+          <t>IEEE_S&amp;P-TreeKEM: A Modular Machine-Checked Symbolic Security Analysis of Group Key Agreement in Messaging Layer Security.</t>
         </is>
       </c>
       <c r="D355" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>University of California, San Diego</t>
+          <t>Microsoft (Germany)</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Zhambyl Shaikhanov</t>
+          <t>Liron David</t>
         </is>
       </c>
       <c r="B356" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Spoofing Eavesdroppers with Audio Misinformation.</t>
+          <t>IEEE_S&amp;P-Extended Diffie-Hellman Encryption for Secure and Efficient Real-Time Beacon Notifications.</t>
         </is>
       </c>
       <c r="D356" t="n">
@@ -8604,14 +8604,14 @@
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>University of Maryland, College Park</t>
+          <t>Google (United States)</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Mahmoud Al-Madi</t>
+          <t>Avinatan Hassidim</t>
         </is>
       </c>
       <c r="B357" t="n">
@@ -8619,22 +8619,22 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Spoofing Eavesdroppers with Audio Misinformation.</t>
+          <t>IEEE_S&amp;P-Extended Diffie-Hellman Encryption for Secure and Efficient Real-Time Beacon Notifications.</t>
         </is>
       </c>
       <c r="D357" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>Rice University</t>
+          <t>Google (United States); Bar-Ilan University</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>Chun-Chieh Chang</t>
+          <t>David Lazarov</t>
         </is>
       </c>
       <c r="B358" t="n">
@@ -8642,7 +8642,7 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Spoofing Eavesdroppers with Audio Misinformation.</t>
+          <t>IEEE_S&amp;P-Extended Diffie-Hellman Encryption for Secure and Efficient Real-Time Beacon Notifications.</t>
         </is>
       </c>
       <c r="D358" t="n">
@@ -8650,14 +8650,14 @@
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>Los Alamos National Laboratory</t>
+          <t>Google (United States)</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>Sadhvikas Addamane</t>
+          <t>Moti Yung</t>
         </is>
       </c>
       <c r="B359" t="n">
@@ -8665,22 +8665,22 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Spoofing Eavesdroppers with Audio Misinformation.</t>
+          <t>IEEE_S&amp;P-Extended Diffie-Hellman Encryption for Secure and Efficient Real-Time Beacon Notifications.</t>
         </is>
       </c>
       <c r="D359" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>Sandia National Laboratories</t>
+          <t>Google (United States)</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Daniel M. Mittleman</t>
+          <t>Darya Kaviani</t>
         </is>
       </c>
       <c r="B360" t="n">
@@ -8688,22 +8688,22 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Spoofing Eavesdroppers with Audio Misinformation.</t>
+          <t>IEEE_S&amp;P-Myco: Unlocking Polylogarithmic Accesses in Metadata-Private Messaging.</t>
         </is>
       </c>
       <c r="D360" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>John Brown University</t>
+          <t>Berkeley College; University of California, Berkeley</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Edward W. Knightly</t>
+          <t>Deevashwer Rathee</t>
         </is>
       </c>
       <c r="B361" t="n">
@@ -8711,22 +8711,22 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Spoofing Eavesdroppers with Audio Misinformation.</t>
+          <t>IEEE_S&amp;P-Myco: Unlocking Polylogarithmic Accesses in Metadata-Private Messaging.</t>
         </is>
       </c>
       <c r="D361" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>Rice University</t>
+          <t>Berkeley College; University of California, Berkeley</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Shengzhi Zhang</t>
+          <t>Raluca Ada Popa</t>
         </is>
       </c>
       <c r="B362" t="n">
@@ -8734,22 +8734,22 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-EvilHarmony: Stealthy Adversarial Attacks Against Black-Box Speech Recognition Systems.</t>
+          <t>IEEE_S&amp;P-Myco: Unlocking Polylogarithmic Accesses in Metadata-Private Messaging.</t>
         </is>
       </c>
       <c r="D362" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>Boston University; Metropolitan College of New York</t>
+          <t>University of California, Berkeley; Berkeley College</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Dun Liu</t>
+          <t>Quang Cao</t>
         </is>
       </c>
       <c r="B363" t="n">
@@ -8757,22 +8757,22 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-EvilHarmony: Stealthy Adversarial Attacks Against Black-Box Speech Recognition Systems.</t>
+          <t>IEEE_S&amp;P-TreePIR: Efficient Private Retrieval of Merkle Proofs via Tree Colorings with Fast Indexing and Zero Storage Overhead.</t>
         </is>
       </c>
       <c r="D363" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>Boston University; Metropolitan College of New York</t>
+          <t>MIT University; RMIT University</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Ruoyu Song 0001</t>
+          <t>Son Hoang Dau</t>
         </is>
       </c>
       <c r="B364" t="n">
@@ -8780,7 +8780,7 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Investigating Physical Latency Attacks Against Camera-Based Perception.</t>
+          <t>IEEE_S&amp;P-TreePIR: Efficient Private Retrieval of Merkle Proofs via Tree Colorings with Fast Indexing and Zero Storage Overhead.</t>
         </is>
       </c>
       <c r="D364" t="n">
@@ -8788,14 +8788,14 @@
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>Purdue University West Lafayette</t>
+          <t>RMIT University; MIT University</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>Chenyi Wang 0005</t>
+          <t>Rinaldo Gagiano</t>
         </is>
       </c>
       <c r="B365" t="n">
@@ -8803,7 +8803,7 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Investigating Physical Latency Attacks Against Camera-Based Perception.</t>
+          <t>IEEE_S&amp;P-TreePIR: Efficient Private Retrieval of Merkle Proofs via Tree Colorings with Fast Indexing and Zero Storage Overhead.</t>
         </is>
       </c>
       <c r="D365" t="n">
@@ -8811,14 +8811,14 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>University of Arizona</t>
+          <t>RMIT University; MIT University</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Yuxia Zhan</t>
+          <t>Duy Huynh</t>
         </is>
       </c>
       <c r="B366" t="n">
@@ -8826,7 +8826,7 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Investigating Physical Latency Attacks Against Camera-Based Perception.</t>
+          <t>IEEE_S&amp;P-TreePIR: Efficient Private Retrieval of Merkle Proofs via Tree Colorings with Fast Indexing and Zero Storage Overhead.</t>
         </is>
       </c>
       <c r="D366" t="n">
@@ -8834,14 +8834,14 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>New York University</t>
+          <t>MIT University; RMIT University</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>Ming Li 0003</t>
+          <t>Xun Yi</t>
         </is>
       </c>
       <c r="B367" t="n">
@@ -8849,22 +8849,22 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Investigating Physical Latency Attacks Against Camera-Based Perception.</t>
+          <t>IEEE_S&amp;P-TreePIR: Efficient Private Retrieval of Merkle Proofs via Tree Colorings with Fast Indexing and Zero Storage Overhead.</t>
         </is>
       </c>
       <c r="D367" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>University of Arizona</t>
+          <t>RMIT University; MIT University</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>Jonathan Petit</t>
+          <t>Quang-Hung Luu</t>
         </is>
       </c>
       <c r="B368" t="n">
@@ -8872,22 +8872,22 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Investigating Physical Latency Attacks Against Camera-Based Perception.</t>
+          <t>IEEE_S&amp;P-TreePIR: Efficient Private Retrieval of Merkle Proofs via Tree Colorings with Fast Indexing and Zero Storage Overhead.</t>
         </is>
       </c>
       <c r="D368" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>Qualcomm (United Kingdom)</t>
+          <t>MIT University; RMIT University</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Z. Berkay Celik</t>
+          <t>Collins W. Munyendo</t>
         </is>
       </c>
       <c r="B369" t="n">
@@ -8895,22 +8895,22 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Investigating Physical Latency Attacks Against Camera-Based Perception.</t>
+          <t>IEEE_S&amp;P-"You Have to Ignore the Dangers": User Perceptions of the Security and Privacy Benefits of WhatsApp Mods.</t>
         </is>
       </c>
       <c r="D369" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>Purdue University West Lafayette</t>
+          <t>George Washington University</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>Trisha Datta</t>
+          <t>Kentrell Owens</t>
         </is>
       </c>
       <c r="B370" t="n">
@@ -8918,22 +8918,22 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-VerITAS: Verifying Image Transformations at Scale.</t>
+          <t>IEEE_S&amp;P-"You Have to Ignore the Dangers": User Perceptions of the Security and Privacy Benefits of WhatsApp Mods.</t>
         </is>
       </c>
       <c r="D370" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>Stanford University</t>
+          <t>University of Washington</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>Binyi Chen</t>
+          <t>Shaoqi Wang</t>
         </is>
       </c>
       <c r="B371" t="n">
@@ -8941,22 +8941,22 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-VerITAS: Verifying Image Transformations at Scale.</t>
+          <t>IEEE_S&amp;P-"You Have to Ignore the Dangers": User Perceptions of the Security and Privacy Benefits of WhatsApp Mods.</t>
         </is>
       </c>
       <c r="D371" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>Stanford University</t>
+          <t>University of Washington</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Dan Boneh</t>
+          <t>Adam J. Aviv</t>
         </is>
       </c>
       <c r="B372" t="n">
@@ -8964,22 +8964,22 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-VerITAS: Verifying Image Transformations at Scale.</t>
+          <t>IEEE_S&amp;P-"You Have to Ignore the Dangers": User Perceptions of the Security and Privacy Benefits of WhatsApp Mods.</t>
         </is>
       </c>
       <c r="D372" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>Stanford University</t>
+          <t>George Washington University</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>Long Huang</t>
+          <t>Tadayoshi Kohno</t>
         </is>
       </c>
       <c r="B373" t="n">
@@ -8987,36 +8987,680 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Sniffing Location Privacy of Video Conference Users Using Free Audio Channels.</t>
+          <t>IEEE_S&amp;P-"You Have to Ignore the Dangers": User Perceptions of the Security and Privacy Benefits of WhatsApp Mods.</t>
         </is>
       </c>
       <c r="D373" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>Southern Methodist University</t>
+          <t>University of Washington</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
+          <t>Franziska Roesner</t>
+        </is>
+      </c>
+      <c r="B374" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>IEEE_S&amp;P-"You Have to Ignore the Dangers": User Perceptions of the Security and Privacy Benefits of WhatsApp Mods.</t>
+        </is>
+      </c>
+      <c r="D374" t="n">
+        <v>6</v>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>University of Washington</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>Jung-Woo Chang</t>
+        </is>
+      </c>
+      <c r="B375" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>IEEE_S&amp;P-EveGuard: Defeating Vibration-based Side-Channel Eavesdropping with Audio Adversarial Perturbations.</t>
+        </is>
+      </c>
+      <c r="D375" t="n">
+        <v>0</v>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>University of California, San Diego</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>Ke Sun 0012</t>
+        </is>
+      </c>
+      <c r="B376" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>IEEE_S&amp;P-EveGuard: Defeating Vibration-based Side-Channel Eavesdropping with Audio Adversarial Perturbations.</t>
+        </is>
+      </c>
+      <c r="D376" t="n">
+        <v>1</v>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>University of California, San Diego</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>David Xia</t>
+        </is>
+      </c>
+      <c r="B377" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>IEEE_S&amp;P-EveGuard: Defeating Vibration-based Side-Channel Eavesdropping with Audio Adversarial Perturbations.</t>
+        </is>
+      </c>
+      <c r="D377" t="n">
+        <v>2</v>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>University of Illinois Urbana-Champaign</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>Xinyu Zhang 0003</t>
+        </is>
+      </c>
+      <c r="B378" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>IEEE_S&amp;P-EveGuard: Defeating Vibration-based Side-Channel Eavesdropping with Audio Adversarial Perturbations.</t>
+        </is>
+      </c>
+      <c r="D378" t="n">
+        <v>3</v>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>University of California, San Diego</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>Farinaz Koushanfar</t>
+        </is>
+      </c>
+      <c r="B379" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>IEEE_S&amp;P-EveGuard: Defeating Vibration-based Side-Channel Eavesdropping with Audio Adversarial Perturbations.</t>
+        </is>
+      </c>
+      <c r="D379" t="n">
+        <v>4</v>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>University of California, San Diego</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>Zhambyl Shaikhanov</t>
+        </is>
+      </c>
+      <c r="B380" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>IEEE_S&amp;P-Spoofing Eavesdroppers with Audio Misinformation.</t>
+        </is>
+      </c>
+      <c r="D380" t="n">
+        <v>0</v>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>University of Maryland, College Park</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>Mahmoud Al-Madi</t>
+        </is>
+      </c>
+      <c r="B381" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>IEEE_S&amp;P-Spoofing Eavesdroppers with Audio Misinformation.</t>
+        </is>
+      </c>
+      <c r="D381" t="n">
+        <v>1</v>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>Rice University</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>Hou-Tong Chen</t>
+        </is>
+      </c>
+      <c r="B382" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>IEEE_S&amp;P-Spoofing Eavesdroppers with Audio Misinformation.</t>
+        </is>
+      </c>
+      <c r="D382" t="n">
+        <v>2</v>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>Los Alamos National Laboratory</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>Chun-Chieh Chang</t>
+        </is>
+      </c>
+      <c r="B383" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>IEEE_S&amp;P-Spoofing Eavesdroppers with Audio Misinformation.</t>
+        </is>
+      </c>
+      <c r="D383" t="n">
+        <v>3</v>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>Los Alamos National Laboratory</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>Sadhvikas Addamane</t>
+        </is>
+      </c>
+      <c r="B384" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>IEEE_S&amp;P-Spoofing Eavesdroppers with Audio Misinformation.</t>
+        </is>
+      </c>
+      <c r="D384" t="n">
+        <v>4</v>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>Sandia National Laboratories</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>Daniel M. Mittleman</t>
+        </is>
+      </c>
+      <c r="B385" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>IEEE_S&amp;P-Spoofing Eavesdroppers with Audio Misinformation.</t>
+        </is>
+      </c>
+      <c r="D385" t="n">
+        <v>5</v>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>John Brown University</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>Edward W. Knightly</t>
+        </is>
+      </c>
+      <c r="B386" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>IEEE_S&amp;P-Spoofing Eavesdroppers with Audio Misinformation.</t>
+        </is>
+      </c>
+      <c r="D386" t="n">
+        <v>6</v>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>Rice University</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>Shengzhi Zhang</t>
+        </is>
+      </c>
+      <c r="B387" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>IEEE_S&amp;P-EvilHarmony: Stealthy Adversarial Attacks Against Black-Box Speech Recognition Systems.</t>
+        </is>
+      </c>
+      <c r="D387" t="n">
+        <v>5</v>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>Boston University; Metropolitan College of New York</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>Dun Liu</t>
+        </is>
+      </c>
+      <c r="B388" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>IEEE_S&amp;P-EvilHarmony: Stealthy Adversarial Attacks Against Black-Box Speech Recognition Systems.</t>
+        </is>
+      </c>
+      <c r="D388" t="n">
+        <v>7</v>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>Boston University; Metropolitan College of New York</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>Raymond Muller</t>
+        </is>
+      </c>
+      <c r="B389" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>IEEE_S&amp;P-Investigating Physical Latency Attacks Against Camera-Based Perception.</t>
+        </is>
+      </c>
+      <c r="D389" t="n">
+        <v>0</v>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>Purdue University West Lafayette</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>Ruoyu Song 0001</t>
+        </is>
+      </c>
+      <c r="B390" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>IEEE_S&amp;P-Investigating Physical Latency Attacks Against Camera-Based Perception.</t>
+        </is>
+      </c>
+      <c r="D390" t="n">
+        <v>1</v>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>Purdue University West Lafayette</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>Chenyi Wang 0005</t>
+        </is>
+      </c>
+      <c r="B391" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>IEEE_S&amp;P-Investigating Physical Latency Attacks Against Camera-Based Perception.</t>
+        </is>
+      </c>
+      <c r="D391" t="n">
+        <v>2</v>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>University of Arizona</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>Yuxia Zhan</t>
+        </is>
+      </c>
+      <c r="B392" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>IEEE_S&amp;P-Investigating Physical Latency Attacks Against Camera-Based Perception.</t>
+        </is>
+      </c>
+      <c r="D392" t="n">
+        <v>3</v>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>New York University</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>Jean-Philippe Monteuuis</t>
+        </is>
+      </c>
+      <c r="B393" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>IEEE_S&amp;P-Investigating Physical Latency Attacks Against Camera-Based Perception.</t>
+        </is>
+      </c>
+      <c r="D393" t="n">
+        <v>4</v>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>Qualcomm (United Kingdom)</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>Ming Li 0003</t>
+        </is>
+      </c>
+      <c r="B394" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>IEEE_S&amp;P-Investigating Physical Latency Attacks Against Camera-Based Perception.</t>
+        </is>
+      </c>
+      <c r="D394" t="n">
+        <v>6</v>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>University of Arizona</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>Ryan M. Gerdes</t>
+        </is>
+      </c>
+      <c r="B395" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>IEEE_S&amp;P-Investigating Physical Latency Attacks Against Camera-Based Perception.</t>
+        </is>
+      </c>
+      <c r="D395" t="n">
+        <v>7</v>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>Virginia Tech</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>Jonathan Petit</t>
+        </is>
+      </c>
+      <c r="B396" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>IEEE_S&amp;P-Investigating Physical Latency Attacks Against Camera-Based Perception.</t>
+        </is>
+      </c>
+      <c r="D396" t="n">
+        <v>8</v>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>Qualcomm (United Kingdom)</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>Z. Berkay Celik</t>
+        </is>
+      </c>
+      <c r="B397" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>IEEE_S&amp;P-Investigating Physical Latency Attacks Against Camera-Based Perception.</t>
+        </is>
+      </c>
+      <c r="D397" t="n">
+        <v>9</v>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>Purdue University West Lafayette</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>Trisha Datta</t>
+        </is>
+      </c>
+      <c r="B398" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>IEEE_S&amp;P-VerITAS: Verifying Image Transformations at Scale.</t>
+        </is>
+      </c>
+      <c r="D398" t="n">
+        <v>0</v>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>Stanford University</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>Binyi Chen</t>
+        </is>
+      </c>
+      <c r="B399" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>IEEE_S&amp;P-VerITAS: Verifying Image Transformations at Scale.</t>
+        </is>
+      </c>
+      <c r="D399" t="n">
+        <v>1</v>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>Stanford University</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>Dan Boneh</t>
+        </is>
+      </c>
+      <c r="B400" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>IEEE_S&amp;P-VerITAS: Verifying Image Transformations at Scale.</t>
+        </is>
+      </c>
+      <c r="D400" t="n">
+        <v>2</v>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>Stanford University</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>Long Huang</t>
+        </is>
+      </c>
+      <c r="B401" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>IEEE_S&amp;P-Sniffing Location Privacy of Video Conference Users Using Free Audio Channels.</t>
+        </is>
+      </c>
+      <c r="D401" t="n">
+        <v>0</v>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>Southern Methodist University</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
           <t>Chen Wang 0009</t>
         </is>
       </c>
-      <c r="B374" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C374" t="inlineStr">
+      <c r="B402" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C402" t="inlineStr">
         <is>
           <t>IEEE_S&amp;P-Sniffing Location Privacy of Video Conference Users Using Free Audio Channels.</t>
         </is>
       </c>
-      <c r="D374" t="n">
+      <c r="D402" t="n">
         <v>1</v>
       </c>
-      <c r="E374" t="inlineStr">
+      <c r="E402" t="inlineStr">
         <is>
           <t>Southern Methodist University</t>
         </is>

--- a/Security-data/data/output/ieee_sp_2025_us_institutions.xlsx
+++ b/Security-data/data/output/ieee_sp_2025_us_institutions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E402"/>
+  <dimension ref="A1:E408"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -607,7 +607,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ariana Mirian</t>
+          <t>Grant Ho</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -619,18 +619,18 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>UC San Diego</t>
+          <t>University of Chicago; UC San Diego</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Elisa Luo</t>
+          <t>Ariana Mirian</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -653,7 +653,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Stefan Savage</t>
+          <t>Elisa Luo</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -676,7 +676,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Geoffrey M. Voelker</t>
+          <t>Stefan Savage</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -699,7 +699,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Runze Zhang</t>
+          <t>Geoffrey M. Voelker</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -707,22 +707,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Identifying Incoherent Search Sessions: Search Click Fraud Remediation Under Real-World Constraints.</t>
+          <t>IEEE_S&amp;P-Understanding the Efficacy of Phishing Training in Practice.</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>UC San Diego</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Ranjita Pai Sridhar</t>
+          <t>Runze Zhang</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -734,18 +734,18 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Microsoft Corporation</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Mingxuan Yao</t>
+          <t>Ranjita Pai Sridhar</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -757,18 +757,18 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>Microsoft Corporation</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Zheng Yang</t>
+          <t>Mingxuan Yao</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>David Oygenblik</t>
+          <t>Zheng Yang</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Haichuan Xu</t>
+          <t>David Oygenblik</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -837,7 +837,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Vacha Dave</t>
+          <t>Haichuan Xu</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -849,18 +849,18 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Microsoft Corporation</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Cormac Herley</t>
+          <t>Vacha Dave</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -883,7 +883,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Paul England</t>
+          <t>Cormac Herley</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Brendan Saltaformaggio</t>
+          <t>Paul England</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -918,18 +918,18 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>Microsoft Corporation</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Jason Liu 0002</t>
+          <t>Brendan Saltaformaggio</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -937,22 +937,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-What We Talk About When We Talk About Logs: Understanding the Effects of Dataset Quality on Endpoint Threat Detection Research.</t>
+          <t>IEEE_S&amp;P-Identifying Incoherent Search Sessions: Search Click Fraud Remediation Under Real-World Constraints.</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Department of Computer Science, University of Illinois at Urbana-Champaign, Urbana, Illinois, USA</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Muhammad Adil Inam</t>
+          <t>Jason Liu 0002</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -964,7 +964,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -975,7 +975,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Akul Goyal</t>
+          <t>Muhammad Adil Inam</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Andy Riddle</t>
+          <t>Akul Goyal</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Kim Westfall</t>
+          <t>Andy Riddle</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1033,7 +1033,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Adam Bates 0001</t>
+          <t>Kim Westfall</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Darya Kaviani</t>
+          <t>Adam Bates 0001</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1075,22 +1075,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Ringtail: Practical Two-Round Threshold Signatures from Learning with Errors.</t>
+          <t>IEEE_S&amp;P-What We Talk About When We Talk About Logs: Understanding the Effects of Dataset Quality on Endpoint Threat Detection Research.</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>UC Berkeley, USA</t>
+          <t>Department of Computer Science, University of Illinois at Urbana-Champaign, Urbana, Illinois, USA</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Akira Takahashi 0002</t>
+          <t>Darya Kaviani</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -1102,18 +1102,18 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>JPMorgan AI Research &amp; AlgoCRYPT CoE, USA</t>
+          <t>UC Berkeley, USA</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Ashish Kashinath</t>
+          <t>Akira Takahashi 0002</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1121,22 +1121,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Groundhog: A Restart-Based Systems Framework for Increasing Availability in Threshold Cryptosystems.</t>
+          <t>IEEE_S&amp;P-Ringtail: Practical Two-Round Threshold Signatures from Learning with Errors.</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>University of Illinois at Urbana-Champaign</t>
+          <t>JPMorgan AI Research &amp; AlgoCRYPT CoE, USA</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Disha Agarwala</t>
+          <t>Ashish Kashinath</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gabriel Kulp</t>
+          <t>Disha Agarwala</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1171,18 +1171,18 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Oregon State University</t>
+          <t>University of Illinois at Urbana-Champaign</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sourav Das</t>
+          <t>Gabriel Kulp</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -1194,18 +1194,18 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>University of Illinois at Urbana-Champaign</t>
+          <t>Oregon State University</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sibin Mohan</t>
+          <t>Sourav Das</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1217,18 +1217,18 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>The George Washington University</t>
+          <t>University of Illinois at Urbana-Champaign</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Chuanqi Xu</t>
+          <t>Sibin Mohan</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -1236,22 +1236,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Security Attacks Abusing Pulse-level Quantum Circuits.</t>
+          <t>IEEE_S&amp;P-Groundhog: A Restart-Based Systems Framework for Increasing Availability in Threshold Cryptosystems.</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Dept. of Electrical &amp; Computer Engineering, Yale University, New Haven, CT, USA</t>
+          <t>The George Washington University</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Jakub Szefer</t>
+          <t>Chuanqi Xu</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1263,7 +1263,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Yibin Yang 0001</t>
+          <t>Jakub Szefer</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -1282,22 +1282,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Gold OPRF: Post-Quantum Oblivious Power-Residue PRF.</t>
+          <t>IEEE_S&amp;P-Security Attacks Abusing Pulse-level Quantum Circuits.</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology, USA</t>
+          <t>Dept. of Electrical &amp; Computer Engineering, Yale University, New Haven, CT, USA</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Fabrice Benhamouda</t>
+          <t>Yibin Yang 0001</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -1309,18 +1309,18 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Amazon Web Services, USA</t>
+          <t>Georgia Institute of Technology, USA</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Shai Halevi</t>
+          <t>Fabrice Benhamouda</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -1332,7 +1332,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Hugo Krawczyk</t>
+          <t>Shai Halevi</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -1355,7 +1355,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Tal Rabin</t>
+          <t>Hugo Krawczyk</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -1378,7 +1378,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Emily Wenger</t>
+          <t>Tal Rabin</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -1397,22 +1397,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Benchmarking Attacks on Learning with Errors.</t>
+          <t>IEEE_S&amp;P-Gold OPRF: Post-Quantum Oblivious Power-Residue PRF.</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Meta AI, USA; Duke University, USA</t>
+          <t>Amazon Web Services, USA</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Eshika Saxena</t>
+          <t>Emily Wenger</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -1424,18 +1424,18 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Meta AI, USA</t>
+          <t>Meta AI, USA; Duke University, USA</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Mohamed Malhou</t>
+          <t>Eshika Saxena</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -1447,18 +1447,18 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Meta AI, USA; Sorbonne Universit, France</t>
+          <t>Meta AI, USA</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Ellie Thieu</t>
+          <t>Mohamed Malhou</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -1470,18 +1470,18 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>University of Wisconsin-Madison, USA</t>
+          <t>Meta AI, USA; Sorbonne Universit, France</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Kristin E. Lauter</t>
+          <t>Ellie Thieu</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -1493,18 +1493,18 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Meta AI, USA</t>
+          <t>University of Wisconsin-Madison, USA</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mutahar Ali</t>
+          <t>Kristin E. Lauter</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -1512,22 +1512,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Understanding Users' Security and Privacy Concerns and Attitudes Towards Conversational AI Platforms.</t>
+          <t>IEEE_S&amp;P-Benchmarking Attacks on Learning with Errors.</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>University of California, Irvine</t>
+          <t>Meta AI, USA</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Arjun Arunasalam</t>
+          <t>Mutahar Ali</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -1539,18 +1539,18 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Purdue University</t>
+          <t>University of California, Irvine</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Habiba Farrukh</t>
+          <t>Arjun Arunasalam</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -1562,18 +1562,18 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>University of California, Irvine</t>
+          <t>Purdue University</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Ning Yu 0006</t>
+          <t>Habiba Farrukh</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Fuzz-Testing Meets LLM-Based Agents: An Automated and Efficient Framework for Jailbreaking Text-to-Image Generation Models.</t>
+          <t>IEEE_S&amp;P-Understanding Users' Security and Privacy Concerns and Attitudes Towards Conversational AI Platforms.</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -1589,14 +1589,14 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Netflix (United States)</t>
+          <t>University of California, Irvine</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Ashish Hooda</t>
+          <t>Ning Yu 0006</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Fun-tuning: Characterizing the Vulnerability of Proprietary LLMs to Optimization-Based Prompt Injection Attacks via the Fine-Tuning Interface.</t>
+          <t>IEEE_S&amp;P-Fuzz-Testing Meets LLM-Based Agents: An Automated and Efficient Framework for Jailbreaking Text-to-Image Generation Models.</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -1612,14 +1612,14 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>University of Wisconsin–Madison</t>
+          <t>Netflix (United States)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Syed Irfan Ali Meerza</t>
+          <t>Ashish Hooda</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -1627,22 +1627,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Harmonycloak: Making Music Unlearnable for Generative AI.</t>
+          <t>IEEE_S&amp;P-Fun-tuning: Characterizing the Vulnerability of Proprietary LLMs to Optimization-Based Prompt Injection Attacks via the Fine-Tuning Interface.</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>University of Tennessee at Knoxville</t>
+          <t>University of Wisconsin–Madison</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Jian Liu 0001</t>
+          <t>Syed Irfan Ali Meerza</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -1654,7 +1654,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Jessy Ayala</t>
+          <t>Jian Liu 0001</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -1673,22 +1673,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-A Deep Dive into How Open-Source Project Maintainers Review and Resolve Bug Bounty Reports.</t>
+          <t>IEEE_S&amp;P-Harmonycloak: Making Music Unlearnable for Generative AI.</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>University of California, Irvine</t>
+          <t>University of Tennessee at Knoxville</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Steven Ngo</t>
+          <t>Jessy Ayala</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -1700,7 +1700,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Joshua Garcia</t>
+          <t>Steven Ngo</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Yue Zhang 0025</t>
+          <t>Joshua Garcia</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -1742,22 +1742,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Make a Feint to the East While Attacking in the West: Blinding LLM-Based Code Auditors with Flashboom Attacks.</t>
+          <t>IEEE_S&amp;P-A Deep Dive into How Open-Source Project Maintainers Review and Resolve Bug Bounty Reports.</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Drexel University</t>
+          <t>University of California, Irvine</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Kaidi Xu</t>
+          <t>Yue Zhang 0025</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -1769,7 +1769,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -1780,7 +1780,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sourav Das 0001</t>
+          <t>Kaidi Xu</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -1788,22 +1788,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Verifiable Secret Sharing Simplified.</t>
+          <t>IEEE_S&amp;P-Make a Feint to the East While Attacking in the West: Blinding LLM-Based Code Auditors with Flashboom Attacks.</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>University of Illinois Urbana-Champaign</t>
+          <t>Drexel University</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Ling Ren 0001</t>
+          <t>Sourav Das 0001</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -1815,7 +1815,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Munshi Rejwan Ala Muid</t>
+          <t>Ling Ren 0001</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -1834,22 +1834,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-AccuRevoke: Enhancing Certificate Revocation with Distributed Cryptographic Accumulators.</t>
+          <t>IEEE_S&amp;P-Verifiable Secret Sharing Simplified.</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Virginia Tech</t>
+          <t>University of Illinois Urbana-Champaign</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Taejoong Chung</t>
+          <t>Munshi Rejwan Ala Muid</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Thang Hoang</t>
+          <t>Taejoong Chung</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -1884,7 +1884,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Doowon Kim</t>
+          <t>Thang Hoang</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Open Sesame! On the Security and Memorability of Verbal Passwords.</t>
+          <t>IEEE_S&amp;P-AccuRevoke: Enhancing Certificate Revocation with Distributed Cryptographic Accumulators.</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -1911,14 +1911,14 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>University of Tennessee at Knoxville</t>
+          <t>Virginia Tech</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Lei Yu</t>
+          <t>Doowon Kim</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -1926,22 +1926,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-CMASan: Custom Memory Allocator-aware Address Sanitizer.</t>
+          <t>IEEE_S&amp;P-Open Sesame! On the Security and Memorability of Verbal Passwords.</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Rensselaer Polytechnic Institute</t>
+          <t>University of Tennessee at Knoxville</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Yonghwi Kwon 0001</t>
+          <t>Lei Yu</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -1953,18 +1953,18 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>University of Maryland, College Park</t>
+          <t>Rensselaer Polytechnic Institute</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Md Sakib Anwar</t>
+          <t>Yonghwi Kwon 0001</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -1972,22 +1972,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-GoSonar: Detecting Logical Vulnerabilities in Memory Safe Language Using Inductive Constraint Reasoning.</t>
+          <t>IEEE_S&amp;P-CMASan: Custom Memory Allocator-aware Address Sanitizer.</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>The Ohio State University</t>
+          <t>University of Maryland, College Park</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Carter Yagemann</t>
+          <t>Md Sakib Anwar</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -1999,7 +1999,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Zhiqiang Lin 0001</t>
+          <t>Carter Yagemann</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -2022,7 +2022,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Zhiyun Qian</t>
+          <t>Zhiqiang Lin 0001</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-SoK: Challenges and Paths Toward Memory Safety for eBPF.</t>
+          <t>IEEE_S&amp;P-GoSonar: Detecting Logical Vulnerabilities in Memory Safe Language Using Inductive Constraint Reasoning.</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2049,14 +2049,14 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>University of California, Riverside</t>
+          <t>The Ohio State University</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Trent Jaeger</t>
+          <t>Zhiyun Qian</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -2068,7 +2068,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Alexander J. Gaidis</t>
+          <t>Trent Jaeger</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -2087,22 +2087,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-IUBIK: Isolating User Bytes in Commodity Operating System Kernels via Memory Tagging Extensions.</t>
+          <t>IEEE_S&amp;P-SoK: Challenges and Paths Toward Memory Safety for eBPF.</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>John Brown University</t>
+          <t>University of California, Riverside</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Vasileios P. Kemerlis</t>
+          <t>Alexander J. Gaidis</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -2114,7 +2114,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Penghui Li 0001</t>
+          <t>Vasileios P. Kemerlis</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -2133,7 +2133,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Predator: Directed Web Application Fuzzing for Efficient Vulnerability Validation.</t>
+          <t>IEEE_S&amp;P-IUBIK: Isolating User Bytes in Commodity Operating System Kernels via Memory Tagging Extensions.</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -2141,14 +2141,14 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Columbia University</t>
+          <t>John Brown University</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Yonghwi Kwon 0001</t>
+          <t>Penghui Li 0001</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -2156,22 +2156,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Racedb: Detecting Request Race Vulnerabilities in Database-Backed Web Applications.</t>
+          <t>IEEE_S&amp;P-Predator: Directed Web Application Fuzzing for Efficient Vulnerability Validation.</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>University of Maryland, College Park</t>
+          <t>Columbia University</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Zifeng Kang</t>
+          <t>Yonghwi Kwon 0001</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -2179,22 +2179,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Follow My Flow: Unveiling Client-Side Prototype Pollution Gadgets from One Million Real-World Websites.</t>
+          <t>IEEE_S&amp;P-Racedb: Detecting Request Race Vulnerabilities in Database-Backed Web Applications.</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Johns Hopkins University</t>
+          <t>University of Maryland, College Park</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Muxi Lyu</t>
+          <t>Zifeng Kang</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -2206,7 +2206,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Zhengyu Liu</t>
+          <t>Muxi Lyu</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -2229,7 +2229,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Jianjia Yu</t>
+          <t>Zhengyu Liu</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Yinzhi Cao</t>
+          <t>Jianjia Yu</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -2275,7 +2275,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Tommaso Innocenti</t>
+          <t>Yinzhi Cao</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -2294,22 +2294,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-"Only as Strong as the Weakest Link": On the Security of Brokered Single Sign-On on the Web.</t>
+          <t>IEEE_S&amp;P-Follow My Flow: Unveiling Client-Side Prototype Pollution Gadgets from One Million Real-World Websites.</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Northeastern University</t>
+          <t>Johns Hopkins University</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Engin Kirda</t>
+          <t>Tommaso Innocenti</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -2321,7 +2321,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Jose Luis Castanon Remy</t>
+          <t>Engin Kirda</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -2340,22 +2340,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-SoK: Space Infrastructures Vulnerabilities, Attacks and Defenses.</t>
+          <t>IEEE_S&amp;P-"Only as Strong as the Weakest Link": On the Security of Brokered Single Sign-On on the Web.</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>University of Colorado Colorado Springs</t>
+          <t>Northeastern University</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Ekzhin Ear</t>
+          <t>Jose Luis Castanon Remy</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -2367,7 +2367,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Caleb Chang</t>
+          <t>Ekzhin Ear</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -2390,7 +2390,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Antonia Feffer</t>
+          <t>Caleb Chang</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -2413,7 +2413,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Shouhuai Xu</t>
+          <t>Antonia Feffer</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -2436,7 +2436,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -2447,7 +2447,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Tao Wan 0004</t>
+          <t>Shouhuai Xu</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -2455,22 +2455,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Invade the Walled Garden: Evaluating GTP Security in Cellular Networks.</t>
+          <t>IEEE_S&amp;P-SoK: Space Infrastructures Vulnerabilities, Attacks and Defenses.</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Cablevision (United States)</t>
+          <t>University of Colorado Colorado Springs</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Jinhe Wen</t>
+          <t>Tao Wan 0004</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -2478,22 +2478,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Teaching Data Science Students to Sketch Privacy Designs Through Heuristics.</t>
+          <t>IEEE_S&amp;P-Invade the Walled Garden: Evaluating GTP Security in Cellular Networks.</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>University of California, San Diego</t>
+          <t>Cablevision (United States)</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Yingxi Zhao</t>
+          <t>Jinhe Wen</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -2505,7 +2505,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Wenqian Xu</t>
+          <t>Yingxi Zhao</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -2528,7 +2528,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Yaxing Yao</t>
+          <t>Wenqian Xu</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -2551,18 +2551,18 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Virginia Tech</t>
+          <t>University of California, San Diego</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Haojian Jin</t>
+          <t>Yaxing Yao</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -2574,18 +2574,18 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>University of California, San Diego</t>
+          <t>Virginia Tech</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Phoebe Moh</t>
+          <t>Haojian Jin</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -2593,22 +2593,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Characterizing the Usability and Usefulness of U.S. Ad Transparency Systems.</t>
+          <t>IEEE_S&amp;P-Teaching Data Science Students to Sketch Privacy Designs Through Heuristics.</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>University of Maryland, College Park</t>
+          <t>University of California, San Diego</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Tobias Lauinger</t>
+          <t>Phoebe Moh</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -2620,18 +2620,18 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>New York University</t>
+          <t>University of Maryland, College Park</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Michelle L. Mazurek</t>
+          <t>Tobias Lauinger</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -2643,18 +2643,18 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>University of Maryland, College Park</t>
+          <t>New York University</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Damon McCoy</t>
+          <t>Michelle L. Mazurek</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -2666,18 +2666,18 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>New York University</t>
+          <t>University of Maryland, College Park</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Zikai Wen</t>
+          <t>Damon McCoy</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -2685,22 +2685,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Supporting Family Discussions About Digital Privacy Through Perspective-Taking: An Empirical Investigation.</t>
+          <t>IEEE_S&amp;P-Characterizing the Usability and Usefulness of U.S. Ad Transparency Systems.</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Virginia Tech</t>
+          <t>New York University</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Lanjing Liu</t>
+          <t>Zikai Wen</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -2712,7 +2712,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Yaxing Yao</t>
+          <t>Lanjing Liu</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -2735,7 +2735,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Elham Pourabbas Vafa</t>
+          <t>Yaxing Yao</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -2754,22 +2754,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Learning from Censored Experiences: Social Media Discussions around Censorship Circumvention Technologies.</t>
+          <t>IEEE_S&amp;P-Supporting Family Discussions About Digital Privacy Through Perspective-Taking: An Empirical Investigation.</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>The University of Texas at Arlington</t>
+          <t>Virginia Tech</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Mohit Singhal</t>
+          <t>Elham Pourabbas Vafa</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -2781,7 +2781,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Poojitha Thota</t>
+          <t>Mohit Singhal</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -2804,7 +2804,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Sayak Saha Roy</t>
+          <t>Poojitha Thota</t>
         </is>
       </c>
       <c r="B105" t="n">
@@ -2827,7 +2827,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Zakir Durumeric</t>
+          <t>Sayak Saha Roy</t>
         </is>
       </c>
       <c r="B106" t="n">
@@ -2846,22 +2846,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-A Wall Behind A Wall: Emerging Regional Censorship in China.</t>
+          <t>IEEE_S&amp;P-Learning from Censored Experiences: Social Media Discussions around Censorship Circumvention Technologies.</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Stanford University</t>
+          <t>The University of Texas at Arlington</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Amir Houmansadr</t>
+          <t>Zakir Durumeric</t>
         </is>
       </c>
       <c r="B107" t="n">
@@ -2873,18 +2873,18 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>University of Massachusetts Amherst</t>
+          <t>Stanford University</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Eric Wustrow</t>
+          <t>Amir Houmansadr</t>
         </is>
       </c>
       <c r="B108" t="n">
@@ -2896,18 +2896,18 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>University of Colorado System; University of Colorado Boulder</t>
+          <t>University of Massachusetts Amherst</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Sadia Nourin</t>
+          <t>Eric Wustrow</t>
         </is>
       </c>
       <c r="B109" t="n">
@@ -2915,22 +2915,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Is Nobody There? Good! Globally Measuring Connection Tampering Without Responsive Endhosts.</t>
+          <t>IEEE_S&amp;P-A Wall Behind A Wall: Emerging Regional Censorship in China.</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>University of Maryland, College Park</t>
+          <t>University of Colorado System; University of Colorado Boulder</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Erik C. Rye</t>
+          <t>Sadia Nourin</t>
         </is>
       </c>
       <c r="B110" t="n">
@@ -2942,7 +2942,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Dave Levin</t>
+          <t>Erik C. Rye</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Kyle Fredrickson</t>
+          <t>Dave Levin</t>
         </is>
       </c>
       <c r="B112" t="n">
@@ -2984,22 +2984,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Sparta: Practical Anonymity with Long-Term Resistance to Traffic Analysis.</t>
+          <t>IEEE_S&amp;P-Is Nobody There? Good! Globally Measuring Connection Tampering Without Responsive Endhosts.</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>University of California, Santa Cruz</t>
+          <t>University of Maryland, College Park</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Ioannis Demertzis</t>
+          <t>Kyle Fredrickson</t>
         </is>
       </c>
       <c r="B113" t="n">
@@ -3011,7 +3011,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -3022,7 +3022,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>James P. Hughes 0001</t>
+          <t>Ioannis Demertzis</t>
         </is>
       </c>
       <c r="B114" t="n">
@@ -3034,7 +3034,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Darrell D. E. Long</t>
+          <t>James P. Hughes 0001</t>
         </is>
       </c>
       <c r="B115" t="n">
@@ -3057,7 +3057,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -3068,7 +3068,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>James Austgen</t>
+          <t>Darrell D. E. Long</t>
         </is>
       </c>
       <c r="B116" t="n">
@@ -3076,22 +3076,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Liquefaction: Privately Liquefying Blockchain Assets.</t>
+          <t>IEEE_S&amp;P-Sparta: Practical Anonymity with Long-Term Resistance to Traffic Analysis.</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Cornell University</t>
+          <t>University of California, Santa Cruz</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Andrés Fábrega</t>
+          <t>James Austgen</t>
         </is>
       </c>
       <c r="B117" t="n">
@@ -3103,7 +3103,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Mahimna Kelkar</t>
+          <t>Andrés Fábrega</t>
         </is>
       </c>
       <c r="B118" t="n">
@@ -3126,7 +3126,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -3137,7 +3137,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Dani Vilardell</t>
+          <t>Mahimna Kelkar</t>
         </is>
       </c>
       <c r="B119" t="n">
@@ -3149,7 +3149,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Kushal Babel</t>
+          <t>Dani Vilardell</t>
         </is>
       </c>
       <c r="B120" t="n">
@@ -3172,7 +3172,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Jay Yu</t>
+          <t>Kushal Babel</t>
         </is>
       </c>
       <c r="B121" t="n">
@@ -3195,18 +3195,18 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Stanford University</t>
+          <t>Cornell University</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Ari Juels</t>
+          <t>Jay Yu</t>
         </is>
       </c>
       <c r="B122" t="n">
@@ -3218,18 +3218,18 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Cornell University</t>
+          <t>Stanford University</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Sen Yang</t>
+          <t>Ari Juels</t>
         </is>
       </c>
       <c r="B123" t="n">
@@ -3237,22 +3237,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Decentralization of Ethereum's Builder Market.</t>
+          <t>IEEE_S&amp;P-Liquefaction: Privately Liquefying Blockchain Assets.</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Yale University</t>
+          <t>Cornell University</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Kartik Nayak</t>
+          <t>Sen Yang</t>
         </is>
       </c>
       <c r="B124" t="n">
@@ -3264,18 +3264,18 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Duke University</t>
+          <t>Yale University</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Fan Zhang 0022</t>
+          <t>Kartik Nayak</t>
         </is>
       </c>
       <c r="B125" t="n">
@@ -3287,18 +3287,18 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Yale University</t>
+          <t>Duke University</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Darya Kaviani</t>
+          <t>Fan Zhang 0022</t>
         </is>
       </c>
       <c r="B126" t="n">
@@ -3306,22 +3306,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Papercraft: Lattice-Based Verifiable Delay Function Implemented.</t>
+          <t>IEEE_S&amp;P-Decentralization of Ethereum's Builder Market.</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Berkeley College; University of California, Berkeley</t>
+          <t>Yale University</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Jiongxiao Wang</t>
+          <t>Darya Kaviani</t>
         </is>
       </c>
       <c r="B127" t="n">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Preference Poisoning Attacks on Reward Model Learning.</t>
+          <t>IEEE_S&amp;P-Papercraft: Lattice-Based Verifiable Delay Function Implemented.</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -3337,14 +3337,14 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>University of Wisconsin–Madison</t>
+          <t>Berkeley College; University of California, Berkeley</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Chaowei Xiao</t>
+          <t>Jiongxiao Wang</t>
         </is>
       </c>
       <c r="B128" t="n">
@@ -3356,7 +3356,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -3367,7 +3367,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Ziqi Zhang</t>
+          <t>Chaowei Xiao</t>
         </is>
       </c>
       <c r="B129" t="n">
@@ -3375,22 +3375,22 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Query Provenance Analysis: Efficient and Robust Defense Against Query-Based Black-Box Attacks.</t>
+          <t>IEEE_S&amp;P-Preference Poisoning Attacks on Reward Model Learning.</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>University of Illinois Urbana-Champaign</t>
+          <t>University of Wisconsin–Madison</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Guangyu Shen</t>
+          <t>Ziqi Zhang</t>
         </is>
       </c>
       <c r="B130" t="n">
@@ -3398,22 +3398,22 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-BAIT: Large Language Model Backdoor Scanning by Inverting Attack Target.</t>
+          <t>IEEE_S&amp;P-Query Provenance Analysis: Efficient and Robust Defense Against Query-Based Black-Box Attacks.</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Purdue University West Lafayette</t>
+          <t>University of Illinois Urbana-Champaign</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Siyuan Cheng 0005</t>
+          <t>Guangyu Shen</t>
         </is>
       </c>
       <c r="B131" t="n">
@@ -3425,7 +3425,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Zhuo Zhang 0002</t>
+          <t>Siyuan Cheng 0005</t>
         </is>
       </c>
       <c r="B132" t="n">
@@ -3448,7 +3448,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Guanhong Tao 0001</t>
+          <t>Zhuo Zhang 0002</t>
         </is>
       </c>
       <c r="B133" t="n">
@@ -3471,18 +3471,18 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>University of Utah</t>
+          <t>Purdue University West Lafayette</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Kaiyuan Zhang 0002</t>
+          <t>Guanhong Tao 0001</t>
         </is>
       </c>
       <c r="B134" t="n">
@@ -3494,18 +3494,18 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Purdue University West Lafayette</t>
+          <t>University of Utah</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Hanxi Guo</t>
+          <t>Kaiyuan Zhang 0002</t>
         </is>
       </c>
       <c r="B135" t="n">
@@ -3517,7 +3517,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Xiaolong Jin 0002</t>
+          <t>Hanxi Guo</t>
         </is>
       </c>
       <c r="B136" t="n">
@@ -3540,7 +3540,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -3551,7 +3551,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Shengwei An</t>
+          <t>Xiaolong Jin 0002</t>
         </is>
       </c>
       <c r="B137" t="n">
@@ -3563,7 +3563,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -3574,7 +3574,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Shiqing Ma</t>
+          <t>Shengwei An</t>
         </is>
       </c>
       <c r="B138" t="n">
@@ -3586,18 +3586,18 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>University of Massachusetts Amherst</t>
+          <t>Purdue University West Lafayette</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Xiangyu Zhang 0001</t>
+          <t>Shiqing Ma</t>
         </is>
       </c>
       <c r="B139" t="n">
@@ -3609,18 +3609,18 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Purdue University West Lafayette</t>
+          <t>University of Massachusetts Amherst</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Yongji Wu</t>
+          <t>Xiangyu Zhang 0001</t>
         </is>
       </c>
       <c r="B140" t="n">
@@ -3628,22 +3628,22 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Prompt Inversion Attack Against Collaborative Inference of Large Language Models.</t>
+          <t>IEEE_S&amp;P-BAIT: Large Language Model Backdoor Scanning by Inverting Attack Target.</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Berkeley College; University of California, Berkeley</t>
+          <t>Purdue University West Lafayette</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Tingsong Xiao</t>
+          <t>Yongji Wu</t>
         </is>
       </c>
       <c r="B141" t="n">
@@ -3655,18 +3655,18 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>University of Florida</t>
+          <t>Berkeley College; University of California, Berkeley</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Qing Deng</t>
+          <t>Tingsong Xiao</t>
         </is>
       </c>
       <c r="B142" t="n">
@@ -3674,22 +3674,22 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Beyond the Horizon: Uncovering Hosts and Services Behind Misconfigured Firewalls.</t>
+          <t>IEEE_S&amp;P-Prompt Inversion Attack Against Collaborative Inference of Large Language Models.</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>University of California, Riverside</t>
+          <t>University of Florida</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Juefei Pu</t>
+          <t>Qing Deng</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -3701,7 +3701,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Zhaowei Tan</t>
+          <t>Juefei Pu</t>
         </is>
       </c>
       <c r="B144" t="n">
@@ -3724,7 +3724,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Zhiyun Qian</t>
+          <t>Zhaowei Tan</t>
         </is>
       </c>
       <c r="B145" t="n">
@@ -3747,7 +3747,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Srikanth V. Krishnamurthy</t>
+          <t>Zhiyun Qian</t>
         </is>
       </c>
       <c r="B146" t="n">
@@ -3770,7 +3770,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
@@ -3781,7 +3781,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Mohamed Nabeel</t>
+          <t>Srikanth V. Krishnamurthy</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -3789,22 +3789,22 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-MANTIS: Detection of Zero-Day Malicious Domains Leveraging Low Reputed Hosting Infrastructure.</t>
+          <t>IEEE_S&amp;P-Beyond the Horizon: Uncovering Hosts and Services Behind Misconfigured Firewalls.</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Palo Alto Networks (United States)</t>
+          <t>University of California, Riverside</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Daiping Liu</t>
+          <t>Mohamed Nabeel</t>
         </is>
       </c>
       <c r="B148" t="n">
@@ -3812,11 +3812,11 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Resolution Without Dissent: In-Path Per-Query Sanitization to Defeat Surreptitious Communication Over DNS.</t>
+          <t>IEEE_S&amp;P-MANTIS: Detection of Zero-Day Malicious Domains Leveraging Low Reputed Hosting Infrastructure.</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Ruian Duan</t>
+          <t>Daiping Liu</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -3839,7 +3839,7 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
@@ -3850,7 +3850,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Jun Wang</t>
+          <t>Ruian Duan</t>
         </is>
       </c>
       <c r="B150" t="n">
@@ -3862,7 +3862,7 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Gene Tsudik</t>
+          <t>Jun Wang</t>
         </is>
       </c>
       <c r="B151" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-SoK: Decoding the Enigma of Encrypted Network Traffic Classifiers.</t>
+          <t>IEEE_S&amp;P-Resolution Without Dissent: In-Path Per-Query Sanitization to Defeat Surreptitious Communication Over DNS.</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -3889,14 +3889,14 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>University of California, Irvine</t>
+          <t>Palo Alto Networks (United States)</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Keyu Man</t>
+          <t>Gene Tsudik</t>
         </is>
       </c>
       <c r="B152" t="n">
@@ -3904,22 +3904,22 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-SCAD: Towards a Universal and Automated Network Side-Channel Vulnerability Detection.</t>
+          <t>IEEE_S&amp;P-SoK: Decoding the Enigma of Encrypted Network Traffic Classifiers.</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>University of California, Riverside</t>
+          <t>University of California, Irvine</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Zhongjie Wang 0002</t>
+          <t>Keyu Man</t>
         </is>
       </c>
       <c r="B153" t="n">
@@ -3931,7 +3931,7 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
@@ -3942,7 +3942,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Shenghan Zheng</t>
+          <t>Zhongjie Wang 0002</t>
         </is>
       </c>
       <c r="B154" t="n">
@@ -3954,7 +3954,7 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Xin'an Zhou</t>
+          <t>Shenghan Zheng</t>
         </is>
       </c>
       <c r="B155" t="n">
@@ -3977,7 +3977,7 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Yue Cao 0003</t>
+          <t>Xin'an Zhou</t>
         </is>
       </c>
       <c r="B156" t="n">
@@ -4000,7 +4000,7 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Zhiyun Qian</t>
+          <t>Yue Cao 0003</t>
         </is>
       </c>
       <c r="B157" t="n">
@@ -4023,7 +4023,7 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Aniket Kate</t>
+          <t>Zhiyun Qian</t>
         </is>
       </c>
       <c r="B158" t="n">
@@ -4042,22 +4042,22 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Sailfish: Towards Improving the Latency of DAG-Based BFT.</t>
+          <t>IEEE_S&amp;P-SCAD: Towards a Universal and Automated Network Side-Channel Vulnerability Detection.</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Purdue University West Lafayette</t>
+          <t>University of California, Riverside</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Kartik Nayak</t>
+          <t>Aniket Kate</t>
         </is>
       </c>
       <c r="B159" t="n">
@@ -4069,18 +4069,18 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Duke University</t>
+          <t>Purdue University West Lafayette</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Zhongtang Luo</t>
+          <t>Kartik Nayak</t>
         </is>
       </c>
       <c r="B160" t="n">
@@ -4088,22 +4088,22 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Cauchyproofs: Batch-Updatable Vector Commitment with Easy Aggregation and Application to Stateless Blockchains.</t>
+          <t>IEEE_S&amp;P-Sailfish: Towards Improving the Latency of DAG-Based BFT.</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Purdue University West Lafayette</t>
+          <t>Duke University</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Yanxue Jia</t>
+          <t>Zhongtang Luo</t>
         </is>
       </c>
       <c r="B161" t="n">
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Srinath T. V. Setty</t>
+          <t>Yanxue Jia</t>
         </is>
       </c>
       <c r="B162" t="n">
@@ -4134,7 +4134,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-MicroNova: Folding-Based Arguments with Efficient (On-Chain) Verification.</t>
+          <t>IEEE_S&amp;P-Cauchyproofs: Batch-Updatable Vector Commitment with Easy Aggregation and Application to Stateless Blockchains.</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -4142,14 +4142,14 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Microsoft Research (United Kingdom)</t>
+          <t>Purdue University West Lafayette</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Weidong Cui</t>
+          <t>Srinath T. V. Setty</t>
         </is>
       </c>
       <c r="B163" t="n">
@@ -4161,7 +4161,7 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Greg Zaverucha</t>
+          <t>Weidong Cui</t>
         </is>
       </c>
       <c r="B164" t="n">
@@ -4184,7 +4184,7 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Ben Fisch</t>
+          <t>Greg Zaverucha</t>
         </is>
       </c>
       <c r="B165" t="n">
@@ -4203,22 +4203,22 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Permissionless Verifiable Information Dispersal (Data Availability for Bitcoin Rollups).</t>
+          <t>IEEE_S&amp;P-MicroNova: Folding-Based Arguments with Efficient (On-Chain) Verification.</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Yale University</t>
+          <t>Microsoft Research (United Kingdom)</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Arthur Lazzaretti</t>
+          <t>Ben Fisch</t>
         </is>
       </c>
       <c r="B166" t="n">
@@ -4230,7 +4230,7 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
@@ -4241,7 +4241,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Zeyu Liu 0004</t>
+          <t>Arthur Lazzaretti</t>
         </is>
       </c>
       <c r="B167" t="n">
@@ -4253,7 +4253,7 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
@@ -4264,7 +4264,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Jiadong Lou</t>
+          <t>Zeyu Liu 0004</t>
         </is>
       </c>
       <c r="B168" t="n">
@@ -4272,22 +4272,22 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-GRID: Protecting Training Graph from Link Stealing Attacks on GNN Models.</t>
+          <t>IEEE_S&amp;P-Permissionless Verifiable Information Dispersal (Data Availability for Bitcoin Rollups).</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>University of Delaware</t>
+          <t>Yale University</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Rui Zhang</t>
+          <t>Jiadong Lou</t>
         </is>
       </c>
       <c r="B169" t="n">
@@ -4299,7 +4299,7 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
@@ -4310,7 +4310,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Neil Zhenqiang Gong</t>
+          <t>Xu Yuan 0001</t>
         </is>
       </c>
       <c r="B170" t="n">
@@ -4322,18 +4322,18 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Duke University</t>
+          <t>University of Delaware; University of Melbourne</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Kang Yang</t>
+          <t>Rui Zhang</t>
         </is>
       </c>
       <c r="B171" t="n">
@@ -4341,22 +4341,22 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Alleviating the Fear of Losing Alignment in LLM Fine-tuning.</t>
+          <t>IEEE_S&amp;P-GRID: Protecting Training Graph from Link Stealing Attacks on GNN Models.</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>University of Utah</t>
+          <t>University of Delaware</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Guanhong Tao 0001</t>
+          <t>Xingliang Yuan</t>
         </is>
       </c>
       <c r="B172" t="n">
@@ -4364,22 +4364,22 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Alleviating the Fear of Losing Alignment in LLM Fine-tuning.</t>
+          <t>IEEE_S&amp;P-GRID: Protecting Training Graph from Link Stealing Attacks on GNN Models.</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>University of Utah</t>
+          <t>University of Melbourne; University of Delaware</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Jun Xu 0024</t>
+          <t>Neil Zhenqiang Gong</t>
         </is>
       </c>
       <c r="B173" t="n">
@@ -4387,22 +4387,22 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Alleviating the Fear of Losing Alignment in LLM Fine-tuning.</t>
+          <t>IEEE_S&amp;P-GRID: Protecting Training Graph from Link Stealing Attacks on GNN Models.</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>University of Utah</t>
+          <t>Duke University</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Yuqi Jia</t>
+          <t>Kang Yang</t>
         </is>
       </c>
       <c r="B174" t="n">
@@ -4410,22 +4410,22 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-DataSentinel: A Game-Theoretic Detection of Prompt Injection Attacks.</t>
+          <t>IEEE_S&amp;P-Alleviating the Fear of Losing Alignment in LLM Fine-tuning.</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Duke University</t>
+          <t>University of Utah</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Dawn Song</t>
+          <t>Guanhong Tao 0001</t>
         </is>
       </c>
       <c r="B175" t="n">
@@ -4433,22 +4433,22 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-DataSentinel: A Game-Theoretic Detection of Prompt Injection Attacks.</t>
+          <t>IEEE_S&amp;P-Alleviating the Fear of Losing Alignment in LLM Fine-tuning.</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>University of California, Berkeley; Berkeley College</t>
+          <t>University of Utah</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Neil Zhenqiang Gong</t>
+          <t>Xun Chen</t>
         </is>
       </c>
       <c r="B176" t="n">
@@ -4456,22 +4456,22 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-DataSentinel: A Game-Theoretic Detection of Prompt Injection Attacks.</t>
+          <t>IEEE_S&amp;P-Alleviating the Fear of Losing Alignment in LLM Fine-tuning.</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Duke University</t>
+          <t>Research!America (United States); Samsung (United States)</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Yasemin Acar</t>
+          <t>Jun Xu 0024</t>
         </is>
       </c>
       <c r="B177" t="n">
@@ -4479,22 +4479,22 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-"It's Time. Time for Digital Security.": An End User Study on Actionable Security and Privacy Advice.</t>
+          <t>IEEE_S&amp;P-Alleviating the Fear of Losing Alignment in LLM Fine-tuning.</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>George Washington University</t>
+          <t>University of Utah</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>John Sadik</t>
+          <t>Yuqi Jia</t>
         </is>
       </c>
       <c r="B178" t="n">
@@ -4502,7 +4502,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Security and Privacy Experiences of First- and Second-Generation Pakistani Immigrants to the US: Perceptions, Practices, Challenges, and Parent-Child Dynamics.</t>
+          <t>IEEE_S&amp;P-DataSentinel: A Game-Theoretic Detection of Prompt Injection Attacks.</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -4510,14 +4510,14 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>University of Tennessee at Knoxville</t>
+          <t>Duke University</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Taha</t>
+          <t>Dawn Song</t>
         </is>
       </c>
       <c r="B179" t="n">
@@ -4525,22 +4525,22 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Security and Privacy Experiences of First- and Second-Generation Pakistani Immigrants to the US: Perceptions, Practices, Challenges, and Parent-Child Dynamics.</t>
+          <t>IEEE_S&amp;P-DataSentinel: A Game-Theoretic Detection of Prompt Injection Attacks.</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Purdue University West Lafayette</t>
+          <t>University of California, Berkeley; Berkeley College</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Ran Elgedawy</t>
+          <t>Neil Zhenqiang Gong</t>
         </is>
       </c>
       <c r="B180" t="n">
@@ -4548,22 +4548,22 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Security and Privacy Experiences of First- and Second-Generation Pakistani Immigrants to the US: Perceptions, Practices, Challenges, and Parent-Child Dynamics.</t>
+          <t>IEEE_S&amp;P-DataSentinel: A Game-Theoretic Detection of Prompt Injection Attacks.</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>University of Tennessee at Knoxville</t>
+          <t>Duke University</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Scott Ruoti</t>
+          <t>Yasemin Acar</t>
         </is>
       </c>
       <c r="B181" t="n">
@@ -4571,7 +4571,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Security and Privacy Experiences of First- and Second-Generation Pakistani Immigrants to the US: Perceptions, Practices, Challenges, and Parent-Child Dynamics.</t>
+          <t>IEEE_S&amp;P-"It's Time. Time for Digital Security.": An End User Study on Actionable Security and Privacy Advice.</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -4579,14 +4579,14 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>University of Tennessee at Knoxville</t>
+          <t>George Washington University</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Yaxin Tu</t>
+          <t>John Sadik</t>
         </is>
       </c>
       <c r="B182" t="n">
@@ -4594,22 +4594,22 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Improved Constructions for Distributed Multi-Point Functions.</t>
+          <t>IEEE_S&amp;P-Security and Privacy Experiences of First- and Second-Generation Pakistani Immigrants to the US: Perceptions, Practices, Challenges, and Parent-Child Dynamics.</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Princeton University</t>
+          <t>University of Tennessee at Knoxville</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Kanav Gupta</t>
+          <t>Taha</t>
         </is>
       </c>
       <c r="B183" t="n">
@@ -4617,22 +4617,22 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-SHARK: Actively Secure Inference Using Function Secret Sharing.</t>
+          <t>IEEE_S&amp;P-Security and Privacy Experiences of First- and Second-Generation Pakistani Immigrants to the US: Perceptions, Practices, Challenges, and Parent-Child Dynamics.</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>University of Maryland, College Park</t>
+          <t>Purdue University West Lafayette</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Nishanth Chandran</t>
+          <t>Ran Elgedawy</t>
         </is>
       </c>
       <c r="B184" t="n">
@@ -4640,22 +4640,22 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-SHARK: Actively Secure Inference Using Function Secret Sharing.</t>
+          <t>IEEE_S&amp;P-Security and Privacy Experiences of First- and Second-Generation Pakistani Immigrants to the US: Perceptions, Practices, Challenges, and Parent-Child Dynamics.</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Microsoft Research (United Kingdom)</t>
+          <t>University of Tennessee at Knoxville</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Divya Gupta 0001</t>
+          <t>Scott Ruoti</t>
         </is>
       </c>
       <c r="B185" t="n">
@@ -4663,22 +4663,22 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-SHARK: Actively Secure Inference Using Function Secret Sharing.</t>
+          <t>IEEE_S&amp;P-Security and Privacy Experiences of First- and Second-Generation Pakistani Immigrants to the US: Perceptions, Practices, Challenges, and Parent-Child Dynamics.</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Microsoft Research (United Kingdom)</t>
+          <t>University of Tennessee at Knoxville</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Jonathan Katz</t>
+          <t>Yaxin Tu</t>
         </is>
       </c>
       <c r="B186" t="n">
@@ -4686,22 +4686,22 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-SHARK: Actively Secure Inference Using Function Secret Sharing.</t>
+          <t>IEEE_S&amp;P-Improved Constructions for Distributed Multi-Point Functions.</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Google (United States)</t>
+          <t>Princeton University</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Rahul Sharma 0001</t>
+          <t>Kanav Gupta</t>
         </is>
       </c>
       <c r="B187" t="n">
@@ -4713,7 +4713,7 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Zhenting Wang</t>
+          <t>Nishanth Chandran</t>
         </is>
       </c>
       <c r="B188" t="n">
@@ -4732,22 +4732,22 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Towards Reliable Verification of Unauthorized Data Usage in Personalized Text-to-Image Diffusion Models.</t>
+          <t>IEEE_S&amp;P-SHARK: Actively Secure Inference Using Function Secret Sharing.</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Rutgers, The State University of New Jersey</t>
+          <t>Microsoft Research (United Kingdom)</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Xuandong Zhao</t>
+          <t>Divya Gupta 0001</t>
         </is>
       </c>
       <c r="B189" t="n">
@@ -4755,22 +4755,22 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-SoK: Watermarking for AI-Generated Content.</t>
+          <t>IEEE_S&amp;P-SHARK: Actively Secure Inference Using Function Secret Sharing.</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Berkeley College; University of California, Berkeley</t>
+          <t>Microsoft Research (United Kingdom)</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Sam Gunn</t>
+          <t>Jonathan Katz</t>
         </is>
       </c>
       <c r="B190" t="n">
@@ -4778,22 +4778,22 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-SoK: Watermarking for AI-Generated Content.</t>
+          <t>IEEE_S&amp;P-SHARK: Actively Secure Inference Using Function Secret Sharing.</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Berkeley College; University of California, Berkeley</t>
+          <t>Google (United States)</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Miranda Christ</t>
+          <t>Rahul Sharma 0001</t>
         </is>
       </c>
       <c r="B191" t="n">
@@ -4801,22 +4801,22 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-SoK: Watermarking for AI-Generated Content.</t>
+          <t>IEEE_S&amp;P-SHARK: Actively Secure Inference Using Function Secret Sharing.</t>
         </is>
       </c>
       <c r="D191" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Columbia University</t>
+          <t>University of Maryland, College Park</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Jaiden Fairoze</t>
+          <t>Zhenting Wang</t>
         </is>
       </c>
       <c r="B192" t="n">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-SoK: Watermarking for AI-Generated Content.</t>
+          <t>IEEE_S&amp;P-Towards Reliable Verification of Unauthorized Data Usage in Personalized Text-to-Image Diffusion Models.</t>
         </is>
       </c>
       <c r="D192" t="n">
@@ -4832,14 +4832,14 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Berkeley College; University of California, Berkeley</t>
+          <t>Rutgers, The State University of New Jersey</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Andrés Fábrega</t>
+          <t>Xuandong Zhao</t>
         </is>
       </c>
       <c r="B193" t="n">
@@ -4851,18 +4851,18 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Cornell University</t>
+          <t>Berkeley College; University of California, Berkeley</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Sanjam Garg</t>
+          <t>Sam Gunn</t>
         </is>
       </c>
       <c r="B194" t="n">
@@ -4874,7 +4874,7 @@
         </is>
       </c>
       <c r="D194" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Sanghyun Hong 0001</t>
+          <t>Miranda Christ</t>
         </is>
       </c>
       <c r="B195" t="n">
@@ -4897,18 +4897,18 @@
         </is>
       </c>
       <c r="D195" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Oregon State University</t>
+          <t>Columbia University</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Milad Nasr</t>
+          <t>Jaiden Fairoze</t>
         </is>
       </c>
       <c r="B196" t="n">
@@ -4920,18 +4920,18 @@
         </is>
       </c>
       <c r="D196" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Google (United States); Google DeepMind (United Kingdom)</t>
+          <t>Berkeley College; University of California, Berkeley</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Somesh Jha</t>
+          <t>Andrés Fábrega</t>
         </is>
       </c>
       <c r="B197" t="n">
@@ -4943,18 +4943,18 @@
         </is>
       </c>
       <c r="D197" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>University of Wisconsin–Madison</t>
+          <t>Cornell University</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Lei Li 0005</t>
+          <t>Sanjam Garg</t>
         </is>
       </c>
       <c r="B198" t="n">
@@ -4966,18 +4966,18 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>Berkeley College; University of California, Berkeley</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Dawn Song</t>
+          <t>Sanghyun Hong 0001</t>
         </is>
       </c>
       <c r="B199" t="n">
@@ -4989,18 +4989,18 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Berkeley College; University of California, Berkeley</t>
+          <t>Oregon State University</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>G. Edward Suh</t>
+          <t>Milad Nasr</t>
         </is>
       </c>
       <c r="B200" t="n">
@@ -5008,22 +5008,22 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Machine Learning with Privacy for Protected Attributes.</t>
+          <t>IEEE_S&amp;P-SoK: Watermarking for AI-Generated Content.</t>
         </is>
       </c>
       <c r="D200" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Cornell University; Nvidia (United Kingdom)</t>
+          <t>Google (United States); Google DeepMind (United Kingdom)</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Byron M. Lowens</t>
+          <t>Somesh Jha</t>
         </is>
       </c>
       <c r="B201" t="n">
@@ -5031,22 +5031,22 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Transparency in Usable Privacy and Security Research: Scholars' Perspectives, Practices, and Recommendations.</t>
+          <t>IEEE_S&amp;P-SoK: Watermarking for AI-Generated Content.</t>
         </is>
       </c>
       <c r="D201" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>University of Michigan–Ann Arbor</t>
+          <t>University of Wisconsin–Madison</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Florian Schaub</t>
+          <t>Lei Li 0005</t>
         </is>
       </c>
       <c r="B202" t="n">
@@ -5054,22 +5054,22 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Transparency in Usable Privacy and Security Research: Scholars' Perspectives, Practices, and Recommendations.</t>
+          <t>IEEE_S&amp;P-SoK: Watermarking for AI-Generated Content.</t>
         </is>
       </c>
       <c r="D202" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>University of Michigan–Ann Arbor</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Anna Crowder</t>
+          <t>Dawn Song</t>
         </is>
       </c>
       <c r="B203" t="n">
@@ -5077,22 +5077,22 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Data to Infinity and Beyond: Examining Data Sharing and Reuse Practices in the Computer Security Community.</t>
+          <t>IEEE_S&amp;P-SoK: Watermarking for AI-Generated Content.</t>
         </is>
       </c>
       <c r="D203" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>University of Florida</t>
+          <t>Berkeley College; University of California, Berkeley</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Allison Lu</t>
+          <t>G. Edward Suh</t>
         </is>
       </c>
       <c r="B204" t="n">
@@ -5100,22 +5100,22 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Data to Infinity and Beyond: Examining Data Sharing and Reuse Practices in the Computer Security Community.</t>
+          <t>IEEE_S&amp;P-Machine Learning with Privacy for Protected Attributes.</t>
         </is>
       </c>
       <c r="D204" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>University of Florida</t>
+          <t>Cornell University; Nvidia (United Kingdom)</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Kevin Childs</t>
+          <t>Byron M. Lowens</t>
         </is>
       </c>
       <c r="B205" t="n">
@@ -5123,7 +5123,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Data to Infinity and Beyond: Examining Data Sharing and Reuse Practices in the Computer Security Community.</t>
+          <t>IEEE_S&amp;P-Transparency in Usable Privacy and Security Research: Scholars' Perspectives, Practices, and Recommendations.</t>
         </is>
       </c>
       <c r="D205" t="n">
@@ -5131,14 +5131,14 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>University of Florida</t>
+          <t>University of Michigan–Ann Arbor</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Carson Stillman</t>
+          <t>Florian Schaub</t>
         </is>
       </c>
       <c r="B206" t="n">
@@ -5146,22 +5146,22 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Data to Infinity and Beyond: Examining Data Sharing and Reuse Practices in the Computer Security Community.</t>
+          <t>IEEE_S&amp;P-Transparency in Usable Privacy and Security Research: Scholars' Perspectives, Practices, and Recommendations.</t>
         </is>
       </c>
       <c r="D206" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>University of Florida</t>
+          <t>University of Michigan–Ann Arbor</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Patrick Traynor</t>
+          <t>Anna Crowder</t>
         </is>
       </c>
       <c r="B207" t="n">
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
@@ -5184,7 +5184,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Kevin R. B. Butler</t>
+          <t>Allison Lu</t>
         </is>
       </c>
       <c r="B208" t="n">
@@ -5196,7 +5196,7 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Yaman Yu</t>
+          <t>Kevin Childs</t>
         </is>
       </c>
       <c r="B209" t="n">
@@ -5215,22 +5215,22 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Exploring Parent-Child Perceptions on Safety in Generative AI: Concerns, Mitigation Strategies, and Design Implications.</t>
+          <t>IEEE_S&amp;P-Data to Infinity and Beyond: Examining Data Sharing and Reuse Practices in the Computer Security Community.</t>
         </is>
       </c>
       <c r="D209" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>University of Illinois Urbana-Champaign</t>
+          <t>University of Florida</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Yang Wang 0005</t>
+          <t>Carson Stillman</t>
         </is>
       </c>
       <c r="B210" t="n">
@@ -5238,22 +5238,22 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Exploring Parent-Child Perceptions on Safety in Generative AI: Concerns, Mitigation Strategies, and Design Implications.</t>
+          <t>IEEE_S&amp;P-Data to Infinity and Beyond: Examining Data Sharing and Reuse Practices in the Computer Security Community.</t>
         </is>
       </c>
       <c r="D210" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>University of Illinois Urbana-Champaign</t>
+          <t>University of Florida</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Yaman Yu</t>
+          <t>Patrick Traynor</t>
         </is>
       </c>
       <c r="B211" t="n">
@@ -5261,22 +5261,22 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Security Perceptions of Users in Stablecoins: Advantages and Risks within the Cryptocurrency Ecosystem.</t>
+          <t>IEEE_S&amp;P-Data to Infinity and Beyond: Examining Data Sharing and Reuse Practices in the Computer Security Community.</t>
         </is>
       </c>
       <c r="D211" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>University of Illinois Urbana-Champaign</t>
+          <t>University of Florida</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Kaihua Qin</t>
+          <t>Kevin R. B. Butler</t>
         </is>
       </c>
       <c r="B212" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Security Perceptions of Users in Stablecoins: Advantages and Risks within the Cryptocurrency Ecosystem.</t>
+          <t>IEEE_S&amp;P-Data to Infinity and Beyond: Examining Data Sharing and Reuse Practices in the Computer Security Community.</t>
         </is>
       </c>
       <c r="D212" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Yale University</t>
+          <t>University of Florida</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Yang Wang 0005</t>
+          <t>Yaman Yu</t>
         </is>
       </c>
       <c r="B213" t="n">
@@ -5307,11 +5307,11 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Security Perceptions of Users in Stablecoins: Advantages and Risks within the Cryptocurrency Ecosystem.</t>
+          <t>IEEE_S&amp;P-Exploring Parent-Child Perceptions on Safety in Generative AI: Concerns, Mitigation Strategies, and Design Implications.</t>
         </is>
       </c>
       <c r="D213" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E213" t="inlineStr">
         <is>
@@ -5322,7 +5322,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Kurt Thomas</t>
+          <t>Yang Wang 0005</t>
         </is>
       </c>
       <c r="B214" t="n">
@@ -5330,22 +5330,22 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Supporting Human Raters with the Detection of Harmful Content Using Large Language Models.</t>
+          <t>IEEE_S&amp;P-Exploring Parent-Child Perceptions on Safety in Generative AI: Concerns, Mitigation Strategies, and Design Implications.</t>
         </is>
       </c>
       <c r="D214" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Google (United States)</t>
+          <t>University of Illinois Urbana-Champaign</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Patrick Gage Kelley</t>
+          <t>Yaman Yu</t>
         </is>
       </c>
       <c r="B215" t="n">
@@ -5353,7 +5353,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Supporting Human Raters with the Detection of Harmful Content Using Large Language Models.</t>
+          <t>IEEE_S&amp;P-Security Perceptions of Users in Stablecoins: Advantages and Risks within the Cryptocurrency Ecosystem.</t>
         </is>
       </c>
       <c r="D215" t="n">
@@ -5361,14 +5361,14 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Google (United States)</t>
+          <t>University of Illinois Urbana-Champaign</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>David Tao</t>
+          <t>Kaihua Qin</t>
         </is>
       </c>
       <c r="B216" t="n">
@@ -5376,22 +5376,22 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Supporting Human Raters with the Detection of Harmful Content Using Large Language Models.</t>
+          <t>IEEE_S&amp;P-Security Perceptions of Users in Stablecoins: Advantages and Risks within the Cryptocurrency Ecosystem.</t>
         </is>
       </c>
       <c r="D216" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Google (United States)</t>
+          <t>Yale University</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Sarah Meiklejohn</t>
+          <t>Yang Wang 0005</t>
         </is>
       </c>
       <c r="B217" t="n">
@@ -5399,22 +5399,22 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Supporting Human Raters with the Detection of Harmful Content Using Large Language Models.</t>
+          <t>IEEE_S&amp;P-Security Perceptions of Users in Stablecoins: Advantages and Risks within the Cryptocurrency Ecosystem.</t>
         </is>
       </c>
       <c r="D217" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Google (United States)</t>
+          <t>University of Illinois Urbana-Champaign</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Owen Vallis</t>
+          <t>Kurt Thomas</t>
         </is>
       </c>
       <c r="B218" t="n">
@@ -5426,7 +5426,7 @@
         </is>
       </c>
       <c r="D218" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E218" t="inlineStr">
         <is>
@@ -5437,7 +5437,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Shunwen Tan</t>
+          <t>Patrick Gage Kelley</t>
         </is>
       </c>
       <c r="B219" t="n">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="D219" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E219" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Felipe Tiengo Ferreira</t>
+          <t>David Tao</t>
         </is>
       </c>
       <c r="B220" t="n">
@@ -5472,18 +5472,18 @@
         </is>
       </c>
       <c r="D220" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Google (United States); DeepMind (United Kingdom)</t>
+          <t>Google (United States)</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Vijay Kumar Eranti</t>
+          <t>Sarah Meiklejohn</t>
         </is>
       </c>
       <c r="B221" t="n">
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="D221" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E221" t="inlineStr">
         <is>
@@ -5506,7 +5506,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Elie Bursztein</t>
+          <t>Owen Vallis</t>
         </is>
       </c>
       <c r="B222" t="n">
@@ -5518,7 +5518,7 @@
         </is>
       </c>
       <c r="D222" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E222" t="inlineStr">
         <is>
@@ -5529,7 +5529,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Ani Meliksetyan</t>
+          <t>Shunwen Tan</t>
         </is>
       </c>
       <c r="B223" t="n">
@@ -5537,22 +5537,22 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-"It's been Lovely Watching you": Institutional Decision-Making on Online Proctoring Software.</t>
+          <t>IEEE_S&amp;P-Supporting Human Raters with the Detection of Harmful Content Using Large Language Models.</t>
         </is>
       </c>
       <c r="D223" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>George Washington University</t>
+          <t>Google (United States)</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Lucy Simko</t>
+          <t>Felipe Tiengo Ferreira</t>
         </is>
       </c>
       <c r="B224" t="n">
@@ -5560,22 +5560,22 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-"It's been Lovely Watching you": Institutional Decision-Making on Online Proctoring Software.</t>
+          <t>IEEE_S&amp;P-Supporting Human Raters with the Detection of Harmful Content Using Large Language Models.</t>
         </is>
       </c>
       <c r="D224" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>George Washington University</t>
+          <t>Google (United States); DeepMind (United Kingdom)</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Ryan Watkins</t>
+          <t>Vijay Kumar Eranti</t>
         </is>
       </c>
       <c r="B225" t="n">
@@ -5583,22 +5583,22 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-"It's been Lovely Watching you": Institutional Decision-Making on Online Proctoring Software.</t>
+          <t>IEEE_S&amp;P-Supporting Human Raters with the Detection of Harmful Content Using Large Language Models.</t>
         </is>
       </c>
       <c r="D225" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>George Washington University</t>
+          <t>Google (United States)</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Adam J. Aviv</t>
+          <t>Elie Bursztein</t>
         </is>
       </c>
       <c r="B226" t="n">
@@ -5606,22 +5606,22 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-"It's been Lovely Watching you": Institutional Decision-Making on Online Proctoring Software.</t>
+          <t>IEEE_S&amp;P-Supporting Human Raters with the Detection of Harmful Content Using Large Language Models.</t>
         </is>
       </c>
       <c r="D226" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>George Washington University</t>
+          <t>Google (United States)</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Tung Le 0005</t>
+          <t>Ani Meliksetyan</t>
         </is>
       </c>
       <c r="B227" t="n">
@@ -5629,22 +5629,22 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Hermes: Efficient and Secure Multi-Writer Encrypted Database.</t>
+          <t>IEEE_S&amp;P-"It's been Lovely Watching you": Institutional Decision-Making on Online Proctoring Software.</t>
         </is>
       </c>
       <c r="D227" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Virginia Tech</t>
+          <t>George Washington University</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Thang Hoang</t>
+          <t>Lucy Simko</t>
         </is>
       </c>
       <c r="B228" t="n">
@@ -5652,22 +5652,22 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Hermes: Efficient and Secure Multi-Writer Encrypted Database.</t>
+          <t>IEEE_S&amp;P-"It's been Lovely Watching you": Institutional Decision-Making on Online Proctoring Software.</t>
         </is>
       </c>
       <c r="D228" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Virginia Tech</t>
+          <t>George Washington University</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Borja Balle</t>
+          <t>Ryan Watkins</t>
         </is>
       </c>
       <c r="B229" t="n">
@@ -5675,22 +5675,22 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Hash-Prune-Invert: Improved Differentially Private Heavy-Hitter Detection in the Two-Server Model.</t>
+          <t>IEEE_S&amp;P-"It's been Lovely Watching you": Institutional Decision-Making on Online Proctoring Software.</t>
         </is>
       </c>
       <c r="D229" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Google (United States); DeepMind (United Kingdom)</t>
+          <t>George Washington University</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>James Bell-Clark</t>
+          <t>Adam J. Aviv</t>
         </is>
       </c>
       <c r="B230" t="n">
@@ -5698,22 +5698,22 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Hash-Prune-Invert: Improved Differentially Private Heavy-Hitter Detection in the Two-Server Model.</t>
+          <t>IEEE_S&amp;P-"It's been Lovely Watching you": Institutional Decision-Making on Online Proctoring Software.</t>
         </is>
       </c>
       <c r="D230" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Google (United States)</t>
+          <t>George Washington University</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Albert Cheu</t>
+          <t>Tung Le 0005</t>
         </is>
       </c>
       <c r="B231" t="n">
@@ -5721,22 +5721,22 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Hash-Prune-Invert: Improved Differentially Private Heavy-Hitter Detection in the Two-Server Model.</t>
+          <t>IEEE_S&amp;P-Hermes: Efficient and Secure Multi-Writer Encrypted Database.</t>
         </is>
       </c>
       <c r="D231" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Google (United States)</t>
+          <t>Virginia Tech</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Adrià Gascón</t>
+          <t>Thang Hoang</t>
         </is>
       </c>
       <c r="B232" t="n">
@@ -5744,22 +5744,22 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Hash-Prune-Invert: Improved Differentially Private Heavy-Hitter Detection in the Two-Server Model.</t>
+          <t>IEEE_S&amp;P-Hermes: Efficient and Secure Multi-Writer Encrypted Database.</t>
         </is>
       </c>
       <c r="D232" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Google (United States)</t>
+          <t>Virginia Tech</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Jonathan Katz</t>
+          <t>Borja Balle</t>
         </is>
       </c>
       <c r="B233" t="n">
@@ -5771,18 +5771,18 @@
         </is>
       </c>
       <c r="D233" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Google (United States)</t>
+          <t>Google (United States); DeepMind (United Kingdom)</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Mariana Raykova 0001</t>
+          <t>James Bell-Clark</t>
         </is>
       </c>
       <c r="B234" t="n">
@@ -5794,7 +5794,7 @@
         </is>
       </c>
       <c r="D234" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E234" t="inlineStr">
         <is>
@@ -5805,7 +5805,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Phillipp Schoppmann</t>
+          <t>Albert Cheu</t>
         </is>
       </c>
       <c r="B235" t="n">
@@ -5817,7 +5817,7 @@
         </is>
       </c>
       <c r="D235" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E235" t="inlineStr">
         <is>
@@ -5828,7 +5828,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Thomas Steinke 0002</t>
+          <t>Adrià Gascón</t>
         </is>
       </c>
       <c r="B236" t="n">
@@ -5840,18 +5840,18 @@
         </is>
       </c>
       <c r="D236" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>DeepMind (United Kingdom); Google (United States)</t>
+          <t>Google (United States)</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Danfeng Zhang</t>
+          <t>Jonathan Katz</t>
         </is>
       </c>
       <c r="B237" t="n">
@@ -5859,22 +5859,22 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Click Without Compromise: Online Advertising Measurement via Per User Differential Privacy.</t>
+          <t>IEEE_S&amp;P-Hash-Prune-Invert: Improved Differentially Private Heavy-Hitter Detection in the Two-Server Model.</t>
         </is>
       </c>
       <c r="D237" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Duke University</t>
+          <t>Google (United States)</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Guoren Li</t>
+          <t>Mariana Raykova 0001</t>
         </is>
       </c>
       <c r="B238" t="n">
@@ -5882,22 +5882,22 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Redefining Indirect Call Analysis with KallGraph.</t>
+          <t>IEEE_S&amp;P-Hash-Prune-Invert: Improved Differentially Private Heavy-Hitter Detection in the Two-Server Model.</t>
         </is>
       </c>
       <c r="D238" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>University of California, Riverside</t>
+          <t>Google (United States)</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Manu Sridharan</t>
+          <t>Phillipp Schoppmann</t>
         </is>
       </c>
       <c r="B239" t="n">
@@ -5905,22 +5905,22 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Redefining Indirect Call Analysis with KallGraph.</t>
+          <t>IEEE_S&amp;P-Hash-Prune-Invert: Improved Differentially Private Heavy-Hitter Detection in the Two-Server Model.</t>
         </is>
       </c>
       <c r="D239" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>University of California, Riverside</t>
+          <t>Google (United States)</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Zhiyun Qian</t>
+          <t>Thomas Steinke 0002</t>
         </is>
       </c>
       <c r="B240" t="n">
@@ -5928,22 +5928,22 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Redefining Indirect Call Analysis with KallGraph.</t>
+          <t>IEEE_S&amp;P-Hash-Prune-Invert: Improved Differentially Private Heavy-Hitter Detection in the Two-Server Model.</t>
         </is>
       </c>
       <c r="D240" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>University of California, Riverside</t>
+          <t>DeepMind (United Kingdom); Google (United States)</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Joshua Wiedemeier</t>
+          <t>Danfeng Zhang</t>
         </is>
       </c>
       <c r="B241" t="n">
@@ -5951,22 +5951,22 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-PyLingual: Toward Perfect Decompilation of Evolving High-Level Languages.</t>
+          <t>IEEE_S&amp;P-Click Without Compromise: Online Advertising Measurement via Per User Differential Privacy.</t>
         </is>
       </c>
       <c r="D241" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>The University of Texas at Dallas</t>
+          <t>Duke University</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Elliot Tarbet</t>
+          <t>Guoren Li</t>
         </is>
       </c>
       <c r="B242" t="n">
@@ -5974,22 +5974,22 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-PyLingual: Toward Perfect Decompilation of Evolving High-Level Languages.</t>
+          <t>IEEE_S&amp;P-Redefining Indirect Call Analysis with KallGraph.</t>
         </is>
       </c>
       <c r="D242" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>The University of Texas at Dallas</t>
+          <t>University of California, Riverside</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Max Zheng</t>
+          <t>Manu Sridharan</t>
         </is>
       </c>
       <c r="B243" t="n">
@@ -5997,22 +5997,22 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-PyLingual: Toward Perfect Decompilation of Evolving High-Level Languages.</t>
+          <t>IEEE_S&amp;P-Redefining Indirect Call Analysis with KallGraph.</t>
         </is>
       </c>
       <c r="D243" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>The University of Texas at Dallas</t>
+          <t>University of California, Riverside</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Sangsoo Ko</t>
+          <t>Zhiyun Qian</t>
         </is>
       </c>
       <c r="B244" t="n">
@@ -6020,22 +6020,22 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-PyLingual: Toward Perfect Decompilation of Evolving High-Level Languages.</t>
+          <t>IEEE_S&amp;P-Redefining Indirect Call Analysis with KallGraph.</t>
         </is>
       </c>
       <c r="D244" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>The University of Texas at Dallas</t>
+          <t>University of California, Riverside</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Jessica Ouyang 0001</t>
+          <t>Joshua Wiedemeier</t>
         </is>
       </c>
       <c r="B245" t="n">
@@ -6047,7 +6047,7 @@
         </is>
       </c>
       <c r="D245" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E245" t="inlineStr">
         <is>
@@ -6058,7 +6058,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Kangkook Jee</t>
+          <t>Elliot Tarbet</t>
         </is>
       </c>
       <c r="B246" t="n">
@@ -6070,7 +6070,7 @@
         </is>
       </c>
       <c r="D246" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E246" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Antonio Flores-Montoya</t>
+          <t>Max Zheng</t>
         </is>
       </c>
       <c r="B247" t="n">
@@ -6089,22 +6089,22 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Disassembly as Weighted Interval Scheduling with Learned Weights.</t>
+          <t>IEEE_S&amp;P-PyLingual: Toward Perfect Decompilation of Evolving High-Level Languages.</t>
         </is>
       </c>
       <c r="D247" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>GrammaTech (United States)</t>
+          <t>The University of Texas at Dallas</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Junghee Lim</t>
+          <t>Sangsoo Ko</t>
         </is>
       </c>
       <c r="B248" t="n">
@@ -6112,22 +6112,22 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Disassembly as Weighted Interval Scheduling with Learned Weights.</t>
+          <t>IEEE_S&amp;P-PyLingual: Toward Perfect Decompilation of Evolving High-Level Languages.</t>
         </is>
       </c>
       <c r="D248" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>GrammaTech (United States)</t>
+          <t>The University of Texas at Dallas</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Adam Seitz</t>
+          <t>Jessica Ouyang 0001</t>
         </is>
       </c>
       <c r="B249" t="n">
@@ -6135,22 +6135,22 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Disassembly as Weighted Interval Scheduling with Learned Weights.</t>
+          <t>IEEE_S&amp;P-PyLingual: Toward Perfect Decompilation of Evolving High-Level Languages.</t>
         </is>
       </c>
       <c r="D249" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>GrammaTech (United States)</t>
+          <t>The University of Texas at Dallas</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Akshay Sood</t>
+          <t>Kangkook Jee</t>
         </is>
       </c>
       <c r="B250" t="n">
@@ -6158,22 +6158,22 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Disassembly as Weighted Interval Scheduling with Learned Weights.</t>
+          <t>IEEE_S&amp;P-PyLingual: Toward Perfect Decompilation of Evolving High-Level Languages.</t>
         </is>
       </c>
       <c r="D250" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>GrammaTech (United States)</t>
+          <t>The University of Texas at Dallas</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Edward Raff</t>
+          <t>Antonio Flores-Montoya</t>
         </is>
       </c>
       <c r="B251" t="n">
@@ -6185,18 +6185,18 @@
         </is>
       </c>
       <c r="D251" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton (United States)</t>
+          <t>GrammaTech (United States)</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Jun Xu 0024</t>
+          <t>Junghee Lim</t>
         </is>
       </c>
       <c r="B252" t="n">
@@ -6204,22 +6204,22 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Inspecting Virtual Machine Diversification Inside Virtualization Obfuscation.</t>
+          <t>IEEE_S&amp;P-Disassembly as Weighted Interval Scheduling with Learned Weights.</t>
         </is>
       </c>
       <c r="D252" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>University of Utah</t>
+          <t>GrammaTech (United States)</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Jiwon Kim 0001</t>
+          <t>Adam Seitz</t>
         </is>
       </c>
       <c r="B253" t="n">
@@ -6227,22 +6227,22 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Chimera: Fuzzing P4 Network Infrastructure for Multi-Plane Bug Detection and Vulnerability Discovery.</t>
+          <t>IEEE_S&amp;P-Disassembly as Weighted Interval Scheduling with Learned Weights.</t>
         </is>
       </c>
       <c r="D253" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Purdue University West Lafayette</t>
+          <t>GrammaTech (United States)</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Dave Jing Tian</t>
+          <t>Akshay Sood</t>
         </is>
       </c>
       <c r="B254" t="n">
@@ -6250,22 +6250,22 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Chimera: Fuzzing P4 Network Infrastructure for Multi-Plane Bug Detection and Vulnerability Discovery.</t>
+          <t>IEEE_S&amp;P-Disassembly as Weighted Interval Scheduling with Learned Weights.</t>
         </is>
       </c>
       <c r="D254" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Purdue University West Lafayette</t>
+          <t>GrammaTech (United States)</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>David Chisnall</t>
+          <t>Edward Raff</t>
         </is>
       </c>
       <c r="B255" t="n">
@@ -6273,22 +6273,22 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-SoK: Software Compartmentalization.</t>
+          <t>IEEE_S&amp;P-Disassembly as Weighted Interval Scheduling with Learned Weights.</t>
         </is>
       </c>
       <c r="D255" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>ON Semiconductor (United States)</t>
+          <t>Booz Allen Hamilton (United States)</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Zheng Yang</t>
+          <t>Jun Xu 0024</t>
         </is>
       </c>
       <c r="B256" t="n">
@@ -6296,22 +6296,22 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-CoinDef: A Comprehensive Code Injection Defense for the Electron Framework.</t>
+          <t>IEEE_S&amp;P-Inspecting Virtual Machine Diversification Inside Virtualization Obfuscation.</t>
         </is>
       </c>
       <c r="D256" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>University of Utah</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Simon P. Chung</t>
+          <t>Jiwon Kim 0001</t>
         </is>
       </c>
       <c r="B257" t="n">
@@ -6319,22 +6319,22 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-CoinDef: A Comprehensive Code Injection Defense for the Electron Framework.</t>
+          <t>IEEE_S&amp;P-Chimera: Fuzzing P4 Network Infrastructure for Multi-Plane Bug Detection and Vulnerability Discovery.</t>
         </is>
       </c>
       <c r="D257" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>Purdue University West Lafayette</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Jizhou Chen</t>
+          <t>Dave Jing Tian</t>
         </is>
       </c>
       <c r="B258" t="n">
@@ -6342,22 +6342,22 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-CoinDef: A Comprehensive Code Injection Defense for the Electron Framework.</t>
+          <t>IEEE_S&amp;P-Chimera: Fuzzing P4 Network Infrastructure for Multi-Plane Bug Detection and Vulnerability Discovery.</t>
         </is>
       </c>
       <c r="D258" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>Purdue University West Lafayette</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Runze Zhang</t>
+          <t>David Chisnall</t>
         </is>
       </c>
       <c r="B259" t="n">
@@ -6365,22 +6365,22 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-CoinDef: A Comprehensive Code Injection Defense for the Electron Framework.</t>
+          <t>IEEE_S&amp;P-SoK: Software Compartmentalization.</t>
         </is>
       </c>
       <c r="D259" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>ON Semiconductor (United States)</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Brendan Saltaformaggio</t>
+          <t>Zheng Yang</t>
         </is>
       </c>
       <c r="B260" t="n">
@@ -6392,7 +6392,7 @@
         </is>
       </c>
       <c r="D260" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E260" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Wenke Lee</t>
+          <t>Simon P. Chung</t>
         </is>
       </c>
       <c r="B261" t="n">
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="D261" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E261" t="inlineStr">
         <is>
@@ -6426,7 +6426,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Quinn Burke 0002</t>
+          <t>Jizhou Chen</t>
         </is>
       </c>
       <c r="B262" t="n">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Efficient Storage Integrity in Adversarial Settings.</t>
+          <t>IEEE_S&amp;P-CoinDef: A Comprehensive Code Injection Defense for the Electron Framework.</t>
         </is>
       </c>
       <c r="D262" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>University of Wisconsin–Madison</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Ryan Sheatsley</t>
+          <t>Runze Zhang</t>
         </is>
       </c>
       <c r="B263" t="n">
@@ -6457,22 +6457,22 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Efficient Storage Integrity in Adversarial Settings.</t>
+          <t>IEEE_S&amp;P-CoinDef: A Comprehensive Code Injection Defense for the Electron Framework.</t>
         </is>
       </c>
       <c r="D263" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>University of Wisconsin–Madison</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Yohan Beugin</t>
+          <t>Brendan Saltaformaggio</t>
         </is>
       </c>
       <c r="B264" t="n">
@@ -6480,22 +6480,22 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Efficient Storage Integrity in Adversarial Settings.</t>
+          <t>IEEE_S&amp;P-CoinDef: A Comprehensive Code Injection Defense for the Electron Framework.</t>
         </is>
       </c>
       <c r="D264" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>University of Wisconsin–Madison</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Eric Pauley</t>
+          <t>Wenke Lee</t>
         </is>
       </c>
       <c r="B265" t="n">
@@ -6503,22 +6503,22 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Efficient Storage Integrity in Adversarial Settings.</t>
+          <t>IEEE_S&amp;P-CoinDef: A Comprehensive Code Injection Defense for the Electron Framework.</t>
         </is>
       </c>
       <c r="D265" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>University of Wisconsin–Madison</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Owen Hines</t>
+          <t>Quinn Burke 0002</t>
         </is>
       </c>
       <c r="B266" t="n">
@@ -6530,7 +6530,7 @@
         </is>
       </c>
       <c r="D266" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E266" t="inlineStr">
         <is>
@@ -6541,7 +6541,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Michael Swift</t>
+          <t>Ryan Sheatsley</t>
         </is>
       </c>
       <c r="B267" t="n">
@@ -6553,7 +6553,7 @@
         </is>
       </c>
       <c r="D267" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E267" t="inlineStr">
         <is>
@@ -6564,7 +6564,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Patrick D. McDaniel</t>
+          <t>Yohan Beugin</t>
         </is>
       </c>
       <c r="B268" t="n">
@@ -6576,7 +6576,7 @@
         </is>
       </c>
       <c r="D268" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E268" t="inlineStr">
         <is>
@@ -6587,7 +6587,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Souradip Nath</t>
+          <t>Eric Pauley</t>
         </is>
       </c>
       <c r="B269" t="n">
@@ -6595,22 +6595,22 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-"It's almost like Frankenstein": Investigating the Complexities of Scientific Collaboration and Privilege Management within Research Computing Infrastructures.</t>
+          <t>IEEE_S&amp;P-Efficient Storage Integrity in Adversarial Settings.</t>
         </is>
       </c>
       <c r="D269" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Arizona State University</t>
+          <t>University of Wisconsin–Madison</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Ananta Soneji</t>
+          <t>Owen Hines</t>
         </is>
       </c>
       <c r="B270" t="n">
@@ -6618,22 +6618,22 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-"It's almost like Frankenstein": Investigating the Complexities of Scientific Collaboration and Privilege Management within Research Computing Infrastructures.</t>
+          <t>IEEE_S&amp;P-Efficient Storage Integrity in Adversarial Settings.</t>
         </is>
       </c>
       <c r="D270" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Arizona State University</t>
+          <t>University of Wisconsin–Madison</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Jaejong Baek</t>
+          <t>Michael Swift</t>
         </is>
       </c>
       <c r="B271" t="n">
@@ -6641,22 +6641,22 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-"It's almost like Frankenstein": Investigating the Complexities of Scientific Collaboration and Privilege Management within Research Computing Infrastructures.</t>
+          <t>IEEE_S&amp;P-Efficient Storage Integrity in Adversarial Settings.</t>
         </is>
       </c>
       <c r="D271" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Arizona State University</t>
+          <t>University of Wisconsin–Madison</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Tiffany Bao</t>
+          <t>Patrick D. McDaniel</t>
         </is>
       </c>
       <c r="B272" t="n">
@@ -6664,22 +6664,22 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-"It's almost like Frankenstein": Investigating the Complexities of Scientific Collaboration and Privilege Management within Research Computing Infrastructures.</t>
+          <t>IEEE_S&amp;P-Efficient Storage Integrity in Adversarial Settings.</t>
         </is>
       </c>
       <c r="D272" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Arizona State University</t>
+          <t>University of Wisconsin–Madison</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Adam Doupé</t>
+          <t>Souradip Nath</t>
         </is>
       </c>
       <c r="B273" t="n">
@@ -6691,7 +6691,7 @@
         </is>
       </c>
       <c r="D273" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E273" t="inlineStr">
         <is>
@@ -6702,7 +6702,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Carlos E. Rubio-Medrano</t>
+          <t>Ananta Soneji</t>
         </is>
       </c>
       <c r="B274" t="n">
@@ -6714,18 +6714,18 @@
         </is>
       </c>
       <c r="D274" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Texas A&amp;M University – Corpus Christi</t>
+          <t>Arizona State University</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Gail-Joon Ahn</t>
+          <t>Jaejong Baek</t>
         </is>
       </c>
       <c r="B275" t="n">
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="D275" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E275" t="inlineStr">
         <is>
@@ -6748,7 +6748,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Anna P. Y. Woo</t>
+          <t>Tiffany Bao</t>
         </is>
       </c>
       <c r="B276" t="n">
@@ -6756,22 +6756,22 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Efficient Proofs of Possession for Legacy Signatures.</t>
+          <t>IEEE_S&amp;P-"It's almost like Frankenstein": Investigating the Complexities of Scientific Collaboration and Privilege Management within Research Computing Infrastructures.</t>
         </is>
       </c>
       <c r="D276" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>University of Michigan–Ann Arbor</t>
+          <t>Arizona State University</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Alex Ozdemir</t>
+          <t>Adam Doupé</t>
         </is>
       </c>
       <c r="B277" t="n">
@@ -6779,22 +6779,22 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Efficient Proofs of Possession for Legacy Signatures.</t>
+          <t>IEEE_S&amp;P-"It's almost like Frankenstein": Investigating the Complexities of Scientific Collaboration and Privilege Management within Research Computing Infrastructures.</t>
         </is>
       </c>
       <c r="D277" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Stanford University</t>
+          <t>Arizona State University</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Chad Sharp</t>
+          <t>Carlos E. Rubio-Medrano</t>
         </is>
       </c>
       <c r="B278" t="n">
@@ -6802,22 +6802,22 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Efficient Proofs of Possession for Legacy Signatures.</t>
+          <t>IEEE_S&amp;P-"It's almost like Frankenstein": Investigating the Complexities of Scientific Collaboration and Privilege Management within Research Computing Infrastructures.</t>
         </is>
       </c>
       <c r="D278" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>University of Michigan–Ann Arbor</t>
+          <t>Texas A&amp;M University – Corpus Christi</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Paul Grubbs</t>
+          <t>Gail-Joon Ahn</t>
         </is>
       </c>
       <c r="B279" t="n">
@@ -6825,22 +6825,22 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Efficient Proofs of Possession for Legacy Signatures.</t>
+          <t>IEEE_S&amp;P-"It's almost like Frankenstein": Investigating the Complexities of Scientific Collaboration and Privilege Management within Research Computing Infrastructures.</t>
         </is>
       </c>
       <c r="D279" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>University of Michigan–Ann Arbor</t>
+          <t>Arizona State University</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Kunming Jiang</t>
+          <t>Anna P. Y. Woo</t>
         </is>
       </c>
       <c r="B280" t="n">
@@ -6848,7 +6848,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-CoBBL: Dynamic Constraint Generation for SNARKs.</t>
+          <t>IEEE_S&amp;P-Efficient Proofs of Possession for Legacy Signatures.</t>
         </is>
       </c>
       <c r="D280" t="n">
@@ -6856,14 +6856,14 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>University of Michigan–Ann Arbor</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Fraser Brown</t>
+          <t>Alex Ozdemir</t>
         </is>
       </c>
       <c r="B281" t="n">
@@ -6871,7 +6871,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-CoBBL: Dynamic Constraint Generation for SNARKs.</t>
+          <t>IEEE_S&amp;P-Efficient Proofs of Possession for Legacy Signatures.</t>
         </is>
       </c>
       <c r="D281" t="n">
@@ -6879,14 +6879,14 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>Stanford University</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Riad S. Wahby</t>
+          <t>Chad Sharp</t>
         </is>
       </c>
       <c r="B282" t="n">
@@ -6894,7 +6894,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-CoBBL: Dynamic Constraint Generation for SNARKs.</t>
+          <t>IEEE_S&amp;P-Efficient Proofs of Possession for Legacy Signatures.</t>
         </is>
       </c>
       <c r="D282" t="n">
@@ -6902,14 +6902,14 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>University of Michigan–Ann Arbor</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Jiwon Kim</t>
+          <t>Paul Grubbs</t>
         </is>
       </c>
       <c r="B283" t="n">
@@ -6917,22 +6917,22 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-ALPACA: Anonymous Blocklisting with Constant-Sized Updatable Proofs.</t>
+          <t>IEEE_S&amp;P-Efficient Proofs of Possession for Legacy Signatures.</t>
         </is>
       </c>
       <c r="D283" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>University of Michigan</t>
+          <t>University of Michigan–Ann Arbor</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Abhiram Kothapalli</t>
+          <t>Kunming Jiang</t>
         </is>
       </c>
       <c r="B284" t="n">
@@ -6940,22 +6940,22 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-ALPACA: Anonymous Blocklisting with Constant-Sized Updatable Proofs.</t>
+          <t>IEEE_S&amp;P-CoBBL: Dynamic Constraint Generation for SNARKs.</t>
         </is>
       </c>
       <c r="D284" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>University of California, Berkeley</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Orestis Chardouvelis</t>
+          <t>Fraser Brown</t>
         </is>
       </c>
       <c r="B285" t="n">
@@ -6963,11 +6963,11 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-ALPACA: Anonymous Blocklisting with Constant-Sized Updatable Proofs.</t>
+          <t>IEEE_S&amp;P-CoBBL: Dynamic Constraint Generation for SNARKs.</t>
         </is>
       </c>
       <c r="D285" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E285" t="inlineStr">
         <is>
@@ -6986,11 +6986,11 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-ALPACA: Anonymous Blocklisting with Constant-Sized Updatable Proofs.</t>
+          <t>IEEE_S&amp;P-CoBBL: Dynamic Constraint Generation for SNARKs.</t>
         </is>
       </c>
       <c r="D286" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E286" t="inlineStr">
         <is>
@@ -7001,7 +7001,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Paul Grubbs</t>
+          <t>Jiwon Kim</t>
         </is>
       </c>
       <c r="B287" t="n">
@@ -7013,7 +7013,7 @@
         </is>
       </c>
       <c r="D287" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E287" t="inlineStr">
         <is>
@@ -7024,7 +7024,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Charalampos Papamanthou</t>
+          <t>Abhiram Kothapalli</t>
         </is>
       </c>
       <c r="B288" t="n">
@@ -7032,22 +7032,22 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-HydraProofs: Optimally Computing All Proofs in a Vector Commitment (With Applications to Efficient zkSNARKs Over Data from Multiple Users).</t>
+          <t>IEEE_S&amp;P-ALPACA: Anonymous Blocklisting with Constant-Sized Updatable Proofs.</t>
         </is>
       </c>
       <c r="D288" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Yale University</t>
+          <t>University of California, Berkeley</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Tianyu Zhang</t>
+          <t>Orestis Chardouvelis</t>
         </is>
       </c>
       <c r="B289" t="n">
@@ -7055,22 +7055,22 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-FairZK: A Scalable System to Prove Machine Learning Fairness in Zero-Knowledge.</t>
+          <t>IEEE_S&amp;P-ALPACA: Anonymous Blocklisting with Constant-Sized Updatable Proofs.</t>
         </is>
       </c>
       <c r="D289" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>University of Illinois Urbana-Champaign</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Shen Dong</t>
+          <t>Riad S. Wahby</t>
         </is>
       </c>
       <c r="B290" t="n">
@@ -7078,22 +7078,22 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-FairZK: A Scalable System to Prove Machine Learning Fairness in Zero-Knowledge.</t>
+          <t>IEEE_S&amp;P-ALPACA: Anonymous Blocklisting with Constant-Sized Updatable Proofs.</t>
         </is>
       </c>
       <c r="D290" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>University of Illinois Urbana-Champaign</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Oyku Deniz Kose</t>
+          <t>Paul Grubbs</t>
         </is>
       </c>
       <c r="B291" t="n">
@@ -7101,22 +7101,22 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-FairZK: A Scalable System to Prove Machine Learning Fairness in Zero-Knowledge.</t>
+          <t>IEEE_S&amp;P-ALPACA: Anonymous Blocklisting with Constant-Sized Updatable Proofs.</t>
         </is>
       </c>
       <c r="D291" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>University of California, Irvine</t>
+          <t>University of Michigan</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Yupeng Zhang</t>
+          <t>Charalampos Papamanthou</t>
         </is>
       </c>
       <c r="B292" t="n">
@@ -7124,22 +7124,22 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-FairZK: A Scalable System to Prove Machine Learning Fairness in Zero-Knowledge.</t>
+          <t>IEEE_S&amp;P-HydraProofs: Optimally Computing All Proofs in a Vector Commitment (With Applications to Efficient zkSNARKs Over Data from Multiple Users).</t>
         </is>
       </c>
       <c r="D292" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>University of Illinois Urbana-Champaign</t>
+          <t>Yale University</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Stephan van Schaik</t>
+          <t>Tianyu Zhang</t>
         </is>
       </c>
       <c r="B293" t="n">
@@ -7147,22 +7147,22 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Slice+Slice Baby: Generating Last-Level Cache Eviction Sets in the Blink of an Eye.</t>
+          <t>IEEE_S&amp;P-FairZK: A Scalable System to Prove Machine Learning Fairness in Zero-Knowledge.</t>
         </is>
       </c>
       <c r="D293" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>University of Michigan–Ann Arbor</t>
+          <t>University of Illinois Urbana-Champaign</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Daniel Genkin</t>
+          <t>Shen Dong</t>
         </is>
       </c>
       <c r="B294" t="n">
@@ -7170,22 +7170,22 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Slice+Slice Baby: Generating Last-Level Cache Eviction Sets in the Blink of an Eye.</t>
+          <t>IEEE_S&amp;P-FairZK: A Scalable System to Prove Machine Learning Fairness in Zero-Knowledge.</t>
         </is>
       </c>
       <c r="D294" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>University of Illinois Urbana-Champaign</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Boru Chen</t>
+          <t>Oyku Deniz Kose</t>
         </is>
       </c>
       <c r="B295" t="n">
@@ -7193,22 +7193,22 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Peek-a-Walk: Leaking Secrets via Page Walk Side Channels.</t>
+          <t>IEEE_S&amp;P-FairZK: A Scalable System to Prove Machine Learning Fairness in Zero-Knowledge.</t>
         </is>
       </c>
       <c r="D295" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Berkeley College; University of California, Berkeley</t>
+          <t>University of California, Irvine</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Yingchen Wang</t>
+          <t>Yupeng Zhang</t>
         </is>
       </c>
       <c r="B296" t="n">
@@ -7216,22 +7216,22 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Peek-a-Walk: Leaking Secrets via Page Walk Side Channels.</t>
+          <t>IEEE_S&amp;P-FairZK: A Scalable System to Prove Machine Learning Fairness in Zero-Knowledge.</t>
         </is>
       </c>
       <c r="D296" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Berkeley College; University of California, Berkeley</t>
+          <t>University of Illinois Urbana-Champaign</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Christopher W. Fletcher</t>
+          <t>Stephan van Schaik</t>
         </is>
       </c>
       <c r="B297" t="n">
@@ -7239,7 +7239,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Peek-a-Walk: Leaking Secrets via Page Walk Side Channels.</t>
+          <t>IEEE_S&amp;P-Slice+Slice Baby: Generating Last-Level Cache Eviction Sets in the Blink of an Eye.</t>
         </is>
       </c>
       <c r="D297" t="n">
@@ -7247,7 +7247,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Berkeley College; University of California, Berkeley</t>
+          <t>University of Michigan–Ann Arbor</t>
         </is>
       </c>
     </row>
@@ -7262,11 +7262,11 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Peek-a-Walk: Leaking Secrets via Page Walk Side Channels.</t>
+          <t>IEEE_S&amp;P-Slice+Slice Baby: Generating Last-Level Cache Eviction Sets in the Blink of an Eye.</t>
         </is>
       </c>
       <c r="D298" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E298" t="inlineStr">
         <is>
@@ -7277,7 +7277,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>David Kohlbrenner</t>
+          <t>Boru Chen</t>
         </is>
       </c>
       <c r="B299" t="n">
@@ -7289,18 +7289,18 @@
         </is>
       </c>
       <c r="D299" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>University of Washington</t>
+          <t>Berkeley College; University of California, Berkeley</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Riccardo Paccagnella</t>
+          <t>Yingchen Wang</t>
         </is>
       </c>
       <c r="B300" t="n">
@@ -7312,18 +7312,18 @@
         </is>
       </c>
       <c r="D300" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>Berkeley College; University of California, Berkeley</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Daniel Genkin</t>
+          <t>Christopher W. Fletcher</t>
         </is>
       </c>
       <c r="B301" t="n">
@@ -7331,22 +7331,22 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-SLAP: Data Speculation Attacks via Load Address Prediction on Apple Silicon.</t>
+          <t>IEEE_S&amp;P-Peek-a-Walk: Leaking Secrets via Page Walk Side Channels.</t>
         </is>
       </c>
       <c r="D301" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>Berkeley College; University of California, Berkeley</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Samy Amer</t>
+          <t>Daniel Genkin</t>
         </is>
       </c>
       <c r="B302" t="n">
@@ -7354,11 +7354,11 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-PQ-Hammer: End-to-End Key Recovery Attacks on Post-Quantum Cryptography Using Rowhammer.</t>
+          <t>IEEE_S&amp;P-Peek-a-Walk: Leaking Secrets via Page Walk Side Channels.</t>
         </is>
       </c>
       <c r="D302" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E302" t="inlineStr">
         <is>
@@ -7369,7 +7369,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Yingchen Wang</t>
+          <t>David Kohlbrenner</t>
         </is>
       </c>
       <c r="B303" t="n">
@@ -7377,22 +7377,22 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-PQ-Hammer: End-to-End Key Recovery Attacks on Post-Quantum Cryptography Using Rowhammer.</t>
+          <t>IEEE_S&amp;P-Peek-a-Walk: Leaking Secrets via Page Walk Side Channels.</t>
         </is>
       </c>
       <c r="D303" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Berkeley College; University of California, Berkeley</t>
+          <t>University of Washington</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Daniel Genkin</t>
+          <t>Riccardo Paccagnella</t>
         </is>
       </c>
       <c r="B304" t="n">
@@ -7400,22 +7400,22 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-PQ-Hammer: End-to-End Key Recovery Attacks on Post-Quantum Cryptography Using Rowhammer.</t>
+          <t>IEEE_S&amp;P-Peek-a-Walk: Leaking Secrets via Page Walk Side Channels.</t>
         </is>
       </c>
       <c r="D304" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Andrew Kwong</t>
+          <t>Daniel Genkin</t>
         </is>
       </c>
       <c r="B305" t="n">
@@ -7423,22 +7423,22 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-PQ-Hammer: End-to-End Key Recovery Attacks on Post-Quantum Cryptography Using Rowhammer.</t>
+          <t>IEEE_S&amp;P-SLAP: Data Speculation Attacks via Load Address Prediction on Apple Silicon.</t>
         </is>
       </c>
       <c r="D305" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>University of North Carolina Health Care; University of North Carolina at Chapel Hill</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Arkady Yerukhimovich</t>
+          <t>Samy Amer</t>
         </is>
       </c>
       <c r="B306" t="n">
@@ -7450,18 +7450,18 @@
         </is>
       </c>
       <c r="D306" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>George Washington University</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Inwhan Chun</t>
+          <t>Yingchen Wang</t>
         </is>
       </c>
       <c r="B307" t="n">
@@ -7469,22 +7469,22 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Scheduled Disclosure: Turning Power into Timing Without Frequency Scaling.</t>
+          <t>IEEE_S&amp;P-PQ-Hammer: End-to-End Key Recovery Attacks on Post-Quantum Cryptography Using Rowhammer.</t>
         </is>
       </c>
       <c r="D307" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>Berkeley College; University of California, Berkeley</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Isabella Siu</t>
+          <t>Daniel Genkin</t>
         </is>
       </c>
       <c r="B308" t="n">
@@ -7492,22 +7492,22 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Scheduled Disclosure: Turning Power into Timing Without Frequency Scaling.</t>
+          <t>IEEE_S&amp;P-PQ-Hammer: End-to-End Key Recovery Attacks on Post-Quantum Cryptography Using Rowhammer.</t>
         </is>
       </c>
       <c r="D308" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Riccardo Paccagnella</t>
+          <t>Andrew Kwong</t>
         </is>
       </c>
       <c r="B309" t="n">
@@ -7515,22 +7515,22 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Scheduled Disclosure: Turning Power into Timing Without Frequency Scaling.</t>
+          <t>IEEE_S&amp;P-PQ-Hammer: End-to-End Key Recovery Attacks on Post-Quantum Cryptography Using Rowhammer.</t>
         </is>
       </c>
       <c r="D309" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Carnegie Mellon University</t>
+          <t>University of North Carolina Health Care; University of North Carolina at Chapel Hill</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Cheng Gu</t>
+          <t>Arkady Yerukhimovich</t>
         </is>
       </c>
       <c r="B310" t="n">
@@ -7538,22 +7538,22 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-I know What You Sync: Covert and Side Channel Attacks on File Systems via syncfs.</t>
+          <t>IEEE_S&amp;P-PQ-Hammer: End-to-End Key Recovery Attacks on Post-Quantum Cryptography Using Rowhammer.</t>
         </is>
       </c>
       <c r="D310" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>University of California, Riverside</t>
+          <t>George Washington University</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Yicheng Zhang 0004</t>
+          <t>Inwhan Chun</t>
         </is>
       </c>
       <c r="B311" t="n">
@@ -7561,22 +7561,22 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-I know What You Sync: Covert and Side Channel Attacks on File Systems via syncfs.</t>
+          <t>IEEE_S&amp;P-Scheduled Disclosure: Turning Power into Timing Without Frequency Scaling.</t>
         </is>
       </c>
       <c r="D311" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>University of California, Riverside</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Muhammad Daniyal Pirwani Dar</t>
+          <t>Isabella Siu</t>
         </is>
       </c>
       <c r="B312" t="n">
@@ -7584,22 +7584,22 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Saecred: A State-Aware, Over-the-Air Protocol Testing Approach for Discovering Parsing Bugs in SAE Handshake Implementations of COTS Wi-Fi Access Points.</t>
+          <t>IEEE_S&amp;P-Scheduled Disclosure: Turning Power into Timing Without Frequency Scaling.</t>
         </is>
       </c>
       <c r="D312" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Stony Brook University</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Robert Lorch</t>
+          <t>Riccardo Paccagnella</t>
         </is>
       </c>
       <c r="B313" t="n">
@@ -7607,22 +7607,22 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Saecred: A State-Aware, Over-the-Air Protocol Testing Approach for Discovering Parsing Bugs in SAE Handshake Implementations of COTS Wi-Fi Access Points.</t>
+          <t>IEEE_S&amp;P-Scheduled Disclosure: Turning Power into Timing Without Frequency Scaling.</t>
         </is>
       </c>
       <c r="D313" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>University of Iowa</t>
+          <t>Carnegie Mellon University</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Aliakbar Sadeghi</t>
+          <t>Cheng Gu</t>
         </is>
       </c>
       <c r="B314" t="n">
@@ -7630,22 +7630,22 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Saecred: A State-Aware, Over-the-Air Protocol Testing Approach for Discovering Parsing Bugs in SAE Handshake Implementations of COTS Wi-Fi Access Points.</t>
+          <t>IEEE_S&amp;P-I know What You Sync: Covert and Side Channel Attacks on File Systems via syncfs.</t>
         </is>
       </c>
       <c r="D314" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Stony Brook University</t>
+          <t>University of California, Riverside</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Vincenzo Sorcigli</t>
+          <t>Yicheng Zhang 0004</t>
         </is>
       </c>
       <c r="B315" t="n">
@@ -7653,22 +7653,22 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Saecred: A State-Aware, Over-the-Air Protocol Testing Approach for Discovering Parsing Bugs in SAE Handshake Implementations of COTS Wi-Fi Access Points.</t>
+          <t>IEEE_S&amp;P-I know What You Sync: Covert and Side Channel Attacks on File Systems via syncfs.</t>
         </is>
       </c>
       <c r="D315" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Stony Brook University</t>
+          <t>University of California, Riverside</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Cesare Tinelli</t>
+          <t>Muhammad Daniyal Pirwani Dar</t>
         </is>
       </c>
       <c r="B316" t="n">
@@ -7680,18 +7680,18 @@
         </is>
       </c>
       <c r="D316" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>University of Iowa</t>
+          <t>Stony Brook University</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Omar Chowdhury</t>
+          <t>Robert Lorch</t>
         </is>
       </c>
       <c r="B317" t="n">
@@ -7703,18 +7703,18 @@
         </is>
       </c>
       <c r="D317" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Stony Brook University</t>
+          <t>University of Iowa</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Lina Pu</t>
+          <t>Aliakbar Sadeghi</t>
         </is>
       </c>
       <c r="B318" t="n">
@@ -7722,22 +7722,22 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Your Cable, My Antenna: Eavesdropping Serial Communication via Backscatter Signals.</t>
+          <t>IEEE_S&amp;P-Saecred: A State-Aware, Over-the-Air Protocol Testing Approach for Discovering Parsing Bugs in SAE Handshake Implementations of COTS Wi-Fi Access Points.</t>
         </is>
       </c>
       <c r="D318" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>University of Alabama</t>
+          <t>Stony Brook University</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Song Han 0002</t>
+          <t>Vincenzo Sorcigli</t>
         </is>
       </c>
       <c r="B319" t="n">
@@ -7745,22 +7745,22 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Your Cable, My Antenna: Eavesdropping Serial Communication via Backscatter Signals.</t>
+          <t>IEEE_S&amp;P-Saecred: A State-Aware, Over-the-Air Protocol Testing Approach for Discovering Parsing Bugs in SAE Handshake Implementations of COTS Wi-Fi Access Points.</t>
         </is>
       </c>
       <c r="D319" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>University of Connecticut</t>
+          <t>Stony Brook University</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Hadjer Benkraouda</t>
+          <t>Cesare Tinelli</t>
         </is>
       </c>
       <c r="B320" t="n">
@@ -7768,22 +7768,22 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-You Can't Judge a Binary by Its Header: Data-Code Separation for Non-Standard ARM Binaries Using Pseudo Labels.</t>
+          <t>IEEE_S&amp;P-Saecred: A State-Aware, Over-the-Air Protocol Testing Approach for Discovering Parsing Bugs in SAE Handshake Implementations of COTS Wi-Fi Access Points.</t>
         </is>
       </c>
       <c r="D320" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>University of Illinois Urbana-Champaign</t>
+          <t>University of Iowa</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Nirav Diwan</t>
+          <t>Omar Chowdhury</t>
         </is>
       </c>
       <c r="B321" t="n">
@@ -7791,22 +7791,22 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-You Can't Judge a Binary by Its Header: Data-Code Separation for Non-Standard ARM Binaries Using Pseudo Labels.</t>
+          <t>IEEE_S&amp;P-Saecred: A State-Aware, Over-the-Air Protocol Testing Approach for Discovering Parsing Bugs in SAE Handshake Implementations of COTS Wi-Fi Access Points.</t>
         </is>
       </c>
       <c r="D321" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>University of Illinois Urbana-Champaign</t>
+          <t>Stony Brook University</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Gang Wang 0011</t>
+          <t>Lina Pu</t>
         </is>
       </c>
       <c r="B322" t="n">
@@ -7814,22 +7814,22 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-You Can't Judge a Binary by Its Header: Data-Code Separation for Non-Standard ARM Binaries Using Pseudo Labels.</t>
+          <t>IEEE_S&amp;P-Your Cable, My Antenna: Eavesdropping Serial Communication via Backscatter Signals.</t>
         </is>
       </c>
       <c r="D322" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>University of Illinois Urbana-Champaign</t>
+          <t>University of Alabama</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Iria Giuffrida</t>
+          <t>Song Han 0002</t>
         </is>
       </c>
       <c r="B323" t="n">
@@ -7837,7 +7837,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-"We can't Allow IoT Vendors to Pass off all Such Liability to the Consumer": Investigating the U.S. Legal Perspectives on Liability for IoT Product Security.</t>
+          <t>IEEE_S&amp;P-Your Cable, My Antenna: Eavesdropping Serial Communication via Backscatter Signals.</t>
         </is>
       </c>
       <c r="D323" t="n">
@@ -7845,14 +7845,14 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>William &amp; Mary; Williams (United States)</t>
+          <t>University of Connecticut</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Daniel Shin</t>
+          <t>Hadjer Benkraouda</t>
         </is>
       </c>
       <c r="B324" t="n">
@@ -7860,22 +7860,22 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-"We can't Allow IoT Vendors to Pass off all Such Liability to the Consumer": Investigating the U.S. Legal Perspectives on Liability for IoT Product Security.</t>
+          <t>IEEE_S&amp;P-You Can't Judge a Binary by Its Header: Data-Code Separation for Non-Standard ARM Binaries Using Pseudo Labels.</t>
         </is>
       </c>
       <c r="D324" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>William &amp; Mary; Williams (United States)</t>
+          <t>University of Illinois Urbana-Champaign</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Ella Sullivan</t>
+          <t>Nirav Diwan</t>
         </is>
       </c>
       <c r="B325" t="n">
@@ -7883,22 +7883,22 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-"We can't Allow IoT Vendors to Pass off all Such Liability to the Consumer": Investigating the U.S. Legal Perspectives on Liability for IoT Product Security.</t>
+          <t>IEEE_S&amp;P-You Can't Judge a Binary by Its Header: Data-Code Separation for Non-Standard ARM Binaries Using Pseudo Labels.</t>
         </is>
       </c>
       <c r="D325" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>William &amp; Mary; Williams (United States)</t>
+          <t>University of Illinois Urbana-Champaign</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Raheem Beyah</t>
+          <t>Gang Wang 0011</t>
         </is>
       </c>
       <c r="B326" t="n">
@@ -7906,22 +7906,22 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Firmrca: Towards Post-Fuzzing Analysis on ARM Embedded Firmware with Efficient Event-Based Fault Localization.</t>
+          <t>IEEE_S&amp;P-You Can't Judge a Binary by Its Header: Data-Code Separation for Non-Standard ARM Binaries Using Pseudo Labels.</t>
         </is>
       </c>
       <c r="D326" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>University of Illinois Urbana-Champaign</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Mayuri Sridhar</t>
+          <t>Iria Giuffrida</t>
         </is>
       </c>
       <c r="B327" t="n">
@@ -7929,22 +7929,22 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-PAC-Private Algorithms.</t>
+          <t>IEEE_S&amp;P-"We can't Allow IoT Vendors to Pass off all Such Liability to the Consumer": Investigating the U.S. Legal Perspectives on Liability for IoT Product Security.</t>
         </is>
       </c>
       <c r="D327" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>IIT@MIT</t>
+          <t>William &amp; Mary; Williams (United States)</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Srinivas Devadas</t>
+          <t>Daniel Shin</t>
         </is>
       </c>
       <c r="B328" t="n">
@@ -7952,22 +7952,22 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-PAC-Private Algorithms.</t>
+          <t>IEEE_S&amp;P-"We can't Allow IoT Vendors to Pass off all Such Liability to the Consumer": Investigating the U.S. Legal Perspectives on Liability for IoT Product Security.</t>
         </is>
       </c>
       <c r="D328" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>IIT@MIT</t>
+          <t>William &amp; Mary; Williams (United States)</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Shlomi Hod</t>
+          <t>Ella Sullivan</t>
         </is>
       </c>
       <c r="B329" t="n">
@@ -7975,22 +7975,22 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Differentially Private Release of Israel's National Registry of Live Births.</t>
+          <t>IEEE_S&amp;P-"We can't Allow IoT Vendors to Pass off all Such Liability to the Consumer": Investigating the U.S. Legal Perspectives on Liability for IoT Product Security.</t>
         </is>
       </c>
       <c r="D329" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>Boston University</t>
+          <t>William &amp; Mary; Williams (United States)</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Ran Canetti</t>
+          <t>Raheem Beyah</t>
         </is>
       </c>
       <c r="B330" t="n">
@@ -7998,22 +7998,22 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Differentially Private Release of Israel's National Registry of Live Births.</t>
+          <t>IEEE_S&amp;P-Firmrca: Towards Post-Fuzzing Analysis on ARM Embedded Firmware with Efficient Event-Based Fault Localization.</t>
         </is>
       </c>
       <c r="D330" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>Boston University</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Alexander Viand</t>
+          <t>Mayuri Sridhar</t>
         </is>
       </c>
       <c r="B331" t="n">
@@ -8021,22 +8021,22 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-DPolicy: Managing Privacy Risks Across Multiple Releases with Differential Privacy.</t>
+          <t>IEEE_S&amp;P-PAC-Private Algorithms.</t>
         </is>
       </c>
       <c r="D331" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>Intel (United States)</t>
+          <t>IIT@MIT</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Chen Gong 0005</t>
+          <t>Srinivas Devadas</t>
         </is>
       </c>
       <c r="B332" t="n">
@@ -8044,22 +8044,22 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-From Easy to Hard: Building a Shortcut for Differentially Private Image Synthesis.</t>
+          <t>IEEE_S&amp;P-PAC-Private Algorithms.</t>
         </is>
       </c>
       <c r="D332" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>University of Virginia</t>
+          <t>IIT@MIT</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Xiaochen Li</t>
+          <t>Shlomi Hod</t>
         </is>
       </c>
       <c r="B333" t="n">
@@ -8067,22 +8067,22 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-From Easy to Hard: Building a Shortcut for Differentially Private Image Synthesis.</t>
+          <t>IEEE_S&amp;P-Differentially Private Release of Israel's National Registry of Live Births.</t>
         </is>
       </c>
       <c r="D333" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>University of Virginia</t>
+          <t>Boston University</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Tianhao Wang 0001</t>
+          <t>Ran Canetti</t>
         </is>
       </c>
       <c r="B334" t="n">
@@ -8090,22 +8090,22 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-From Easy to Hard: Building a Shortcut for Differentially Private Image Synthesis.</t>
+          <t>IEEE_S&amp;P-Differentially Private Release of Israel's National Registry of Live Births.</t>
         </is>
       </c>
       <c r="D334" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>University of Virginia</t>
+          <t>Boston University</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Emiliano De Cristofaro</t>
+          <t>Alexander Viand</t>
         </is>
       </c>
       <c r="B335" t="n">
@@ -8113,7 +8113,7 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-The Inadequacy of Similarity-Based Privacy Metrics: Privacy Attacks Against "Truly Anonymous" Synthetic Datasets.</t>
+          <t>IEEE_S&amp;P-DPolicy: Managing Privacy Risks Across Multiple Releases with Differential Privacy.</t>
         </is>
       </c>
       <c r="D335" t="n">
@@ -8121,14 +8121,14 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>University of California, Riverside</t>
+          <t>Intel (United States)</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Arnabjyoti Kalita</t>
+          <t>Chen Gong 0005</t>
         </is>
       </c>
       <c r="B336" t="n">
@@ -8136,11 +8136,11 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Ceviche: Capability-Enhanced Secure Virtualization of Caches.</t>
+          <t>IEEE_S&amp;P-From Easy to Hard: Building a Shortcut for Differentially Private Image Synthesis.</t>
         </is>
       </c>
       <c r="D336" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E336" t="inlineStr">
         <is>
@@ -8151,7 +8151,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Yilong Yang</t>
+          <t>Xiaochen Li</t>
         </is>
       </c>
       <c r="B337" t="n">
@@ -8159,11 +8159,11 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Ceviche: Capability-Enhanced Secure Virtualization of Caches.</t>
+          <t>IEEE_S&amp;P-From Easy to Hard: Building a Shortcut for Differentially Private Image Synthesis.</t>
         </is>
       </c>
       <c r="D337" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E337" t="inlineStr">
         <is>
@@ -8174,7 +8174,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Alenkruth Krishnan Murali</t>
+          <t>Tianhao Wang 0001</t>
         </is>
       </c>
       <c r="B338" t="n">
@@ -8182,11 +8182,11 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Ceviche: Capability-Enhanced Secure Virtualization of Caches.</t>
+          <t>IEEE_S&amp;P-From Easy to Hard: Building a Shortcut for Differentially Private Image Synthesis.</t>
         </is>
       </c>
       <c r="D338" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E338" t="inlineStr">
         <is>
@@ -8197,7 +8197,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Ashish Venkat</t>
+          <t>Emiliano De Cristofaro</t>
         </is>
       </c>
       <c r="B339" t="n">
@@ -8205,22 +8205,22 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Ceviche: Capability-Enhanced Secure Virtualization of Caches.</t>
+          <t>IEEE_S&amp;P-The Inadequacy of Similarity-Based Privacy Metrics: Privacy Attacks Against "Truly Anonymous" Synthetic Datasets.</t>
         </is>
       </c>
       <c r="D339" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>University of Virginia</t>
+          <t>University of California, Riverside</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Fan Sang</t>
+          <t>Arnabjyoti Kalita</t>
         </is>
       </c>
       <c r="B340" t="n">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Portal: Fast and Secure Device Access with Arm CCA for Modern Arm Mobile System-on-Chips (SoCs).</t>
+          <t>IEEE_S&amp;P-Ceviche: Capability-Enhanced Secure Virtualization of Caches.</t>
         </is>
       </c>
       <c r="D340" t="n">
@@ -8236,14 +8236,14 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>University of Virginia</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Jaehyuk Lee</t>
+          <t>Yilong Yang</t>
         </is>
       </c>
       <c r="B341" t="n">
@@ -8251,7 +8251,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Portal: Fast and Secure Device Access with Arm CCA for Modern Arm Mobile System-on-Chips (SoCs).</t>
+          <t>IEEE_S&amp;P-Ceviche: Capability-Enhanced Secure Virtualization of Caches.</t>
         </is>
       </c>
       <c r="D341" t="n">
@@ -8259,14 +8259,14 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>University of Virginia</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Xiaokuan Zhang</t>
+          <t>Alenkruth Krishnan Murali</t>
         </is>
       </c>
       <c r="B342" t="n">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Portal: Fast and Secure Device Access with Arm CCA for Modern Arm Mobile System-on-Chips (SoCs).</t>
+          <t>IEEE_S&amp;P-Ceviche: Capability-Enhanced Secure Virtualization of Caches.</t>
         </is>
       </c>
       <c r="D342" t="n">
@@ -8282,14 +8282,14 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>George Mason University</t>
+          <t>University of Virginia</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Taesoo Kim</t>
+          <t>Ashish Venkat</t>
         </is>
       </c>
       <c r="B343" t="n">
@@ -8297,7 +8297,7 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Portal: Fast and Secure Device Access with Arm CCA for Modern Arm Mobile System-on-Chips (SoCs).</t>
+          <t>IEEE_S&amp;P-Ceviche: Capability-Enhanced Secure Virtualization of Caches.</t>
         </is>
       </c>
       <c r="D343" t="n">
@@ -8305,14 +8305,14 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>Georgia Institute of Technology</t>
+          <t>University of Virginia</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>Shidong Pan</t>
+          <t>Fan Sang</t>
         </is>
       </c>
       <c r="B344" t="n">
@@ -8320,22 +8320,22 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-A Big Step Forward? A User-Centric Examination of iOS App Privacy Report and Enhancements.</t>
+          <t>IEEE_S&amp;P-Portal: Fast and Secure Device Access with Arm CCA for Modern Arm Mobile System-on-Chips (SoCs).</t>
         </is>
       </c>
       <c r="D344" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>Columbia University</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Mona Wang</t>
+          <t>Jaehyuk Lee</t>
         </is>
       </c>
       <c r="B345" t="n">
@@ -8343,22 +8343,22 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-WireWatch: Measuring the Security of Proprietary Network Encryption in the Global Android Ecosystem.</t>
+          <t>IEEE_S&amp;P-Portal: Fast and Secure Device Access with Arm CCA for Modern Arm Mobile System-on-Chips (SoCs).</t>
         </is>
       </c>
       <c r="D345" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>Princeton University</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Prateek Mittal</t>
+          <t>Xiaokuan Zhang</t>
         </is>
       </c>
       <c r="B346" t="n">
@@ -8366,22 +8366,22 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-WireWatch: Measuring the Security of Proprietary Network Encryption in the Global Android Ecosystem.</t>
+          <t>IEEE_S&amp;P-Portal: Fast and Secure Device Access with Arm CCA for Modern Arm Mobile System-on-Chips (SoCs).</t>
         </is>
       </c>
       <c r="D346" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>Princeton University</t>
+          <t>George Mason University</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Jonathan R. Mayer</t>
+          <t>Taesoo Kim</t>
         </is>
       </c>
       <c r="B347" t="n">
@@ -8389,22 +8389,22 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-WireWatch: Measuring the Security of Proprietary Network Encryption in the Global Android Ecosystem.</t>
+          <t>IEEE_S&amp;P-Portal: Fast and Secure Device Access with Arm CCA for Modern Arm Mobile System-on-Chips (SoCs).</t>
         </is>
       </c>
       <c r="D347" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>Princeton University</t>
+          <t>Georgia Institute of Technology</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Zhiqiang Lin 0001</t>
+          <t>Shidong Pan</t>
         </is>
       </c>
       <c r="B348" t="n">
@@ -8412,7 +8412,7 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Code Speaks Louder: Exploring Security and Privacy Relevant Regional Variations in Mobile Applications.</t>
+          <t>IEEE_S&amp;P-A Big Step Forward? A User-Centric Examination of iOS App Privacy Report and Enhancements.</t>
         </is>
       </c>
       <c r="D348" t="n">
@@ -8420,14 +8420,14 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>The Ohio State University</t>
+          <t>Columbia University</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Aafaq Sabir</t>
+          <t>Mona Wang</t>
         </is>
       </c>
       <c r="B349" t="n">
@@ -8435,7 +8435,7 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Analyzing Ad Prevalence, Characteristics, and Compliance in Alexa Skills.</t>
+          <t>IEEE_S&amp;P-WireWatch: Measuring the Security of Proprietary Network Encryption in the Global Android Ecosystem.</t>
         </is>
       </c>
       <c r="D349" t="n">
@@ -8443,14 +8443,14 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>North Carolina State University</t>
+          <t>Princeton University</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Dilawer Ahmed</t>
+          <t>Prateek Mittal</t>
         </is>
       </c>
       <c r="B350" t="n">
@@ -8458,22 +8458,22 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Analyzing Ad Prevalence, Characteristics, and Compliance in Alexa Skills.</t>
+          <t>IEEE_S&amp;P-WireWatch: Measuring the Security of Proprietary Network Encryption in the Global Android Ecosystem.</t>
         </is>
       </c>
       <c r="D350" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>North Carolina State University</t>
+          <t>Princeton University</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Anupam Das 0001</t>
+          <t>Jonathan R. Mayer</t>
         </is>
       </c>
       <c r="B351" t="n">
@@ -8481,22 +8481,22 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Analyzing Ad Prevalence, Characteristics, and Compliance in Alexa Skills.</t>
+          <t>IEEE_S&amp;P-WireWatch: Measuring the Security of Proprietary Network Encryption in the Global Android Ecosystem.</t>
         </is>
       </c>
       <c r="D351" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>North Carolina State University</t>
+          <t>Princeton University</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Ahmed Tanvir Mahdad</t>
+          <t>Zhiqiang Lin 0001</t>
         </is>
       </c>
       <c r="B352" t="n">
@@ -8504,22 +8504,22 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-BPSniff: Continuously Surveilling Private Blood Pressure Information in the Metaverse via Unrestricted Inbuilt Motion Sensors.</t>
+          <t>IEEE_S&amp;P-Code Speaks Louder: Exploring Security and Privacy Relevant Regional Variations in Mobile Applications.</t>
         </is>
       </c>
       <c r="D352" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>Texas A&amp;M University</t>
+          <t>The Ohio State University</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Yingying Chen 0001</t>
+          <t>Aafaq Sabir</t>
         </is>
       </c>
       <c r="B353" t="n">
@@ -8527,22 +8527,22 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-BPSniff: Continuously Surveilling Private Blood Pressure Information in the Metaverse via Unrestricted Inbuilt Motion Sensors.</t>
+          <t>IEEE_S&amp;P-Analyzing Ad Prevalence, Characteristics, and Compliance in Alexa Skills.</t>
         </is>
       </c>
       <c r="D353" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>Rutgers, The State University of New Jersey</t>
+          <t>North Carolina State University</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>Nitesh Saxena</t>
+          <t>Dilawer Ahmed</t>
         </is>
       </c>
       <c r="B354" t="n">
@@ -8550,22 +8550,22 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-BPSniff: Continuously Surveilling Private Blood Pressure Information in the Metaverse via Unrestricted Inbuilt Motion Sensors.</t>
+          <t>IEEE_S&amp;P-Analyzing Ad Prevalence, Characteristics, and Compliance in Alexa Skills.</t>
         </is>
       </c>
       <c r="D354" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>Texas A&amp;M University</t>
+          <t>North Carolina State University</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Jonathan Protzenko</t>
+          <t>Anupam Das 0001</t>
         </is>
       </c>
       <c r="B355" t="n">
@@ -8573,22 +8573,22 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-TreeKEM: A Modular Machine-Checked Symbolic Security Analysis of Group Key Agreement in Messaging Layer Security.</t>
+          <t>IEEE_S&amp;P-Analyzing Ad Prevalence, Characteristics, and Compliance in Alexa Skills.</t>
         </is>
       </c>
       <c r="D355" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>Microsoft (Germany)</t>
+          <t>North Carolina State University</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Liron David</t>
+          <t>Ahmed Tanvir Mahdad</t>
         </is>
       </c>
       <c r="B356" t="n">
@@ -8596,22 +8596,22 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Extended Diffie-Hellman Encryption for Secure and Efficient Real-Time Beacon Notifications.</t>
+          <t>IEEE_S&amp;P-BPSniff: Continuously Surveilling Private Blood Pressure Information in the Metaverse via Unrestricted Inbuilt Motion Sensors.</t>
         </is>
       </c>
       <c r="D356" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>Google (United States)</t>
+          <t>Texas A&amp;M University</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Avinatan Hassidim</t>
+          <t>Yingying Chen 0001</t>
         </is>
       </c>
       <c r="B357" t="n">
@@ -8619,22 +8619,22 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Extended Diffie-Hellman Encryption for Secure and Efficient Real-Time Beacon Notifications.</t>
+          <t>IEEE_S&amp;P-BPSniff: Continuously Surveilling Private Blood Pressure Information in the Metaverse via Unrestricted Inbuilt Motion Sensors.</t>
         </is>
       </c>
       <c r="D357" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>Google (United States); Bar-Ilan University</t>
+          <t>Rutgers, The State University of New Jersey</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>David Lazarov</t>
+          <t>Nitesh Saxena</t>
         </is>
       </c>
       <c r="B358" t="n">
@@ -8642,22 +8642,22 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Extended Diffie-Hellman Encryption for Secure and Efficient Real-Time Beacon Notifications.</t>
+          <t>IEEE_S&amp;P-BPSniff: Continuously Surveilling Private Blood Pressure Information in the Metaverse via Unrestricted Inbuilt Motion Sensors.</t>
         </is>
       </c>
       <c r="D358" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>Google (United States)</t>
+          <t>Texas A&amp;M University</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>Moti Yung</t>
+          <t>Jonathan Protzenko</t>
         </is>
       </c>
       <c r="B359" t="n">
@@ -8665,22 +8665,22 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Extended Diffie-Hellman Encryption for Secure and Efficient Real-Time Beacon Notifications.</t>
+          <t>IEEE_S&amp;P-TreeKEM: A Modular Machine-Checked Symbolic Security Analysis of Group Key Agreement in Messaging Layer Security.</t>
         </is>
       </c>
       <c r="D359" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>Google (United States)</t>
+          <t>Microsoft (Germany)</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Darya Kaviani</t>
+          <t>Liron David</t>
         </is>
       </c>
       <c r="B360" t="n">
@@ -8688,7 +8688,7 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Myco: Unlocking Polylogarithmic Accesses in Metadata-Private Messaging.</t>
+          <t>IEEE_S&amp;P-Extended Diffie-Hellman Encryption for Secure and Efficient Real-Time Beacon Notifications.</t>
         </is>
       </c>
       <c r="D360" t="n">
@@ -8696,14 +8696,14 @@
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>Berkeley College; University of California, Berkeley</t>
+          <t>Google (United States)</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Deevashwer Rathee</t>
+          <t>Omer Berkman</t>
         </is>
       </c>
       <c r="B361" t="n">
@@ -8711,7 +8711,7 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Myco: Unlocking Polylogarithmic Accesses in Metadata-Private Messaging.</t>
+          <t>IEEE_S&amp;P-Extended Diffie-Hellman Encryption for Secure and Efficient Real-Time Beacon Notifications.</t>
         </is>
       </c>
       <c r="D361" t="n">
@@ -8719,14 +8719,14 @@
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>Berkeley College; University of California, Berkeley</t>
+          <t>Google (United States); Academic College of Tel Aviv-Yafo</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Raluca Ada Popa</t>
+          <t>Avinatan Hassidim</t>
         </is>
       </c>
       <c r="B362" t="n">
@@ -8734,22 +8734,22 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Myco: Unlocking Polylogarithmic Accesses in Metadata-Private Messaging.</t>
+          <t>IEEE_S&amp;P-Extended Diffie-Hellman Encryption for Secure and Efficient Real-Time Beacon Notifications.</t>
         </is>
       </c>
       <c r="D362" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>University of California, Berkeley; Berkeley College</t>
+          <t>Google (United States); Bar-Ilan University</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Quang Cao</t>
+          <t>David Lazarov</t>
         </is>
       </c>
       <c r="B363" t="n">
@@ -8757,22 +8757,22 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-TreePIR: Efficient Private Retrieval of Merkle Proofs via Tree Colorings with Fast Indexing and Zero Storage Overhead.</t>
+          <t>IEEE_S&amp;P-Extended Diffie-Hellman Encryption for Secure and Efficient Real-Time Beacon Notifications.</t>
         </is>
       </c>
       <c r="D363" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>MIT University; RMIT University</t>
+          <t>Google (United States)</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Son Hoang Dau</t>
+          <t>Yossi Matias</t>
         </is>
       </c>
       <c r="B364" t="n">
@@ -8780,22 +8780,22 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-TreePIR: Efficient Private Retrieval of Merkle Proofs via Tree Colorings with Fast Indexing and Zero Storage Overhead.</t>
+          <t>IEEE_S&amp;P-Extended Diffie-Hellman Encryption for Secure and Efficient Real-Time Beacon Notifications.</t>
         </is>
       </c>
       <c r="D364" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>RMIT University; MIT University</t>
+          <t>Tel Aviv University; Google (Israel)</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>Rinaldo Gagiano</t>
+          <t>Moti Yung</t>
         </is>
       </c>
       <c r="B365" t="n">
@@ -8803,22 +8803,22 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-TreePIR: Efficient Private Retrieval of Merkle Proofs via Tree Colorings with Fast Indexing and Zero Storage Overhead.</t>
+          <t>IEEE_S&amp;P-Extended Diffie-Hellman Encryption for Secure and Efficient Real-Time Beacon Notifications.</t>
         </is>
       </c>
       <c r="D365" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>RMIT University; MIT University</t>
+          <t>Google (United States)</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Duy Huynh</t>
+          <t>Darya Kaviani</t>
         </is>
       </c>
       <c r="B366" t="n">
@@ -8826,22 +8826,22 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-TreePIR: Efficient Private Retrieval of Merkle Proofs via Tree Colorings with Fast Indexing and Zero Storage Overhead.</t>
+          <t>IEEE_S&amp;P-Myco: Unlocking Polylogarithmic Accesses in Metadata-Private Messaging.</t>
         </is>
       </c>
       <c r="D366" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>MIT University; RMIT University</t>
+          <t>Berkeley College; University of California, Berkeley</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>Xun Yi</t>
+          <t>Deevashwer Rathee</t>
         </is>
       </c>
       <c r="B367" t="n">
@@ -8849,22 +8849,22 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-TreePIR: Efficient Private Retrieval of Merkle Proofs via Tree Colorings with Fast Indexing and Zero Storage Overhead.</t>
+          <t>IEEE_S&amp;P-Myco: Unlocking Polylogarithmic Accesses in Metadata-Private Messaging.</t>
         </is>
       </c>
       <c r="D367" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>RMIT University; MIT University</t>
+          <t>Berkeley College; University of California, Berkeley</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>Quang-Hung Luu</t>
+          <t>Raluca Ada Popa</t>
         </is>
       </c>
       <c r="B368" t="n">
@@ -8872,22 +8872,22 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-TreePIR: Efficient Private Retrieval of Merkle Proofs via Tree Colorings with Fast Indexing and Zero Storage Overhead.</t>
+          <t>IEEE_S&amp;P-Myco: Unlocking Polylogarithmic Accesses in Metadata-Private Messaging.</t>
         </is>
       </c>
       <c r="D368" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>MIT University; RMIT University</t>
+          <t>University of California, Berkeley; Berkeley College</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Collins W. Munyendo</t>
+          <t>Quang Cao</t>
         </is>
       </c>
       <c r="B369" t="n">
@@ -8895,7 +8895,7 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-"You Have to Ignore the Dangers": User Perceptions of the Security and Privacy Benefits of WhatsApp Mods.</t>
+          <t>IEEE_S&amp;P-TreePIR: Efficient Private Retrieval of Merkle Proofs via Tree Colorings with Fast Indexing and Zero Storage Overhead.</t>
         </is>
       </c>
       <c r="D369" t="n">
@@ -8903,14 +8903,14 @@
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>George Washington University</t>
+          <t>MIT University; RMIT University</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>Kentrell Owens</t>
+          <t>Son Hoang Dau</t>
         </is>
       </c>
       <c r="B370" t="n">
@@ -8918,7 +8918,7 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-"You Have to Ignore the Dangers": User Perceptions of the Security and Privacy Benefits of WhatsApp Mods.</t>
+          <t>IEEE_S&amp;P-TreePIR: Efficient Private Retrieval of Merkle Proofs via Tree Colorings with Fast Indexing and Zero Storage Overhead.</t>
         </is>
       </c>
       <c r="D370" t="n">
@@ -8926,14 +8926,14 @@
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>University of Washington</t>
+          <t>RMIT University; MIT University</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>Shaoqi Wang</t>
+          <t>Rinaldo Gagiano</t>
         </is>
       </c>
       <c r="B371" t="n">
@@ -8941,22 +8941,22 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-"You Have to Ignore the Dangers": User Perceptions of the Security and Privacy Benefits of WhatsApp Mods.</t>
+          <t>IEEE_S&amp;P-TreePIR: Efficient Private Retrieval of Merkle Proofs via Tree Colorings with Fast Indexing and Zero Storage Overhead.</t>
         </is>
       </c>
       <c r="D371" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>University of Washington</t>
+          <t>RMIT University; MIT University</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Adam J. Aviv</t>
+          <t>Duy Huynh</t>
         </is>
       </c>
       <c r="B372" t="n">
@@ -8964,22 +8964,22 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-"You Have to Ignore the Dangers": User Perceptions of the Security and Privacy Benefits of WhatsApp Mods.</t>
+          <t>IEEE_S&amp;P-TreePIR: Efficient Private Retrieval of Merkle Proofs via Tree Colorings with Fast Indexing and Zero Storage Overhead.</t>
         </is>
       </c>
       <c r="D372" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>George Washington University</t>
+          <t>MIT University; RMIT University</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>Tadayoshi Kohno</t>
+          <t>Xun Yi</t>
         </is>
       </c>
       <c r="B373" t="n">
@@ -8987,22 +8987,22 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-"You Have to Ignore the Dangers": User Perceptions of the Security and Privacy Benefits of WhatsApp Mods.</t>
+          <t>IEEE_S&amp;P-TreePIR: Efficient Private Retrieval of Merkle Proofs via Tree Colorings with Fast Indexing and Zero Storage Overhead.</t>
         </is>
       </c>
       <c r="D373" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>University of Washington</t>
+          <t>RMIT University; MIT University</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>Franziska Roesner</t>
+          <t>Quang-Hung Luu</t>
         </is>
       </c>
       <c r="B374" t="n">
@@ -9010,7 +9010,7 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-"You Have to Ignore the Dangers": User Perceptions of the Security and Privacy Benefits of WhatsApp Mods.</t>
+          <t>IEEE_S&amp;P-TreePIR: Efficient Private Retrieval of Merkle Proofs via Tree Colorings with Fast Indexing and Zero Storage Overhead.</t>
         </is>
       </c>
       <c r="D374" t="n">
@@ -9018,14 +9018,14 @@
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>University of Washington</t>
+          <t>MIT University; RMIT University</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Jung-Woo Chang</t>
+          <t>Collins W. Munyendo</t>
         </is>
       </c>
       <c r="B375" t="n">
@@ -9033,7 +9033,7 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-EveGuard: Defeating Vibration-based Side-Channel Eavesdropping with Audio Adversarial Perturbations.</t>
+          <t>IEEE_S&amp;P-"You Have to Ignore the Dangers": User Perceptions of the Security and Privacy Benefits of WhatsApp Mods.</t>
         </is>
       </c>
       <c r="D375" t="n">
@@ -9041,14 +9041,14 @@
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>University of California, San Diego</t>
+          <t>George Washington University</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>Ke Sun 0012</t>
+          <t>Kentrell Owens</t>
         </is>
       </c>
       <c r="B376" t="n">
@@ -9056,7 +9056,7 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-EveGuard: Defeating Vibration-based Side-Channel Eavesdropping with Audio Adversarial Perturbations.</t>
+          <t>IEEE_S&amp;P-"You Have to Ignore the Dangers": User Perceptions of the Security and Privacy Benefits of WhatsApp Mods.</t>
         </is>
       </c>
       <c r="D376" t="n">
@@ -9064,14 +9064,14 @@
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>University of California, San Diego</t>
+          <t>University of Washington</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>David Xia</t>
+          <t>Shaoqi Wang</t>
         </is>
       </c>
       <c r="B377" t="n">
@@ -9079,22 +9079,22 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-EveGuard: Defeating Vibration-based Side-Channel Eavesdropping with Audio Adversarial Perturbations.</t>
+          <t>IEEE_S&amp;P-"You Have to Ignore the Dangers": User Perceptions of the Security and Privacy Benefits of WhatsApp Mods.</t>
         </is>
       </c>
       <c r="D377" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>University of Illinois Urbana-Champaign</t>
+          <t>University of Washington</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>Xinyu Zhang 0003</t>
+          <t>Adam J. Aviv</t>
         </is>
       </c>
       <c r="B378" t="n">
@@ -9102,22 +9102,22 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-EveGuard: Defeating Vibration-based Side-Channel Eavesdropping with Audio Adversarial Perturbations.</t>
+          <t>IEEE_S&amp;P-"You Have to Ignore the Dangers": User Perceptions of the Security and Privacy Benefits of WhatsApp Mods.</t>
         </is>
       </c>
       <c r="D378" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>University of California, San Diego</t>
+          <t>George Washington University</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>Farinaz Koushanfar</t>
+          <t>Tadayoshi Kohno</t>
         </is>
       </c>
       <c r="B379" t="n">
@@ -9125,22 +9125,22 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-EveGuard: Defeating Vibration-based Side-Channel Eavesdropping with Audio Adversarial Perturbations.</t>
+          <t>IEEE_S&amp;P-"You Have to Ignore the Dangers": User Perceptions of the Security and Privacy Benefits of WhatsApp Mods.</t>
         </is>
       </c>
       <c r="D379" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>University of California, San Diego</t>
+          <t>University of Washington</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>Zhambyl Shaikhanov</t>
+          <t>Franziska Roesner</t>
         </is>
       </c>
       <c r="B380" t="n">
@@ -9148,22 +9148,22 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Spoofing Eavesdroppers with Audio Misinformation.</t>
+          <t>IEEE_S&amp;P-"You Have to Ignore the Dangers": User Perceptions of the Security and Privacy Benefits of WhatsApp Mods.</t>
         </is>
       </c>
       <c r="D380" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>University of Maryland, College Park</t>
+          <t>University of Washington</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>Mahmoud Al-Madi</t>
+          <t>Jung-Woo Chang</t>
         </is>
       </c>
       <c r="B381" t="n">
@@ -9171,22 +9171,22 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Spoofing Eavesdroppers with Audio Misinformation.</t>
+          <t>IEEE_S&amp;P-EveGuard: Defeating Vibration-based Side-Channel Eavesdropping with Audio Adversarial Perturbations.</t>
         </is>
       </c>
       <c r="D381" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>Rice University</t>
+          <t>University of California, San Diego</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>Hou-Tong Chen</t>
+          <t>Ke Sun 0012</t>
         </is>
       </c>
       <c r="B382" t="n">
@@ -9194,22 +9194,22 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Spoofing Eavesdroppers with Audio Misinformation.</t>
+          <t>IEEE_S&amp;P-EveGuard: Defeating Vibration-based Side-Channel Eavesdropping with Audio Adversarial Perturbations.</t>
         </is>
       </c>
       <c r="D382" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>Los Alamos National Laboratory</t>
+          <t>University of California, San Diego</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>Chun-Chieh Chang</t>
+          <t>David Xia</t>
         </is>
       </c>
       <c r="B383" t="n">
@@ -9217,22 +9217,22 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Spoofing Eavesdroppers with Audio Misinformation.</t>
+          <t>IEEE_S&amp;P-EveGuard: Defeating Vibration-based Side-Channel Eavesdropping with Audio Adversarial Perturbations.</t>
         </is>
       </c>
       <c r="D383" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>Los Alamos National Laboratory</t>
+          <t>University of Illinois Urbana-Champaign</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>Sadhvikas Addamane</t>
+          <t>Xinyu Zhang 0003</t>
         </is>
       </c>
       <c r="B384" t="n">
@@ -9240,22 +9240,22 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Spoofing Eavesdroppers with Audio Misinformation.</t>
+          <t>IEEE_S&amp;P-EveGuard: Defeating Vibration-based Side-Channel Eavesdropping with Audio Adversarial Perturbations.</t>
         </is>
       </c>
       <c r="D384" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>Sandia National Laboratories</t>
+          <t>University of California, San Diego</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>Daniel M. Mittleman</t>
+          <t>Farinaz Koushanfar</t>
         </is>
       </c>
       <c r="B385" t="n">
@@ -9263,22 +9263,22 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Spoofing Eavesdroppers with Audio Misinformation.</t>
+          <t>IEEE_S&amp;P-EveGuard: Defeating Vibration-based Side-Channel Eavesdropping with Audio Adversarial Perturbations.</t>
         </is>
       </c>
       <c r="D385" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>John Brown University</t>
+          <t>University of California, San Diego</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>Edward W. Knightly</t>
+          <t>Zhambyl Shaikhanov</t>
         </is>
       </c>
       <c r="B386" t="n">
@@ -9290,18 +9290,18 @@
         </is>
       </c>
       <c r="D386" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>Rice University</t>
+          <t>University of Maryland, College Park</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>Shengzhi Zhang</t>
+          <t>Mahmoud Al-Madi</t>
         </is>
       </c>
       <c r="B387" t="n">
@@ -9309,22 +9309,22 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-EvilHarmony: Stealthy Adversarial Attacks Against Black-Box Speech Recognition Systems.</t>
+          <t>IEEE_S&amp;P-Spoofing Eavesdroppers with Audio Misinformation.</t>
         </is>
       </c>
       <c r="D387" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>Boston University; Metropolitan College of New York</t>
+          <t>Rice University</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Dun Liu</t>
+          <t>Hou-Tong Chen</t>
         </is>
       </c>
       <c r="B388" t="n">
@@ -9332,22 +9332,22 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-EvilHarmony: Stealthy Adversarial Attacks Against Black-Box Speech Recognition Systems.</t>
+          <t>IEEE_S&amp;P-Spoofing Eavesdroppers with Audio Misinformation.</t>
         </is>
       </c>
       <c r="D388" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>Boston University; Metropolitan College of New York</t>
+          <t>Los Alamos National Laboratory</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>Raymond Muller</t>
+          <t>Chun-Chieh Chang</t>
         </is>
       </c>
       <c r="B389" t="n">
@@ -9355,22 +9355,22 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Investigating Physical Latency Attacks Against Camera-Based Perception.</t>
+          <t>IEEE_S&amp;P-Spoofing Eavesdroppers with Audio Misinformation.</t>
         </is>
       </c>
       <c r="D389" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>Purdue University West Lafayette</t>
+          <t>Los Alamos National Laboratory</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>Ruoyu Song 0001</t>
+          <t>Sadhvikas Addamane</t>
         </is>
       </c>
       <c r="B390" t="n">
@@ -9378,22 +9378,22 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Investigating Physical Latency Attacks Against Camera-Based Perception.</t>
+          <t>IEEE_S&amp;P-Spoofing Eavesdroppers with Audio Misinformation.</t>
         </is>
       </c>
       <c r="D390" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>Purdue University West Lafayette</t>
+          <t>Sandia National Laboratories</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>Chenyi Wang 0005</t>
+          <t>Daniel M. Mittleman</t>
         </is>
       </c>
       <c r="B391" t="n">
@@ -9401,22 +9401,22 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Investigating Physical Latency Attacks Against Camera-Based Perception.</t>
+          <t>IEEE_S&amp;P-Spoofing Eavesdroppers with Audio Misinformation.</t>
         </is>
       </c>
       <c r="D391" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>University of Arizona</t>
+          <t>John Brown University</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>Yuxia Zhan</t>
+          <t>Edward W. Knightly</t>
         </is>
       </c>
       <c r="B392" t="n">
@@ -9424,22 +9424,22 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Investigating Physical Latency Attacks Against Camera-Based Perception.</t>
+          <t>IEEE_S&amp;P-Spoofing Eavesdroppers with Audio Misinformation.</t>
         </is>
       </c>
       <c r="D392" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>New York University</t>
+          <t>Rice University</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>Jean-Philippe Monteuuis</t>
+          <t>Shengzhi Zhang</t>
         </is>
       </c>
       <c r="B393" t="n">
@@ -9447,22 +9447,22 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Investigating Physical Latency Attacks Against Camera-Based Perception.</t>
+          <t>IEEE_S&amp;P-EvilHarmony: Stealthy Adversarial Attacks Against Black-Box Speech Recognition Systems.</t>
         </is>
       </c>
       <c r="D393" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>Qualcomm (United Kingdom)</t>
+          <t>Boston University; Metropolitan College of New York</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>Ming Li 0003</t>
+          <t>Dun Liu</t>
         </is>
       </c>
       <c r="B394" t="n">
@@ -9470,22 +9470,22 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Investigating Physical Latency Attacks Against Camera-Based Perception.</t>
+          <t>IEEE_S&amp;P-EvilHarmony: Stealthy Adversarial Attacks Against Black-Box Speech Recognition Systems.</t>
         </is>
       </c>
       <c r="D394" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>University of Arizona</t>
+          <t>Boston University; Metropolitan College of New York</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>Ryan M. Gerdes</t>
+          <t>Raymond Muller</t>
         </is>
       </c>
       <c r="B395" t="n">
@@ -9497,18 +9497,18 @@
         </is>
       </c>
       <c r="D395" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>Virginia Tech</t>
+          <t>Purdue University West Lafayette</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>Jonathan Petit</t>
+          <t>Ruoyu Song 0001</t>
         </is>
       </c>
       <c r="B396" t="n">
@@ -9520,18 +9520,18 @@
         </is>
       </c>
       <c r="D396" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>Qualcomm (United Kingdom)</t>
+          <t>Purdue University West Lafayette</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>Z. Berkay Celik</t>
+          <t>Chenyi Wang 0005</t>
         </is>
       </c>
       <c r="B397" t="n">
@@ -9543,18 +9543,18 @@
         </is>
       </c>
       <c r="D397" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>Purdue University West Lafayette</t>
+          <t>University of Arizona</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>Trisha Datta</t>
+          <t>Yuxia Zhan</t>
         </is>
       </c>
       <c r="B398" t="n">
@@ -9562,22 +9562,22 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-VerITAS: Verifying Image Transformations at Scale.</t>
+          <t>IEEE_S&amp;P-Investigating Physical Latency Attacks Against Camera-Based Perception.</t>
         </is>
       </c>
       <c r="D398" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>Stanford University</t>
+          <t>New York University</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>Binyi Chen</t>
+          <t>Jean-Philippe Monteuuis</t>
         </is>
       </c>
       <c r="B399" t="n">
@@ -9585,22 +9585,22 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-VerITAS: Verifying Image Transformations at Scale.</t>
+          <t>IEEE_S&amp;P-Investigating Physical Latency Attacks Against Camera-Based Perception.</t>
         </is>
       </c>
       <c r="D399" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>Stanford University</t>
+          <t>Qualcomm (United Kingdom)</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>Dan Boneh</t>
+          <t>Ming Li 0003</t>
         </is>
       </c>
       <c r="B400" t="n">
@@ -9608,22 +9608,22 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-VerITAS: Verifying Image Transformations at Scale.</t>
+          <t>IEEE_S&amp;P-Investigating Physical Latency Attacks Against Camera-Based Perception.</t>
         </is>
       </c>
       <c r="D400" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>Stanford University</t>
+          <t>University of Arizona</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>Long Huang</t>
+          <t>Ryan M. Gerdes</t>
         </is>
       </c>
       <c r="B401" t="n">
@@ -9631,36 +9631,174 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>IEEE_S&amp;P-Sniffing Location Privacy of Video Conference Users Using Free Audio Channels.</t>
+          <t>IEEE_S&amp;P-Investigating Physical Latency Attacks Against Camera-Based Perception.</t>
         </is>
       </c>
       <c r="D401" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>Southern Methodist University</t>
+          <t>Virginia Tech</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
+          <t>Jonathan Petit</t>
+        </is>
+      </c>
+      <c r="B402" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>IEEE_S&amp;P-Investigating Physical Latency Attacks Against Camera-Based Perception.</t>
+        </is>
+      </c>
+      <c r="D402" t="n">
+        <v>8</v>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>Qualcomm (United Kingdom)</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>Z. Berkay Celik</t>
+        </is>
+      </c>
+      <c r="B403" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>IEEE_S&amp;P-Investigating Physical Latency Attacks Against Camera-Based Perception.</t>
+        </is>
+      </c>
+      <c r="D403" t="n">
+        <v>9</v>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>Purdue University West Lafayette</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>Trisha Datta</t>
+        </is>
+      </c>
+      <c r="B404" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>IEEE_S&amp;P-VerITAS: Verifying Image Transformations at Scale.</t>
+        </is>
+      </c>
+      <c r="D404" t="n">
+        <v>0</v>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>Stanford University</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>Binyi Chen</t>
+        </is>
+      </c>
+      <c r="B405" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>IEEE_S&amp;P-VerITAS: Verifying Image Transformations at Scale.</t>
+        </is>
+      </c>
+      <c r="D405" t="n">
+        <v>1</v>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>Stanford University</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>Dan Boneh</t>
+        </is>
+      </c>
+      <c r="B406" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>IEEE_S&amp;P-VerITAS: Verifying Image Transformations at Scale.</t>
+        </is>
+      </c>
+      <c r="D406" t="n">
+        <v>2</v>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>Stanford University</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>Long Huang</t>
+        </is>
+      </c>
+      <c r="B407" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>IEEE_S&amp;P-Sniffing Location Privacy of Video Conference Users Using Free Audio Channels.</t>
+        </is>
+      </c>
+      <c r="D407" t="n">
+        <v>0</v>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>Southern Methodist University</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
           <t>Chen Wang 0009</t>
         </is>
       </c>
-      <c r="B402" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C402" t="inlineStr">
+      <c r="B408" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C408" t="inlineStr">
         <is>
           <t>IEEE_S&amp;P-Sniffing Location Privacy of Video Conference Users Using Free Audio Channels.</t>
         </is>
       </c>
-      <c r="D402" t="n">
+      <c r="D408" t="n">
         <v>1</v>
       </c>
-      <c r="E402" t="inlineStr">
+      <c r="E408" t="inlineStr">
         <is>
           <t>Southern Methodist University</t>
         </is>
